--- a/Översikt LIDKÖPING.xlsx
+++ b/Översikt LIDKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>44631</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>46006</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 24727-2026</t>
+          <t>A 6898-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46171</v>
+        <v>44967</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -861,25 +861,20 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I4" t="n">
-        <v>6.9</v>
+        <v>18</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -891,21 +886,139 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
       </c>
       <c r="T4" t="n">
+        <v>5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>5</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Grönsångare
+Göktyta
+Älg
+Buskskvätta
+Röd glada</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 6898-2023 artfynd.xlsx", "A 6898-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 6898-2023 karta.png", "A 6898-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 6898-2023 georefererad karta.tif", "A 6898-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 6898-2023 FSC-klagomål.docx", "A 6898-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 6898-2023 FSC-klagomål mail.docx", "A 6898-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 6898-2023 tillsynsbegäran.docx", "A 6898-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 6898-2023 tillsynsbegäran mail.docx", "A 6898-2023")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 6898-2023 prioriterade fågelarter.docx", "A 6898-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 24727-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="n">
         <v>8</v>
       </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Veckticka
@@ -914,160 +1027,47 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 24727-2026 artfynd.xlsx", "A 24727-2026")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 24727-2026 karta.png", "A 24727-2026")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 24727-2026 georefererad karta.tif", "A 24727-2026")</f>
         <v/>
       </c>
-      <c r="Z4">
+      <c r="Z5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/knärot/A 24727-2026 karta knärot.png", "A 24727-2026")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 24727-2026 FSC-klagomål.docx", "A 24727-2026")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 24727-2026 FSC-klagomål mail.docx", "A 24727-2026")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 24727-2026 tillsynsbegäran.docx", "A 24727-2026")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 24727-2026 tillsynsbegäran mail.docx", "A 24727-2026")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 24727-2026 prioriterade fågelarter.docx", "A 24727-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 6898-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>44967</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>18</v>
-      </c>
-      <c r="J5" t="n">
-        <v>4</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>3</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>5</v>
-      </c>
-      <c r="T5" t="n">
-        <v>5</v>
-      </c>
-      <c r="U5" t="n">
-        <v>5</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Grönsångare
-Göktyta
-Älg
-Buskskvätta
-Röd glada</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 6898-2023 artfynd.xlsx", "A 6898-2023")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 6898-2023 karta.png", "A 6898-2023")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 6898-2023 georefererad karta.tif", "A 6898-2023")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 6898-2023 FSC-klagomål.docx", "A 6898-2023")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 6898-2023 FSC-klagomål mail.docx", "A 6898-2023")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 6898-2023 tillsynsbegäran.docx", "A 6898-2023")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 6898-2023 tillsynsbegäran mail.docx", "A 6898-2023")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 6898-2023 prioriterade fågelarter.docx", "A 6898-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 32280-2022</t>
+          <t>A 28849-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44781</v>
+        <v>45478</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1097,13 +1097,13 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>8.6</v>
+        <v>2.6</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -1136,6 +1136,118 @@
         <v>0</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Talltita
+Grönsiska
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 28849-2024 artfynd.xlsx", "A 28849-2024")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 28849-2024 karta.png", "A 28849-2024")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 28849-2024 georefererad karta.tif", "A 28849-2024")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 28849-2024 FSC-klagomål.docx", "A 28849-2024")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 28849-2024 FSC-klagomål mail.docx", "A 28849-2024")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 28849-2024 tillsynsbegäran.docx", "A 28849-2024")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 28849-2024 tillsynsbegäran mail.docx", "A 28849-2024")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 28849-2024 prioriterade fågelarter.docx", "A 28849-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 34942-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Gulsparv
 Nötkråka
@@ -1143,155 +1255,43 @@
 Skogsduva</t>
         </is>
       </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 32280-2022 artfynd.xlsx", "A 32280-2022")</f>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 34942-2026 artfynd.xlsx", "A 34942-2026")</f>
         <v/>
       </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 32280-2022 karta.png", "A 32280-2022")</f>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 34942-2026 karta.png", "A 34942-2026")</f>
         <v/>
       </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 32280-2022 georefererad karta.tif", "A 32280-2022")</f>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 34942-2026 georefererad karta.tif", "A 34942-2026")</f>
         <v/>
       </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 32280-2022 FSC-klagomål.docx", "A 32280-2022")</f>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 34942-2026 FSC-klagomål.docx", "A 34942-2026")</f>
         <v/>
       </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 32280-2022 FSC-klagomål mail.docx", "A 32280-2022")</f>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 34942-2026 FSC-klagomål mail.docx", "A 34942-2026")</f>
         <v/>
       </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 32280-2022 tillsynsbegäran.docx", "A 32280-2022")</f>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 34942-2026 tillsynsbegäran.docx", "A 34942-2026")</f>
         <v/>
       </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 32280-2022 tillsynsbegäran mail.docx", "A 32280-2022")</f>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 34942-2026 tillsynsbegäran mail.docx", "A 34942-2026")</f>
         <v/>
       </c>
-      <c r="AE6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 32280-2022 prioriterade fågelarter.docx", "A 32280-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 28849-2024</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45478</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>4</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Talltita
-Grönsiska
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 28849-2024 artfynd.xlsx", "A 28849-2024")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 28849-2024 karta.png", "A 28849-2024")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 28849-2024 georefererad karta.tif", "A 28849-2024")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 28849-2024 FSC-klagomål.docx", "A 28849-2024")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 28849-2024 FSC-klagomål mail.docx", "A 28849-2024")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 28849-2024 tillsynsbegäran.docx", "A 28849-2024")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 28849-2024 tillsynsbegäran mail.docx", "A 28849-2024")</f>
-        <v/>
-      </c>
       <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 28849-2024 prioriterade fågelarter.docx", "A 28849-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 34942-2026 prioriterade fågelarter.docx", "A 34942-2026")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 34942-2026</t>
+          <t>A 32280-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46259</v>
+        <v>44781</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>18.1</v>
+        <v>8.6</v>
       </c>
       <c r="J8" t="n">
         <v>3</v>
@@ -1368,42 +1368,42 @@
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 34942-2026 artfynd.xlsx", "A 34942-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 32280-2022 artfynd.xlsx", "A 32280-2022")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 34942-2026 karta.png", "A 34942-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 32280-2022 karta.png", "A 32280-2022")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 34942-2026 georefererad karta.tif", "A 34942-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 32280-2022 georefererad karta.tif", "A 32280-2022")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 34942-2026 FSC-klagomål.docx", "A 34942-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 32280-2022 FSC-klagomål.docx", "A 32280-2022")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 34942-2026 FSC-klagomål mail.docx", "A 34942-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 32280-2022 FSC-klagomål mail.docx", "A 32280-2022")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 34942-2026 tillsynsbegäran.docx", "A 34942-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 32280-2022 tillsynsbegäran.docx", "A 32280-2022")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 34942-2026 tillsynsbegäran mail.docx", "A 34942-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 32280-2022 tillsynsbegäran mail.docx", "A 32280-2022")</f>
         <v/>
       </c>
       <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 34942-2026 prioriterade fågelarter.docx", "A 34942-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 32280-2022 prioriterade fågelarter.docx", "A 32280-2022")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 15219-2024</t>
+          <t>A 4831-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1413,14 +1413,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45400</v>
+        <v>45688</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1433,22 +1433,22 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>6.7</v>
+        <v>1.3</v>
       </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>1</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
       <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>2</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1460,7 +1460,7 @@
         <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1472,148 +1472,148 @@
         <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Skogsalm
+Barkticka</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 4831-2025 artfynd.xlsx", "A 4831-2025")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 4831-2025 karta.png", "A 4831-2025")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 4831-2025 georefererad karta.tif", "A 4831-2025")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 4831-2025 FSC-klagomål.docx", "A 4831-2025")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 4831-2025 FSC-klagomål mail.docx", "A 4831-2025")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 4831-2025 tillsynsbegäran.docx", "A 4831-2025")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 4831-2025 tillsynsbegäran mail.docx", "A 4831-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 15219-2024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45400</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Tårkragskivling
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 15219-2024 artfynd.xlsx", "A 15219-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 15219-2024 karta.png", "A 15219-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 15219-2024 georefererad karta.tif", "A 15219-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 15219-2024 FSC-klagomål.docx", "A 15219-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 15219-2024 FSC-klagomål mail.docx", "A 15219-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 15219-2024 tillsynsbegäran.docx", "A 15219-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 15219-2024 tillsynsbegäran mail.docx", "A 15219-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 4831-2025</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45688</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Skogsalm
-Barkticka</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 4831-2025 artfynd.xlsx", "A 4831-2025")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 4831-2025 karta.png", "A 4831-2025")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 4831-2025 georefererad karta.tif", "A 4831-2025")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 4831-2025 FSC-klagomål.docx", "A 4831-2025")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 4831-2025 FSC-klagomål mail.docx", "A 4831-2025")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 4831-2025 tillsynsbegäran.docx", "A 4831-2025")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 4831-2025 tillsynsbegäran mail.docx", "A 4831-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>45202</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>45898</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>45702</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>44630</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 44680-2023</t>
+          <t>A 24352-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2070,14 +2070,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45189</v>
+        <v>45797</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2130,684 +2130,684 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 24352-2025 artfynd.xlsx", "A 24352-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 24352-2025 karta.png", "A 24352-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 24352-2025 georefererad karta.tif", "A 24352-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 24352-2025 FSC-klagomål.docx", "A 24352-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 24352-2025 FSC-klagomål mail.docx", "A 24352-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 24352-2025 tillsynsbegäran.docx", "A 24352-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 24352-2025 tillsynsbegäran mail.docx", "A 24352-2025")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 24352-2025 prioriterade fågelarter.docx", "A 24352-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 10476-2023</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>44987</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 10476-2023 artfynd.xlsx", "A 10476-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 10476-2023 karta.png", "A 10476-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 10476-2023 georefererad karta.tif", "A 10476-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 10476-2023 FSC-klagomål.docx", "A 10476-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 10476-2023 FSC-klagomål mail.docx", "A 10476-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 10476-2023 tillsynsbegäran.docx", "A 10476-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 10476-2023 tillsynsbegäran mail.docx", "A 10476-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 62629-2022</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>44925</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Igelkott</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 62629-2022 artfynd.xlsx", "A 62629-2022")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 62629-2022 karta.png", "A 62629-2022")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 62629-2022 georefererad karta.tif", "A 62629-2022")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 62629-2022 FSC-klagomål.docx", "A 62629-2022")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 62629-2022 FSC-klagomål mail.docx", "A 62629-2022")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 62629-2022 tillsynsbegäran.docx", "A 62629-2022")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 62629-2022 tillsynsbegäran mail.docx", "A 62629-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 44680-2023</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45189</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
           <t>Trädlärka</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 44680-2023 artfynd.xlsx", "A 44680-2023")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 44680-2023 karta.png", "A 44680-2023")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 44680-2023 georefererad karta.tif", "A 44680-2023")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 44680-2023 FSC-klagomål.docx", "A 44680-2023")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 44680-2023 FSC-klagomål mail.docx", "A 44680-2023")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 44680-2023 tillsynsbegäran.docx", "A 44680-2023")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 44680-2023 tillsynsbegäran mail.docx", "A 44680-2023")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 44680-2023 prioriterade fågelarter.docx", "A 44680-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>A 61818-2024</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
         <v>45649</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
+      <c r="E19" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>6.2</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>1</v>
       </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>1</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T19" t="n">
         <v>1</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U19" t="n">
         <v>1</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Rödvingetrast</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 61818-2024 artfynd.xlsx", "A 61818-2024")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 61818-2024 karta.png", "A 61818-2024")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 61818-2024 georefererad karta.tif", "A 61818-2024")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 61818-2024 FSC-klagomål.docx", "A 61818-2024")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 61818-2024 FSC-klagomål mail.docx", "A 61818-2024")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 61818-2024 tillsynsbegäran.docx", "A 61818-2024")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 61818-2024 tillsynsbegäran mail.docx", "A 61818-2024")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 61818-2024 prioriterade fågelarter.docx", "A 61818-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>A 62569-2022</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
         <v>44924</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
+      <c r="E20" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
         <v>0.9</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
         <v>1</v>
       </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
         <v>1</v>
       </c>
-      <c r="R17" t="n">
+      <c r="R20" t="n">
         <v>1</v>
       </c>
-      <c r="S17" t="n">
+      <c r="S20" t="n">
         <v>1</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T20" t="n">
         <v>1</v>
       </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Skogsalm</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 62569-2022 artfynd.xlsx", "A 62569-2022")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 62569-2022 karta.png", "A 62569-2022")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 62569-2022 georefererad karta.tif", "A 62569-2022")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 62569-2022 FSC-klagomål.docx", "A 62569-2022")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 62569-2022 FSC-klagomål mail.docx", "A 62569-2022")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 62569-2022 tillsynsbegäran.docx", "A 62569-2022")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 62569-2022 tillsynsbegäran mail.docx", "A 62569-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 10476-2023</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>44987</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J18" t="n">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 37136-2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J21" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
         <v>1</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T21" t="n">
         <v>1</v>
       </c>
-      <c r="U18" t="n">
-        <v>1</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 10476-2023 artfynd.xlsx", "A 10476-2023")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 10476-2023 karta.png", "A 10476-2023")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 10476-2023 georefererad karta.tif", "A 10476-2023")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 10476-2023 FSC-klagomål.docx", "A 10476-2023")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 10476-2023 FSC-klagomål mail.docx", "A 10476-2023")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 10476-2023 tillsynsbegäran.docx", "A 10476-2023")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 10476-2023 tillsynsbegäran mail.docx", "A 10476-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 37136-2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>46274</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Fiskgjuse</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 37136-2026 artfynd.xlsx", "A 37136-2026")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 37136-2026 karta.png", "A 37136-2026")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 37136-2026 georefererad karta.tif", "A 37136-2026")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 37136-2026 FSC-klagomål.docx", "A 37136-2026")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 37136-2026 FSC-klagomål mail.docx", "A 37136-2026")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 37136-2026 tillsynsbegäran.docx", "A 37136-2026")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 37136-2026 tillsynsbegäran mail.docx", "A 37136-2026")</f>
         <v/>
       </c>
-      <c r="AE19">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 37136-2026 prioriterade fågelarter.docx", "A 37136-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 24352-2025</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45797</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 24352-2025 artfynd.xlsx", "A 24352-2025")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 24352-2025 karta.png", "A 24352-2025")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 24352-2025 georefererad karta.tif", "A 24352-2025")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 24352-2025 FSC-klagomål.docx", "A 24352-2025")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 24352-2025 FSC-klagomål mail.docx", "A 24352-2025")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 24352-2025 tillsynsbegäran.docx", "A 24352-2025")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 24352-2025 tillsynsbegäran mail.docx", "A 24352-2025")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 24352-2025 prioriterade fågelarter.docx", "A 24352-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 62629-2022</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>44925</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Igelkott</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 62629-2022 artfynd.xlsx", "A 62629-2022")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 62629-2022 karta.png", "A 62629-2022")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 62629-2022 georefererad karta.tif", "A 62629-2022")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 62629-2022 FSC-klagomål.docx", "A 62629-2022")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 62629-2022 FSC-klagomål mail.docx", "A 62629-2022")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 62629-2022 tillsynsbegäran.docx", "A 62629-2022")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 62629-2022 tillsynsbegäran mail.docx", "A 62629-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>44788</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>44466</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>44831</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>44820</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>44714</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>44566</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>44546</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>44627</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>44627</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>44725</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>44805</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>44705</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 58120-2021</t>
+          <t>A 9528-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3701,10 +3701,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44487</v>
+        <v>44617</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>20.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3760,7 +3760,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 9528-2022</t>
+          <t>A 58120-2021</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3774,10 +3774,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44617</v>
+        <v>44487</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>20.3</v>
+        <v>0.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3850,7 +3850,7 @@
         <v>44487</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>44770</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>44742</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>44806</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         <v>44515</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>44614</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>44747</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 7248-2025</t>
+          <t>A 8124-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4363,10 +4363,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45702</v>
+        <v>44974</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4422,7 +4422,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 53273-2023</t>
+          <t>A 60465-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4432,14 +4432,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45229</v>
+        <v>45643</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>6.3</v>
+        <v>0.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4495,7 +4495,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 49755-2022</t>
+          <t>A 48301-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4509,10 +4509,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44859</v>
+        <v>45590</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4568,7 +4568,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 6940-2024</t>
+          <t>A 60642-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4578,14 +4578,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45343</v>
+        <v>45260</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4641,7 +4641,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 59068-2023</t>
+          <t>A 7247-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4651,14 +4651,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45252</v>
+        <v>45702</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>6.4</v>
+        <v>1.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 136-2023</t>
+          <t>A 30399-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4728,10 +4728,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44928</v>
+        <v>45111</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4.5</v>
+        <v>1.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4787,7 +4787,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 18768-2024</t>
+          <t>A 24356-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4801,10 +4801,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45426</v>
+        <v>45797</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4860,7 +4860,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 9422-2024</t>
+          <t>A 53275-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4870,14 +4870,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45359</v>
+        <v>45229</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>8.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4933,7 +4933,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 31605-2024</t>
+          <t>A 48411-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4947,10 +4947,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45506</v>
+        <v>44858</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4962,13 +4962,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5011,7 +5006,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 45608-2022</t>
+          <t>A 44104-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5025,10 +5020,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44845</v>
+        <v>45572</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5041,7 +5036,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>17</v>
+        <v>2.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5084,7 +5079,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 28850-2024</t>
+          <t>A 11563-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5094,14 +5089,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45478</v>
+        <v>45727</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5113,8 +5108,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5157,7 +5157,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 37098-2023</t>
+          <t>A 19840-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5167,14 +5167,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45155</v>
+        <v>45771</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>4.8</v>
+        <v>0.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5230,7 +5230,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 36816-2024</t>
+          <t>A 58420-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5240,14 +5240,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45538</v>
+        <v>45250</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5259,13 +5259,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5308,7 +5303,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 36622-2023</t>
+          <t>A 36945-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5322,10 +5317,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45153</v>
+        <v>45538</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5337,8 +5332,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5381,7 +5381,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 8950-2024</t>
+          <t>A 17892-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5395,10 +5395,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45357</v>
+        <v>45758</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5454,7 +5454,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 10524-2024</t>
+          <t>A 11795-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5468,10 +5468,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45366</v>
+        <v>45375</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5527,7 +5527,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 58672-2022</t>
+          <t>A 29495-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5541,10 +5541,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44902</v>
+        <v>45824</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5557,7 +5557,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.4</v>
+        <v>5.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5600,7 +5600,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 43445-2023</t>
+          <t>A 55974-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5614,10 +5614,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45184</v>
+        <v>45623</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5673,7 +5673,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 32395-2023</t>
+          <t>A 31844-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5687,10 +5687,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45120</v>
+        <v>45834</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.1</v>
+        <v>6.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5746,7 +5746,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 8124-2023</t>
+          <t>A 31825-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5760,10 +5760,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44974</v>
+        <v>45834</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5819,7 +5819,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 40291-2024</t>
+          <t>A 5514-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5833,10 +5833,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45554</v>
+        <v>46050</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5848,8 +5848,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5892,7 +5897,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 29495-2025</t>
+          <t>A 48346-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5906,10 +5911,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45824</v>
+        <v>45590</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5922,7 +5927,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>5.2</v>
+        <v>0.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5965,7 +5970,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 31844-2025</t>
+          <t>A 39800-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5979,10 +5984,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45834</v>
+        <v>44819</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5995,7 +6000,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>6.2</v>
+        <v>2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6038,7 +6043,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 31825-2025</t>
+          <t>A 32355-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6052,10 +6057,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45834</v>
+        <v>45837</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6068,7 +6073,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6111,7 +6116,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 32355-2025</t>
+          <t>A 59069-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6121,14 +6126,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45837</v>
+        <v>45252</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6141,7 +6146,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.3</v>
+        <v>4.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6184,7 +6189,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 7247-2025</t>
+          <t>A 49755-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6198,10 +6203,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45702</v>
+        <v>44859</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6214,7 +6219,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6274,7 +6279,7 @@
         <v>45805</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6330,7 +6335,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 9738-2026</t>
+          <t>A 63778-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6340,14 +6345,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46072</v>
+        <v>45278</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6360,7 +6365,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6403,7 +6408,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 59069-2023</t>
+          <t>A 53279-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6417,10 +6422,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45252</v>
+        <v>45229</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6433,7 +6438,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4.9</v>
+        <v>0.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6476,7 +6481,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 53814-2024</t>
+          <t>A 7592-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6490,10 +6495,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45615</v>
+        <v>46061</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6506,7 +6511,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6549,7 +6554,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 55984-2024</t>
+          <t>A 136-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6563,10 +6568,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45623</v>
+        <v>44928</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6579,7 +6584,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.7</v>
+        <v>4.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6622,7 +6627,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 56419-2024</t>
+          <t>A 58620-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6636,10 +6641,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45623</v>
+        <v>44902</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6652,7 +6657,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>5.6</v>
+        <v>0.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6695,7 +6700,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 55897-2024</t>
+          <t>A 12819-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6709,10 +6714,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45622</v>
+        <v>44642</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6725,7 +6730,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6768,7 +6773,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 50577-2024</t>
+          <t>A 1455-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6782,10 +6787,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45601</v>
+        <v>45670</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6798,7 +6803,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6841,7 +6846,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 63778-2023</t>
+          <t>A 37169-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6851,14 +6856,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45278</v>
+        <v>44806</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6871,7 +6876,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.2</v>
+        <v>17.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6931,7 +6936,7 @@
         <v>45867</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6987,7 +6992,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 13530-2023</t>
+          <t>A 9738-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7001,10 +7006,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45006</v>
+        <v>46072</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7017,7 +7022,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7060,7 +7065,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 5577-2023</t>
+          <t>A 7223-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7074,10 +7079,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44960</v>
+        <v>45702</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7090,7 +7095,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.8</v>
+        <v>3.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7133,7 +7138,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 60290-2024</t>
+          <t>A 49906-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7147,10 +7152,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45642</v>
+        <v>45940</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7163,7 +7168,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7206,7 +7211,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 37195-2025</t>
+          <t>A 49909-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7216,14 +7221,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45875</v>
+        <v>45940</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7236,7 +7241,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7279,7 +7284,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 48411-2022</t>
+          <t>A 37195-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7289,14 +7294,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44858</v>
+        <v>45875</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7309,7 +7314,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7352,7 +7357,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 12819-2022</t>
+          <t>A 59068-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7362,14 +7367,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44642</v>
+        <v>45252</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7382,7 +7387,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.5</v>
+        <v>6.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7425,7 +7430,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 12175-2023</t>
+          <t>A 7248-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7439,10 +7444,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44998</v>
+        <v>45702</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7455,7 +7460,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7498,7 +7503,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 49906-2025</t>
+          <t>A 50577-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7512,10 +7517,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45940</v>
+        <v>45601</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7528,7 +7533,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7571,7 +7576,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 49909-2025</t>
+          <t>A 25762-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7585,10 +7590,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45940</v>
+        <v>45090</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7601,7 +7606,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7644,7 +7649,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 62527-2021</t>
+          <t>A 32952-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7658,10 +7663,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44503</v>
+        <v>45125</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7674,7 +7679,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>22.6</v>
+        <v>5.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7734,7 +7739,7 @@
         <v>46100</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7790,7 +7795,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 53275-2025</t>
+          <t>A 52719-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7804,10 +7809,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45958</v>
+        <v>45957</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7820,7 +7825,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7880,7 +7885,7 @@
         <v>45954</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7936,7 +7941,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 53274-2025</t>
+          <t>A 53275-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7953,7 +7958,7 @@
         <v>45958</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7966,7 +7971,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8009,7 +8014,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 52719-2025</t>
+          <t>A 53274-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8023,10 +8028,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8039,7 +8044,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8082,7 +8087,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 54191-2025</t>
+          <t>A 43445-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8096,10 +8101,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45964</v>
+        <v>45184</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8112,7 +8117,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8155,7 +8160,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 1949-2025</t>
+          <t>A 54191-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8169,10 +8174,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45672</v>
+        <v>45964</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8185,7 +8190,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.7</v>
+        <v>0.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8228,7 +8233,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 17527-2026</t>
+          <t>A 17533-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8242,10 +8247,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8258,7 +8263,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8301,7 +8306,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 17524-2026</t>
+          <t>A 17527-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8318,7 +8323,7 @@
         <v>46119</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8331,7 +8336,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.2</v>
+        <v>4.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8374,7 +8379,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 17533-2026</t>
+          <t>A 17495-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8391,7 +8396,7 @@
         <v>46120</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8404,7 +8409,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8447,7 +8452,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 17495-2026</t>
+          <t>A 17524-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8461,10 +8466,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46120</v>
+        <v>46119</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8477,7 +8482,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.6</v>
+        <v>0.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8537,7 +8542,7 @@
         <v>46122</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8598,7 +8603,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 62541-2021</t>
+          <t>A 37098-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8612,10 +8617,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44503</v>
+        <v>45155</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8628,7 +8633,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.3</v>
+        <v>4.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8688,7 +8693,7 @@
         <v>46129</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8761,7 +8766,7 @@
         <v>46129</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8817,7 +8822,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 59155-2025</t>
+          <t>A 49997-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8831,10 +8836,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45988</v>
+        <v>45943</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8847,7 +8852,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8890,7 +8895,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 54582-2023</t>
+          <t>A 61312-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8904,10 +8909,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45233</v>
+        <v>45264</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8963,7 +8968,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 58393-2022</t>
+          <t>A 15374-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8973,14 +8978,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44901</v>
+        <v>45747</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8993,7 +8998,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9036,7 +9041,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 11949-2023</t>
+          <t>A 6913-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9050,10 +9055,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44994</v>
+        <v>44967</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9066,7 +9071,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9109,7 +9114,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 33209-2023</t>
+          <t>A 41937-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9123,10 +9128,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45127</v>
+        <v>45903</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9139,7 +9144,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9182,7 +9187,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 8626-2024</t>
+          <t>A 59155-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9196,10 +9201,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45355</v>
+        <v>45988</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9212,7 +9217,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>6.4</v>
+        <v>2.2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9255,7 +9260,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 44849-2024</t>
+          <t>A 30904-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9269,10 +9274,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45574</v>
+        <v>44767</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9285,7 +9290,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9328,7 +9333,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 62551-2021</t>
+          <t>A 12175-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9342,10 +9347,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44503</v>
+        <v>44998</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9358,7 +9363,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.9</v>
+        <v>4.3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9401,7 +9406,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 11795-2024</t>
+          <t>A 20614-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9415,10 +9420,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45375</v>
+        <v>45776</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9431,7 +9436,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>3.8</v>
+        <v>0.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9474,7 +9479,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 35047-2024</t>
+          <t>A 24234-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9488,10 +9493,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45527</v>
+        <v>45797</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9504,7 +9509,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9547,7 +9552,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 39800-2022</t>
+          <t>A 8953-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9561,10 +9566,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44819</v>
+        <v>44979</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9577,7 +9582,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9620,7 +9625,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 49997-2025</t>
+          <t>A 246-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9634,10 +9639,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45943</v>
+        <v>45660</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9650,7 +9655,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9693,7 +9698,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 6913-2023</t>
+          <t>A 21017-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9707,10 +9712,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44967</v>
+        <v>46144</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9723,7 +9728,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9766,7 +9771,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 30484-2023</t>
+          <t>A 7760-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9780,10 +9785,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45111</v>
+        <v>45706</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9796,7 +9801,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9839,7 +9844,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 5514-2026</t>
+          <t>A 61405-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9853,10 +9858,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46050</v>
+        <v>46001</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9874,7 +9879,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.5</v>
+        <v>6.6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9917,7 +9922,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 15374-2025</t>
+          <t>A 2086-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9931,10 +9936,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45747</v>
+        <v>45672</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9947,7 +9952,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9990,7 +9995,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 20614-2025</t>
+          <t>A 62527-2021</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10004,10 +10009,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45776</v>
+        <v>44503</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10020,7 +10025,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.7</v>
+        <v>22.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10063,7 +10068,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 41937-2025</t>
+          <t>A 29433-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10077,10 +10082,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45903</v>
+        <v>45824</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10093,7 +10098,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10136,7 +10141,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 35087-2024</t>
+          <t>A 8936-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10150,10 +10155,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45527</v>
+        <v>46069</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10166,7 +10171,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10209,7 +10214,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 35112-2024</t>
+          <t>A 24279-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10223,10 +10228,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45529</v>
+        <v>46169</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10239,7 +10244,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.6</v>
+        <v>11.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10282,7 +10287,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 24234-2025</t>
+          <t>A 60290-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10296,10 +10301,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45797</v>
+        <v>45642</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10312,7 +10317,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10355,7 +10360,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 7592-2026</t>
+          <t>A 24736-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10369,10 +10374,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46061</v>
+        <v>46171</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10384,8 +10389,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10428,7 +10438,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 61312-2023</t>
+          <t>A 33654-2022</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10442,10 +10452,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45264</v>
+        <v>44789</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10458,7 +10468,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10501,7 +10511,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 21017-2026</t>
+          <t>A 35112-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10515,10 +10525,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46144</v>
+        <v>45529</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10531,7 +10541,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10574,7 +10584,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 246-2025</t>
+          <t>A 25814-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10588,10 +10598,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45660</v>
+        <v>46178</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10604,7 +10614,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10647,7 +10657,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 48301-2024</t>
+          <t>A 26148-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10661,10 +10671,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45590</v>
+        <v>46181</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10677,7 +10687,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10720,7 +10730,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 30399-2023</t>
+          <t>A 27552-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10734,10 +10744,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45111</v>
+        <v>46190</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10750,7 +10760,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.4</v>
+        <v>5.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10793,7 +10803,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 60465-2024</t>
+          <t>A 32504-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10807,10 +10817,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45643</v>
+        <v>46239</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10822,8 +10832,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10866,7 +10881,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 25322-2024</t>
+          <t>A 32497-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10880,10 +10895,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45462</v>
+        <v>46239</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10895,8 +10910,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10939,7 +10959,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 35202-2023</t>
+          <t>A 28068-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10953,10 +10973,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45145</v>
+        <v>46195</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10969,7 +10989,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>11.1</v>
+        <v>0.7</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11012,7 +11032,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 31596-2024</t>
+          <t>A 28056-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11026,10 +11046,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45506</v>
+        <v>46195</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11041,13 +11061,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>4.3</v>
+        <v>1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11090,7 +11105,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 40257-2023</t>
+          <t>A 28309-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11104,10 +11119,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45169</v>
+        <v>46196</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11120,7 +11135,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11163,7 +11178,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 19759-2024</t>
+          <t>A 32477-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11177,10 +11192,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45432</v>
+        <v>46239</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11192,8 +11207,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11236,7 +11256,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 56542-2024</t>
+          <t>A 19759-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11246,14 +11266,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45625</v>
+        <v>45432</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11309,7 +11329,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 24759-2023</t>
+          <t>A 56413-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11323,10 +11343,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45084</v>
+        <v>45623</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11339,7 +11359,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11382,7 +11402,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 61405-2025</t>
+          <t>A 32923-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11396,10 +11416,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46001</v>
+        <v>46244</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11411,13 +11431,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>6.6</v>
+        <v>2.1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11460,7 +11475,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 29433-2025</t>
+          <t>A 1949-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11474,10 +11489,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45824</v>
+        <v>45672</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11490,7 +11505,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11533,7 +11548,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 8936-2026</t>
+          <t>A 696-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11547,10 +11562,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46069</v>
+        <v>45665</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11563,7 +11578,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11606,7 +11621,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 37169-2022</t>
+          <t>A 34779-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11620,10 +11635,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44806</v>
+        <v>45141</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11636,7 +11651,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>17.4</v>
+        <v>3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11679,7 +11694,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 60118-2024</t>
+          <t>A 32944-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11693,10 +11708,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45642</v>
+        <v>46244</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11709,7 +11724,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11752,7 +11767,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 53769-2024</t>
+          <t>A 33984-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11762,14 +11777,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45615</v>
+        <v>46252</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11782,7 +11797,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11825,7 +11840,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 696-2025</t>
+          <t>A 36835-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11839,10 +11854,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45665</v>
+        <v>45538</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11854,8 +11869,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I145" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11898,7 +11918,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 60642-2023</t>
+          <t>A 34112-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11908,14 +11928,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45260</v>
+        <v>46253</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11928,7 +11948,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11971,7 +11991,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 24279-2026</t>
+          <t>A 58393-2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11981,14 +12001,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46169</v>
+        <v>44901</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12001,7 +12021,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>11.7</v>
+        <v>2.1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12044,7 +12064,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 24736-2026</t>
+          <t>A 2872-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12058,10 +12078,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46171</v>
+        <v>44945</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12073,13 +12093,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12122,7 +12137,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 44308-2023</t>
+          <t>A 11949-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12136,10 +12151,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45188</v>
+        <v>44994</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12152,7 +12167,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12195,7 +12210,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 54279-2023</t>
+          <t>A 54582-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12209,10 +12224,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45232</v>
+        <v>45233</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12225,7 +12240,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12268,7 +12283,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 33654-2022</t>
+          <t>A 54279-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12282,10 +12297,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44789</v>
+        <v>45232</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12298,7 +12313,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12341,7 +12356,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 25814-2026</t>
+          <t>A 36816-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12355,10 +12370,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46178</v>
+        <v>45538</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12370,8 +12385,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12414,7 +12434,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 7212-2025</t>
+          <t>A 55984-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12428,10 +12448,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45702</v>
+        <v>45623</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12444,7 +12464,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12487,7 +12507,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 26148-2026</t>
+          <t>A 35047-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12501,10 +12521,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46181</v>
+        <v>45527</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12517,7 +12537,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12560,7 +12580,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 8953-2023</t>
+          <t>A 25322-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12574,10 +12594,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44979</v>
+        <v>45462</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12590,7 +12610,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12633,7 +12653,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 59644-2023</t>
+          <t>A 36878-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12647,10 +12667,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45254</v>
+        <v>46273</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12663,7 +12683,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12706,7 +12726,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 6080-2023</t>
+          <t>A 36716-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12716,14 +12736,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>44964</v>
+        <v>46272</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12736,7 +12756,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12779,7 +12799,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 27552-2026</t>
+          <t>A 31826-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12793,10 +12813,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46190</v>
+        <v>46230</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12809,7 +12829,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>5.3</v>
+        <v>0.8</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12852,7 +12872,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 28056-2026</t>
+          <t>A 34936-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12866,10 +12886,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46195</v>
+        <v>46259</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12882,7 +12902,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1</v>
+        <v>7.4</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12925,7 +12945,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 28068-2026</t>
+          <t>A 34941-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12939,10 +12959,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46195</v>
+        <v>46259</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12955,7 +12975,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12998,7 +13018,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 59010-2024</t>
+          <t>A 34945-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13012,10 +13032,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45635</v>
+        <v>46259</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13028,7 +13048,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>3.5</v>
+        <v>6.2</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13071,7 +13091,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 32504-2026</t>
+          <t>A 31897-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13085,10 +13105,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46239</v>
+        <v>46231</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13100,13 +13120,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I162" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13149,7 +13164,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 28309-2026</t>
+          <t>A 31899-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13163,10 +13178,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46196</v>
+        <v>46231</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13179,7 +13194,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13222,7 +13237,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 32477-2026</t>
+          <t>A 31596-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13236,10 +13251,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46239</v>
+        <v>45506</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13253,11 +13268,11 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I164" t="n">
-        <v>2.4</v>
+        <v>4.3</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13300,7 +13315,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 32497-2026</t>
+          <t>A 31902-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13314,10 +13329,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46239</v>
+        <v>46231</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13329,13 +13344,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I165" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13378,7 +13388,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 32923-2026</t>
+          <t>A 52999-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13392,10 +13402,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46244</v>
+        <v>45226</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13408,7 +13418,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13451,7 +13461,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 32944-2026</t>
+          <t>A 53273-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13461,14 +13471,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46244</v>
+        <v>45229</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13481,7 +13491,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.7</v>
+        <v>6.3</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13524,7 +13534,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 58620-2022</t>
+          <t>A 24759-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13538,10 +13548,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44902</v>
+        <v>45084</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13554,7 +13564,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13597,7 +13607,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 34779-2023</t>
+          <t>A 52853-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13611,10 +13621,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45141</v>
+        <v>45226</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13627,7 +13637,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13670,7 +13680,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 60112-2024</t>
+          <t>A 7212-2025</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13684,10 +13694,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45642</v>
+        <v>45702</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13700,7 +13710,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13743,7 +13753,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 53279-2023</t>
+          <t>A 32395-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13753,14 +13763,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45229</v>
+        <v>45120</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13773,7 +13783,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13816,7 +13826,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 6102-2023</t>
+          <t>A 6080-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13826,14 +13836,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D172" s="1" t="n">
         <v>44964</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13846,7 +13856,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13889,7 +13899,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 43460-2024</t>
+          <t>A 35202-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13903,10 +13913,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45568</v>
+        <v>45145</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13919,7 +13929,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>0.8</v>
+        <v>11.1</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13962,7 +13972,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 13522-2023</t>
+          <t>A 5577-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13976,10 +13986,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45006</v>
+        <v>44960</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13992,7 +14002,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14035,7 +14045,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 33984-2026</t>
+          <t>A 30484-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14045,14 +14055,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46252</v>
+        <v>45111</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14065,7 +14075,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>2.9</v>
+        <v>0.2</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14108,7 +14118,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 25762-2023</t>
+          <t>A 8950-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14122,10 +14132,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45090</v>
+        <v>45357</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14138,7 +14148,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14181,7 +14191,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 2872-2023</t>
+          <t>A 46876-2022</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14195,10 +14205,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44945</v>
+        <v>44851</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14211,7 +14221,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.5</v>
+        <v>7.5</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14254,7 +14264,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 46876-2022</t>
+          <t>A 13522-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14268,10 +14278,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44851</v>
+        <v>45006</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14284,7 +14294,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>7.5</v>
+        <v>2.4</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14327,7 +14337,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 1455-2025</t>
+          <t>A 56419-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14341,10 +14351,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45670</v>
+        <v>45623</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14357,7 +14367,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.4</v>
+        <v>5.6</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14400,7 +14410,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 48346-2024</t>
+          <t>A 8626-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14414,10 +14424,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45590</v>
+        <v>45355</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14430,7 +14440,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.8</v>
+        <v>6.4</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14473,7 +14483,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 34112-2026</t>
+          <t>A 60112-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14487,10 +14497,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46253</v>
+        <v>45642</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14503,7 +14513,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14546,7 +14556,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 36835-2024</t>
+          <t>A 31605-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14560,10 +14570,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45538</v>
+        <v>45506</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14581,7 +14591,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14624,7 +14634,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 32952-2023</t>
+          <t>A 60118-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14638,10 +14648,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45125</v>
+        <v>45642</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14654,7 +14664,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>5.1</v>
+        <v>0.6</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14697,7 +14707,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 2086-2025</t>
+          <t>A 62551-2021</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14711,10 +14721,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45672</v>
+        <v>44503</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14727,7 +14737,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14770,7 +14780,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 30904-2022</t>
+          <t>A 56542-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14780,14 +14790,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44767</v>
+        <v>45625</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14800,7 +14810,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>5</v>
+        <v>0.9</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14843,7 +14853,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 56740-2023</t>
+          <t>A 53814-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14857,10 +14867,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45244</v>
+        <v>45615</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14873,7 +14883,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>4.5</v>
+        <v>1.8</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14916,7 +14926,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 52853-2023</t>
+          <t>A 10524-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14930,10 +14940,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45226</v>
+        <v>45366</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14946,7 +14956,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14989,7 +14999,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 55974-2024</t>
+          <t>A 9422-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15003,10 +15013,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45623</v>
+        <v>45359</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15019,7 +15029,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15062,7 +15072,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 53764-2024</t>
+          <t>A 45608-2022</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15076,10 +15086,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45615</v>
+        <v>44845</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15092,7 +15102,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.1</v>
+        <v>17</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15135,7 +15145,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 41163-2023</t>
+          <t>A 58672-2022</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15149,10 +15159,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45174</v>
+        <v>44902</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15165,7 +15175,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15208,7 +15218,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 36716-2026</t>
+          <t>A 55897-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15222,10 +15232,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46272</v>
+        <v>45622</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15238,7 +15248,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15281,7 +15291,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 31902-2026</t>
+          <t>A 41163-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15295,10 +15305,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46231</v>
+        <v>45174</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15311,7 +15321,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15354,7 +15364,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 7223-2025</t>
+          <t>A 40257-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15368,10 +15378,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45702</v>
+        <v>45169</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15384,7 +15394,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15427,7 +15437,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 36878-2026</t>
+          <t>A 36622-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15441,10 +15451,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46273</v>
+        <v>45153</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15457,7 +15467,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15500,7 +15510,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 31897-2026</t>
+          <t>A 62541-2021</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15514,10 +15524,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46231</v>
+        <v>44503</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15530,7 +15540,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15573,7 +15583,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 31899-2026</t>
+          <t>A 28850-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15587,10 +15597,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46231</v>
+        <v>45478</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15603,7 +15613,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15646,7 +15656,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 56365-2024</t>
+          <t>A 44849-2024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15660,10 +15670,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45625</v>
+        <v>45574</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15676,7 +15686,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15719,7 +15729,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 31826-2026</t>
+          <t>A 59644-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15733,10 +15743,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46230</v>
+        <v>45254</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15749,7 +15759,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15792,7 +15802,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 52999-2023</t>
+          <t>A 56365-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15806,10 +15816,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45226</v>
+        <v>45625</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15822,7 +15832,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15865,7 +15875,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 34941-2026</t>
+          <t>A 6940-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15879,10 +15889,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46259</v>
+        <v>45343</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15895,7 +15905,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>9.300000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15938,7 +15948,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 7760-2025</t>
+          <t>A 40291-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15952,10 +15962,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45706</v>
+        <v>45554</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15968,7 +15978,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>8.300000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16011,7 +16021,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 56413-2024</t>
+          <t>A 33209-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16025,10 +16035,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45623</v>
+        <v>45127</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16041,7 +16051,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16084,7 +16094,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 34945-2026</t>
+          <t>A 53764-2024</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16098,10 +16108,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46259</v>
+        <v>45615</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16114,7 +16124,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>6.2</v>
+        <v>1.1</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16157,7 +16167,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 34936-2026</t>
+          <t>A 44308-2023</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16171,10 +16181,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46259</v>
+        <v>45188</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16187,7 +16197,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>7.4</v>
+        <v>0.7</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16230,7 +16240,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 56373-2024</t>
+          <t>A 13530-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16244,10 +16254,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45625</v>
+        <v>45006</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16260,7 +16270,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16303,7 +16313,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 61817-2024</t>
+          <t>A 35087-2024</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16317,10 +16327,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45649</v>
+        <v>45527</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16333,7 +16343,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16376,7 +16386,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 9973-2024</t>
+          <t>A 53769-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16390,10 +16400,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45363</v>
+        <v>45615</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16406,7 +16416,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>4.7</v>
+        <v>1.2</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16449,7 +16459,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 53805-2024</t>
+          <t>A 6102-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16463,10 +16473,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45615</v>
+        <v>44964</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16479,7 +16489,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16522,7 +16532,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 11393-2025</t>
+          <t>A 18768-2024</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16536,10 +16546,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45726</v>
+        <v>45426</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16552,7 +16562,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16595,7 +16605,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 11563-2025</t>
+          <t>A 56740-2023</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16605,14 +16615,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45727</v>
+        <v>45244</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16624,13 +16634,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I210" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16673,7 +16678,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 53275-2023</t>
+          <t>A 43460-2024</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16683,14 +16688,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45229</v>
+        <v>45568</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16703,7 +16708,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>8.5</v>
+        <v>0.8</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16746,7 +16751,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 44104-2024</t>
+          <t>A 59010-2024</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16760,10 +16765,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45572</v>
+        <v>45635</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16776,7 +16781,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16819,7 +16824,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 24356-2025</t>
+          <t>A 61817-2024</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16833,10 +16838,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45797</v>
+        <v>45649</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16849,7 +16854,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>0.2</v>
+        <v>4.6</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16892,7 +16897,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 19840-2025</t>
+          <t>A 9973-2024</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16902,14 +16907,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45771</v>
+        <v>45363</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16922,7 +16927,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>0.2</v>
+        <v>4.7</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16965,7 +16970,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 58420-2023</t>
+          <t>A 56373-2024</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16975,14 +16980,14 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45250</v>
+        <v>45625</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16995,7 +17000,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17038,7 +17043,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 36945-2024</t>
+          <t>A 53805-2024</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17052,10 +17057,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45538</v>
+        <v>45615</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17067,13 +17072,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I216" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17116,7 +17116,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 17892-2025</t>
+          <t>A 11393-2025</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17130,10 +17130,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45758</v>
+        <v>45726</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17146,7 +17146,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17189,7 +17189,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>S 1807-2022</t>
+          <t>S 3762-2024</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17199,14 +17199,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Skogsbilväg</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>44656</v>
+        <v>45558</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17218,13 +17218,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I218" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17267,7 +17262,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>S 3762-2024</t>
+          <t>S 1807-2022</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17277,14 +17272,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Skogsbilväg</t>
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45558</v>
+        <v>44656</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17296,8 +17291,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I219" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17357,7 +17357,7 @@
         <v>45688</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17430,7 +17430,7 @@
         <v>45688</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17503,7 +17503,7 @@
         <v>44705</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>

--- a/Översikt LIDKÖPING.xlsx
+++ b/Översikt LIDKÖPING.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE222"/>
+  <dimension ref="A1:AE225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44631</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>46006</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>44967</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
         <v>46171</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 28849-2024</t>
+          <t>A 32280-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45478</v>
+        <v>44781</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1097,13 +1097,13 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.6</v>
+        <v>8.6</v>
       </c>
       <c r="J6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -1136,6 +1136,118 @@
         <v>0</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Gulsparv
+Nötkråka
+Sotriska
+Skogsduva</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 32280-2022 artfynd.xlsx", "A 32280-2022")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 32280-2022 karta.png", "A 32280-2022")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 32280-2022 georefererad karta.tif", "A 32280-2022")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 32280-2022 FSC-klagomål.docx", "A 32280-2022")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 32280-2022 FSC-klagomål mail.docx", "A 32280-2022")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 32280-2022 tillsynsbegäran.docx", "A 32280-2022")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 32280-2022 tillsynsbegäran mail.docx", "A 32280-2022")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 32280-2022 prioriterade fågelarter.docx", "A 32280-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 28849-2024</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45478</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Entita
 Talltita
@@ -1143,111 +1255,111 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 28849-2024 artfynd.xlsx", "A 28849-2024")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 28849-2024 karta.png", "A 28849-2024")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 28849-2024 georefererad karta.tif", "A 28849-2024")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 28849-2024 FSC-klagomål.docx", "A 28849-2024")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 28849-2024 FSC-klagomål mail.docx", "A 28849-2024")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 28849-2024 tillsynsbegäran.docx", "A 28849-2024")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 28849-2024 tillsynsbegäran mail.docx", "A 28849-2024")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 28849-2024 prioriterade fågelarter.docx", "A 28849-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>A 34942-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
         <v>46259</v>
       </c>
-      <c r="E7" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
+      <c r="E8" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
         <v>18.1</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J8" t="n">
         <v>3</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K8" t="n">
         <v>1</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L8" t="n">
         <v>2</v>
       </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>2</v>
       </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
         <v>4</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T8" t="n">
         <v>4</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Gulsparv
 Nötkråka
@@ -1255,155 +1367,43 @@
 Skogsduva</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 34942-2026 artfynd.xlsx", "A 34942-2026")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 34942-2026 karta.png", "A 34942-2026")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 34942-2026 georefererad karta.tif", "A 34942-2026")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 34942-2026 FSC-klagomål.docx", "A 34942-2026")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 34942-2026 FSC-klagomål mail.docx", "A 34942-2026")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 34942-2026 tillsynsbegäran.docx", "A 34942-2026")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 34942-2026 tillsynsbegäran mail.docx", "A 34942-2026")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 34942-2026 prioriterade fågelarter.docx", "A 34942-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 32280-2022</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>44781</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>4</v>
-      </c>
-      <c r="T8" t="n">
-        <v>4</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Gulsparv
-Nötkråka
-Sotriska
-Skogsduva</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 32280-2022 artfynd.xlsx", "A 32280-2022")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 32280-2022 karta.png", "A 32280-2022")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 32280-2022 georefererad karta.tif", "A 32280-2022")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 32280-2022 FSC-klagomål.docx", "A 32280-2022")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 32280-2022 FSC-klagomål mail.docx", "A 32280-2022")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 32280-2022 tillsynsbegäran.docx", "A 32280-2022")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 32280-2022 tillsynsbegäran mail.docx", "A 32280-2022")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 32280-2022 prioriterade fågelarter.docx", "A 32280-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 4831-2025</t>
+          <t>A 15219-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1413,14 +1413,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45688</v>
+        <v>45400</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1433,22 +1433,22 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.3</v>
+        <v>6.7</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1460,7 +1460,7 @@
         <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1472,148 +1472,148 @@
         <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Tårkragskivling
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 15219-2024 artfynd.xlsx", "A 15219-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 15219-2024 karta.png", "A 15219-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 15219-2024 georefererad karta.tif", "A 15219-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 15219-2024 FSC-klagomål.docx", "A 15219-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 15219-2024 FSC-klagomål mail.docx", "A 15219-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 15219-2024 tillsynsbegäran.docx", "A 15219-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 15219-2024 tillsynsbegäran mail.docx", "A 15219-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 4831-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45688</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Ask
 Skogsalm
 Barkticka</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 4831-2025 artfynd.xlsx", "A 4831-2025")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 4831-2025 karta.png", "A 4831-2025")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 4831-2025 georefererad karta.tif", "A 4831-2025")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 4831-2025 FSC-klagomål.docx", "A 4831-2025")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 4831-2025 FSC-klagomål mail.docx", "A 4831-2025")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 4831-2025 tillsynsbegäran.docx", "A 4831-2025")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 4831-2025 tillsynsbegäran mail.docx", "A 4831-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 15219-2024</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45400</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Tårkragskivling
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 15219-2024 artfynd.xlsx", "A 15219-2024")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 15219-2024 karta.png", "A 15219-2024")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 15219-2024 georefererad karta.tif", "A 15219-2024")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 15219-2024 FSC-klagomål.docx", "A 15219-2024")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 15219-2024 FSC-klagomål mail.docx", "A 15219-2024")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 15219-2024 tillsynsbegäran.docx", "A 15219-2024")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 15219-2024 tillsynsbegäran mail.docx", "A 15219-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>45202</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>45898</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>45702</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>44630</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 24352-2025</t>
+          <t>A 44680-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2070,14 +2070,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45797</v>
+        <v>45189</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2130,39 +2130,39 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 24352-2025 artfynd.xlsx", "A 24352-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 44680-2023 artfynd.xlsx", "A 44680-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 24352-2025 karta.png", "A 24352-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 44680-2023 karta.png", "A 44680-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 24352-2025 georefererad karta.tif", "A 24352-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 44680-2023 georefererad karta.tif", "A 44680-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 24352-2025 FSC-klagomål.docx", "A 24352-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 44680-2023 FSC-klagomål.docx", "A 44680-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 24352-2025 FSC-klagomål mail.docx", "A 24352-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 44680-2023 FSC-klagomål mail.docx", "A 44680-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 24352-2025 tillsynsbegäran.docx", "A 24352-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 44680-2023 tillsynsbegäran.docx", "A 44680-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 24352-2025 tillsynsbegäran mail.docx", "A 24352-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 44680-2023 tillsynsbegäran mail.docx", "A 44680-2023")</f>
         <v/>
       </c>
       <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 24352-2025 prioriterade fågelarter.docx", "A 24352-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 44680-2023 prioriterade fågelarter.docx", "A 44680-2023")</f>
         <v/>
       </c>
     </row>
@@ -2186,7 +2186,7 @@
         <v>44987</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 62629-2022</t>
+          <t>A 62569-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44925</v>
+        <v>44924</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2316,10 +2316,10 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
         <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2340,474 +2340,474 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 62569-2022 artfynd.xlsx", "A 62569-2022")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 62569-2022 karta.png", "A 62569-2022")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 62569-2022 georefererad karta.tif", "A 62569-2022")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 62569-2022 FSC-klagomål.docx", "A 62569-2022")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 62569-2022 FSC-klagomål mail.docx", "A 62569-2022")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 62569-2022 tillsynsbegäran.docx", "A 62569-2022")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 62569-2022 tillsynsbegäran mail.docx", "A 62569-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 37136-2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J18" t="n">
         <v>1</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Fiskgjuse</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 37136-2026 artfynd.xlsx", "A 37136-2026")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 37136-2026 karta.png", "A 37136-2026")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 37136-2026 georefererad karta.tif", "A 37136-2026")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 37136-2026 FSC-klagomål.docx", "A 37136-2026")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 37136-2026 FSC-klagomål mail.docx", "A 37136-2026")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 37136-2026 tillsynsbegäran.docx", "A 37136-2026")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 37136-2026 tillsynsbegäran mail.docx", "A 37136-2026")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 37136-2026 prioriterade fågelarter.docx", "A 37136-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 24352-2025</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45797</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 24352-2025 artfynd.xlsx", "A 24352-2025")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 24352-2025 karta.png", "A 24352-2025")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 24352-2025 georefererad karta.tif", "A 24352-2025")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 24352-2025 FSC-klagomål.docx", "A 24352-2025")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 24352-2025 FSC-klagomål mail.docx", "A 24352-2025")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 24352-2025 tillsynsbegäran.docx", "A 24352-2025")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 24352-2025 tillsynsbegäran mail.docx", "A 24352-2025")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 24352-2025 prioriterade fågelarter.docx", "A 24352-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 62629-2022</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>44925</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Igelkott</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 62629-2022 artfynd.xlsx", "A 62629-2022")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 62629-2022 karta.png", "A 62629-2022")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 62629-2022 georefererad karta.tif", "A 62629-2022")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 62629-2022 FSC-klagomål.docx", "A 62629-2022")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 62629-2022 FSC-klagomål mail.docx", "A 62629-2022")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 62629-2022 tillsynsbegäran.docx", "A 62629-2022")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 62629-2022 tillsynsbegäran mail.docx", "A 62629-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 44680-2023</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45189</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J18" t="n">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 61818-2024</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45649</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J21" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
         <v>1</v>
       </c>
-      <c r="T18" t="n">
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>1</v>
       </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Trädlärka</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 44680-2023 artfynd.xlsx", "A 44680-2023")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 44680-2023 karta.png", "A 44680-2023")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 44680-2023 georefererad karta.tif", "A 44680-2023")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 44680-2023 FSC-klagomål.docx", "A 44680-2023")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 44680-2023 FSC-klagomål mail.docx", "A 44680-2023")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 44680-2023 tillsynsbegäran.docx", "A 44680-2023")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 44680-2023 tillsynsbegäran mail.docx", "A 44680-2023")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 44680-2023 prioriterade fågelarter.docx", "A 44680-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 61818-2024</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45649</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J19" t="n">
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
+      <c r="T21" t="n">
         <v>1</v>
       </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="U21" t="n">
         <v>1</v>
       </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Rödvingetrast</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 61818-2024 artfynd.xlsx", "A 61818-2024")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 61818-2024 karta.png", "A 61818-2024")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 61818-2024 georefererad karta.tif", "A 61818-2024")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 61818-2024 FSC-klagomål.docx", "A 61818-2024")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 61818-2024 FSC-klagomål mail.docx", "A 61818-2024")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 61818-2024 tillsynsbegäran.docx", "A 61818-2024")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 61818-2024 tillsynsbegäran mail.docx", "A 61818-2024")</f>
         <v/>
       </c>
-      <c r="AE19">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 61818-2024 prioriterade fågelarter.docx", "A 61818-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 62569-2022</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>44924</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>1</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 62569-2022 artfynd.xlsx", "A 62569-2022")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 62569-2022 karta.png", "A 62569-2022")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 62569-2022 georefererad karta.tif", "A 62569-2022")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 62569-2022 FSC-klagomål.docx", "A 62569-2022")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 62569-2022 FSC-klagomål mail.docx", "A 62569-2022")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 62569-2022 tillsynsbegäran.docx", "A 62569-2022")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 62569-2022 tillsynsbegäran mail.docx", "A 62569-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 37136-2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>46274</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Fiskgjuse</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 37136-2026 artfynd.xlsx", "A 37136-2026")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 37136-2026 karta.png", "A 37136-2026")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 37136-2026 georefererad karta.tif", "A 37136-2026")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 37136-2026 FSC-klagomål.docx", "A 37136-2026")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 37136-2026 FSC-klagomål mail.docx", "A 37136-2026")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 37136-2026 tillsynsbegäran.docx", "A 37136-2026")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 37136-2026 tillsynsbegäran mail.docx", "A 37136-2026")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 37136-2026 prioriterade fågelarter.docx", "A 37136-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>44788</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>44466</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>44831</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>44820</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>44714</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>44566</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>44546</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>44627</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>44627</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>44725</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>44805</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>44705</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>44617</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>44487</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>44487</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>44770</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>44742</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>44806</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         <v>44515</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 8790-2022</t>
+          <t>A 53273-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4208,14 +4208,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44614</v>
+        <v>45229</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4227,13 +4227,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>2.1</v>
+        <v>6.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4293,7 +4288,7 @@
         <v>44747</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4349,7 +4344,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 8124-2023</t>
+          <t>A 49755-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4363,10 +4358,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44974</v>
+        <v>44859</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4379,7 +4374,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4422,7 +4417,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 60465-2024</t>
+          <t>A 8790-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4436,10 +4431,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45643</v>
+        <v>44614</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4451,8 +4446,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4495,7 +4495,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 48301-2024</t>
+          <t>A 44308-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4509,10 +4509,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45590</v>
+        <v>45188</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4568,7 +4568,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 60642-2023</t>
+          <t>A 6940-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4578,14 +4578,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45260</v>
+        <v>45343</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4641,7 +4641,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 7247-2025</t>
+          <t>A 59068-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4651,14 +4651,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45702</v>
+        <v>45252</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.3</v>
+        <v>6.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 30399-2023</t>
+          <t>A 136-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4728,10 +4728,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45111</v>
+        <v>44928</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.4</v>
+        <v>4.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4787,7 +4787,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 24356-2025</t>
+          <t>A 37195-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4797,14 +4797,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45797</v>
+        <v>45875</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4860,7 +4860,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 53275-2023</t>
+          <t>A 7248-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4870,14 +4870,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45229</v>
+        <v>45702</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>8.5</v>
+        <v>1.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4933,7 +4933,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 48411-2022</t>
+          <t>A 54279-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4947,10 +4947,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44858</v>
+        <v>45232</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5006,7 +5006,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 44104-2024</t>
+          <t>A 7212-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5020,10 +5020,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45572</v>
+        <v>45702</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5079,7 +5079,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 11563-2025</t>
+          <t>A 8953-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5089,14 +5089,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45727</v>
+        <v>44979</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5108,13 +5108,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5157,7 +5152,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 19840-2025</t>
+          <t>A 18768-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5167,14 +5162,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45771</v>
+        <v>45426</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5187,7 +5182,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5230,7 +5225,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 58420-2023</t>
+          <t>A 48411-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5240,14 +5235,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45250</v>
+        <v>44858</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5260,7 +5255,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5303,7 +5298,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 36945-2024</t>
+          <t>A 59644-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5317,10 +5312,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45538</v>
+        <v>45254</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5332,13 +5327,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5381,7 +5371,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 17892-2025</t>
+          <t>A 9422-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5395,10 +5385,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45758</v>
+        <v>45359</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5411,7 +5401,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5454,7 +5444,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 11795-2024</t>
+          <t>A 6080-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5464,14 +5454,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45375</v>
+        <v>44964</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5484,7 +5474,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.8</v>
+        <v>1.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5527,7 +5517,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 29495-2025</t>
+          <t>A 45608-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5541,10 +5531,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45824</v>
+        <v>44845</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5557,7 +5547,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>5.2</v>
+        <v>17</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5600,7 +5590,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 55974-2024</t>
+          <t>A 31605-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5614,10 +5604,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45623</v>
+        <v>45506</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5629,8 +5619,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5673,7 +5668,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 31844-2025</t>
+          <t>A 28850-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5687,10 +5682,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45834</v>
+        <v>45478</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5703,7 +5698,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>6.2</v>
+        <v>1.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5746,7 +5741,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 31825-2025</t>
+          <t>A 37098-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5760,10 +5755,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45834</v>
+        <v>45155</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5776,7 +5771,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.2</v>
+        <v>4.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5819,7 +5814,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 5514-2026</t>
+          <t>A 14536-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5833,10 +5828,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46050</v>
+        <v>46100</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5848,13 +5843,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5897,7 +5887,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 48346-2024</t>
+          <t>A 36816-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5911,10 +5901,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45590</v>
+        <v>45538</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5926,8 +5916,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5970,7 +5965,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 39800-2022</t>
+          <t>A 36622-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5984,10 +5979,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44819</v>
+        <v>45153</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6000,7 +5995,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6043,7 +6038,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 32355-2025</t>
+          <t>A 10524-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6057,10 +6052,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45837</v>
+        <v>45366</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6073,7 +6068,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6116,7 +6111,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 59069-2023</t>
+          <t>A 8950-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6126,14 +6121,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45252</v>
+        <v>45357</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6146,7 +6141,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4.9</v>
+        <v>0.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6189,7 +6184,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 49755-2022</t>
+          <t>A 58672-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6203,10 +6198,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44859</v>
+        <v>44902</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6219,7 +6214,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6262,7 +6257,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 26356-2025</t>
+          <t>A 43445-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6276,10 +6271,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45805</v>
+        <v>45184</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6292,7 +6287,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6335,7 +6330,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 63778-2023</t>
+          <t>A 59010-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6345,14 +6340,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45278</v>
+        <v>45635</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6365,7 +6360,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6408,7 +6403,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 53279-2023</t>
+          <t>A 32395-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6418,14 +6413,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45229</v>
+        <v>45120</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6438,7 +6433,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6481,7 +6476,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 7592-2026</t>
+          <t>A 8124-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6495,10 +6490,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46061</v>
+        <v>44974</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6511,7 +6506,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6554,7 +6549,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 136-2023</t>
+          <t>A 17527-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6568,10 +6563,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44928</v>
+        <v>46119</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6584,7 +6579,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6627,7 +6622,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 58620-2022</t>
+          <t>A 17524-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6641,10 +6636,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44902</v>
+        <v>46119</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6657,7 +6652,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6700,7 +6695,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 12819-2022</t>
+          <t>A 17533-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6714,10 +6709,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44642</v>
+        <v>46120</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6730,7 +6725,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6773,7 +6768,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 1455-2025</t>
+          <t>A 17495-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6787,10 +6782,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45670</v>
+        <v>46120</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6803,7 +6798,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6846,7 +6841,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 37169-2022</t>
+          <t>A 17958-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6860,10 +6855,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44806</v>
+        <v>46122</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6875,8 +6870,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>17.4</v>
+        <v>0.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6919,7 +6919,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 36208-2025</t>
+          <t>A 40291-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6933,10 +6933,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45867</v>
+        <v>45554</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6992,7 +6992,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 9738-2026</t>
+          <t>A 12819-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7006,10 +7006,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46072</v>
+        <v>44642</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7065,7 +7065,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 7223-2025</t>
+          <t>A 18834-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7079,10 +7079,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45702</v>
+        <v>46129</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7138,7 +7138,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 49906-2025</t>
+          <t>A 18979-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7152,10 +7152,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45940</v>
+        <v>46129</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7211,7 +7211,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 49909-2025</t>
+          <t>A 49906-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7228,7 +7228,7 @@
         <v>45940</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7241,7 +7241,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7284,7 +7284,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 37195-2025</t>
+          <t>A 49909-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7294,14 +7294,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45875</v>
+        <v>45940</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7314,7 +7314,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7357,7 +7357,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 59068-2023</t>
+          <t>A 7247-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7367,14 +7367,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45252</v>
+        <v>45702</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>6.4</v>
+        <v>1.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7430,7 +7430,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 7248-2025</t>
+          <t>A 53814-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45702</v>
+        <v>45615</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7503,7 +7503,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 50577-2024</t>
+          <t>A 53275-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7517,10 +7517,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45601</v>
+        <v>45958</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7533,7 +7533,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7576,7 +7576,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 25762-2023</t>
+          <t>A 55984-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7590,10 +7590,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45090</v>
+        <v>45623</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7606,7 +7606,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7649,7 +7649,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 32952-2023</t>
+          <t>A 52640-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7663,10 +7663,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45125</v>
+        <v>45954</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>5.1</v>
+        <v>1.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7722,7 +7722,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 14536-2026</t>
+          <t>A 53274-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7736,10 +7736,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46100</v>
+        <v>45958</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7812,7 +7812,7 @@
         <v>45957</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 52640-2025</t>
+          <t>A 56419-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7882,10 +7882,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45954</v>
+        <v>45623</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7898,7 +7898,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.9</v>
+        <v>5.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7941,7 +7941,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 53275-2025</t>
+          <t>A 55897-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7955,10 +7955,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45958</v>
+        <v>45622</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7971,7 +7971,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8014,7 +8014,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 53274-2025</t>
+          <t>A 50577-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8028,10 +8028,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45958</v>
+        <v>45601</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8044,7 +8044,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8087,7 +8087,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 43445-2023</t>
+          <t>A 63778-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8097,14 +8097,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45184</v>
+        <v>45278</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8177,7 +8177,7 @@
         <v>45964</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 17533-2026</t>
+          <t>A 13530-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8247,10 +8247,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46120</v>
+        <v>45006</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8306,7 +8306,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 17527-2026</t>
+          <t>A 5577-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8320,10 +8320,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46119</v>
+        <v>44960</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8336,7 +8336,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4.4</v>
+        <v>0.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8379,7 +8379,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 17495-2026</t>
+          <t>A 60290-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8393,10 +8393,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46120</v>
+        <v>45642</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8452,7 +8452,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 17524-2026</t>
+          <t>A 49997-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8466,10 +8466,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46119</v>
+        <v>45943</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8482,7 +8482,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8525,7 +8525,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 17958-2026</t>
+          <t>A 6913-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8539,10 +8539,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46122</v>
+        <v>44967</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8554,13 +8554,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8603,7 +8598,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 37098-2023</t>
+          <t>A 15374-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8617,10 +8612,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45155</v>
+        <v>45747</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8633,7 +8628,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8676,7 +8671,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 18834-2026</t>
+          <t>A 20614-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8690,10 +8685,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46129</v>
+        <v>45776</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8706,7 +8701,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8749,7 +8744,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 18979-2026</t>
+          <t>A 58620-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8763,10 +8758,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46129</v>
+        <v>44902</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8779,7 +8774,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8822,7 +8817,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 49997-2025</t>
+          <t>A 41937-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8836,10 +8831,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45943</v>
+        <v>45903</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8852,7 +8847,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8895,7 +8890,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 61312-2023</t>
+          <t>A 24234-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8909,10 +8904,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45264</v>
+        <v>45797</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8925,7 +8920,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8968,7 +8963,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 15374-2025</t>
+          <t>A 12175-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8982,10 +8977,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45747</v>
+        <v>44998</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8998,7 +8993,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1</v>
+        <v>4.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9041,7 +9036,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 6913-2023</t>
+          <t>A 34779-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9055,10 +9050,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44967</v>
+        <v>45141</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9071,7 +9066,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9114,7 +9109,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 41937-2025</t>
+          <t>A 60112-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9128,10 +9123,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45903</v>
+        <v>45642</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9144,7 +9139,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9187,7 +9182,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 59155-2025</t>
+          <t>A 62527-2021</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9201,10 +9196,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45988</v>
+        <v>44503</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9217,7 +9212,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.2</v>
+        <v>22.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9260,7 +9255,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 30904-2022</t>
+          <t>A 21017-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9274,10 +9269,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44767</v>
+        <v>46144</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9290,7 +9285,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9333,7 +9328,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 12175-2023</t>
+          <t>A 59155-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9347,10 +9342,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44998</v>
+        <v>45988</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9363,7 +9358,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>4.3</v>
+        <v>2.2</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9406,7 +9401,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 20614-2025</t>
+          <t>A 61405-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9420,10 +9415,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45776</v>
+        <v>46001</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9435,8 +9430,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>0.7</v>
+        <v>6.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9479,7 +9479,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 24234-2025</t>
+          <t>A 29433-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9493,10 +9493,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45797</v>
+        <v>45824</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9552,7 +9552,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 8953-2023</t>
+          <t>A 8936-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9566,10 +9566,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44979</v>
+        <v>46069</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9625,7 +9625,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 246-2025</t>
+          <t>A 1949-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9639,10 +9639,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45660</v>
+        <v>45672</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9655,7 +9655,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9698,7 +9698,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 21017-2026</t>
+          <t>A 53279-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9708,14 +9708,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46144</v>
+        <v>45229</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9728,7 +9728,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9771,7 +9771,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 7760-2025</t>
+          <t>A 62541-2021</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9785,10 +9785,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45706</v>
+        <v>44503</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>8.300000000000001</v>
+        <v>2.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9844,7 +9844,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 61405-2025</t>
+          <t>A 6102-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9858,10 +9858,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46001</v>
+        <v>44964</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9873,13 +9873,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>6.6</v>
+        <v>0.8</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9922,7 +9917,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 2086-2025</t>
+          <t>A 43460-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9936,10 +9931,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45672</v>
+        <v>45568</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9952,7 +9947,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9995,7 +9990,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 62527-2021</t>
+          <t>A 13522-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10009,10 +10004,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44503</v>
+        <v>45006</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10025,7 +10020,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>22.6</v>
+        <v>2.4</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10068,7 +10063,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 29433-2025</t>
+          <t>A 24279-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10082,10 +10077,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45824</v>
+        <v>46169</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10098,7 +10093,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.4</v>
+        <v>11.7</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10141,7 +10136,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 8936-2026</t>
+          <t>A 24736-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10155,10 +10150,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46069</v>
+        <v>46171</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10170,8 +10165,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10214,7 +10214,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 24279-2026</t>
+          <t>A 25762-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10228,10 +10228,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46169</v>
+        <v>45090</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10244,7 +10244,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>11.7</v>
+        <v>0.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10287,7 +10287,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 60290-2024</t>
+          <t>A 54582-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10301,10 +10301,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45642</v>
+        <v>45233</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10317,7 +10317,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10360,7 +10360,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 24736-2026</t>
+          <t>A 2872-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10374,10 +10374,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46171</v>
+        <v>44945</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10389,13 +10389,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10438,7 +10433,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 33654-2022</t>
+          <t>A 46876-2022</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10452,10 +10447,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44789</v>
+        <v>44851</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10468,7 +10463,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.8</v>
+        <v>7.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10511,7 +10506,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 35112-2024</t>
+          <t>A 5514-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10525,10 +10520,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45529</v>
+        <v>46050</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10540,8 +10535,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10584,7 +10584,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 25814-2026</t>
+          <t>A 33654-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10598,10 +10598,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46178</v>
+        <v>44789</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10657,7 +10657,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 26148-2026</t>
+          <t>A 58393-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10667,14 +10667,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46181</v>
+        <v>44901</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10687,7 +10687,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10730,7 +10730,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 27552-2026</t>
+          <t>A 25814-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10744,10 +10744,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46190</v>
+        <v>46178</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10760,7 +10760,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>5.3</v>
+        <v>0.7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10803,7 +10803,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 32504-2026</t>
+          <t>A 1455-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10817,10 +10817,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46239</v>
+        <v>45670</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10832,13 +10832,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10881,7 +10876,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 32497-2026</t>
+          <t>A 11949-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10895,10 +10890,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46239</v>
+        <v>44994</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10910,13 +10905,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10959,7 +10949,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 28068-2026</t>
+          <t>A 26148-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10973,10 +10963,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46195</v>
+        <v>46181</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10989,7 +10979,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11032,7 +11022,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 28056-2026</t>
+          <t>A 33209-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11046,10 +11036,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46195</v>
+        <v>45127</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11062,7 +11052,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11105,7 +11095,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 28309-2026</t>
+          <t>A 7592-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11119,10 +11109,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46196</v>
+        <v>46061</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11135,7 +11125,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11178,7 +11168,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 32477-2026</t>
+          <t>A 8626-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11192,10 +11182,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46239</v>
+        <v>45355</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11207,13 +11197,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>2.4</v>
+        <v>6.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11256,7 +11241,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 19759-2024</t>
+          <t>A 44849-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11270,10 +11255,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45432</v>
+        <v>45574</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11286,7 +11271,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11329,7 +11314,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 56413-2024</t>
+          <t>A 9738-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11343,10 +11328,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45623</v>
+        <v>46072</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11359,7 +11344,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11402,7 +11387,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 32923-2026</t>
+          <t>A 62551-2021</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11416,10 +11401,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46244</v>
+        <v>44503</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11432,7 +11417,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11475,7 +11460,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 1949-2025</t>
+          <t>A 11795-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11489,10 +11474,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45672</v>
+        <v>45375</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11505,7 +11490,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11548,7 +11533,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 696-2025</t>
+          <t>A 35047-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11562,10 +11547,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45665</v>
+        <v>45527</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11578,7 +11563,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11621,7 +11606,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 34779-2023</t>
+          <t>A 39800-2022</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11635,10 +11620,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45141</v>
+        <v>44819</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11651,7 +11636,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11694,7 +11679,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 32944-2026</t>
+          <t>A 48346-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11708,10 +11693,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46244</v>
+        <v>45590</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11724,7 +11709,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11767,7 +11752,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 33984-2026</t>
+          <t>A 30484-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11777,14 +11762,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46252</v>
+        <v>45111</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11797,7 +11782,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2.9</v>
+        <v>0.2</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11840,7 +11825,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 36835-2024</t>
+          <t>A 27552-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11854,10 +11839,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45538</v>
+        <v>46190</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11869,13 +11854,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I145" t="n">
-        <v>2.4</v>
+        <v>5.3</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11918,7 +11898,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 34112-2026</t>
+          <t>A 28056-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11932,10 +11912,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46253</v>
+        <v>46195</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11948,7 +11928,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11991,7 +11971,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 58393-2022</t>
+          <t>A 28068-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12001,14 +11981,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44901</v>
+        <v>46195</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12021,7 +12001,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12064,7 +12044,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 2872-2023</t>
+          <t>A 36835-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12078,10 +12058,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44945</v>
+        <v>45538</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12093,8 +12073,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12137,7 +12122,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 11949-2023</t>
+          <t>A 32504-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12151,10 +12136,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44994</v>
+        <v>46239</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12166,8 +12151,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12210,7 +12200,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 54582-2023</t>
+          <t>A 32952-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12224,10 +12214,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45233</v>
+        <v>45125</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12240,7 +12230,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.7</v>
+        <v>5.1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12283,7 +12273,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 54279-2023</t>
+          <t>A 28309-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12297,10 +12287,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45232</v>
+        <v>46196</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12313,7 +12303,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12356,7 +12346,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 36816-2024</t>
+          <t>A 32477-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12370,10 +12360,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45538</v>
+        <v>46239</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12387,11 +12377,11 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12434,7 +12424,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 55984-2024</t>
+          <t>A 32497-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12448,10 +12438,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45623</v>
+        <v>46239</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12463,8 +12453,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I153" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12507,7 +12502,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 35047-2024</t>
+          <t>A 32923-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12521,10 +12516,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45527</v>
+        <v>46244</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12537,7 +12532,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12580,7 +12575,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 25322-2024</t>
+          <t>A 32944-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12594,10 +12589,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45462</v>
+        <v>46244</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12610,7 +12605,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12653,7 +12648,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 36878-2026</t>
+          <t>A 35087-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12667,10 +12662,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46273</v>
+        <v>45527</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12683,7 +12678,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12726,7 +12721,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 36716-2026</t>
+          <t>A 35112-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12740,10 +12735,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46272</v>
+        <v>45529</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12756,7 +12751,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12799,7 +12794,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 31826-2026</t>
+          <t>A 2086-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12813,10 +12808,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46230</v>
+        <v>45672</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12829,7 +12824,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12872,7 +12867,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 34936-2026</t>
+          <t>A 61312-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12886,10 +12881,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46259</v>
+        <v>45264</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12902,7 +12897,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>7.4</v>
+        <v>0.7</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12945,7 +12940,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 34941-2026</t>
+          <t>A 246-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12959,10 +12954,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46259</v>
+        <v>45660</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12975,7 +12970,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>9.300000000000001</v>
+        <v>1.7</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13018,7 +13013,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 34945-2026</t>
+          <t>A 48301-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13032,10 +13027,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46259</v>
+        <v>45590</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13048,7 +13043,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>6.2</v>
+        <v>1.8</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13091,7 +13086,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 31897-2026</t>
+          <t>A 30399-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13105,10 +13100,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46231</v>
+        <v>45111</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13121,7 +13116,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13164,7 +13159,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 31899-2026</t>
+          <t>A 60465-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13178,10 +13173,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46231</v>
+        <v>45643</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13194,7 +13189,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13237,7 +13232,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 31596-2024</t>
+          <t>A 25322-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13251,10 +13246,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45506</v>
+        <v>45462</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13266,13 +13261,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I164" t="n">
-        <v>4.3</v>
+        <v>1.3</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13315,7 +13305,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 31902-2026</t>
+          <t>A 35202-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13329,10 +13319,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46231</v>
+        <v>45145</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13345,7 +13335,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0.5</v>
+        <v>11.1</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13388,7 +13378,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 52999-2023</t>
+          <t>A 31596-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13402,10 +13392,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45226</v>
+        <v>45506</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13417,8 +13407,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I166" t="n">
-        <v>0.9</v>
+        <v>4.3</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13461,7 +13456,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 53273-2023</t>
+          <t>A 40257-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13471,14 +13466,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45229</v>
+        <v>45169</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13491,7 +13486,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>6.3</v>
+        <v>0.6</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13534,7 +13529,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 24759-2023</t>
+          <t>A 33984-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13544,14 +13539,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45084</v>
+        <v>46252</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13607,7 +13602,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 52853-2023</t>
+          <t>A 19759-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13621,10 +13616,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45226</v>
+        <v>45432</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13637,7 +13632,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13680,7 +13675,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 7212-2025</t>
+          <t>A 56542-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13690,14 +13685,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45702</v>
+        <v>45625</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13710,7 +13705,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13753,7 +13748,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 32395-2023</t>
+          <t>A 24759-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13767,10 +13762,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45120</v>
+        <v>45084</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13783,7 +13778,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13826,7 +13821,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 6080-2023</t>
+          <t>A 34112-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13836,14 +13831,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44964</v>
+        <v>46253</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13856,7 +13851,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13899,7 +13894,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 35202-2023</t>
+          <t>A 37169-2022</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13913,10 +13908,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45145</v>
+        <v>44806</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13929,7 +13924,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>11.1</v>
+        <v>17.4</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13972,7 +13967,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 5577-2023</t>
+          <t>A 60118-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13986,10 +13981,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44960</v>
+        <v>45642</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14002,7 +13997,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14045,7 +14040,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 30484-2023</t>
+          <t>A 53769-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14059,10 +14054,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45111</v>
+        <v>45615</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14075,7 +14070,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14118,7 +14113,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 8950-2024</t>
+          <t>A 696-2025</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14132,10 +14127,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45357</v>
+        <v>45665</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14148,7 +14143,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14191,7 +14186,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 46876-2022</t>
+          <t>A 30904-2022</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14205,10 +14200,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44851</v>
+        <v>44767</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14221,7 +14216,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14264,7 +14259,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 13522-2023</t>
+          <t>A 56740-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14278,10 +14273,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45006</v>
+        <v>45244</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14294,7 +14289,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14337,7 +14332,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 56419-2024</t>
+          <t>A 52853-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14351,10 +14346,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45623</v>
+        <v>45226</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14367,7 +14362,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>5.6</v>
+        <v>1.6</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14410,7 +14405,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 8626-2024</t>
+          <t>A 60642-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14420,14 +14415,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45355</v>
+        <v>45260</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14440,7 +14435,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>6.4</v>
+        <v>1.3</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14483,7 +14478,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 60112-2024</t>
+          <t>A 55974-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14497,10 +14492,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45642</v>
+        <v>45623</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14513,7 +14508,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14556,7 +14551,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 31605-2024</t>
+          <t>A 53764-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14570,10 +14565,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45506</v>
+        <v>45615</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14585,13 +14580,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I182" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14634,7 +14624,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 60118-2024</t>
+          <t>A 41163-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14648,10 +14638,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45642</v>
+        <v>45174</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14664,7 +14654,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>0.6</v>
+        <v>3.2</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14707,7 +14697,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 62551-2021</t>
+          <t>A 7223-2025</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14721,10 +14711,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44503</v>
+        <v>45702</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14737,7 +14727,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14780,7 +14770,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 56542-2024</t>
+          <t>A 36716-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14790,14 +14780,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45625</v>
+        <v>46272</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14810,7 +14800,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14853,7 +14843,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 53814-2024</t>
+          <t>A 31902-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14867,10 +14857,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45615</v>
+        <v>46231</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14883,7 +14873,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14926,7 +14916,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 10524-2024</t>
+          <t>A 56365-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14940,10 +14930,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45366</v>
+        <v>45625</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14999,7 +14989,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 9422-2024</t>
+          <t>A 36878-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15013,10 +15003,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45359</v>
+        <v>46273</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15029,7 +15019,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15072,7 +15062,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 45608-2022</t>
+          <t>A 52999-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15086,10 +15076,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>44845</v>
+        <v>45226</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15102,7 +15092,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>17</v>
+        <v>0.9</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15145,7 +15135,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 58672-2022</t>
+          <t>A 31897-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15159,10 +15149,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>44902</v>
+        <v>46231</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15175,7 +15165,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15218,7 +15208,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 55897-2024</t>
+          <t>A 31899-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15232,10 +15222,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45622</v>
+        <v>46231</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15248,7 +15238,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15291,7 +15281,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 41163-2023</t>
+          <t>A 7760-2025</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15305,10 +15295,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45174</v>
+        <v>45706</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15321,7 +15311,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>3.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15364,7 +15354,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 40257-2023</t>
+          <t>A 31826-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15378,10 +15368,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45169</v>
+        <v>46230</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15394,7 +15384,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15437,7 +15427,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 36622-2023</t>
+          <t>A 56413-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15451,10 +15441,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45153</v>
+        <v>45623</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15467,7 +15457,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0.4</v>
+        <v>3.5</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15510,7 +15500,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 62541-2021</t>
+          <t>A 34941-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15524,10 +15514,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44503</v>
+        <v>46259</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15540,7 +15530,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>2.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15583,7 +15573,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 28850-2024</t>
+          <t>A 34945-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15597,10 +15587,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45478</v>
+        <v>46259</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15613,7 +15603,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.2</v>
+        <v>6.2</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15656,7 +15646,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 44849-2024</t>
+          <t>A 34936-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15670,10 +15660,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45574</v>
+        <v>46259</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15686,7 +15676,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>3.8</v>
+        <v>7.4</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15729,7 +15719,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 59644-2023</t>
+          <t>A 37997-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15743,10 +15733,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45254</v>
+        <v>46280</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15802,7 +15792,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 56365-2024</t>
+          <t>A 37994-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15816,10 +15806,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45625</v>
+        <v>46280</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15832,7 +15822,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15875,7 +15865,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 6940-2024</t>
+          <t>A 38009-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15889,10 +15879,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45343</v>
+        <v>46280</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15948,7 +15938,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 40291-2024</t>
+          <t>A 56373-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15962,10 +15952,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45554</v>
+        <v>45625</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16021,7 +16011,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 33209-2023</t>
+          <t>A 61817-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16035,10 +16025,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45127</v>
+        <v>45649</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16051,7 +16041,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.9</v>
+        <v>4.6</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16094,7 +16084,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 53764-2024</t>
+          <t>A 9973-2024</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16108,10 +16098,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45615</v>
+        <v>45363</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16124,7 +16114,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.1</v>
+        <v>4.7</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16167,7 +16157,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 44308-2023</t>
+          <t>A 53805-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16181,10 +16171,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45188</v>
+        <v>45615</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16197,7 +16187,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16240,7 +16230,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 13530-2023</t>
+          <t>A 11393-2025</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16254,10 +16244,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45006</v>
+        <v>45726</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16270,7 +16260,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16313,7 +16303,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 35087-2024</t>
+          <t>A 11563-2025</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16323,14 +16313,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45527</v>
+        <v>45727</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16342,8 +16332,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I206" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16386,7 +16381,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 53769-2024</t>
+          <t>A 53275-2023</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16396,14 +16391,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45615</v>
+        <v>45229</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16416,7 +16411,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1.2</v>
+        <v>8.5</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16459,7 +16454,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 6102-2023</t>
+          <t>A 44104-2024</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16473,10 +16468,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>44964</v>
+        <v>45572</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16489,7 +16484,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16532,7 +16527,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 18768-2024</t>
+          <t>A 24356-2025</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16546,10 +16541,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45426</v>
+        <v>45797</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16562,7 +16557,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16605,7 +16600,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 56740-2023</t>
+          <t>A 19840-2025</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16615,14 +16610,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45244</v>
+        <v>45771</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16635,7 +16630,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>4.5</v>
+        <v>0.2</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16678,7 +16673,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 43460-2024</t>
+          <t>A 58420-2023</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16688,14 +16683,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45568</v>
+        <v>45250</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16708,7 +16703,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16751,7 +16746,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 59010-2024</t>
+          <t>A 36945-2024</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16765,10 +16760,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45635</v>
+        <v>45538</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16780,8 +16775,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I212" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16824,7 +16824,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 61817-2024</t>
+          <t>A 17892-2025</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16838,10 +16838,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45649</v>
+        <v>45758</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16854,7 +16854,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>4.6</v>
+        <v>1.3</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16897,7 +16897,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 9973-2024</t>
+          <t>A 29495-2025</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16911,10 +16911,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45363</v>
+        <v>45824</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16927,7 +16927,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16970,7 +16970,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 56373-2024</t>
+          <t>A 31844-2025</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16984,10 +16984,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45625</v>
+        <v>45834</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17000,7 +17000,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.3</v>
+        <v>6.2</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17043,7 +17043,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 53805-2024</t>
+          <t>A 31825-2025</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17057,10 +17057,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45615</v>
+        <v>45834</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17073,7 +17073,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17116,7 +17116,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 11393-2025</t>
+          <t>A 32355-2025</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17130,10 +17130,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45726</v>
+        <v>45837</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17146,7 +17146,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>0.2</v>
+        <v>2.3</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17189,24 +17189,24 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>S 3762-2024</t>
+          <t>A 26356-2025</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45558</v>
+        <v>45805</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17262,24 +17262,24 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>S 1807-2022</t>
+          <t>A 59069-2023</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Skogsbilväg</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>44656</v>
+        <v>45252</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17291,13 +17291,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I219" t="n">
-        <v>1.3</v>
+        <v>4.9</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17340,24 +17335,24 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>S 320-2025</t>
+          <t>A 36208-2025</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45688</v>
+        <v>45867</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17370,7 +17365,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17413,148 +17408,372 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
+          <t>S 1807-2022</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Skogsbilväg</t>
+        </is>
+      </c>
+      <c r="D221" s="1" t="n">
+        <v>44656</v>
+      </c>
+      <c r="E221" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I221" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J221" t="n">
+        <v>0</v>
+      </c>
+      <c r="K221" t="n">
+        <v>0</v>
+      </c>
+      <c r="L221" t="n">
+        <v>0</v>
+      </c>
+      <c r="M221" t="n">
+        <v>0</v>
+      </c>
+      <c r="N221" t="n">
+        <v>0</v>
+      </c>
+      <c r="O221" t="n">
+        <v>0</v>
+      </c>
+      <c r="P221" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q221" t="n">
+        <v>0</v>
+      </c>
+      <c r="R221" t="n">
+        <v>0</v>
+      </c>
+      <c r="S221" t="n">
+        <v>0</v>
+      </c>
+      <c r="T221" t="n">
+        <v>0</v>
+      </c>
+      <c r="U221" t="n">
+        <v>0</v>
+      </c>
+      <c r="V221" s="2" t="inlineStr"/>
+    </row>
+    <row r="222" ht="15" customHeight="1">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>S 3762-2024</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D222" s="1" t="n">
+        <v>45558</v>
+      </c>
+      <c r="E222" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I222" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J222" t="n">
+        <v>0</v>
+      </c>
+      <c r="K222" t="n">
+        <v>0</v>
+      </c>
+      <c r="L222" t="n">
+        <v>0</v>
+      </c>
+      <c r="M222" t="n">
+        <v>0</v>
+      </c>
+      <c r="N222" t="n">
+        <v>0</v>
+      </c>
+      <c r="O222" t="n">
+        <v>0</v>
+      </c>
+      <c r="P222" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q222" t="n">
+        <v>0</v>
+      </c>
+      <c r="R222" t="n">
+        <v>0</v>
+      </c>
+      <c r="S222" t="n">
+        <v>0</v>
+      </c>
+      <c r="T222" t="n">
+        <v>0</v>
+      </c>
+      <c r="U222" t="n">
+        <v>0</v>
+      </c>
+      <c r="V222" s="2" t="inlineStr"/>
+    </row>
+    <row r="223" ht="15" customHeight="1">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>S 320-2025</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D223" s="1" t="n">
+        <v>45688</v>
+      </c>
+      <c r="E223" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I223" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J223" t="n">
+        <v>0</v>
+      </c>
+      <c r="K223" t="n">
+        <v>0</v>
+      </c>
+      <c r="L223" t="n">
+        <v>0</v>
+      </c>
+      <c r="M223" t="n">
+        <v>0</v>
+      </c>
+      <c r="N223" t="n">
+        <v>0</v>
+      </c>
+      <c r="O223" t="n">
+        <v>0</v>
+      </c>
+      <c r="P223" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q223" t="n">
+        <v>0</v>
+      </c>
+      <c r="R223" t="n">
+        <v>0</v>
+      </c>
+      <c r="S223" t="n">
+        <v>0</v>
+      </c>
+      <c r="T223" t="n">
+        <v>0</v>
+      </c>
+      <c r="U223" t="n">
+        <v>0</v>
+      </c>
+      <c r="V223" s="2" t="inlineStr"/>
+    </row>
+    <row r="224" ht="15" customHeight="1">
+      <c r="A224" t="inlineStr">
+        <is>
           <t>S 319-2025</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr">
+      <c r="B224" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C221" t="inlineStr">
+      <c r="C224" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D221" s="1" t="n">
+      <c r="D224" s="1" t="n">
         <v>45688</v>
       </c>
-      <c r="E221" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I221" t="n">
+      <c r="E224" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I224" t="n">
         <v>2.9</v>
       </c>
-      <c r="J221" t="n">
-        <v>0</v>
-      </c>
-      <c r="K221" t="n">
-        <v>0</v>
-      </c>
-      <c r="L221" t="n">
-        <v>0</v>
-      </c>
-      <c r="M221" t="n">
-        <v>0</v>
-      </c>
-      <c r="N221" t="n">
-        <v>0</v>
-      </c>
-      <c r="O221" t="n">
-        <v>0</v>
-      </c>
-      <c r="P221" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
-      <c r="R221" t="n">
-        <v>0</v>
-      </c>
-      <c r="S221" t="n">
-        <v>0</v>
-      </c>
-      <c r="T221" t="n">
-        <v>0</v>
-      </c>
-      <c r="U221" t="n">
-        <v>0</v>
-      </c>
-      <c r="V221" s="2" t="inlineStr"/>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
+      <c r="J224" t="n">
+        <v>0</v>
+      </c>
+      <c r="K224" t="n">
+        <v>0</v>
+      </c>
+      <c r="L224" t="n">
+        <v>0</v>
+      </c>
+      <c r="M224" t="n">
+        <v>0</v>
+      </c>
+      <c r="N224" t="n">
+        <v>0</v>
+      </c>
+      <c r="O224" t="n">
+        <v>0</v>
+      </c>
+      <c r="P224" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q224" t="n">
+        <v>0</v>
+      </c>
+      <c r="R224" t="n">
+        <v>0</v>
+      </c>
+      <c r="S224" t="n">
+        <v>0</v>
+      </c>
+      <c r="T224" t="n">
+        <v>0</v>
+      </c>
+      <c r="U224" t="n">
+        <v>0</v>
+      </c>
+      <c r="V224" s="2" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
         <is>
           <t>S 2767-2022</t>
         </is>
       </c>
-      <c r="B222" t="inlineStr">
+      <c r="B225" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C222" t="inlineStr">
+      <c r="C225" t="inlineStr">
         <is>
           <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
-      <c r="D222" s="1" t="n">
+      <c r="D225" s="1" t="n">
         <v>44705</v>
       </c>
-      <c r="E222" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I222" t="n">
+      <c r="E225" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I225" t="n">
         <v>0.1</v>
       </c>
-      <c r="J222" t="n">
-        <v>0</v>
-      </c>
-      <c r="K222" t="n">
-        <v>0</v>
-      </c>
-      <c r="L222" t="n">
-        <v>0</v>
-      </c>
-      <c r="M222" t="n">
-        <v>0</v>
-      </c>
-      <c r="N222" t="n">
-        <v>0</v>
-      </c>
-      <c r="O222" t="n">
-        <v>0</v>
-      </c>
-      <c r="P222" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
-      <c r="R222" t="n">
-        <v>0</v>
-      </c>
-      <c r="S222" t="n">
-        <v>0</v>
-      </c>
-      <c r="T222" t="n">
-        <v>0</v>
-      </c>
-      <c r="U222" t="n">
-        <v>0</v>
-      </c>
-      <c r="V222" s="2" t="inlineStr"/>
+      <c r="J225" t="n">
+        <v>0</v>
+      </c>
+      <c r="K225" t="n">
+        <v>0</v>
+      </c>
+      <c r="L225" t="n">
+        <v>0</v>
+      </c>
+      <c r="M225" t="n">
+        <v>0</v>
+      </c>
+      <c r="N225" t="n">
+        <v>0</v>
+      </c>
+      <c r="O225" t="n">
+        <v>0</v>
+      </c>
+      <c r="P225" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q225" t="n">
+        <v>0</v>
+      </c>
+      <c r="R225" t="n">
+        <v>0</v>
+      </c>
+      <c r="S225" t="n">
+        <v>0</v>
+      </c>
+      <c r="T225" t="n">
+        <v>0</v>
+      </c>
+      <c r="U225" t="n">
+        <v>0</v>
+      </c>
+      <c r="V225" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt LIDKÖPING.xlsx
+++ b/Översikt LIDKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>44631</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>46006</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>44967</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
         <v>46171</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 32280-2022</t>
+          <t>A 28849-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44781</v>
+        <v>45478</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1097,13 +1097,13 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>8.6</v>
+        <v>2.6</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -1136,6 +1136,118 @@
         <v>0</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Talltita
+Grönsiska
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 28849-2024 artfynd.xlsx", "A 28849-2024")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 28849-2024 karta.png", "A 28849-2024")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 28849-2024 georefererad karta.tif", "A 28849-2024")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 28849-2024 FSC-klagomål.docx", "A 28849-2024")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 28849-2024 FSC-klagomål mail.docx", "A 28849-2024")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 28849-2024 tillsynsbegäran.docx", "A 28849-2024")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 28849-2024 tillsynsbegäran mail.docx", "A 28849-2024")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 28849-2024 prioriterade fågelarter.docx", "A 28849-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 34942-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Gulsparv
 Nötkråka
@@ -1143,155 +1255,43 @@
 Skogsduva</t>
         </is>
       </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 32280-2022 artfynd.xlsx", "A 32280-2022")</f>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 34942-2026 artfynd.xlsx", "A 34942-2026")</f>
         <v/>
       </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 32280-2022 karta.png", "A 32280-2022")</f>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 34942-2026 karta.png", "A 34942-2026")</f>
         <v/>
       </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 32280-2022 georefererad karta.tif", "A 32280-2022")</f>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 34942-2026 georefererad karta.tif", "A 34942-2026")</f>
         <v/>
       </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 32280-2022 FSC-klagomål.docx", "A 32280-2022")</f>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 34942-2026 FSC-klagomål.docx", "A 34942-2026")</f>
         <v/>
       </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 32280-2022 FSC-klagomål mail.docx", "A 32280-2022")</f>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 34942-2026 FSC-klagomål mail.docx", "A 34942-2026")</f>
         <v/>
       </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 32280-2022 tillsynsbegäran.docx", "A 32280-2022")</f>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 34942-2026 tillsynsbegäran.docx", "A 34942-2026")</f>
         <v/>
       </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 32280-2022 tillsynsbegäran mail.docx", "A 32280-2022")</f>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 34942-2026 tillsynsbegäran mail.docx", "A 34942-2026")</f>
         <v/>
       </c>
-      <c r="AE6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 32280-2022 prioriterade fågelarter.docx", "A 32280-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 28849-2024</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45478</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>4</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Talltita
-Grönsiska
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 28849-2024 artfynd.xlsx", "A 28849-2024")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 28849-2024 karta.png", "A 28849-2024")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 28849-2024 georefererad karta.tif", "A 28849-2024")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 28849-2024 FSC-klagomål.docx", "A 28849-2024")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 28849-2024 FSC-klagomål mail.docx", "A 28849-2024")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 28849-2024 tillsynsbegäran.docx", "A 28849-2024")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 28849-2024 tillsynsbegäran mail.docx", "A 28849-2024")</f>
-        <v/>
-      </c>
       <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 28849-2024 prioriterade fågelarter.docx", "A 28849-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 34942-2026 prioriterade fågelarter.docx", "A 34942-2026")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 34942-2026</t>
+          <t>A 32280-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46259</v>
+        <v>44781</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>18.1</v>
+        <v>8.6</v>
       </c>
       <c r="J8" t="n">
         <v>3</v>
@@ -1368,42 +1368,42 @@
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 34942-2026 artfynd.xlsx", "A 34942-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 32280-2022 artfynd.xlsx", "A 32280-2022")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 34942-2026 karta.png", "A 34942-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 32280-2022 karta.png", "A 32280-2022")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 34942-2026 georefererad karta.tif", "A 34942-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 32280-2022 georefererad karta.tif", "A 32280-2022")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 34942-2026 FSC-klagomål.docx", "A 34942-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 32280-2022 FSC-klagomål.docx", "A 32280-2022")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 34942-2026 FSC-klagomål mail.docx", "A 34942-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 32280-2022 FSC-klagomål mail.docx", "A 32280-2022")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 34942-2026 tillsynsbegäran.docx", "A 34942-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 32280-2022 tillsynsbegäran.docx", "A 32280-2022")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 34942-2026 tillsynsbegäran mail.docx", "A 34942-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 32280-2022 tillsynsbegäran mail.docx", "A 32280-2022")</f>
         <v/>
       </c>
       <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 34942-2026 prioriterade fågelarter.docx", "A 34942-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 32280-2022 prioriterade fågelarter.docx", "A 32280-2022")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 15219-2024</t>
+          <t>A 4831-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1413,14 +1413,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45400</v>
+        <v>45688</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1433,22 +1433,22 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>6.7</v>
+        <v>1.3</v>
       </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>1</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
       <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>2</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1460,7 +1460,7 @@
         <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1472,148 +1472,148 @@
         <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Skogsalm
+Barkticka</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 4831-2025 artfynd.xlsx", "A 4831-2025")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 4831-2025 karta.png", "A 4831-2025")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 4831-2025 georefererad karta.tif", "A 4831-2025")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 4831-2025 FSC-klagomål.docx", "A 4831-2025")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 4831-2025 FSC-klagomål mail.docx", "A 4831-2025")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 4831-2025 tillsynsbegäran.docx", "A 4831-2025")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 4831-2025 tillsynsbegäran mail.docx", "A 4831-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 15219-2024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45400</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Tårkragskivling
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 15219-2024 artfynd.xlsx", "A 15219-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 15219-2024 karta.png", "A 15219-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 15219-2024 georefererad karta.tif", "A 15219-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 15219-2024 FSC-klagomål.docx", "A 15219-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 15219-2024 FSC-klagomål mail.docx", "A 15219-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 15219-2024 tillsynsbegäran.docx", "A 15219-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 15219-2024 tillsynsbegäran mail.docx", "A 15219-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 4831-2025</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45688</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Skogsalm
-Barkticka</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 4831-2025 artfynd.xlsx", "A 4831-2025")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 4831-2025 karta.png", "A 4831-2025")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 4831-2025 georefererad karta.tif", "A 4831-2025")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 4831-2025 FSC-klagomål.docx", "A 4831-2025")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 4831-2025 FSC-klagomål mail.docx", "A 4831-2025")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 4831-2025 tillsynsbegäran.docx", "A 4831-2025")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 4831-2025 tillsynsbegäran mail.docx", "A 4831-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>45202</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>45898</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>45702</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>44630</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 44680-2023</t>
+          <t>A 10476-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45189</v>
+        <v>44987</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2126,155 +2126,155 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 10476-2023 artfynd.xlsx", "A 10476-2023")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 10476-2023 karta.png", "A 10476-2023")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 10476-2023 georefererad karta.tif", "A 10476-2023")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 10476-2023 FSC-klagomål.docx", "A 10476-2023")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 10476-2023 FSC-klagomål mail.docx", "A 10476-2023")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 10476-2023 tillsynsbegäran.docx", "A 10476-2023")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 10476-2023 tillsynsbegäran mail.docx", "A 10476-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 44680-2023</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45189</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>Trädlärka</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 44680-2023 artfynd.xlsx", "A 44680-2023")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 44680-2023 karta.png", "A 44680-2023")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 44680-2023 georefererad karta.tif", "A 44680-2023")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 44680-2023 FSC-klagomål.docx", "A 44680-2023")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 44680-2023 FSC-klagomål mail.docx", "A 44680-2023")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 44680-2023 tillsynsbegäran.docx", "A 44680-2023")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 44680-2023 tillsynsbegäran mail.docx", "A 44680-2023")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 44680-2023 prioriterade fågelarter.docx", "A 44680-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 10476-2023</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>44987</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 10476-2023 artfynd.xlsx", "A 10476-2023")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 10476-2023 karta.png", "A 10476-2023")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 10476-2023 georefererad karta.tif", "A 10476-2023")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 10476-2023 FSC-klagomål.docx", "A 10476-2023")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 10476-2023 FSC-klagomål mail.docx", "A 10476-2023")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 10476-2023 tillsynsbegäran.docx", "A 10476-2023")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 10476-2023 tillsynsbegäran mail.docx", "A 10476-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 62569-2022</t>
+          <t>A 62629-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44924</v>
+        <v>44925</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2316,10 +2316,10 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2340,474 +2340,474 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
+          <t>Igelkott</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 62629-2022 artfynd.xlsx", "A 62629-2022")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 62629-2022 karta.png", "A 62629-2022")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 62629-2022 georefererad karta.tif", "A 62629-2022")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 62629-2022 FSC-klagomål.docx", "A 62629-2022")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 62629-2022 FSC-klagomål mail.docx", "A 62629-2022")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 62629-2022 tillsynsbegäran.docx", "A 62629-2022")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 62629-2022 tillsynsbegäran mail.docx", "A 62629-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 61818-2024</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45649</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 61818-2024 artfynd.xlsx", "A 61818-2024")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 61818-2024 karta.png", "A 61818-2024")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 61818-2024 georefererad karta.tif", "A 61818-2024")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 61818-2024 FSC-klagomål.docx", "A 61818-2024")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 61818-2024 FSC-klagomål mail.docx", "A 61818-2024")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 61818-2024 tillsynsbegäran.docx", "A 61818-2024")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 61818-2024 tillsynsbegäran mail.docx", "A 61818-2024")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 61818-2024 prioriterade fågelarter.docx", "A 61818-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 62569-2022</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>44924</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
           <t>Skogsalm</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 62569-2022 artfynd.xlsx", "A 62569-2022")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 62569-2022 karta.png", "A 62569-2022")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 62569-2022 georefererad karta.tif", "A 62569-2022")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 62569-2022 FSC-klagomål.docx", "A 62569-2022")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 62569-2022 FSC-klagomål mail.docx", "A 62569-2022")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 62569-2022 tillsynsbegäran.docx", "A 62569-2022")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 62569-2022 tillsynsbegäran mail.docx", "A 62569-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>A 37136-2026</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
         <v>46274</v>
       </c>
-      <c r="E18" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
+      <c r="E20" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
         <v>6.6</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J20" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>1</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T20" t="n">
         <v>1</v>
       </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Fiskgjuse</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 37136-2026 artfynd.xlsx", "A 37136-2026")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 37136-2026 karta.png", "A 37136-2026")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 37136-2026 georefererad karta.tif", "A 37136-2026")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 37136-2026 FSC-klagomål.docx", "A 37136-2026")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 37136-2026 FSC-klagomål mail.docx", "A 37136-2026")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 37136-2026 tillsynsbegäran.docx", "A 37136-2026")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 37136-2026 tillsynsbegäran mail.docx", "A 37136-2026")</f>
         <v/>
       </c>
-      <c r="AE18">
+      <c r="AE20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 37136-2026 prioriterade fågelarter.docx", "A 37136-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>A 24352-2025</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
-      <c r="D19" s="1" t="n">
+      <c r="D21" s="1" t="n">
         <v>45797</v>
       </c>
-      <c r="E19" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
+      <c r="E21" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
         <v>1.1</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J21" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
         <v>1</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T21" t="n">
         <v>1</v>
       </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Spillkråka</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 24352-2025 artfynd.xlsx", "A 24352-2025")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 24352-2025 karta.png", "A 24352-2025")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 24352-2025 georefererad karta.tif", "A 24352-2025")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 24352-2025 FSC-klagomål.docx", "A 24352-2025")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 24352-2025 FSC-klagomål mail.docx", "A 24352-2025")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 24352-2025 tillsynsbegäran.docx", "A 24352-2025")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 24352-2025 tillsynsbegäran mail.docx", "A 24352-2025")</f>
         <v/>
       </c>
-      <c r="AE19">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 24352-2025 prioriterade fågelarter.docx", "A 24352-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 62629-2022</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>44925</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Igelkott</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 62629-2022 artfynd.xlsx", "A 62629-2022")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 62629-2022 karta.png", "A 62629-2022")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 62629-2022 georefererad karta.tif", "A 62629-2022")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 62629-2022 FSC-klagomål.docx", "A 62629-2022")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 62629-2022 FSC-klagomål mail.docx", "A 62629-2022")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 62629-2022 tillsynsbegäran.docx", "A 62629-2022")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 62629-2022 tillsynsbegäran mail.docx", "A 62629-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 61818-2024</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45649</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Rödvingetrast</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 61818-2024 artfynd.xlsx", "A 61818-2024")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 61818-2024 karta.png", "A 61818-2024")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 61818-2024 georefererad karta.tif", "A 61818-2024")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 61818-2024 FSC-klagomål.docx", "A 61818-2024")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 61818-2024 FSC-klagomål mail.docx", "A 61818-2024")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 61818-2024 tillsynsbegäran.docx", "A 61818-2024")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 61818-2024 tillsynsbegäran mail.docx", "A 61818-2024")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 61818-2024 prioriterade fågelarter.docx", "A 61818-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>44788</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>44466</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>44831</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>44820</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>44714</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>44566</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>44546</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>44627</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>44627</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>44725</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>44805</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>44705</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>44617</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>44487</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>44487</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>44770</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>44742</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>44806</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         <v>44515</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 53273-2023</t>
+          <t>A 8790-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4208,14 +4208,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45229</v>
+        <v>44614</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4227,8 +4227,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>6.3</v>
+        <v>2.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4288,7 +4293,7 @@
         <v>44747</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4344,7 +4349,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 49755-2022</t>
+          <t>A 8124-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4358,10 +4363,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44859</v>
+        <v>44974</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4374,7 +4379,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4417,7 +4422,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 8790-2022</t>
+          <t>A 60465-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4431,10 +4436,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44614</v>
+        <v>45643</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4446,13 +4451,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4495,7 +4495,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 44308-2023</t>
+          <t>A 60642-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4505,14 +4505,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45188</v>
+        <v>45260</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4568,7 +4568,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 6940-2024</t>
+          <t>A 48301-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4582,10 +4582,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45343</v>
+        <v>45590</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4641,7 +4641,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 59068-2023</t>
+          <t>A 7247-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4651,14 +4651,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45252</v>
+        <v>45702</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>6.4</v>
+        <v>1.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 136-2023</t>
+          <t>A 30399-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4728,10 +4728,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44928</v>
+        <v>45111</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4.5</v>
+        <v>1.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4787,7 +4787,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 37195-2025</t>
+          <t>A 19840-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4797,14 +4797,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45875</v>
+        <v>45771</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4860,7 +4860,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 7248-2025</t>
+          <t>A 48411-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4874,10 +4874,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45702</v>
+        <v>44858</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4933,7 +4933,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 54279-2023</t>
+          <t>A 11795-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4947,10 +4947,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45232</v>
+        <v>45375</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.3</v>
+        <v>3.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5006,7 +5006,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 7212-2025</t>
+          <t>A 58420-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5016,14 +5016,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45702</v>
+        <v>45250</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5079,7 +5079,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 8953-2023</t>
+          <t>A 36945-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5093,10 +5093,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44979</v>
+        <v>45538</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5108,8 +5108,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5152,7 +5157,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 18768-2024</t>
+          <t>A 55974-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5166,10 +5171,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45426</v>
+        <v>45623</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5182,7 +5187,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5225,7 +5230,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 48411-2022</t>
+          <t>A 17892-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5239,10 +5244,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44858</v>
+        <v>45758</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5255,7 +5260,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5298,7 +5303,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 59644-2023</t>
+          <t>A 48346-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5312,10 +5317,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45254</v>
+        <v>45590</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5328,7 +5333,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5371,7 +5376,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 9422-2024</t>
+          <t>A 39800-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5385,10 +5390,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45359</v>
+        <v>44819</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5401,7 +5406,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5444,7 +5449,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 6080-2023</t>
+          <t>A 29495-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5454,14 +5459,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44964</v>
+        <v>45824</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5474,7 +5479,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.9</v>
+        <v>5.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5517,7 +5522,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 45608-2022</t>
+          <t>A 49755-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5531,10 +5536,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44845</v>
+        <v>44859</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5547,7 +5552,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>17</v>
+        <v>1.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5590,7 +5595,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 31605-2024</t>
+          <t>A 63778-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5600,14 +5605,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45506</v>
+        <v>45278</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5619,13 +5624,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5668,7 +5668,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 28850-2024</t>
+          <t>A 53279-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5678,14 +5678,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45478</v>
+        <v>45229</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5741,7 +5741,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 37098-2023</t>
+          <t>A 136-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5755,10 +5755,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45155</v>
+        <v>44928</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5771,7 +5771,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5814,7 +5814,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 14536-2026</t>
+          <t>A 58620-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5828,10 +5828,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46100</v>
+        <v>44902</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5887,7 +5887,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 36816-2024</t>
+          <t>A 31844-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45538</v>
+        <v>45834</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5916,13 +5916,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>1.4</v>
+        <v>6.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5965,7 +5960,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 36622-2023</t>
+          <t>A 31825-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5979,10 +5974,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45153</v>
+        <v>45834</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5995,7 +5990,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6038,7 +6033,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 10524-2024</t>
+          <t>A 1455-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6052,10 +6047,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45366</v>
+        <v>45670</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6068,7 +6063,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6111,7 +6106,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 8950-2024</t>
+          <t>A 37169-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6125,10 +6120,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45357</v>
+        <v>44806</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6141,7 +6136,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.6</v>
+        <v>17.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6184,7 +6179,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 58672-2022</t>
+          <t>A 32355-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6198,10 +6193,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44902</v>
+        <v>45837</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6214,7 +6209,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6257,7 +6252,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 43445-2023</t>
+          <t>A 59069-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6267,14 +6262,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45184</v>
+        <v>45252</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6287,7 +6282,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.1</v>
+        <v>4.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6330,7 +6325,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 59010-2024</t>
+          <t>A 7223-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6344,10 +6339,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45635</v>
+        <v>45702</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6403,7 +6398,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 32395-2023</t>
+          <t>A 26356-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6417,10 +6412,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45120</v>
+        <v>45805</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6433,7 +6428,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6476,7 +6471,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 8124-2023</t>
+          <t>A 59068-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6486,14 +6481,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44974</v>
+        <v>45252</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6506,7 +6501,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.5</v>
+        <v>6.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6549,7 +6544,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 17527-2026</t>
+          <t>A 7248-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6563,10 +6558,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46119</v>
+        <v>45702</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6579,7 +6574,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>4.4</v>
+        <v>1.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6622,7 +6617,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 17524-2026</t>
+          <t>A 50577-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6636,10 +6631,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46119</v>
+        <v>45601</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6652,7 +6647,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6695,7 +6690,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 17533-2026</t>
+          <t>A 12819-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6709,10 +6704,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46120</v>
+        <v>44642</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6725,7 +6720,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6768,7 +6763,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 17495-2026</t>
+          <t>A 25762-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6782,10 +6777,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46120</v>
+        <v>45090</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6798,7 +6793,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6841,7 +6836,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 17958-2026</t>
+          <t>A 36208-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6855,10 +6850,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46122</v>
+        <v>45867</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6868,11 +6863,6 @@
       <c r="G77" t="inlineStr">
         <is>
           <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I77" t="n">
@@ -6919,7 +6909,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 40291-2024</t>
+          <t>A 49906-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6933,10 +6923,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45554</v>
+        <v>45940</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6949,7 +6939,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6992,7 +6982,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 12819-2022</t>
+          <t>A 37195-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7002,14 +6992,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44642</v>
+        <v>45875</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7022,7 +7012,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7065,7 +7055,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 18834-2026</t>
+          <t>A 49909-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7079,10 +7069,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46129</v>
+        <v>45940</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7095,7 +7085,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7138,7 +7128,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 18979-2026</t>
+          <t>A 32952-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7152,10 +7142,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46129</v>
+        <v>45125</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7168,7 +7158,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.8</v>
+        <v>5.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7211,7 +7201,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 49906-2025</t>
+          <t>A 5514-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7225,10 +7215,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45940</v>
+        <v>46050</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7240,8 +7230,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7284,7 +7279,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 49909-2025</t>
+          <t>A 52719-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7298,10 +7293,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45940</v>
+        <v>45957</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7314,7 +7309,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7357,7 +7352,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 7247-2025</t>
+          <t>A 43445-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7371,10 +7366,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45702</v>
+        <v>45184</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7387,7 +7382,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7430,7 +7425,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 53814-2024</t>
+          <t>A 52640-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7444,10 +7439,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45615</v>
+        <v>45954</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7460,7 +7455,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7520,7 +7515,7 @@
         <v>45958</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7576,7 +7571,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 55984-2024</t>
+          <t>A 53274-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7590,10 +7585,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45623</v>
+        <v>45958</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7606,7 +7601,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7649,7 +7644,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 52640-2025</t>
+          <t>A 37098-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7663,10 +7658,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45954</v>
+        <v>45155</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7679,7 +7674,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.9</v>
+        <v>4.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7722,7 +7717,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 53274-2025</t>
+          <t>A 54191-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7736,10 +7731,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45958</v>
+        <v>45964</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7752,7 +7747,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7795,7 +7790,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 52719-2025</t>
+          <t>A 7592-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7809,10 +7804,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45957</v>
+        <v>46061</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7825,7 +7820,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7868,7 +7863,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 56419-2024</t>
+          <t>A 61312-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7882,10 +7877,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45623</v>
+        <v>45264</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7898,7 +7893,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>5.6</v>
+        <v>0.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7941,7 +7936,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 55897-2024</t>
+          <t>A 9738-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7955,10 +7950,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45622</v>
+        <v>46072</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7971,7 +7966,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8014,7 +8009,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 50577-2024</t>
+          <t>A 30904-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8028,10 +8023,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45601</v>
+        <v>44767</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8044,7 +8039,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8087,7 +8082,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 63778-2023</t>
+          <t>A 12175-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8097,14 +8092,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45278</v>
+        <v>44998</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8117,7 +8112,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8160,7 +8155,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 54191-2025</t>
+          <t>A 59155-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8174,10 +8169,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45964</v>
+        <v>45988</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8190,7 +8185,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8233,7 +8228,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 13530-2023</t>
+          <t>A 8953-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8247,10 +8242,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45006</v>
+        <v>44979</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8263,7 +8258,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8306,7 +8301,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 5577-2023</t>
+          <t>A 246-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8320,10 +8315,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44960</v>
+        <v>45660</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8336,7 +8331,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8379,7 +8374,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 60290-2024</t>
+          <t>A 14536-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8393,10 +8388,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45642</v>
+        <v>46100</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8409,7 +8404,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8452,7 +8447,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 49997-2025</t>
+          <t>A 7760-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8466,10 +8461,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45943</v>
+        <v>45706</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8482,7 +8477,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8525,7 +8520,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 6913-2023</t>
+          <t>A 2086-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8539,10 +8534,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44967</v>
+        <v>45672</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8555,7 +8550,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8598,7 +8593,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 15374-2025</t>
+          <t>A 62527-2021</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8612,10 +8607,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45747</v>
+        <v>44503</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8628,7 +8623,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1</v>
+        <v>22.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8671,7 +8666,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 20614-2025</t>
+          <t>A 17533-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8685,10 +8680,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45776</v>
+        <v>46120</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8701,7 +8696,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.7</v>
+        <v>3.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8744,7 +8739,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 58620-2022</t>
+          <t>A 17527-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8758,10 +8753,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44902</v>
+        <v>46119</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8774,7 +8769,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.5</v>
+        <v>4.4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8817,7 +8812,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 41937-2025</t>
+          <t>A 17495-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8831,10 +8826,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45903</v>
+        <v>46120</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8847,7 +8842,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8890,7 +8885,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 24234-2025</t>
+          <t>A 17524-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8904,10 +8899,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45797</v>
+        <v>46119</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8920,7 +8915,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8963,7 +8958,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 12175-2023</t>
+          <t>A 17958-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8977,10 +8972,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44998</v>
+        <v>46122</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8992,8 +8987,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>4.3</v>
+        <v>0.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9036,7 +9036,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 34779-2023</t>
+          <t>A 60290-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9050,10 +9050,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45141</v>
+        <v>45642</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9066,7 +9066,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9109,7 +9109,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 60112-2024</t>
+          <t>A 35112-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9123,10 +9123,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45642</v>
+        <v>45529</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9182,7 +9182,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 62527-2021</t>
+          <t>A 19759-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9196,10 +9196,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44503</v>
+        <v>45432</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9212,7 +9212,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>22.6</v>
+        <v>0.9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9255,7 +9255,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 21017-2026</t>
+          <t>A 18834-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9269,10 +9269,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46144</v>
+        <v>46129</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 59155-2025</t>
+          <t>A 18979-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9342,10 +9342,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45988</v>
+        <v>46129</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9358,7 +9358,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9401,7 +9401,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 61405-2025</t>
+          <t>A 56413-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9415,10 +9415,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46001</v>
+        <v>45623</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9430,13 +9430,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>6.6</v>
+        <v>3.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9479,7 +9474,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 29433-2025</t>
+          <t>A 1949-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9493,10 +9488,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45824</v>
+        <v>45672</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9509,7 +9504,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9552,7 +9547,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 8936-2026</t>
+          <t>A 696-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9566,10 +9561,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46069</v>
+        <v>45665</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9582,7 +9577,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9625,7 +9620,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 1949-2025</t>
+          <t>A 34779-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9639,10 +9634,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45672</v>
+        <v>45141</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9655,7 +9650,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9698,7 +9693,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 53279-2023</t>
+          <t>A 36835-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9708,14 +9703,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45229</v>
+        <v>45538</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9727,8 +9722,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9771,7 +9771,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 62541-2021</t>
+          <t>A 58393-2022</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9781,14 +9781,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44503</v>
+        <v>44901</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9844,7 +9844,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 6102-2023</t>
+          <t>A 49997-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9858,10 +9858,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44964</v>
+        <v>45943</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9917,7 +9917,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 43460-2024</t>
+          <t>A 2872-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9931,10 +9931,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45568</v>
+        <v>44945</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9947,7 +9947,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9990,7 +9990,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 13522-2023</t>
+          <t>A 15374-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10004,10 +10004,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45006</v>
+        <v>45747</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10063,7 +10063,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 24279-2026</t>
+          <t>A 6913-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10077,10 +10077,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46169</v>
+        <v>44967</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10093,7 +10093,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>11.7</v>
+        <v>1.4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10136,7 +10136,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 24736-2026</t>
+          <t>A 11949-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10150,10 +10150,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46171</v>
+        <v>44994</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10165,13 +10165,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10214,7 +10209,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 25762-2023</t>
+          <t>A 54582-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10228,10 +10223,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45090</v>
+        <v>45233</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10244,7 +10239,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10287,7 +10282,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 54582-2023</t>
+          <t>A 54279-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10301,10 +10296,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45233</v>
+        <v>45232</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10317,7 +10312,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10360,7 +10355,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 2872-2023</t>
+          <t>A 41937-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10374,10 +10369,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44945</v>
+        <v>45903</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10390,7 +10385,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10433,7 +10428,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 46876-2022</t>
+          <t>A 36816-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10447,10 +10442,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44851</v>
+        <v>45538</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10462,8 +10457,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>7.5</v>
+        <v>1.4</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10506,7 +10506,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 5514-2026</t>
+          <t>A 55984-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10520,10 +10520,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46050</v>
+        <v>45623</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10535,13 +10535,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10584,7 +10579,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 33654-2022</t>
+          <t>A 35047-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10598,10 +10593,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44789</v>
+        <v>45527</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10614,7 +10609,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10657,7 +10652,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 58393-2022</t>
+          <t>A 25322-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10667,14 +10662,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44901</v>
+        <v>45462</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10687,7 +10682,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10730,7 +10725,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 25814-2026</t>
+          <t>A 20614-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10744,10 +10739,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46178</v>
+        <v>45776</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10803,7 +10798,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 1455-2025</t>
+          <t>A 24234-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10817,10 +10812,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45670</v>
+        <v>45797</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10833,7 +10828,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10876,7 +10871,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 11949-2023</t>
+          <t>A 31596-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10890,10 +10885,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44994</v>
+        <v>45506</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10905,8 +10900,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>2.3</v>
+        <v>4.3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10949,7 +10949,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 26148-2026</t>
+          <t>A 52999-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10963,10 +10963,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46181</v>
+        <v>45226</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10979,7 +10979,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11022,7 +11022,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 33209-2023</t>
+          <t>A 21017-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11036,10 +11036,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45127</v>
+        <v>46144</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 7592-2026</t>
+          <t>A 53273-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11105,14 +11105,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46061</v>
+        <v>45229</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11125,7 +11125,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.1</v>
+        <v>6.3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11168,7 +11168,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 8626-2024</t>
+          <t>A 24759-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11182,10 +11182,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45355</v>
+        <v>45084</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>6.4</v>
+        <v>2.9</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11241,7 +11241,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 44849-2024</t>
+          <t>A 61405-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11255,10 +11255,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45574</v>
+        <v>46001</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11270,8 +11270,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I137" t="n">
-        <v>3.8</v>
+        <v>6.6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11314,7 +11319,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 9738-2026</t>
+          <t>A 29433-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11328,10 +11333,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46072</v>
+        <v>45824</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11387,7 +11392,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 62551-2021</t>
+          <t>A 52853-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11401,10 +11406,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44503</v>
+        <v>45226</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11417,7 +11422,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11460,7 +11465,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 11795-2024</t>
+          <t>A 8936-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11474,10 +11479,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45375</v>
+        <v>46069</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11490,7 +11495,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11533,7 +11538,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 35047-2024</t>
+          <t>A 7212-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11547,10 +11552,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45527</v>
+        <v>45702</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11563,7 +11568,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11606,7 +11611,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 39800-2022</t>
+          <t>A 24279-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11620,10 +11625,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44819</v>
+        <v>46169</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11636,7 +11641,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2</v>
+        <v>11.7</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11679,7 +11684,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 48346-2024</t>
+          <t>A 32395-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11693,10 +11698,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45590</v>
+        <v>45120</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11709,7 +11714,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11752,7 +11757,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 30484-2023</t>
+          <t>A 6080-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11762,14 +11767,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45111</v>
+        <v>44964</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11782,7 +11787,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.2</v>
+        <v>1.9</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11825,7 +11830,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 27552-2026</t>
+          <t>A 35202-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11839,10 +11844,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46190</v>
+        <v>45145</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11855,7 +11860,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>5.3</v>
+        <v>11.1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11898,7 +11903,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 28056-2026</t>
+          <t>A 24736-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11912,10 +11917,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46195</v>
+        <v>46171</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11927,8 +11932,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>1</v>
+        <v>3.8</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11971,7 +11981,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 28068-2026</t>
+          <t>A 5577-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11985,10 +11995,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46195</v>
+        <v>44960</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12001,7 +12011,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12044,7 +12054,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 36835-2024</t>
+          <t>A 33654-2022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12058,10 +12068,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45538</v>
+        <v>44789</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12073,13 +12083,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12122,7 +12127,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 32504-2026</t>
+          <t>A 30484-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12136,10 +12141,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46239</v>
+        <v>45111</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12151,13 +12156,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12200,7 +12200,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 32952-2023</t>
+          <t>A 8950-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12214,10 +12214,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45125</v>
+        <v>45357</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12230,7 +12230,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>5.1</v>
+        <v>0.6</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12273,7 +12273,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 28309-2026</t>
+          <t>A 46876-2022</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12287,10 +12287,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46196</v>
+        <v>44851</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>3.1</v>
+        <v>7.5</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12346,7 +12346,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 32477-2026</t>
+          <t>A 13522-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12360,10 +12360,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46239</v>
+        <v>45006</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12373,11 +12373,6 @@
       <c r="G152" t="inlineStr">
         <is>
           <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I152" t="n">
@@ -12424,7 +12419,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 32497-2026</t>
+          <t>A 25814-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12438,10 +12433,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46239</v>
+        <v>46178</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12453,13 +12448,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12502,7 +12492,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 32923-2026</t>
+          <t>A 56419-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12516,10 +12506,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46244</v>
+        <v>45623</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12532,7 +12522,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2.1</v>
+        <v>5.6</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12575,7 +12565,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 32944-2026</t>
+          <t>A 8626-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12589,10 +12579,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46244</v>
+        <v>45355</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12605,7 +12595,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.7</v>
+        <v>6.4</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12648,7 +12638,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 35087-2024</t>
+          <t>A 60112-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12662,10 +12652,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45527</v>
+        <v>45642</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12678,7 +12668,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12721,7 +12711,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 35112-2024</t>
+          <t>A 31605-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12735,10 +12725,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45529</v>
+        <v>45506</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12750,8 +12740,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I157" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12794,7 +12789,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 2086-2025</t>
+          <t>A 26148-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12808,10 +12803,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45672</v>
+        <v>46181</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12824,7 +12819,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12867,7 +12862,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 61312-2023</t>
+          <t>A 60118-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12881,10 +12876,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45264</v>
+        <v>45642</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12897,7 +12892,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12940,7 +12935,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 246-2025</t>
+          <t>A 62551-2021</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12954,10 +12949,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45660</v>
+        <v>44503</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12970,7 +12965,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13013,7 +13008,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 48301-2024</t>
+          <t>A 56542-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13023,14 +13018,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45590</v>
+        <v>45625</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13043,7 +13038,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13086,7 +13081,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 30399-2023</t>
+          <t>A 53814-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13100,10 +13095,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45111</v>
+        <v>45615</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13116,7 +13111,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13159,7 +13154,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 60465-2024</t>
+          <t>A 27552-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13173,10 +13168,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45643</v>
+        <v>46190</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13189,7 +13184,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.8</v>
+        <v>5.3</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13232,7 +13227,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 25322-2024</t>
+          <t>A 10524-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13246,10 +13241,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45462</v>
+        <v>45366</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13262,7 +13257,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13305,7 +13300,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 35202-2023</t>
+          <t>A 9422-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13319,10 +13314,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45145</v>
+        <v>45359</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13335,7 +13330,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>11.1</v>
+        <v>1</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13378,7 +13373,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 31596-2024</t>
+          <t>A 28068-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13392,10 +13387,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45506</v>
+        <v>46195</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13407,13 +13402,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I166" t="n">
-        <v>4.3</v>
+        <v>0.7</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13456,7 +13446,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 40257-2023</t>
+          <t>A 28056-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13470,10 +13460,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45169</v>
+        <v>46195</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13486,7 +13476,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13529,7 +13519,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 33984-2026</t>
+          <t>A 45608-2022</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13539,14 +13529,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46252</v>
+        <v>44845</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13559,7 +13549,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2.9</v>
+        <v>17</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13602,7 +13592,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 19759-2024</t>
+          <t>A 28309-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13616,10 +13606,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45432</v>
+        <v>46196</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13632,7 +13622,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13675,7 +13665,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 56542-2024</t>
+          <t>A 58672-2022</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13685,14 +13675,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45625</v>
+        <v>44902</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13705,7 +13695,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13748,7 +13738,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 24759-2023</t>
+          <t>A 55897-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13762,10 +13752,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45084</v>
+        <v>45622</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13778,7 +13768,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13821,7 +13811,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 34112-2026</t>
+          <t>A 32923-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13835,10 +13825,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46253</v>
+        <v>46244</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13851,7 +13841,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13894,7 +13884,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 37169-2022</t>
+          <t>A 32944-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13908,10 +13898,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44806</v>
+        <v>46244</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13924,7 +13914,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>17.4</v>
+        <v>1.7</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13967,7 +13957,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 60118-2024</t>
+          <t>A 41163-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13981,10 +13971,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45642</v>
+        <v>45174</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13997,7 +13987,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>0.6</v>
+        <v>3.2</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14040,7 +14030,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 53769-2024</t>
+          <t>A 33984-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14050,14 +14040,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45615</v>
+        <v>46252</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14070,7 +14060,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14113,7 +14103,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 696-2025</t>
+          <t>A 34112-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14127,10 +14117,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45665</v>
+        <v>46253</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14143,7 +14133,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14186,7 +14176,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 30904-2022</t>
+          <t>A 40257-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14200,10 +14190,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44767</v>
+        <v>45169</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14216,7 +14206,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14259,7 +14249,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 56740-2023</t>
+          <t>A 36622-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14273,10 +14263,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45244</v>
+        <v>45153</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14289,7 +14279,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>4.5</v>
+        <v>0.4</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14332,7 +14322,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 52853-2023</t>
+          <t>A 62541-2021</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14346,10 +14336,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45226</v>
+        <v>44503</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14362,7 +14352,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14405,7 +14395,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 60642-2023</t>
+          <t>A 28850-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14415,14 +14405,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45260</v>
+        <v>45478</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14435,7 +14425,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14478,7 +14468,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 55974-2024</t>
+          <t>A 44849-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14492,10 +14482,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45623</v>
+        <v>45574</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14508,7 +14498,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14551,7 +14541,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 53764-2024</t>
+          <t>A 59644-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14565,10 +14555,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45615</v>
+        <v>45254</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14581,7 +14571,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14624,7 +14614,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 41163-2023</t>
+          <t>A 56365-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14638,10 +14628,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45174</v>
+        <v>45625</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14654,7 +14644,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>3.2</v>
+        <v>0.6</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14697,7 +14687,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 7223-2025</t>
+          <t>A 6940-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14711,10 +14701,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45702</v>
+        <v>45343</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14727,7 +14717,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14770,7 +14760,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 36716-2026</t>
+          <t>A 40291-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14784,10 +14774,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46272</v>
+        <v>45554</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14843,7 +14833,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 31902-2026</t>
+          <t>A 33209-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14857,10 +14847,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46231</v>
+        <v>45127</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14873,7 +14863,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14916,7 +14906,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 56365-2024</t>
+          <t>A 53764-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14930,10 +14920,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45625</v>
+        <v>45615</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14946,7 +14936,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14989,7 +14979,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 36878-2026</t>
+          <t>A 44308-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15003,10 +14993,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46273</v>
+        <v>45188</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15019,7 +15009,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15062,7 +15052,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 52999-2023</t>
+          <t>A 13530-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15076,10 +15066,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45226</v>
+        <v>45006</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15092,7 +15082,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15135,7 +15125,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 31897-2026</t>
+          <t>A 36878-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15149,10 +15139,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46231</v>
+        <v>46273</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15165,7 +15155,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15208,7 +15198,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 31899-2026</t>
+          <t>A 35087-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15222,10 +15212,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46231</v>
+        <v>45527</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15238,7 +15228,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15281,7 +15271,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 7760-2025</t>
+          <t>A 36716-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15295,10 +15285,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45706</v>
+        <v>46272</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15311,7 +15301,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>8.300000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15354,7 +15344,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 31826-2026</t>
+          <t>A 53769-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15368,10 +15358,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46230</v>
+        <v>45615</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15384,7 +15374,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15427,7 +15417,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 56413-2024</t>
+          <t>A 6102-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15441,10 +15431,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45623</v>
+        <v>44964</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15457,7 +15447,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>3.5</v>
+        <v>0.8</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15500,7 +15490,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 34941-2026</t>
+          <t>A 31826-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15514,10 +15504,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46259</v>
+        <v>46230</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15530,7 +15520,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>9.300000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15573,7 +15563,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 34945-2026</t>
+          <t>A 34936-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15590,7 +15580,7 @@
         <v>46259</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15603,7 +15593,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15646,7 +15636,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 34936-2026</t>
+          <t>A 18768-2024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15660,10 +15650,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46259</v>
+        <v>45426</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15676,7 +15666,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>7.4</v>
+        <v>0.8</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15719,7 +15709,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 37997-2026</t>
+          <t>A 56740-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15733,10 +15723,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46280</v>
+        <v>45244</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15749,7 +15739,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.6</v>
+        <v>4.5</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15792,7 +15782,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 37994-2026</t>
+          <t>A 31897-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15806,10 +15796,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46280</v>
+        <v>46231</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15822,7 +15812,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15865,7 +15855,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 38009-2026</t>
+          <t>A 31899-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15879,10 +15869,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46280</v>
+        <v>46231</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15895,7 +15885,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15938,7 +15928,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 56373-2024</t>
+          <t>A 31902-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15952,10 +15942,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45625</v>
+        <v>46231</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15968,7 +15958,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16011,7 +16001,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 61817-2024</t>
+          <t>A 43460-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16025,10 +16015,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45649</v>
+        <v>45568</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16041,7 +16031,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>4.6</v>
+        <v>0.8</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16084,7 +16074,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 9973-2024</t>
+          <t>A 59010-2024</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16098,10 +16088,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45363</v>
+        <v>45635</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16114,7 +16104,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16157,7 +16147,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 53805-2024</t>
+          <t>A 37994-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16171,10 +16161,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45615</v>
+        <v>46280</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16187,7 +16177,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16230,7 +16220,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 11393-2025</t>
+          <t>A 34941-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16244,10 +16234,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45726</v>
+        <v>46259</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16260,7 +16250,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>0.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16303,7 +16293,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 11563-2025</t>
+          <t>A 37997-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16313,14 +16303,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45727</v>
+        <v>46280</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16332,13 +16322,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I206" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16381,7 +16366,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 53275-2023</t>
+          <t>A 32497-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16391,14 +16376,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45229</v>
+        <v>46239</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16410,8 +16395,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I207" t="n">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16454,7 +16444,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 44104-2024</t>
+          <t>A 34945-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16468,10 +16458,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45572</v>
+        <v>46259</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16484,7 +16474,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>2.4</v>
+        <v>6.2</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16527,7 +16517,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 24356-2025</t>
+          <t>A 32504-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16541,10 +16531,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45797</v>
+        <v>46239</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16556,8 +16546,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I209" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16600,7 +16595,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 19840-2025</t>
+          <t>A 32477-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16610,14 +16605,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45771</v>
+        <v>46239</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16629,8 +16624,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I210" t="n">
-        <v>0.2</v>
+        <v>2.4</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16673,7 +16673,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 58420-2023</t>
+          <t>A 38009-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16683,14 +16683,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45250</v>
+        <v>46280</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16703,7 +16703,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16746,7 +16746,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 36945-2024</t>
+          <t>A 61817-2024</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16760,10 +16760,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45538</v>
+        <v>45649</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16775,13 +16775,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I212" t="n">
-        <v>1</v>
+        <v>4.6</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16824,7 +16819,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 17892-2025</t>
+          <t>A 9973-2024</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16838,10 +16833,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45758</v>
+        <v>45363</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16854,7 +16849,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.3</v>
+        <v>4.7</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16897,7 +16892,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 29495-2025</t>
+          <t>A 56373-2024</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16911,10 +16906,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45824</v>
+        <v>45625</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16927,7 +16922,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>5.2</v>
+        <v>1.3</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16970,7 +16965,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 31844-2025</t>
+          <t>A 53805-2024</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16984,10 +16979,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45834</v>
+        <v>45615</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17000,7 +16995,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>6.2</v>
+        <v>1.1</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17043,7 +17038,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 31825-2025</t>
+          <t>A 11393-2025</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17057,10 +17052,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45834</v>
+        <v>45726</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17073,7 +17068,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17116,7 +17111,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 32355-2025</t>
+          <t>A 24356-2025</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17130,10 +17125,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45837</v>
+        <v>45797</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17146,7 +17141,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>2.3</v>
+        <v>0.2</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17189,7 +17184,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 26356-2025</t>
+          <t>A 53275-2023</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17199,14 +17194,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45805</v>
+        <v>45229</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17219,7 +17214,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>0.4</v>
+        <v>8.5</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17262,7 +17257,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 59069-2023</t>
+          <t>A 44104-2024</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17272,14 +17267,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45252</v>
+        <v>45572</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17292,7 +17287,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>4.9</v>
+        <v>2.4</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17335,7 +17330,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 36208-2025</t>
+          <t>A 11563-2025</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17345,14 +17340,14 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45867</v>
+        <v>45727</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17364,8 +17359,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I220" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17408,7 +17408,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>S 1807-2022</t>
+          <t>S 3762-2024</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17418,14 +17418,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Skogsbilväg</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>44656</v>
+        <v>45558</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17437,13 +17437,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I221" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17486,7 +17481,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>S 3762-2024</t>
+          <t>S 1807-2022</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17496,14 +17491,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Skogsbilväg</t>
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45558</v>
+        <v>44656</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17515,8 +17510,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I222" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17576,7 +17576,7 @@
         <v>45688</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17649,7 +17649,7 @@
         <v>45688</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>44705</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>

--- a/Översikt LIDKÖPING.xlsx
+++ b/Översikt LIDKÖPING.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE225"/>
+  <dimension ref="A1:AE226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44631</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>46006</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 6898-2023</t>
+          <t>A 24727-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44967</v>
+        <v>46171</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -861,20 +861,25 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I4" t="n">
-        <v>18</v>
+        <v>6.9</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -886,21 +891,138 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
       </c>
       <c r="T4" t="n">
+        <v>8</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Veckticka
+Blodticka
+Västlig hakmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 24727-2026 artfynd.xlsx", "A 24727-2026")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 24727-2026 karta.png", "A 24727-2026")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 24727-2026 georefererad karta.tif", "A 24727-2026")</f>
+        <v/>
+      </c>
+      <c r="Z4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/knärot/A 24727-2026 karta knärot.png", "A 24727-2026")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 24727-2026 FSC-klagomål.docx", "A 24727-2026")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 24727-2026 FSC-klagomål mail.docx", "A 24727-2026")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 24727-2026 tillsynsbegäran.docx", "A 24727-2026")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 24727-2026 tillsynsbegäran mail.docx", "A 24727-2026")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 24727-2026 prioriterade fågelarter.docx", "A 24727-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 6898-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44967</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>18</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
         <v>5</v>
       </c>
-      <c r="U4" t="n">
+      <c r="T5" t="n">
         <v>5</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="U5" t="n">
+        <v>5</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Grönsångare
 Göktyta
@@ -909,165 +1031,43 @@
 Röd glada</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 6898-2023 artfynd.xlsx", "A 6898-2023")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 6898-2023 karta.png", "A 6898-2023")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 6898-2023 georefererad karta.tif", "A 6898-2023")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 6898-2023 FSC-klagomål.docx", "A 6898-2023")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 6898-2023 FSC-klagomål mail.docx", "A 6898-2023")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 6898-2023 tillsynsbegäran.docx", "A 6898-2023")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 6898-2023 tillsynsbegäran mail.docx", "A 6898-2023")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 6898-2023 prioriterade fågelarter.docx", "A 6898-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 24727-2026</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>46171</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>5</v>
-      </c>
-      <c r="T5" t="n">
-        <v>8</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Veckticka
-Blodticka
-Västlig hakmossa
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 24727-2026 artfynd.xlsx", "A 24727-2026")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 24727-2026 karta.png", "A 24727-2026")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 24727-2026 georefererad karta.tif", "A 24727-2026")</f>
-        <v/>
-      </c>
-      <c r="Z5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/knärot/A 24727-2026 karta knärot.png", "A 24727-2026")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 24727-2026 FSC-klagomål.docx", "A 24727-2026")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 24727-2026 FSC-klagomål mail.docx", "A 24727-2026")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 24727-2026 tillsynsbegäran.docx", "A 24727-2026")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 24727-2026 tillsynsbegäran mail.docx", "A 24727-2026")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 24727-2026 prioriterade fågelarter.docx", "A 24727-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 28849-2024</t>
+          <t>A 32280-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45478</v>
+        <v>44781</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1097,13 +1097,13 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.6</v>
+        <v>8.6</v>
       </c>
       <c r="J6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -1136,6 +1136,118 @@
         <v>0</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Gulsparv
+Nötkråka
+Sotriska
+Skogsduva</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 32280-2022 artfynd.xlsx", "A 32280-2022")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 32280-2022 karta.png", "A 32280-2022")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 32280-2022 georefererad karta.tif", "A 32280-2022")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 32280-2022 FSC-klagomål.docx", "A 32280-2022")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 32280-2022 FSC-klagomål mail.docx", "A 32280-2022")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 32280-2022 tillsynsbegäran.docx", "A 32280-2022")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 32280-2022 tillsynsbegäran mail.docx", "A 32280-2022")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 32280-2022 prioriterade fågelarter.docx", "A 32280-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 28849-2024</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45478</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Entita
 Talltita
@@ -1143,111 +1255,111 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 28849-2024 artfynd.xlsx", "A 28849-2024")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 28849-2024 karta.png", "A 28849-2024")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 28849-2024 georefererad karta.tif", "A 28849-2024")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 28849-2024 FSC-klagomål.docx", "A 28849-2024")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 28849-2024 FSC-klagomål mail.docx", "A 28849-2024")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 28849-2024 tillsynsbegäran.docx", "A 28849-2024")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 28849-2024 tillsynsbegäran mail.docx", "A 28849-2024")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 28849-2024 prioriterade fågelarter.docx", "A 28849-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>A 34942-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
         <v>46259</v>
       </c>
-      <c r="E7" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
+      <c r="E8" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
         <v>18.1</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J8" t="n">
         <v>3</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K8" t="n">
         <v>1</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L8" t="n">
         <v>2</v>
       </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>2</v>
       </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
         <v>4</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T8" t="n">
         <v>4</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Gulsparv
 Nötkråka
@@ -1255,155 +1367,43 @@
 Skogsduva</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 34942-2026 artfynd.xlsx", "A 34942-2026")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 34942-2026 karta.png", "A 34942-2026")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 34942-2026 georefererad karta.tif", "A 34942-2026")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 34942-2026 FSC-klagomål.docx", "A 34942-2026")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 34942-2026 FSC-klagomål mail.docx", "A 34942-2026")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 34942-2026 tillsynsbegäran.docx", "A 34942-2026")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 34942-2026 tillsynsbegäran mail.docx", "A 34942-2026")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 34942-2026 prioriterade fågelarter.docx", "A 34942-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 32280-2022</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>44781</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>4</v>
-      </c>
-      <c r="T8" t="n">
-        <v>4</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Gulsparv
-Nötkråka
-Sotriska
-Skogsduva</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 32280-2022 artfynd.xlsx", "A 32280-2022")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 32280-2022 karta.png", "A 32280-2022")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 32280-2022 georefererad karta.tif", "A 32280-2022")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 32280-2022 FSC-klagomål.docx", "A 32280-2022")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 32280-2022 FSC-klagomål mail.docx", "A 32280-2022")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 32280-2022 tillsynsbegäran.docx", "A 32280-2022")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 32280-2022 tillsynsbegäran mail.docx", "A 32280-2022")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 32280-2022 prioriterade fågelarter.docx", "A 32280-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 4831-2025</t>
+          <t>A 15219-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1413,14 +1413,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45688</v>
+        <v>45400</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1433,22 +1433,22 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.3</v>
+        <v>6.7</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1460,7 +1460,7 @@
         <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1472,148 +1472,148 @@
         <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Tårkragskivling
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 15219-2024 artfynd.xlsx", "A 15219-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 15219-2024 karta.png", "A 15219-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 15219-2024 georefererad karta.tif", "A 15219-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 15219-2024 FSC-klagomål.docx", "A 15219-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 15219-2024 FSC-klagomål mail.docx", "A 15219-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 15219-2024 tillsynsbegäran.docx", "A 15219-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 15219-2024 tillsynsbegäran mail.docx", "A 15219-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 4831-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45688</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Ask
 Skogsalm
 Barkticka</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 4831-2025 artfynd.xlsx", "A 4831-2025")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 4831-2025 karta.png", "A 4831-2025")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 4831-2025 georefererad karta.tif", "A 4831-2025")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 4831-2025 FSC-klagomål.docx", "A 4831-2025")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 4831-2025 FSC-klagomål mail.docx", "A 4831-2025")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 4831-2025 tillsynsbegäran.docx", "A 4831-2025")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 4831-2025 tillsynsbegäran mail.docx", "A 4831-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 15219-2024</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45400</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Tårkragskivling
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 15219-2024 artfynd.xlsx", "A 15219-2024")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 15219-2024 karta.png", "A 15219-2024")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 15219-2024 georefererad karta.tif", "A 15219-2024")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 15219-2024 FSC-klagomål.docx", "A 15219-2024")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 15219-2024 FSC-klagomål mail.docx", "A 15219-2024")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 15219-2024 tillsynsbegäran.docx", "A 15219-2024")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 15219-2024 tillsynsbegäran mail.docx", "A 15219-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>45202</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>45898</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>45702</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>44630</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 10476-2023</t>
+          <t>A 44680-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44987</v>
+        <v>45189</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2126,688 +2126,688 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Trädlärka</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 44680-2023 artfynd.xlsx", "A 44680-2023")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 44680-2023 karta.png", "A 44680-2023")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 44680-2023 georefererad karta.tif", "A 44680-2023")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 44680-2023 FSC-klagomål.docx", "A 44680-2023")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 44680-2023 FSC-klagomål mail.docx", "A 44680-2023")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 44680-2023 tillsynsbegäran.docx", "A 44680-2023")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 44680-2023 tillsynsbegäran mail.docx", "A 44680-2023")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 44680-2023 prioriterade fågelarter.docx", "A 44680-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 61818-2024</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45649</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J16" t="n">
         <v>1</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 61818-2024 artfynd.xlsx", "A 61818-2024")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 61818-2024 karta.png", "A 61818-2024")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 61818-2024 georefererad karta.tif", "A 61818-2024")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 61818-2024 FSC-klagomål.docx", "A 61818-2024")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 61818-2024 FSC-klagomål mail.docx", "A 61818-2024")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 61818-2024 tillsynsbegäran.docx", "A 61818-2024")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 61818-2024 tillsynsbegäran mail.docx", "A 61818-2024")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 61818-2024 prioriterade fågelarter.docx", "A 61818-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 62569-2022</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>44924</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 62569-2022 artfynd.xlsx", "A 62569-2022")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 62569-2022 karta.png", "A 62569-2022")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 62569-2022 georefererad karta.tif", "A 62569-2022")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 62569-2022 FSC-klagomål.docx", "A 62569-2022")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 62569-2022 FSC-klagomål mail.docx", "A 62569-2022")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 62569-2022 tillsynsbegäran.docx", "A 62569-2022")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 62569-2022 tillsynsbegäran mail.docx", "A 62569-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 37136-2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Fiskgjuse</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 37136-2026 artfynd.xlsx", "A 37136-2026")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 37136-2026 karta.png", "A 37136-2026")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 37136-2026 georefererad karta.tif", "A 37136-2026")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 37136-2026 FSC-klagomål.docx", "A 37136-2026")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 37136-2026 FSC-klagomål mail.docx", "A 37136-2026")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 37136-2026 tillsynsbegäran.docx", "A 37136-2026")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 37136-2026 tillsynsbegäran mail.docx", "A 37136-2026")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 37136-2026 prioriterade fågelarter.docx", "A 37136-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 10476-2023</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>44987</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Kungsfågel</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 10476-2023 artfynd.xlsx", "A 10476-2023")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 10476-2023 karta.png", "A 10476-2023")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 10476-2023 georefererad karta.tif", "A 10476-2023")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 10476-2023 FSC-klagomål.docx", "A 10476-2023")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 10476-2023 FSC-klagomål mail.docx", "A 10476-2023")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 10476-2023 tillsynsbegäran.docx", "A 10476-2023")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 10476-2023 tillsynsbegäran mail.docx", "A 10476-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 44680-2023</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45189</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J16" t="n">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 24352-2025</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45797</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J20" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>1</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T20" t="n">
         <v>1</v>
       </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Trädlärka</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 44680-2023 artfynd.xlsx", "A 44680-2023")</f>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 24352-2025 artfynd.xlsx", "A 24352-2025")</f>
         <v/>
       </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 44680-2023 karta.png", "A 44680-2023")</f>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 24352-2025 karta.png", "A 24352-2025")</f>
         <v/>
       </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 44680-2023 georefererad karta.tif", "A 44680-2023")</f>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 24352-2025 georefererad karta.tif", "A 24352-2025")</f>
         <v/>
       </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 44680-2023 FSC-klagomål.docx", "A 44680-2023")</f>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 24352-2025 FSC-klagomål.docx", "A 24352-2025")</f>
         <v/>
       </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 44680-2023 FSC-klagomål mail.docx", "A 44680-2023")</f>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 24352-2025 FSC-klagomål mail.docx", "A 24352-2025")</f>
         <v/>
       </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 44680-2023 tillsynsbegäran.docx", "A 44680-2023")</f>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 24352-2025 tillsynsbegäran.docx", "A 24352-2025")</f>
         <v/>
       </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 44680-2023 tillsynsbegäran mail.docx", "A 44680-2023")</f>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 24352-2025 tillsynsbegäran mail.docx", "A 24352-2025")</f>
         <v/>
       </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 44680-2023 prioriterade fågelarter.docx", "A 44680-2023")</f>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 24352-2025 prioriterade fågelarter.docx", "A 24352-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>A 62629-2022</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
         <v>44925</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
+      <c r="E21" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
         <v>1.8</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>1</v>
       </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>1</v>
       </c>
-      <c r="R17" t="n">
+      <c r="R21" t="n">
         <v>1</v>
       </c>
-      <c r="S17" t="n">
+      <c r="S21" t="n">
         <v>1</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T21" t="n">
         <v>1</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U21" t="n">
         <v>1</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Igelkott</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 62629-2022 artfynd.xlsx", "A 62629-2022")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 62629-2022 karta.png", "A 62629-2022")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 62629-2022 georefererad karta.tif", "A 62629-2022")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 62629-2022 FSC-klagomål.docx", "A 62629-2022")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 62629-2022 FSC-klagomål mail.docx", "A 62629-2022")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 62629-2022 tillsynsbegäran.docx", "A 62629-2022")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 62629-2022 tillsynsbegäran mail.docx", "A 62629-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 61818-2024</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45649</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Rödvingetrast</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 61818-2024 artfynd.xlsx", "A 61818-2024")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 61818-2024 karta.png", "A 61818-2024")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 61818-2024 georefererad karta.tif", "A 61818-2024")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 61818-2024 FSC-klagomål.docx", "A 61818-2024")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 61818-2024 FSC-klagomål mail.docx", "A 61818-2024")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 61818-2024 tillsynsbegäran.docx", "A 61818-2024")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 61818-2024 tillsynsbegäran mail.docx", "A 61818-2024")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 61818-2024 prioriterade fågelarter.docx", "A 61818-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 62569-2022</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>44924</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>1</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 62569-2022 artfynd.xlsx", "A 62569-2022")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 62569-2022 karta.png", "A 62569-2022")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 62569-2022 georefererad karta.tif", "A 62569-2022")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 62569-2022 FSC-klagomål.docx", "A 62569-2022")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 62569-2022 FSC-klagomål mail.docx", "A 62569-2022")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 62569-2022 tillsynsbegäran.docx", "A 62569-2022")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 62569-2022 tillsynsbegäran mail.docx", "A 62569-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 37136-2026</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>46274</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Fiskgjuse</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 37136-2026 artfynd.xlsx", "A 37136-2026")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 37136-2026 karta.png", "A 37136-2026")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 37136-2026 georefererad karta.tif", "A 37136-2026")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 37136-2026 FSC-klagomål.docx", "A 37136-2026")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 37136-2026 FSC-klagomål mail.docx", "A 37136-2026")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 37136-2026 tillsynsbegäran.docx", "A 37136-2026")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 37136-2026 tillsynsbegäran mail.docx", "A 37136-2026")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 37136-2026 prioriterade fågelarter.docx", "A 37136-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 24352-2025</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45797</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 24352-2025 artfynd.xlsx", "A 24352-2025")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 24352-2025 karta.png", "A 24352-2025")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 24352-2025 georefererad karta.tif", "A 24352-2025")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 24352-2025 FSC-klagomål.docx", "A 24352-2025")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 24352-2025 FSC-klagomål mail.docx", "A 24352-2025")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 24352-2025 tillsynsbegäran.docx", "A 24352-2025")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 24352-2025 tillsynsbegäran mail.docx", "A 24352-2025")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 24352-2025 prioriterade fågelarter.docx", "A 24352-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>44788</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>44466</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>44831</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>44820</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>44714</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>44566</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>44546</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>44627</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>44627</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>44725</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>44805</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>44705</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>44617</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>44487</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>44487</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>44770</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>44742</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>44806</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         <v>44515</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>44614</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>44747</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 8124-2023</t>
+          <t>A 7248-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4363,10 +4363,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44974</v>
+        <v>45702</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4422,7 +4422,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 60465-2024</t>
+          <t>A 53273-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4432,14 +4432,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45643</v>
+        <v>45229</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.8</v>
+        <v>6.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4495,7 +4495,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 60642-2023</t>
+          <t>A 6940-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4505,14 +4505,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45260</v>
+        <v>45343</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4568,7 +4568,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 48301-2024</t>
+          <t>A 59068-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4578,14 +4578,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45590</v>
+        <v>45252</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.8</v>
+        <v>6.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4641,7 +4641,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 7247-2025</t>
+          <t>A 136-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4655,10 +4655,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45702</v>
+        <v>44928</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.3</v>
+        <v>4.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 30399-2023</t>
+          <t>A 49755-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4728,10 +4728,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45111</v>
+        <v>44859</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4787,7 +4787,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 19840-2025</t>
+          <t>A 18768-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4797,14 +4797,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45771</v>
+        <v>45426</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4860,7 +4860,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 48411-2022</t>
+          <t>A 9422-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4874,10 +4874,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44858</v>
+        <v>45359</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4933,7 +4933,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 11795-2024</t>
+          <t>A 28850-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4947,10 +4947,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45375</v>
+        <v>45478</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.8</v>
+        <v>1.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5006,7 +5006,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 58420-2023</t>
+          <t>A 31605-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5016,14 +5016,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45250</v>
+        <v>45506</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5035,8 +5035,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5079,7 +5084,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 36945-2024</t>
+          <t>A 45608-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5093,10 +5098,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45538</v>
+        <v>44845</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5108,13 +5113,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5157,7 +5157,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 55974-2024</t>
+          <t>A 37098-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5171,10 +5171,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45623</v>
+        <v>45155</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5230,7 +5230,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 17892-2025</t>
+          <t>A 36622-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5244,10 +5244,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45758</v>
+        <v>45153</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5303,7 +5303,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 48346-2024</t>
+          <t>A 36816-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45590</v>
+        <v>45538</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5332,8 +5332,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5376,7 +5381,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 39800-2022</t>
+          <t>A 8950-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5390,10 +5395,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44819</v>
+        <v>45357</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5406,7 +5411,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5449,7 +5454,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 29495-2025</t>
+          <t>A 10524-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5463,10 +5468,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45824</v>
+        <v>45366</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5479,7 +5484,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>5.2</v>
+        <v>0.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5522,7 +5527,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 49755-2022</t>
+          <t>A 58672-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5536,10 +5541,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44859</v>
+        <v>44902</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5552,7 +5557,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5595,7 +5600,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 63778-2023</t>
+          <t>A 43445-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5605,14 +5610,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45278</v>
+        <v>45184</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5625,7 +5630,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5668,7 +5673,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 53279-2023</t>
+          <t>A 32395-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5678,14 +5683,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45229</v>
+        <v>45120</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5698,7 +5703,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5741,7 +5746,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 136-2023</t>
+          <t>A 8124-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5755,10 +5760,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44928</v>
+        <v>44974</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5771,7 +5776,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5814,7 +5819,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 58620-2022</t>
+          <t>A 40291-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5828,10 +5833,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44902</v>
+        <v>45554</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5844,7 +5849,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5887,7 +5892,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 31844-2025</t>
+          <t>A 29495-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5901,10 +5906,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45834</v>
+        <v>45824</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5917,7 +5922,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5960,7 +5965,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 31825-2025</t>
+          <t>A 9738-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5974,10 +5979,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45834</v>
+        <v>46072</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5990,7 +5995,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6033,7 +6038,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 1455-2025</t>
+          <t>A 31844-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6047,10 +6052,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45670</v>
+        <v>45834</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6063,7 +6068,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.4</v>
+        <v>6.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6106,7 +6111,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 37169-2022</t>
+          <t>A 31825-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6120,10 +6125,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44806</v>
+        <v>45834</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6136,7 +6141,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>17.4</v>
+        <v>1.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6196,7 +6201,7 @@
         <v>45837</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6252,7 +6257,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 59069-2023</t>
+          <t>A 7247-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6262,14 +6267,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45252</v>
+        <v>45702</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6282,7 +6287,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>4.9</v>
+        <v>1.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6325,7 +6330,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 7223-2025</t>
+          <t>A 53814-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6339,10 +6344,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45702</v>
+        <v>45615</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6355,7 +6360,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6398,7 +6403,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 26356-2025</t>
+          <t>A 55984-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6412,10 +6417,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45805</v>
+        <v>45623</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6428,7 +6433,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6471,7 +6476,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 59068-2023</t>
+          <t>A 26356-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6481,14 +6486,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45252</v>
+        <v>45805</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6501,7 +6506,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>6.4</v>
+        <v>0.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6544,7 +6549,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 7248-2025</t>
+          <t>A 56419-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6558,10 +6563,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45702</v>
+        <v>45623</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6574,7 +6579,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.4</v>
+        <v>5.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6617,7 +6622,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 50577-2024</t>
+          <t>A 59069-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6627,14 +6632,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45601</v>
+        <v>45252</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6647,7 +6652,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.1</v>
+        <v>4.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6690,7 +6695,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 12819-2022</t>
+          <t>A 55897-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6704,10 +6709,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44642</v>
+        <v>45622</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6720,7 +6725,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6763,7 +6768,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 25762-2023</t>
+          <t>A 50577-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6777,10 +6782,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45090</v>
+        <v>45601</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6793,7 +6798,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6836,7 +6841,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 36208-2025</t>
+          <t>A 63778-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6846,14 +6851,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45867</v>
+        <v>45278</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6866,7 +6871,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6909,7 +6914,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 49906-2025</t>
+          <t>A 14536-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6923,10 +6928,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45940</v>
+        <v>46100</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6939,7 +6944,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6982,7 +6987,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 37195-2025</t>
+          <t>A 13530-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6992,14 +6997,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45875</v>
+        <v>45006</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7055,7 +7060,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 49909-2025</t>
+          <t>A 5577-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7069,10 +7074,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45940</v>
+        <v>44960</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7085,7 +7090,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7128,7 +7133,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 32952-2023</t>
+          <t>A 60290-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7142,10 +7147,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45125</v>
+        <v>45642</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7158,7 +7163,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>5.1</v>
+        <v>1.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7201,7 +7206,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 5514-2026</t>
+          <t>A 36208-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7215,10 +7220,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46050</v>
+        <v>45867</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7230,13 +7235,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7279,7 +7279,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 52719-2025</t>
+          <t>A 17527-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7293,10 +7293,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45957</v>
+        <v>46119</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7309,7 +7309,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7352,7 +7352,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 43445-2023</t>
+          <t>A 17524-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7366,10 +7366,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45184</v>
+        <v>46119</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7382,7 +7382,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.1</v>
+        <v>0.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7425,7 +7425,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 52640-2025</t>
+          <t>A 17533-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7439,10 +7439,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45954</v>
+        <v>46120</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7498,7 +7498,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 53275-2025</t>
+          <t>A 17495-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7512,10 +7512,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45958</v>
+        <v>46120</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7571,7 +7571,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 53274-2025</t>
+          <t>A 37195-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7581,14 +7581,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45958</v>
+        <v>45875</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 37098-2023</t>
+          <t>A 17958-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7658,10 +7658,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45155</v>
+        <v>46122</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7673,8 +7673,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>4.8</v>
+        <v>0.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7717,7 +7722,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 54191-2025</t>
+          <t>A 12175-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7731,10 +7736,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45964</v>
+        <v>44998</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7747,7 +7752,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.4</v>
+        <v>4.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7790,7 +7795,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 7592-2026</t>
+          <t>A 18834-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7804,10 +7809,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46061</v>
+        <v>46129</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7820,7 +7825,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7863,7 +7868,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 61312-2023</t>
+          <t>A 18979-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7877,10 +7882,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45264</v>
+        <v>46129</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7893,7 +7898,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7936,7 +7941,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 9738-2026</t>
+          <t>A 48411-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7950,10 +7955,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46072</v>
+        <v>44858</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7966,7 +7971,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8009,7 +8014,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 30904-2022</t>
+          <t>A 62527-2021</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8023,10 +8028,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44767</v>
+        <v>44503</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8039,7 +8044,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>5</v>
+        <v>22.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8082,7 +8087,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 12175-2023</t>
+          <t>A 1949-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8096,10 +8101,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44998</v>
+        <v>45672</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8112,7 +8117,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8155,7 +8160,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 59155-2025</t>
+          <t>A 49997-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8169,10 +8174,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45988</v>
+        <v>45943</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8185,7 +8190,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8228,7 +8233,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 8953-2023</t>
+          <t>A 6913-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8242,10 +8247,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44979</v>
+        <v>44967</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8258,7 +8263,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8301,7 +8306,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 246-2025</t>
+          <t>A 62541-2021</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8315,10 +8320,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45660</v>
+        <v>44503</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8331,7 +8336,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8374,7 +8379,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 14536-2026</t>
+          <t>A 15374-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8388,10 +8393,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46100</v>
+        <v>45747</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8404,7 +8409,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8447,7 +8452,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 7760-2025</t>
+          <t>A 20614-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8461,10 +8466,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45706</v>
+        <v>45776</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8477,7 +8482,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>8.300000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8520,7 +8525,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 2086-2025</t>
+          <t>A 41937-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8534,10 +8539,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45672</v>
+        <v>45903</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8593,7 +8598,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 62527-2021</t>
+          <t>A 24234-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8607,10 +8612,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44503</v>
+        <v>45797</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8623,7 +8628,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>22.6</v>
+        <v>0.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8666,7 +8671,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 17533-2026</t>
+          <t>A 21017-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8680,10 +8685,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46120</v>
+        <v>46144</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8696,7 +8701,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8739,7 +8744,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 17527-2026</t>
+          <t>A 54582-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8753,10 +8758,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46119</v>
+        <v>45233</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8769,7 +8774,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>4.4</v>
+        <v>0.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8812,7 +8817,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 17495-2026</t>
+          <t>A 12819-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8826,10 +8831,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46120</v>
+        <v>44642</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8842,7 +8847,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8885,7 +8890,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 17524-2026</t>
+          <t>A 58393-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8895,14 +8900,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46119</v>
+        <v>44901</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8915,7 +8920,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.2</v>
+        <v>2.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8958,7 +8963,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 17958-2026</t>
+          <t>A 11949-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8972,10 +8977,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46122</v>
+        <v>44994</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8987,13 +8992,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9036,7 +9036,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 60290-2024</t>
+          <t>A 33209-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9050,10 +9050,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45642</v>
+        <v>45127</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9066,7 +9066,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9109,7 +9109,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 35112-2024</t>
+          <t>A 61405-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9123,10 +9123,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45529</v>
+        <v>46001</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9138,8 +9138,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>1.6</v>
+        <v>6.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9182,7 +9187,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 19759-2024</t>
+          <t>A 29433-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9196,10 +9201,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45432</v>
+        <v>45824</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9212,7 +9217,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9255,7 +9260,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 18834-2026</t>
+          <t>A 8936-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9269,10 +9274,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46129</v>
+        <v>46069</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9285,7 +9290,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9328,7 +9333,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 18979-2026</t>
+          <t>A 8626-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9342,10 +9347,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46129</v>
+        <v>45355</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9358,7 +9363,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.8</v>
+        <v>6.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9401,7 +9406,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 56413-2024</t>
+          <t>A 44849-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9415,10 +9420,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45623</v>
+        <v>45574</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9431,7 +9436,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9474,7 +9479,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 1949-2025</t>
+          <t>A 62551-2021</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9488,10 +9493,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45672</v>
+        <v>44503</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9504,7 +9509,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9547,7 +9552,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 696-2025</t>
+          <t>A 49906-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9561,10 +9566,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45665</v>
+        <v>45940</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9577,7 +9582,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9620,7 +9625,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 34779-2023</t>
+          <t>A 11795-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9634,10 +9639,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45141</v>
+        <v>45375</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9650,7 +9655,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9693,7 +9698,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 36835-2024</t>
+          <t>A 35047-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9707,10 +9712,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45538</v>
+        <v>45527</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9722,13 +9727,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9771,7 +9771,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 58393-2022</t>
+          <t>A 39800-2022</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9781,14 +9781,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44901</v>
+        <v>44819</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9844,7 +9844,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 49997-2025</t>
+          <t>A 49909-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9858,10 +9858,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45943</v>
+        <v>45940</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9917,7 +9917,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 2872-2023</t>
+          <t>A 30484-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9931,10 +9931,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44945</v>
+        <v>45111</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9947,7 +9947,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9990,7 +9990,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 15374-2025</t>
+          <t>A 24279-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10004,10 +10004,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45747</v>
+        <v>46169</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1</v>
+        <v>11.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10063,7 +10063,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 6913-2023</t>
+          <t>A 24736-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10077,10 +10077,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44967</v>
+        <v>46171</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10092,8 +10092,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10136,7 +10141,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 11949-2023</t>
+          <t>A 35087-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10150,10 +10155,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44994</v>
+        <v>45527</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10166,7 +10171,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10209,7 +10214,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 54582-2023</t>
+          <t>A 35112-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10223,10 +10228,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45233</v>
+        <v>45529</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10239,7 +10244,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10282,7 +10287,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 54279-2023</t>
+          <t>A 61312-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10296,10 +10301,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45232</v>
+        <v>45264</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10312,7 +10317,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10355,7 +10360,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 41937-2025</t>
+          <t>A 33654-2022</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10369,10 +10374,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45903</v>
+        <v>44789</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10385,7 +10390,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10428,7 +10433,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 36816-2024</t>
+          <t>A 25814-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10442,10 +10447,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45538</v>
+        <v>46178</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10457,13 +10462,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10506,7 +10506,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 55984-2024</t>
+          <t>A 26148-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10520,10 +10520,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45623</v>
+        <v>46181</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10579,7 +10579,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 35047-2024</t>
+          <t>A 53275-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10593,10 +10593,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45527</v>
+        <v>45958</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10609,7 +10609,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10652,7 +10652,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 25322-2024</t>
+          <t>A 246-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10666,10 +10666,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45462</v>
+        <v>45660</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10725,7 +10725,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 20614-2025</t>
+          <t>A 52640-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10739,10 +10739,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45776</v>
+        <v>45954</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10755,7 +10755,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10798,7 +10798,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 24234-2025</t>
+          <t>A 53274-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10812,10 +10812,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45797</v>
+        <v>45958</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10828,7 +10828,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10871,7 +10871,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 31596-2024</t>
+          <t>A 52719-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10885,10 +10885,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45506</v>
+        <v>45957</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10900,13 +10900,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>4.3</v>
+        <v>1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10949,7 +10944,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 52999-2023</t>
+          <t>A 48301-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10963,10 +10958,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45226</v>
+        <v>45590</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10979,7 +10974,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11022,7 +11017,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 21017-2026</t>
+          <t>A 30399-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11036,10 +11031,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46144</v>
+        <v>45111</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11052,7 +11047,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11095,7 +11090,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 53273-2023</t>
+          <t>A 60465-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11105,14 +11100,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45229</v>
+        <v>45643</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11125,7 +11120,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>6.3</v>
+        <v>0.8</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11168,7 +11163,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 24759-2023</t>
+          <t>A 25322-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11182,10 +11177,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45084</v>
+        <v>45462</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11198,7 +11193,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11241,7 +11236,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 61405-2025</t>
+          <t>A 35202-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11255,10 +11250,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46001</v>
+        <v>45145</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11270,13 +11265,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I137" t="n">
-        <v>6.6</v>
+        <v>11.1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11319,7 +11309,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 29433-2025</t>
+          <t>A 31596-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11333,10 +11323,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45824</v>
+        <v>45506</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11348,8 +11338,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11392,7 +11387,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 52853-2023</t>
+          <t>A 40257-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11406,10 +11401,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45226</v>
+        <v>45169</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11422,7 +11417,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11465,7 +11460,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 8936-2026</t>
+          <t>A 27552-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11479,10 +11474,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46069</v>
+        <v>46190</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11495,7 +11490,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>3</v>
+        <v>5.3</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11538,7 +11533,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 7212-2025</t>
+          <t>A 19759-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11552,10 +11547,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45702</v>
+        <v>45432</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11568,7 +11563,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11611,7 +11606,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 24279-2026</t>
+          <t>A 56542-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11621,14 +11616,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46169</v>
+        <v>45625</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11641,7 +11636,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>11.7</v>
+        <v>0.9</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11684,7 +11679,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 32395-2023</t>
+          <t>A 28056-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11698,10 +11693,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45120</v>
+        <v>46195</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11714,7 +11709,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11757,7 +11752,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 6080-2023</t>
+          <t>A 28068-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11767,14 +11762,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44964</v>
+        <v>46195</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11787,7 +11782,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11830,7 +11825,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 35202-2023</t>
+          <t>A 24759-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11844,10 +11839,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45145</v>
+        <v>45084</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11860,7 +11855,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>11.1</v>
+        <v>2.9</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11903,7 +11898,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 24736-2026</t>
+          <t>A 54191-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11917,10 +11912,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46171</v>
+        <v>45964</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11932,13 +11927,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I146" t="n">
-        <v>3.8</v>
+        <v>0.4</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11981,7 +11971,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 5577-2023</t>
+          <t>A 28309-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11995,10 +11985,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44960</v>
+        <v>46196</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12011,7 +12001,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12054,7 +12044,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 33654-2022</t>
+          <t>A 32923-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12068,10 +12058,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44789</v>
+        <v>46244</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12084,7 +12074,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12127,7 +12117,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 30484-2023</t>
+          <t>A 32944-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12141,10 +12131,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45111</v>
+        <v>46244</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12157,7 +12147,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.2</v>
+        <v>1.7</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12200,7 +12190,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 8950-2024</t>
+          <t>A 37169-2022</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12214,10 +12204,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45357</v>
+        <v>44806</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12230,7 +12220,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.6</v>
+        <v>17.4</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12273,7 +12263,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 46876-2022</t>
+          <t>A 60118-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12287,10 +12277,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44851</v>
+        <v>45642</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12303,7 +12293,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>7.5</v>
+        <v>0.6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12346,7 +12336,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 13522-2023</t>
+          <t>A 53769-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12360,10 +12350,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45006</v>
+        <v>45615</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12376,7 +12366,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12419,7 +12409,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 25814-2026</t>
+          <t>A 696-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12433,10 +12423,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46178</v>
+        <v>45665</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12449,7 +12439,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12492,7 +12482,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 56419-2024</t>
+          <t>A 60642-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12502,14 +12492,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45623</v>
+        <v>45260</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12522,7 +12512,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>5.6</v>
+        <v>1.3</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12565,7 +12555,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 8626-2024</t>
+          <t>A 33984-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12575,14 +12565,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45355</v>
+        <v>46252</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12595,7 +12585,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>6.4</v>
+        <v>2.9</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12638,7 +12628,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 60112-2024</t>
+          <t>A 44308-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12652,10 +12642,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45642</v>
+        <v>45188</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12668,7 +12658,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12711,7 +12701,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 31605-2024</t>
+          <t>A 34112-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12725,10 +12715,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45506</v>
+        <v>46253</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12740,13 +12730,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I157" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12789,7 +12774,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 26148-2026</t>
+          <t>A 54279-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12803,10 +12788,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46181</v>
+        <v>45232</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12819,7 +12804,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12862,7 +12847,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 60118-2024</t>
+          <t>A 7212-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12876,10 +12861,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45642</v>
+        <v>45702</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12892,7 +12877,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12935,7 +12920,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 62551-2021</t>
+          <t>A 8953-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12949,10 +12934,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44503</v>
+        <v>44979</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12965,7 +12950,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13008,7 +12993,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 56542-2024</t>
+          <t>A 59644-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13018,14 +13003,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45625</v>
+        <v>45254</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13038,7 +13023,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13081,7 +13066,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 53814-2024</t>
+          <t>A 59155-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13095,10 +13080,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45615</v>
+        <v>45988</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13111,7 +13096,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13154,7 +13139,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 27552-2026</t>
+          <t>A 6080-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13164,14 +13149,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46190</v>
+        <v>44964</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13184,7 +13169,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>5.3</v>
+        <v>1.9</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13227,7 +13212,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 10524-2024</t>
+          <t>A 36716-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13241,10 +13226,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45366</v>
+        <v>46272</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13257,7 +13242,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13300,7 +13285,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 9422-2024</t>
+          <t>A 59010-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13314,10 +13299,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45359</v>
+        <v>45635</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13330,7 +13315,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13373,7 +13358,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 28068-2026</t>
+          <t>A 31902-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13387,10 +13372,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46195</v>
+        <v>46231</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13403,7 +13388,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13446,7 +13431,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 28056-2026</t>
+          <t>A 36878-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13460,10 +13445,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46195</v>
+        <v>46273</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13476,7 +13461,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13519,7 +13504,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 45608-2022</t>
+          <t>A 31897-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13533,10 +13518,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44845</v>
+        <v>46231</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13549,7 +13534,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>17</v>
+        <v>1.5</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13592,7 +13577,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 28309-2026</t>
+          <t>A 31899-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13606,10 +13591,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46196</v>
+        <v>46231</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13622,7 +13607,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13665,7 +13650,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 58672-2022</t>
+          <t>A 31826-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13679,10 +13664,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44902</v>
+        <v>46230</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13695,7 +13680,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13738,7 +13723,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 55897-2024</t>
+          <t>A 58620-2022</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13752,10 +13737,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45622</v>
+        <v>44902</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13768,7 +13753,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13811,7 +13796,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 32923-2026</t>
+          <t>A 37997-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13825,10 +13810,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46244</v>
+        <v>46280</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13841,7 +13826,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13884,7 +13869,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 32944-2026</t>
+          <t>A 37994-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13898,10 +13883,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46244</v>
+        <v>46280</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13914,7 +13899,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13957,7 +13942,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 41163-2023</t>
+          <t>A 38009-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13971,10 +13956,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45174</v>
+        <v>46280</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13987,7 +13972,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>3.2</v>
+        <v>0.6</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14030,7 +14015,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 33984-2026</t>
+          <t>A 32497-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14040,14 +14025,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46252</v>
+        <v>46239</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14059,8 +14044,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I175" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14103,7 +14093,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 34112-2026</t>
+          <t>A 34779-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14117,10 +14107,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46253</v>
+        <v>45141</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14133,7 +14123,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14176,7 +14166,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 40257-2023</t>
+          <t>A 32504-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14190,10 +14180,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45169</v>
+        <v>46239</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14205,8 +14195,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I177" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14249,7 +14244,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 36622-2023</t>
+          <t>A 60112-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14263,10 +14258,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45153</v>
+        <v>45642</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14279,7 +14274,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14322,7 +14317,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 62541-2021</t>
+          <t>A 34936-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14336,10 +14331,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44503</v>
+        <v>46259</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14352,7 +14347,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>2.3</v>
+        <v>7.4</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14395,7 +14390,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 28850-2024</t>
+          <t>A 34941-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14409,10 +14404,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45478</v>
+        <v>46259</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14425,7 +14420,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14468,7 +14463,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 44849-2024</t>
+          <t>A 37946-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14482,10 +14477,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45574</v>
+        <v>46280</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14498,7 +14493,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14541,7 +14536,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 59644-2023</t>
+          <t>A 32477-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14555,10 +14550,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45254</v>
+        <v>46239</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14570,8 +14565,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I182" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14614,7 +14614,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 56365-2024</t>
+          <t>A 34945-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14628,10 +14628,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45625</v>
+        <v>46259</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14644,7 +14644,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>0.6</v>
+        <v>6.2</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14687,7 +14687,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 6940-2024</t>
+          <t>A 53279-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14697,14 +14697,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45343</v>
+        <v>45229</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 40291-2024</t>
+          <t>A 6102-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14774,10 +14774,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45554</v>
+        <v>44964</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14790,7 +14790,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14833,7 +14833,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 33209-2023</t>
+          <t>A 43460-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14847,10 +14847,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45127</v>
+        <v>45568</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14863,7 +14863,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14906,7 +14906,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 53764-2024</t>
+          <t>A 13522-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14920,10 +14920,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45615</v>
+        <v>45006</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14936,7 +14936,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14979,7 +14979,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 44308-2023</t>
+          <t>A 25762-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14993,10 +14993,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45188</v>
+        <v>45090</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15009,7 +15009,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15052,7 +15052,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 13530-2023</t>
+          <t>A 2872-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15066,10 +15066,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45006</v>
+        <v>44945</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15125,7 +15125,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 36878-2026</t>
+          <t>A 46876-2022</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15139,10 +15139,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46273</v>
+        <v>44851</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15155,7 +15155,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.4</v>
+        <v>7.5</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15198,7 +15198,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 35087-2024</t>
+          <t>A 1455-2025</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45527</v>
+        <v>45670</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15228,7 +15228,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15271,7 +15271,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 36716-2026</t>
+          <t>A 48346-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15285,10 +15285,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46272</v>
+        <v>45590</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15301,7 +15301,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15344,7 +15344,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 53769-2024</t>
+          <t>A 5514-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15358,10 +15358,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45615</v>
+        <v>46050</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15373,8 +15373,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I193" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15417,7 +15422,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 6102-2023</t>
+          <t>A 36835-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15431,10 +15436,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44964</v>
+        <v>45538</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15446,8 +15451,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I194" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15490,7 +15500,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 31826-2026</t>
+          <t>A 32952-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15504,10 +15514,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46230</v>
+        <v>45125</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15520,7 +15530,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0.8</v>
+        <v>5.1</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15563,7 +15573,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 34936-2026</t>
+          <t>A 7592-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15577,10 +15587,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46259</v>
+        <v>46061</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15593,7 +15603,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>7.4</v>
+        <v>1.1</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15636,7 +15646,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 18768-2024</t>
+          <t>A 2086-2025</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15650,10 +15660,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45426</v>
+        <v>45672</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15666,7 +15676,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15709,7 +15719,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 56740-2023</t>
+          <t>A 30904-2022</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15723,10 +15733,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45244</v>
+        <v>44767</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15739,7 +15749,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15782,7 +15792,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 31897-2026</t>
+          <t>A 56740-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15796,10 +15806,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46231</v>
+        <v>45244</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15812,7 +15822,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15855,7 +15865,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 31899-2026</t>
+          <t>A 52853-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15869,10 +15879,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46231</v>
+        <v>45226</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15885,7 +15895,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15928,7 +15938,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 31902-2026</t>
+          <t>A 55974-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15942,10 +15952,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46231</v>
+        <v>45623</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15958,7 +15968,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16001,7 +16011,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 43460-2024</t>
+          <t>A 53764-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16015,10 +16025,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45568</v>
+        <v>45615</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16031,7 +16041,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16074,7 +16084,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 59010-2024</t>
+          <t>A 41163-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16088,10 +16098,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45635</v>
+        <v>45174</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16104,7 +16114,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16147,7 +16157,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 37994-2026</t>
+          <t>A 7223-2025</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16161,10 +16171,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46280</v>
+        <v>45702</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16177,7 +16187,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16220,7 +16230,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 34941-2026</t>
+          <t>A 56365-2024</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16234,10 +16244,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46259</v>
+        <v>45625</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16250,7 +16260,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>9.300000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16293,7 +16303,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 37997-2026</t>
+          <t>A 52999-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16307,10 +16317,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46280</v>
+        <v>45226</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16323,7 +16333,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16366,7 +16376,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 32497-2026</t>
+          <t>A 7760-2025</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16380,10 +16390,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46239</v>
+        <v>45706</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16395,13 +16405,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I207" t="n">
-        <v>1.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16444,7 +16449,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 34945-2026</t>
+          <t>A 56413-2024</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16458,10 +16463,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46259</v>
+        <v>45623</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16474,7 +16479,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>6.2</v>
+        <v>3.5</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16517,7 +16522,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 32504-2026</t>
+          <t>A 56373-2024</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16531,10 +16536,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46239</v>
+        <v>45625</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16544,11 +16549,6 @@
       <c r="G209" t="inlineStr">
         <is>
           <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I209" t="n">
@@ -16595,7 +16595,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 32477-2026</t>
+          <t>A 61817-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16609,10 +16609,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46239</v>
+        <v>45649</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16624,13 +16624,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I210" t="n">
-        <v>2.4</v>
+        <v>4.6</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16673,7 +16668,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 38009-2026</t>
+          <t>A 9973-2024</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16687,10 +16682,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46280</v>
+        <v>45363</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16703,7 +16698,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>0.6</v>
+        <v>4.7</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16746,7 +16741,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 61817-2024</t>
+          <t>A 53805-2024</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16760,10 +16755,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45649</v>
+        <v>45615</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16776,7 +16771,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>4.6</v>
+        <v>1.1</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16819,7 +16814,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 9973-2024</t>
+          <t>A 11393-2025</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16833,10 +16828,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45363</v>
+        <v>45726</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16849,7 +16844,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>4.7</v>
+        <v>0.2</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16892,7 +16887,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 56373-2024</t>
+          <t>A 11563-2025</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16902,14 +16897,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45625</v>
+        <v>45727</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16921,8 +16916,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I214" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16965,7 +16965,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 53805-2024</t>
+          <t>A 53275-2023</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16975,14 +16975,14 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45615</v>
+        <v>45229</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16995,7 +16995,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.1</v>
+        <v>8.5</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17038,7 +17038,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 11393-2025</t>
+          <t>A 44104-2024</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17052,10 +17052,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45726</v>
+        <v>45572</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17068,7 +17068,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>0.2</v>
+        <v>2.4</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17128,7 +17128,7 @@
         <v>45797</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17184,7 +17184,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 53275-2023</t>
+          <t>A 19840-2025</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17198,10 +17198,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45229</v>
+        <v>45771</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17214,7 +17214,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>8.5</v>
+        <v>0.2</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17257,7 +17257,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 44104-2024</t>
+          <t>A 58420-2023</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17267,14 +17267,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45572</v>
+        <v>45250</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17287,7 +17287,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17330,7 +17330,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 11563-2025</t>
+          <t>A 36945-2024</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17340,14 +17340,14 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45727</v>
+        <v>45538</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17365,7 +17365,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17408,24 +17408,24 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>S 3762-2024</t>
+          <t>A 17892-2025</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45558</v>
+        <v>45758</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17438,7 +17438,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
         <v>44656</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17559,7 +17559,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>S 320-2025</t>
+          <t>S 3762-2024</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17573,10 +17573,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45688</v>
+        <v>45558</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17632,7 +17632,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>S 319-2025</t>
+          <t>S 320-2025</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17649,7 +17649,7 @@
         <v>45688</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17662,118 +17662,191 @@
         </is>
       </c>
       <c r="I224" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J224" t="n">
+        <v>0</v>
+      </c>
+      <c r="K224" t="n">
+        <v>0</v>
+      </c>
+      <c r="L224" t="n">
+        <v>0</v>
+      </c>
+      <c r="M224" t="n">
+        <v>0</v>
+      </c>
+      <c r="N224" t="n">
+        <v>0</v>
+      </c>
+      <c r="O224" t="n">
+        <v>0</v>
+      </c>
+      <c r="P224" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q224" t="n">
+        <v>0</v>
+      </c>
+      <c r="R224" t="n">
+        <v>0</v>
+      </c>
+      <c r="S224" t="n">
+        <v>0</v>
+      </c>
+      <c r="T224" t="n">
+        <v>0</v>
+      </c>
+      <c r="U224" t="n">
+        <v>0</v>
+      </c>
+      <c r="V224" s="2" t="inlineStr"/>
+    </row>
+    <row r="225" ht="15" customHeight="1">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>S 319-2025</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D225" s="1" t="n">
+        <v>45688</v>
+      </c>
+      <c r="E225" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I225" t="n">
         <v>2.9</v>
       </c>
-      <c r="J224" t="n">
-        <v>0</v>
-      </c>
-      <c r="K224" t="n">
-        <v>0</v>
-      </c>
-      <c r="L224" t="n">
-        <v>0</v>
-      </c>
-      <c r="M224" t="n">
-        <v>0</v>
-      </c>
-      <c r="N224" t="n">
-        <v>0</v>
-      </c>
-      <c r="O224" t="n">
-        <v>0</v>
-      </c>
-      <c r="P224" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
-      <c r="R224" t="n">
-        <v>0</v>
-      </c>
-      <c r="S224" t="n">
-        <v>0</v>
-      </c>
-      <c r="T224" t="n">
-        <v>0</v>
-      </c>
-      <c r="U224" t="n">
-        <v>0</v>
-      </c>
-      <c r="V224" s="2" t="inlineStr"/>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
+      <c r="J225" t="n">
+        <v>0</v>
+      </c>
+      <c r="K225" t="n">
+        <v>0</v>
+      </c>
+      <c r="L225" t="n">
+        <v>0</v>
+      </c>
+      <c r="M225" t="n">
+        <v>0</v>
+      </c>
+      <c r="N225" t="n">
+        <v>0</v>
+      </c>
+      <c r="O225" t="n">
+        <v>0</v>
+      </c>
+      <c r="P225" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q225" t="n">
+        <v>0</v>
+      </c>
+      <c r="R225" t="n">
+        <v>0</v>
+      </c>
+      <c r="S225" t="n">
+        <v>0</v>
+      </c>
+      <c r="T225" t="n">
+        <v>0</v>
+      </c>
+      <c r="U225" t="n">
+        <v>0</v>
+      </c>
+      <c r="V225" s="2" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
         <is>
           <t>S 2767-2022</t>
         </is>
       </c>
-      <c r="B225" t="inlineStr">
+      <c r="B226" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C225" t="inlineStr">
+      <c r="C226" t="inlineStr">
         <is>
           <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
-      <c r="D225" s="1" t="n">
+      <c r="D226" s="1" t="n">
         <v>44705</v>
       </c>
-      <c r="E225" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I225" t="n">
+      <c r="E226" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I226" t="n">
         <v>0.1</v>
       </c>
-      <c r="J225" t="n">
-        <v>0</v>
-      </c>
-      <c r="K225" t="n">
-        <v>0</v>
-      </c>
-      <c r="L225" t="n">
-        <v>0</v>
-      </c>
-      <c r="M225" t="n">
-        <v>0</v>
-      </c>
-      <c r="N225" t="n">
-        <v>0</v>
-      </c>
-      <c r="O225" t="n">
-        <v>0</v>
-      </c>
-      <c r="P225" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
-      <c r="R225" t="n">
-        <v>0</v>
-      </c>
-      <c r="S225" t="n">
-        <v>0</v>
-      </c>
-      <c r="T225" t="n">
-        <v>0</v>
-      </c>
-      <c r="U225" t="n">
-        <v>0</v>
-      </c>
-      <c r="V225" s="2" t="inlineStr"/>
+      <c r="J226" t="n">
+        <v>0</v>
+      </c>
+      <c r="K226" t="n">
+        <v>0</v>
+      </c>
+      <c r="L226" t="n">
+        <v>0</v>
+      </c>
+      <c r="M226" t="n">
+        <v>0</v>
+      </c>
+      <c r="N226" t="n">
+        <v>0</v>
+      </c>
+      <c r="O226" t="n">
+        <v>0</v>
+      </c>
+      <c r="P226" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q226" t="n">
+        <v>0</v>
+      </c>
+      <c r="R226" t="n">
+        <v>0</v>
+      </c>
+      <c r="S226" t="n">
+        <v>0</v>
+      </c>
+      <c r="T226" t="n">
+        <v>0</v>
+      </c>
+      <c r="U226" t="n">
+        <v>0</v>
+      </c>
+      <c r="V226" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt LIDKÖPING.xlsx
+++ b/Översikt LIDKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>44631</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>46006</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 24727-2026</t>
+          <t>A 6898-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46171</v>
+        <v>44967</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -861,25 +861,20 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I4" t="n">
-        <v>6.9</v>
+        <v>18</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -891,21 +886,139 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
       </c>
       <c r="T4" t="n">
+        <v>5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>5</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Grönsångare
+Göktyta
+Älg
+Buskskvätta
+Röd glada</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 6898-2023 artfynd.xlsx", "A 6898-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 6898-2023 karta.png", "A 6898-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 6898-2023 georefererad karta.tif", "A 6898-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 6898-2023 FSC-klagomål.docx", "A 6898-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 6898-2023 FSC-klagomål mail.docx", "A 6898-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 6898-2023 tillsynsbegäran.docx", "A 6898-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 6898-2023 tillsynsbegäran mail.docx", "A 6898-2023")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 6898-2023 prioriterade fågelarter.docx", "A 6898-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 24727-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="n">
         <v>8</v>
       </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Veckticka
@@ -914,160 +1027,47 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 24727-2026 artfynd.xlsx", "A 24727-2026")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 24727-2026 karta.png", "A 24727-2026")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 24727-2026 georefererad karta.tif", "A 24727-2026")</f>
         <v/>
       </c>
-      <c r="Z4">
+      <c r="Z5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/knärot/A 24727-2026 karta knärot.png", "A 24727-2026")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 24727-2026 FSC-klagomål.docx", "A 24727-2026")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 24727-2026 FSC-klagomål mail.docx", "A 24727-2026")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 24727-2026 tillsynsbegäran.docx", "A 24727-2026")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 24727-2026 tillsynsbegäran mail.docx", "A 24727-2026")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 24727-2026 prioriterade fågelarter.docx", "A 24727-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 6898-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>44967</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>18</v>
-      </c>
-      <c r="J5" t="n">
-        <v>4</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>3</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>5</v>
-      </c>
-      <c r="T5" t="n">
-        <v>5</v>
-      </c>
-      <c r="U5" t="n">
-        <v>5</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Grönsångare
-Göktyta
-Älg
-Buskskvätta
-Röd glada</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 6898-2023 artfynd.xlsx", "A 6898-2023")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 6898-2023 karta.png", "A 6898-2023")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 6898-2023 georefererad karta.tif", "A 6898-2023")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 6898-2023 FSC-klagomål.docx", "A 6898-2023")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 6898-2023 FSC-klagomål mail.docx", "A 6898-2023")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 6898-2023 tillsynsbegäran.docx", "A 6898-2023")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 6898-2023 tillsynsbegäran mail.docx", "A 6898-2023")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 6898-2023 prioriterade fågelarter.docx", "A 6898-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 32280-2022</t>
+          <t>A 28849-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44781</v>
+        <v>45478</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1097,13 +1097,13 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>8.6</v>
+        <v>2.6</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -1136,6 +1136,118 @@
         <v>0</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Talltita
+Grönsiska
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 28849-2024 artfynd.xlsx", "A 28849-2024")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 28849-2024 karta.png", "A 28849-2024")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 28849-2024 georefererad karta.tif", "A 28849-2024")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 28849-2024 FSC-klagomål.docx", "A 28849-2024")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 28849-2024 FSC-klagomål mail.docx", "A 28849-2024")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 28849-2024 tillsynsbegäran.docx", "A 28849-2024")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 28849-2024 tillsynsbegäran mail.docx", "A 28849-2024")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 28849-2024 prioriterade fågelarter.docx", "A 28849-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 32280-2022</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>44781</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Gulsparv
 Nötkråka
@@ -1143,151 +1255,39 @@
 Skogsduva</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 32280-2022 artfynd.xlsx", "A 32280-2022")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 32280-2022 karta.png", "A 32280-2022")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 32280-2022 georefererad karta.tif", "A 32280-2022")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 32280-2022 FSC-klagomål.docx", "A 32280-2022")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 32280-2022 FSC-klagomål mail.docx", "A 32280-2022")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 32280-2022 tillsynsbegäran.docx", "A 32280-2022")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 32280-2022 tillsynsbegäran mail.docx", "A 32280-2022")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 32280-2022 prioriterade fågelarter.docx", "A 32280-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 28849-2024</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45478</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>4</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Talltita
-Grönsiska
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 28849-2024 artfynd.xlsx", "A 28849-2024")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 28849-2024 karta.png", "A 28849-2024")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 28849-2024 georefererad karta.tif", "A 28849-2024")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 28849-2024 FSC-klagomål.docx", "A 28849-2024")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 28849-2024 FSC-klagomål mail.docx", "A 28849-2024")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 28849-2024 tillsynsbegäran.docx", "A 28849-2024")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 28849-2024 tillsynsbegäran mail.docx", "A 28849-2024")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 28849-2024 prioriterade fågelarter.docx", "A 28849-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>46259</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 15219-2024</t>
+          <t>A 4831-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1413,14 +1413,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45400</v>
+        <v>45688</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1433,22 +1433,22 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>6.7</v>
+        <v>1.3</v>
       </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>1</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
       <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>2</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1460,7 +1460,7 @@
         <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1472,148 +1472,148 @@
         <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Skogsalm
+Barkticka</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 4831-2025 artfynd.xlsx", "A 4831-2025")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 4831-2025 karta.png", "A 4831-2025")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 4831-2025 georefererad karta.tif", "A 4831-2025")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 4831-2025 FSC-klagomål.docx", "A 4831-2025")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 4831-2025 FSC-klagomål mail.docx", "A 4831-2025")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 4831-2025 tillsynsbegäran.docx", "A 4831-2025")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 4831-2025 tillsynsbegäran mail.docx", "A 4831-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 15219-2024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45400</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Tårkragskivling
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 15219-2024 artfynd.xlsx", "A 15219-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 15219-2024 karta.png", "A 15219-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 15219-2024 georefererad karta.tif", "A 15219-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 15219-2024 FSC-klagomål.docx", "A 15219-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 15219-2024 FSC-klagomål mail.docx", "A 15219-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 15219-2024 tillsynsbegäran.docx", "A 15219-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 15219-2024 tillsynsbegäran mail.docx", "A 15219-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 4831-2025</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45688</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Skogsalm
-Barkticka</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 4831-2025 artfynd.xlsx", "A 4831-2025")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 4831-2025 karta.png", "A 4831-2025")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 4831-2025 georefererad karta.tif", "A 4831-2025")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 4831-2025 FSC-klagomål.docx", "A 4831-2025")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 4831-2025 FSC-klagomål mail.docx", "A 4831-2025")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 4831-2025 tillsynsbegäran.docx", "A 4831-2025")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 4831-2025 tillsynsbegäran mail.docx", "A 4831-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>45202</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>45898</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>45702</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>44630</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 44680-2023</t>
+          <t>A 10476-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45189</v>
+        <v>44987</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2126,155 +2126,151 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 10476-2023 artfynd.xlsx", "A 10476-2023")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 10476-2023 karta.png", "A 10476-2023")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 10476-2023 georefererad karta.tif", "A 10476-2023")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 10476-2023 FSC-klagomål.docx", "A 10476-2023")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 10476-2023 FSC-klagomål mail.docx", "A 10476-2023")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 10476-2023 tillsynsbegäran.docx", "A 10476-2023")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 10476-2023 tillsynsbegäran mail.docx", "A 10476-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 44680-2023</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45189</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>Trädlärka</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 44680-2023 artfynd.xlsx", "A 44680-2023")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 44680-2023 karta.png", "A 44680-2023")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 44680-2023 georefererad karta.tif", "A 44680-2023")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 44680-2023 FSC-klagomål.docx", "A 44680-2023")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 44680-2023 FSC-klagomål mail.docx", "A 44680-2023")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 44680-2023 tillsynsbegäran.docx", "A 44680-2023")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 44680-2023 tillsynsbegäran mail.docx", "A 44680-2023")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 44680-2023 prioriterade fågelarter.docx", "A 44680-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 61818-2024</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45649</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Rödvingetrast</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 61818-2024 artfynd.xlsx", "A 61818-2024")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 61818-2024 karta.png", "A 61818-2024")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 61818-2024 georefererad karta.tif", "A 61818-2024")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 61818-2024 FSC-klagomål.docx", "A 61818-2024")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 61818-2024 FSC-klagomål mail.docx", "A 61818-2024")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 61818-2024 tillsynsbegäran.docx", "A 61818-2024")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 61818-2024 tillsynsbegäran mail.docx", "A 61818-2024")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 61818-2024 prioriterade fågelarter.docx", "A 61818-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
@@ -2295,7 +2291,7 @@
         <v>44924</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2400,7 +2396,7 @@
         <v>46274</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2492,7 +2488,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 10476-2023</t>
+          <t>A 24352-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2502,14 +2498,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44987</v>
+        <v>45797</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2522,7 +2518,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2558,46 +2554,50 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 10476-2023 artfynd.xlsx", "A 10476-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 24352-2025 artfynd.xlsx", "A 24352-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 10476-2023 karta.png", "A 10476-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 24352-2025 karta.png", "A 24352-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 10476-2023 georefererad karta.tif", "A 10476-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 24352-2025 georefererad karta.tif", "A 24352-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 10476-2023 FSC-klagomål.docx", "A 10476-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 24352-2025 FSC-klagomål.docx", "A 24352-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 10476-2023 FSC-klagomål mail.docx", "A 10476-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 24352-2025 FSC-klagomål mail.docx", "A 24352-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 10476-2023 tillsynsbegäran.docx", "A 10476-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 24352-2025 tillsynsbegäran.docx", "A 24352-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 10476-2023 tillsynsbegäran mail.docx", "A 10476-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 24352-2025 tillsynsbegäran mail.docx", "A 24352-2025")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 24352-2025 prioriterade fågelarter.docx", "A 24352-2025")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 24352-2025</t>
+          <t>A 62629-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2607,14 +2607,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45797</v>
+        <v>44925</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2627,20 +2627,20 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>1</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
@@ -2651,10 +2651,10 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2663,50 +2663,46 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 24352-2025 artfynd.xlsx", "A 24352-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 62629-2022 artfynd.xlsx", "A 62629-2022")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 24352-2025 karta.png", "A 24352-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 62629-2022 karta.png", "A 62629-2022")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 24352-2025 georefererad karta.tif", "A 24352-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 62629-2022 georefererad karta.tif", "A 62629-2022")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 24352-2025 FSC-klagomål.docx", "A 24352-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 62629-2022 FSC-klagomål.docx", "A 62629-2022")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 24352-2025 FSC-klagomål mail.docx", "A 24352-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 62629-2022 FSC-klagomål mail.docx", "A 62629-2022")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 24352-2025 tillsynsbegäran.docx", "A 24352-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 62629-2022 tillsynsbegäran.docx", "A 62629-2022")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 24352-2025 tillsynsbegäran mail.docx", "A 24352-2025")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 24352-2025 prioriterade fågelarter.docx", "A 24352-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 62629-2022 tillsynsbegäran mail.docx", "A 62629-2022")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 62629-2022</t>
+          <t>A 61818-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2720,10 +2716,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44925</v>
+        <v>45649</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2736,19 +2732,19 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.8</v>
+        <v>6.2</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2763,7 +2759,7 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2776,35 +2772,39 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 62629-2022 artfynd.xlsx", "A 62629-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 61818-2024 artfynd.xlsx", "A 61818-2024")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 62629-2022 karta.png", "A 62629-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 61818-2024 karta.png", "A 61818-2024")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 62629-2022 georefererad karta.tif", "A 62629-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 61818-2024 georefererad karta.tif", "A 61818-2024")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 62629-2022 FSC-klagomål.docx", "A 62629-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 61818-2024 FSC-klagomål.docx", "A 61818-2024")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 62629-2022 FSC-klagomål mail.docx", "A 62629-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 61818-2024 FSC-klagomål mail.docx", "A 61818-2024")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 62629-2022 tillsynsbegäran.docx", "A 62629-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 61818-2024 tillsynsbegäran.docx", "A 61818-2024")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 62629-2022 tillsynsbegäran mail.docx", "A 62629-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 61818-2024 tillsynsbegäran mail.docx", "A 61818-2024")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 61818-2024 prioriterade fågelarter.docx", "A 61818-2024")</f>
         <v/>
       </c>
     </row>
@@ -2828,7 +2828,7 @@
         <v>44788</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>44466</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>44831</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>44820</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>44714</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>44566</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>44546</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>44627</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>44627</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>44725</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>44805</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>44705</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>44617</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>44487</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>44487</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>44770</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>44742</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>44806</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         <v>44515</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>44614</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>44747</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 7248-2025</t>
+          <t>A 8124-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4363,10 +4363,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45702</v>
+        <v>44974</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4422,7 +4422,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 53273-2023</t>
+          <t>A 60465-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4432,14 +4432,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45229</v>
+        <v>45643</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>6.3</v>
+        <v>0.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4495,7 +4495,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 6940-2024</t>
+          <t>A 60642-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4505,14 +4505,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45343</v>
+        <v>45260</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4568,7 +4568,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 59068-2023</t>
+          <t>A 48301-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4578,14 +4578,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45252</v>
+        <v>45590</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>6.4</v>
+        <v>1.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4641,7 +4641,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 136-2023</t>
+          <t>A 7247-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4655,10 +4655,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44928</v>
+        <v>45702</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4.5</v>
+        <v>1.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 49755-2022</t>
+          <t>A 30399-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4728,10 +4728,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44859</v>
+        <v>45111</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4787,7 +4787,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 18768-2024</t>
+          <t>A 11795-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4801,10 +4801,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45426</v>
+        <v>45375</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4860,7 +4860,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 9422-2024</t>
+          <t>A 48346-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4874,10 +4874,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45359</v>
+        <v>45590</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4933,7 +4933,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 28850-2024</t>
+          <t>A 49755-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4947,10 +4947,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45478</v>
+        <v>44859</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5006,7 +5006,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 31605-2024</t>
+          <t>A 39800-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5020,10 +5020,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45506</v>
+        <v>44819</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5035,13 +5035,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5084,7 +5079,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 45608-2022</t>
+          <t>A 55974-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5098,10 +5093,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44845</v>
+        <v>45623</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5114,7 +5109,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>17</v>
+        <v>1.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5157,7 +5152,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 37098-2023</t>
+          <t>A 63778-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5167,14 +5162,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45155</v>
+        <v>45278</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5187,7 +5182,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5230,7 +5225,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 36622-2023</t>
+          <t>A 58620-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5244,10 +5239,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45153</v>
+        <v>44902</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5260,7 +5255,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5303,7 +5298,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 36816-2024</t>
+          <t>A 53279-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5313,14 +5308,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45538</v>
+        <v>45229</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5332,13 +5327,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5381,7 +5371,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 8950-2024</t>
+          <t>A 1455-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5395,10 +5385,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45357</v>
+        <v>45670</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5411,7 +5401,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5454,7 +5444,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 10524-2024</t>
+          <t>A 37169-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5468,10 +5458,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45366</v>
+        <v>44806</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5484,7 +5474,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.6</v>
+        <v>17.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5527,7 +5517,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 58672-2022</t>
+          <t>A 136-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5541,10 +5531,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44902</v>
+        <v>44928</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5557,7 +5547,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5600,7 +5590,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 43445-2023</t>
+          <t>A 7223-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5614,10 +5604,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45184</v>
+        <v>45702</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5630,7 +5620,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5673,7 +5663,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 32395-2023</t>
+          <t>A 7248-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5687,10 +5677,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45120</v>
+        <v>45702</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5703,7 +5693,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5746,7 +5736,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 8124-2023</t>
+          <t>A 59068-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5756,14 +5746,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44974</v>
+        <v>45252</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5776,7 +5766,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.5</v>
+        <v>6.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5819,7 +5809,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 40291-2024</t>
+          <t>A 25762-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5833,10 +5823,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45554</v>
+        <v>45090</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5849,7 +5839,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5892,7 +5882,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 29495-2025</t>
+          <t>A 50577-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5906,10 +5896,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45824</v>
+        <v>45601</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5922,7 +5912,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>5.2</v>
+        <v>1.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5965,7 +5955,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 9738-2026</t>
+          <t>A 32952-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5979,10 +5969,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46072</v>
+        <v>45125</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5995,7 +5985,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.4</v>
+        <v>5.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6038,7 +6028,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 31844-2025</t>
+          <t>A 43445-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6052,10 +6042,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45834</v>
+        <v>45184</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6068,7 +6058,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>6.2</v>
+        <v>2.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6111,7 +6101,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 31825-2025</t>
+          <t>A 37098-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6125,10 +6115,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45834</v>
+        <v>45155</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6141,7 +6131,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.2</v>
+        <v>4.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6184,7 +6174,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 32355-2025</t>
+          <t>A 61312-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6198,10 +6188,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45837</v>
+        <v>45264</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6214,7 +6204,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6257,7 +6247,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 7247-2025</t>
+          <t>A 6913-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6271,10 +6261,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45702</v>
+        <v>44967</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6287,7 +6277,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6330,7 +6320,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 53814-2024</t>
+          <t>A 41937-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6344,10 +6334,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45615</v>
+        <v>45903</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6360,7 +6350,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6403,7 +6393,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 55984-2024</t>
+          <t>A 30904-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6417,10 +6407,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45623</v>
+        <v>44767</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6433,7 +6423,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6476,7 +6466,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 26356-2025</t>
+          <t>A 12175-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6490,10 +6480,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45805</v>
+        <v>44998</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6506,7 +6496,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.4</v>
+        <v>4.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6549,7 +6539,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 56419-2024</t>
+          <t>A 48411-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6563,10 +6553,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45623</v>
+        <v>44858</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6579,7 +6569,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>5.6</v>
+        <v>2.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6622,7 +6612,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 59069-2023</t>
+          <t>A 20614-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6632,14 +6622,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45252</v>
+        <v>45776</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6652,7 +6642,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.9</v>
+        <v>0.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6695,7 +6685,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 55897-2024</t>
+          <t>A 24234-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6709,10 +6699,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45622</v>
+        <v>45797</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6725,7 +6715,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6768,7 +6758,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 50577-2024</t>
+          <t>A 8953-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6782,10 +6772,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45601</v>
+        <v>44979</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6841,7 +6831,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 63778-2023</t>
+          <t>A 246-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6851,14 +6841,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45278</v>
+        <v>45660</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6871,7 +6861,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.2</v>
+        <v>1.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6914,7 +6904,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 14536-2026</t>
+          <t>A 12819-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6928,10 +6918,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46100</v>
+        <v>44642</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6944,7 +6934,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6987,7 +6977,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 13530-2023</t>
+          <t>A 7760-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7001,10 +6991,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45006</v>
+        <v>45706</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7017,7 +7007,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7060,7 +7050,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 5577-2023</t>
+          <t>A 21017-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7074,10 +7064,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44960</v>
+        <v>46144</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7090,7 +7080,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7133,7 +7123,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 60290-2024</t>
+          <t>A 2086-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7147,10 +7137,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45642</v>
+        <v>45672</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7163,7 +7153,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7206,7 +7196,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 36208-2025</t>
+          <t>A 62527-2021</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7220,10 +7210,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45867</v>
+        <v>44503</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7236,7 +7226,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.9</v>
+        <v>22.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7279,7 +7269,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 17527-2026</t>
+          <t>A 49906-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7293,10 +7283,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46119</v>
+        <v>45940</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7309,7 +7299,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7352,7 +7342,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 17524-2026</t>
+          <t>A 49909-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7366,10 +7356,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46119</v>
+        <v>45940</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7382,7 +7372,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.2</v>
+        <v>2.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7425,7 +7415,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 17533-2026</t>
+          <t>A 60290-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7439,10 +7429,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46120</v>
+        <v>45642</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7455,7 +7445,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7498,7 +7488,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 17495-2026</t>
+          <t>A 35112-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7512,10 +7502,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46120</v>
+        <v>45529</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7528,7 +7518,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7571,7 +7561,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 37195-2025</t>
+          <t>A 19759-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7581,14 +7571,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45875</v>
+        <v>45432</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7601,7 +7591,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7644,7 +7634,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 17958-2026</t>
+          <t>A 56413-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7658,10 +7648,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46122</v>
+        <v>45623</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7673,13 +7663,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7722,7 +7707,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 12175-2023</t>
+          <t>A 52719-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7736,10 +7721,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44998</v>
+        <v>45957</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7752,7 +7737,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4.3</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7795,7 +7780,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 18834-2026</t>
+          <t>A 1949-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7809,10 +7794,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46129</v>
+        <v>45672</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7825,7 +7810,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7868,7 +7853,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 18979-2026</t>
+          <t>A 696-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7882,10 +7867,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46129</v>
+        <v>45665</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7898,7 +7883,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7941,7 +7926,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 48411-2022</t>
+          <t>A 52640-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7955,10 +7940,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44858</v>
+        <v>45954</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7971,7 +7956,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8014,7 +7999,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 62527-2021</t>
+          <t>A 34779-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8028,10 +8013,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44503</v>
+        <v>45141</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8044,7 +8029,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>22.6</v>
+        <v>3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8087,7 +8072,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 1949-2025</t>
+          <t>A 53275-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8101,10 +8086,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45672</v>
+        <v>45958</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8117,7 +8102,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8160,7 +8145,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 49997-2025</t>
+          <t>A 53274-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8174,10 +8159,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45943</v>
+        <v>45958</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8190,7 +8175,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8233,7 +8218,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 6913-2023</t>
+          <t>A 36835-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8247,10 +8232,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44967</v>
+        <v>45538</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8262,8 +8247,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8306,7 +8296,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 62541-2021</t>
+          <t>A 58393-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8316,14 +8306,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44503</v>
+        <v>44901</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8336,7 +8326,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8379,7 +8369,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 15374-2025</t>
+          <t>A 61405-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8393,10 +8383,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45747</v>
+        <v>46001</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8408,8 +8398,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>6.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8452,7 +8447,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 20614-2025</t>
+          <t>A 54191-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8466,10 +8461,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45776</v>
+        <v>45964</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8482,7 +8477,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8525,7 +8520,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 41937-2025</t>
+          <t>A 2872-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8539,10 +8534,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45903</v>
+        <v>44945</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8555,7 +8550,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8598,7 +8593,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 24234-2025</t>
+          <t>A 11949-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8612,10 +8607,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45797</v>
+        <v>44994</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8628,7 +8623,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8671,7 +8666,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 21017-2026</t>
+          <t>A 54582-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8685,10 +8680,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46144</v>
+        <v>45233</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8701,7 +8696,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8744,7 +8739,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 54582-2023</t>
+          <t>A 54279-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8758,10 +8753,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45233</v>
+        <v>45232</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8774,7 +8769,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8817,7 +8812,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 12819-2022</t>
+          <t>A 36816-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8831,10 +8826,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44642</v>
+        <v>45538</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8846,8 +8841,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8890,7 +8890,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 58393-2022</t>
+          <t>A 55984-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8900,14 +8900,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44901</v>
+        <v>45623</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8920,7 +8920,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8963,7 +8963,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 11949-2023</t>
+          <t>A 35047-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8977,10 +8977,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44994</v>
+        <v>45527</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8993,7 +8993,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9036,7 +9036,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 33209-2023</t>
+          <t>A 29433-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9050,10 +9050,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45127</v>
+        <v>45824</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9066,7 +9066,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9109,7 +9109,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 61405-2025</t>
+          <t>A 25322-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9123,10 +9123,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46001</v>
+        <v>45462</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9138,13 +9138,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>6.6</v>
+        <v>1.3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9187,7 +9182,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 29433-2025</t>
+          <t>A 8936-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9201,10 +9196,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45824</v>
+        <v>46069</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9217,7 +9212,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9260,7 +9255,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 8936-2026</t>
+          <t>A 31596-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9274,10 +9269,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46069</v>
+        <v>45506</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9289,8 +9284,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9333,7 +9333,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 8626-2024</t>
+          <t>A 52999-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9347,10 +9347,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45355</v>
+        <v>45226</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9363,7 +9363,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>6.4</v>
+        <v>0.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9406,7 +9406,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 44849-2024</t>
+          <t>A 59155-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9420,10 +9420,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45574</v>
+        <v>45988</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9436,7 +9436,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9479,7 +9479,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 62551-2021</t>
+          <t>A 53273-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9489,14 +9489,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44503</v>
+        <v>45229</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.9</v>
+        <v>6.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9552,7 +9552,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 49906-2025</t>
+          <t>A 24279-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9566,10 +9566,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45940</v>
+        <v>46169</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>3.2</v>
+        <v>11.7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9625,7 +9625,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 11795-2024</t>
+          <t>A 24759-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9639,10 +9639,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45375</v>
+        <v>45084</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9655,7 +9655,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9698,7 +9698,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 35047-2024</t>
+          <t>A 52853-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9712,10 +9712,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45527</v>
+        <v>45226</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9728,7 +9728,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9771,7 +9771,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 39800-2022</t>
+          <t>A 7212-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9785,10 +9785,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44819</v>
+        <v>45702</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9844,7 +9844,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 49909-2025</t>
+          <t>A 24736-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9858,10 +9858,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45940</v>
+        <v>46171</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9873,8 +9873,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9917,7 +9922,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 30484-2023</t>
+          <t>A 33654-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9931,10 +9936,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45111</v>
+        <v>44789</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9947,7 +9952,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9990,7 +9995,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 24279-2026</t>
+          <t>A 32395-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10004,10 +10009,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46169</v>
+        <v>45120</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10020,7 +10025,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>11.7</v>
+        <v>1.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10063,7 +10068,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 24736-2026</t>
+          <t>A 5514-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10077,10 +10082,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46171</v>
+        <v>46050</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10098,7 +10103,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10141,7 +10146,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 35087-2024</t>
+          <t>A 6080-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10151,14 +10156,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45527</v>
+        <v>44964</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10171,7 +10176,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10214,7 +10219,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 35112-2024</t>
+          <t>A 35202-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10228,10 +10233,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45529</v>
+        <v>45145</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10244,7 +10249,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.6</v>
+        <v>11.1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10287,7 +10292,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 61312-2023</t>
+          <t>A 25814-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10301,10 +10306,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45264</v>
+        <v>46178</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10360,7 +10365,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 33654-2022</t>
+          <t>A 5577-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10374,10 +10379,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44789</v>
+        <v>44960</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10433,7 +10438,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 25814-2026</t>
+          <t>A 7592-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10447,10 +10452,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46178</v>
+        <v>46061</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10463,7 +10468,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10506,7 +10511,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 26148-2026</t>
+          <t>A 30484-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10520,10 +10525,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46181</v>
+        <v>45111</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10536,7 +10541,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10579,7 +10584,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 53275-2025</t>
+          <t>A 8950-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10593,10 +10598,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45958</v>
+        <v>45357</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10609,7 +10614,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10652,7 +10657,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 246-2025</t>
+          <t>A 46876-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10666,10 +10671,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45660</v>
+        <v>44851</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10682,7 +10687,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.7</v>
+        <v>7.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10725,7 +10730,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 52640-2025</t>
+          <t>A 13522-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10739,10 +10744,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45954</v>
+        <v>45006</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10755,7 +10760,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10798,7 +10803,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 53274-2025</t>
+          <t>A 26148-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10812,10 +10817,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45958</v>
+        <v>46181</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10828,7 +10833,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10871,7 +10876,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 52719-2025</t>
+          <t>A 56419-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10885,10 +10890,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45957</v>
+        <v>45623</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10901,7 +10906,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1</v>
+        <v>5.6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10944,7 +10949,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 48301-2024</t>
+          <t>A 8626-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10958,10 +10963,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45590</v>
+        <v>45355</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10974,7 +10979,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.8</v>
+        <v>6.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11017,7 +11022,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 30399-2023</t>
+          <t>A 9738-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11031,10 +11036,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45111</v>
+        <v>46072</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11090,7 +11095,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 60465-2024</t>
+          <t>A 60112-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11104,10 +11109,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45643</v>
+        <v>45642</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11120,7 +11125,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11163,7 +11168,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 25322-2024</t>
+          <t>A 31605-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11177,10 +11182,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45462</v>
+        <v>45506</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11192,8 +11197,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11236,7 +11246,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 35202-2023</t>
+          <t>A 60118-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11250,10 +11260,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45145</v>
+        <v>45642</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11266,7 +11276,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>11.1</v>
+        <v>0.6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11309,7 +11319,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 31596-2024</t>
+          <t>A 62551-2021</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11323,10 +11333,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45506</v>
+        <v>44503</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11338,13 +11348,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>4.3</v>
+        <v>0.9</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11387,7 +11392,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 40257-2023</t>
+          <t>A 56542-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11397,14 +11402,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45169</v>
+        <v>45625</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11417,7 +11422,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11460,7 +11465,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 27552-2026</t>
+          <t>A 53814-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11474,10 +11479,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46190</v>
+        <v>45615</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11490,7 +11495,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>5.3</v>
+        <v>1.8</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11533,7 +11538,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 19759-2024</t>
+          <t>A 27552-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11547,10 +11552,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45432</v>
+        <v>46190</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11563,7 +11568,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.9</v>
+        <v>5.3</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11606,7 +11611,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 56542-2024</t>
+          <t>A 28068-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11616,14 +11621,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45625</v>
+        <v>46195</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11636,7 +11641,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11679,7 +11684,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 28056-2026</t>
+          <t>A 10524-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11693,10 +11698,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46195</v>
+        <v>45366</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11709,7 +11714,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11752,7 +11757,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 28068-2026</t>
+          <t>A 9422-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11766,10 +11771,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46195</v>
+        <v>45359</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11782,7 +11787,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11825,7 +11830,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 24759-2023</t>
+          <t>A 28056-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11839,10 +11844,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45084</v>
+        <v>46195</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11855,7 +11860,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11898,7 +11903,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 54191-2025</t>
+          <t>A 14536-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11912,10 +11917,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45964</v>
+        <v>46100</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11928,7 +11933,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11988,7 +11993,7 @@
         <v>46196</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12044,7 +12049,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 32923-2026</t>
+          <t>A 45608-2022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12058,10 +12063,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46244</v>
+        <v>44845</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12074,7 +12079,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2.1</v>
+        <v>17</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12117,7 +12122,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 32944-2026</t>
+          <t>A 58672-2022</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12131,10 +12136,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46244</v>
+        <v>44902</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12147,7 +12152,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12190,7 +12195,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 37169-2022</t>
+          <t>A 55897-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12204,10 +12209,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44806</v>
+        <v>45622</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12220,7 +12225,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>17.4</v>
+        <v>1.8</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12263,7 +12268,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 60118-2024</t>
+          <t>A 32923-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12277,10 +12282,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45642</v>
+        <v>46244</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12293,7 +12298,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12336,7 +12341,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 53769-2024</t>
+          <t>A 17533-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12350,10 +12355,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45615</v>
+        <v>46120</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12366,7 +12371,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12409,7 +12414,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 696-2025</t>
+          <t>A 17527-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12423,10 +12428,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45665</v>
+        <v>46119</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12439,7 +12444,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12482,7 +12487,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 60642-2023</t>
+          <t>A 17495-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12492,14 +12497,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45260</v>
+        <v>46120</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12512,7 +12517,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12555,7 +12560,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 33984-2026</t>
+          <t>A 17524-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12565,14 +12570,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46252</v>
+        <v>46119</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12585,7 +12590,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2.9</v>
+        <v>0.2</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12628,7 +12633,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 44308-2023</t>
+          <t>A 17958-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12642,10 +12647,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45188</v>
+        <v>46122</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12657,8 +12662,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I156" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12701,7 +12711,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 34112-2026</t>
+          <t>A 32944-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12715,10 +12725,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46253</v>
+        <v>46244</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12731,7 +12741,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12774,7 +12784,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 54279-2023</t>
+          <t>A 18834-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12788,10 +12798,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45232</v>
+        <v>46129</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12804,7 +12814,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12847,7 +12857,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 7212-2025</t>
+          <t>A 18979-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12861,10 +12871,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45702</v>
+        <v>46129</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12877,7 +12887,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12920,7 +12930,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 8953-2023</t>
+          <t>A 41163-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12934,10 +12944,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44979</v>
+        <v>45174</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12950,7 +12960,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12993,7 +13003,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 59644-2023</t>
+          <t>A 49997-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13007,10 +13017,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45254</v>
+        <v>45943</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13023,7 +13033,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13066,7 +13076,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 59155-2025</t>
+          <t>A 40257-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13080,10 +13090,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45988</v>
+        <v>45169</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13096,7 +13106,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13139,7 +13149,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 6080-2023</t>
+          <t>A 36622-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13149,14 +13159,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44964</v>
+        <v>45153</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13169,7 +13179,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13212,7 +13222,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 36716-2026</t>
+          <t>A 15374-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13226,10 +13236,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46272</v>
+        <v>45747</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13242,7 +13252,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13285,7 +13295,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 59010-2024</t>
+          <t>A 62541-2021</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13299,10 +13309,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45635</v>
+        <v>44503</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13315,7 +13325,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13358,7 +13368,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 31902-2026</t>
+          <t>A 28850-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13372,10 +13382,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46231</v>
+        <v>45478</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13388,7 +13398,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13431,7 +13441,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 36878-2026</t>
+          <t>A 44849-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13445,10 +13455,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46273</v>
+        <v>45574</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13461,7 +13471,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13504,7 +13514,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 31897-2026</t>
+          <t>A 59644-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13518,10 +13528,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46231</v>
+        <v>45254</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13534,7 +13544,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13577,7 +13587,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 31899-2026</t>
+          <t>A 56365-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13591,10 +13601,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46231</v>
+        <v>45625</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13607,7 +13617,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13650,7 +13660,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 31826-2026</t>
+          <t>A 33984-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13660,14 +13670,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46230</v>
+        <v>46252</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13680,7 +13690,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13723,7 +13733,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 58620-2022</t>
+          <t>A 6940-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13737,10 +13747,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44902</v>
+        <v>45343</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13753,7 +13763,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13796,7 +13806,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 37997-2026</t>
+          <t>A 40291-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13810,10 +13820,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46280</v>
+        <v>45554</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13826,7 +13836,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13869,7 +13879,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 37994-2026</t>
+          <t>A 34112-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13883,10 +13893,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46280</v>
+        <v>46253</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13899,7 +13909,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13942,7 +13952,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 38009-2026</t>
+          <t>A 33209-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13956,10 +13966,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46280</v>
+        <v>45127</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13972,7 +13982,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14015,7 +14025,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 32497-2026</t>
+          <t>A 53764-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14029,10 +14039,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46239</v>
+        <v>45615</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14044,13 +14054,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I175" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14093,7 +14098,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 34779-2023</t>
+          <t>A 44308-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14107,10 +14112,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45141</v>
+        <v>45188</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14123,7 +14128,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14166,7 +14171,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 32504-2026</t>
+          <t>A 13530-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14180,10 +14185,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46239</v>
+        <v>45006</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14195,13 +14200,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I177" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14244,7 +14244,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 60112-2024</t>
+          <t>A 35087-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14258,10 +14258,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45642</v>
+        <v>45527</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14274,7 +14274,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14317,7 +14317,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 34936-2026</t>
+          <t>A 53769-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14331,10 +14331,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46259</v>
+        <v>45615</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>7.4</v>
+        <v>1.2</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14390,7 +14390,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 34941-2026</t>
+          <t>A 6102-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14404,10 +14404,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46259</v>
+        <v>44964</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14420,7 +14420,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>9.300000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14463,7 +14463,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 37946-2026</t>
+          <t>A 18768-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14477,10 +14477,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46280</v>
+        <v>45426</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14493,7 +14493,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14536,7 +14536,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 32477-2026</t>
+          <t>A 56740-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14550,10 +14550,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46239</v>
+        <v>45244</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14565,13 +14565,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I182" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14614,7 +14609,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 34945-2026</t>
+          <t>A 43460-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14628,10 +14623,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46259</v>
+        <v>45568</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14644,7 +14639,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>6.2</v>
+        <v>0.8</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14687,7 +14682,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 53279-2023</t>
+          <t>A 59010-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14697,14 +14692,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45229</v>
+        <v>45635</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14717,7 +14712,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14760,7 +14755,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 6102-2023</t>
+          <t>A 36878-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14774,10 +14769,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44964</v>
+        <v>46273</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14790,7 +14785,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14833,7 +14828,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 43460-2024</t>
+          <t>A 36716-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14847,10 +14842,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45568</v>
+        <v>46272</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14863,7 +14858,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14906,7 +14901,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 13522-2023</t>
+          <t>A 31826-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14920,10 +14915,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45006</v>
+        <v>46230</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14936,7 +14931,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14979,7 +14974,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 25762-2023</t>
+          <t>A 31897-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14993,10 +14988,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45090</v>
+        <v>46231</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15009,7 +15004,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15052,7 +15047,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 2872-2023</t>
+          <t>A 31899-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15066,10 +15061,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>44945</v>
+        <v>46231</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15082,7 +15077,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15125,7 +15120,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 46876-2022</t>
+          <t>A 61817-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15139,10 +15134,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>44851</v>
+        <v>45649</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15155,7 +15150,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>7.5</v>
+        <v>4.6</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15198,7 +15193,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 1455-2025</t>
+          <t>A 31902-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15212,10 +15207,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45670</v>
+        <v>46231</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15228,7 +15223,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15271,7 +15266,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 48346-2024</t>
+          <t>A 9973-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15285,10 +15280,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45590</v>
+        <v>45363</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15301,7 +15296,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.8</v>
+        <v>4.7</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15344,7 +15339,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 5514-2026</t>
+          <t>A 56373-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15358,10 +15353,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46050</v>
+        <v>45625</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15373,13 +15368,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I193" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15422,7 +15412,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 36835-2024</t>
+          <t>A 37994-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15436,10 +15426,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45538</v>
+        <v>46280</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15451,13 +15441,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I194" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15500,7 +15485,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 32952-2023</t>
+          <t>A 34941-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15514,10 +15499,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45125</v>
+        <v>46259</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15530,7 +15515,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>5.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15573,7 +15558,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 7592-2026</t>
+          <t>A 53805-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15587,10 +15572,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46061</v>
+        <v>45615</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15646,7 +15631,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 2086-2025</t>
+          <t>A 37997-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15660,10 +15645,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45672</v>
+        <v>46280</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15676,7 +15661,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15719,7 +15704,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 30904-2022</t>
+          <t>A 11393-2025</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15733,10 +15718,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>44767</v>
+        <v>45726</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15749,7 +15734,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>5</v>
+        <v>0.2</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15792,7 +15777,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 56740-2023</t>
+          <t>A 34945-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15806,10 +15791,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45244</v>
+        <v>46259</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15822,7 +15807,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15865,7 +15850,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 52853-2023</t>
+          <t>A 38009-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15879,10 +15864,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45226</v>
+        <v>46280</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15895,7 +15880,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15938,7 +15923,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 55974-2024</t>
+          <t>A 34936-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15952,10 +15937,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45623</v>
+        <v>46259</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15968,7 +15953,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.8</v>
+        <v>7.4</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16011,7 +15996,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 53764-2024</t>
+          <t>A 32504-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16025,10 +16010,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45615</v>
+        <v>46239</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16040,8 +16025,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I202" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16084,7 +16074,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 41163-2023</t>
+          <t>A 24356-2025</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16098,10 +16088,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45174</v>
+        <v>45797</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16114,7 +16104,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>3.2</v>
+        <v>0.2</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16157,7 +16147,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 7223-2025</t>
+          <t>A 53275-2023</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16167,14 +16157,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45702</v>
+        <v>45229</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16187,7 +16177,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>3.5</v>
+        <v>8.5</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16230,7 +16220,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 56365-2024</t>
+          <t>A 44104-2024</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16244,10 +16234,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45625</v>
+        <v>45572</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16260,7 +16250,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16303,7 +16293,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 52999-2023</t>
+          <t>A 32477-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16317,10 +16307,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45226</v>
+        <v>46239</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16332,8 +16322,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I206" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16376,7 +16371,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 7760-2025</t>
+          <t>A 11563-2025</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16386,14 +16381,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45706</v>
+        <v>45727</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16405,8 +16400,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I207" t="n">
-        <v>8.300000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16449,7 +16449,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 56413-2024</t>
+          <t>A 32497-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16463,10 +16463,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45623</v>
+        <v>46239</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16478,8 +16478,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I208" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16522,7 +16527,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 56373-2024</t>
+          <t>A 19840-2025</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16532,14 +16537,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45625</v>
+        <v>45771</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16552,7 +16557,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16595,7 +16600,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 61817-2024</t>
+          <t>A 37946-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16609,10 +16614,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45649</v>
+        <v>46280</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16625,7 +16630,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>4.6</v>
+        <v>1.3</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16668,7 +16673,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 9973-2024</t>
+          <t>A 58420-2023</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16678,14 +16683,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45363</v>
+        <v>45250</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16698,7 +16703,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>4.7</v>
+        <v>2.5</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16741,7 +16746,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 53805-2024</t>
+          <t>A 36945-2024</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16755,10 +16760,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45615</v>
+        <v>45538</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16770,8 +16775,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I212" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16814,7 +16824,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 11393-2025</t>
+          <t>A 17892-2025</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16828,10 +16838,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45726</v>
+        <v>45758</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16844,7 +16854,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16887,7 +16897,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 11563-2025</t>
+          <t>A 29495-2025</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16897,14 +16907,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45727</v>
+        <v>45824</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16916,13 +16926,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I214" t="n">
-        <v>0.7</v>
+        <v>5.2</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16965,7 +16970,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 53275-2023</t>
+          <t>A 31844-2025</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16975,14 +16980,14 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45229</v>
+        <v>45834</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16995,7 +17000,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>8.5</v>
+        <v>6.2</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17038,7 +17043,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 44104-2024</t>
+          <t>A 31825-2025</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17052,10 +17057,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45572</v>
+        <v>45834</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17068,7 +17073,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17111,7 +17116,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 24356-2025</t>
+          <t>A 32355-2025</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17125,10 +17130,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45797</v>
+        <v>45837</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17141,7 +17146,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>0.2</v>
+        <v>2.3</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17184,7 +17189,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 19840-2025</t>
+          <t>A 59069-2023</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17198,10 +17203,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45771</v>
+        <v>45252</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17214,7 +17219,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>0.2</v>
+        <v>4.9</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17257,7 +17262,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 58420-2023</t>
+          <t>A 26356-2025</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17267,14 +17272,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45250</v>
+        <v>45805</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17287,7 +17292,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17330,7 +17335,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 36945-2024</t>
+          <t>A 36208-2025</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17344,10 +17349,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45538</v>
+        <v>45867</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17359,13 +17364,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I220" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17408,7 +17408,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 17892-2025</t>
+          <t>A 37195-2025</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17418,14 +17418,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45758</v>
+        <v>45875</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17438,7 +17438,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17481,7 +17481,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>S 1807-2022</t>
+          <t>S 3762-2024</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17491,14 +17491,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Skogsbilväg</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>44656</v>
+        <v>45558</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17510,13 +17510,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I222" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17559,7 +17554,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>S 3762-2024</t>
+          <t>S 1807-2022</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17569,14 +17564,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Skogsbilväg</t>
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45558</v>
+        <v>44656</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17588,8 +17583,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I223" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17649,7 +17649,7 @@
         <v>45688</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>45688</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17795,7 +17795,7 @@
         <v>44705</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>

--- a/Översikt LIDKÖPING.xlsx
+++ b/Översikt LIDKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>44631</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>46006</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>44967</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
         <v>46171</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>45478</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>44781</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>46259</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>45688</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>45400</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>45202</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>45898</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>45702</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>44630</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>44987</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>45189</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>44924</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>46274</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>45797</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>44925</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>45649</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>44788</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>44466</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>44831</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>44820</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>44714</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>44566</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>44546</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>44627</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>44627</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>44725</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>44805</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>44705</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>44617</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>44487</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>44487</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>44770</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>44742</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>44806</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         <v>44515</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>44614</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>44747</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
         <v>44974</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         <v>45643</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>45260</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
         <v>45590</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>45702</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4731,7 +4731,7 @@
         <v>45111</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4804,7 +4804,7 @@
         <v>45375</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4877,7 +4877,7 @@
         <v>45590</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4950,7 +4950,7 @@
         <v>44859</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>44819</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         <v>45623</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>45278</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>44902</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5315,7 +5315,7 @@
         <v>45229</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         <v>45670</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>44806</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5534,7 +5534,7 @@
         <v>44928</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>45702</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         <v>45702</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>45252</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>45090</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5899,7 +5899,7 @@
         <v>45601</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>45125</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         <v>45184</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>45155</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>45264</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
         <v>44967</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         <v>45903</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>44767</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6483,7 +6483,7 @@
         <v>44998</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>44858</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6629,7 +6629,7 @@
         <v>45776</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>45797</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
         <v>44979</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>45660</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>44642</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
         <v>45706</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
         <v>46144</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>45672</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
         <v>44503</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>45940</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7359,7 +7359,7 @@
         <v>45940</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7432,7 +7432,7 @@
         <v>45642</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         <v>45529</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7578,7 +7578,7 @@
         <v>45432</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>45623</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7724,7 +7724,7 @@
         <v>45957</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>45672</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7870,7 +7870,7 @@
         <v>45665</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
         <v>45954</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         <v>45141</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         <v>45958</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         <v>45958</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         <v>45538</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8313,7 +8313,7 @@
         <v>44901</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>46001</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>45964</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         <v>44945</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         <v>44994</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8683,7 +8683,7 @@
         <v>45233</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         <v>45232</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         <v>45538</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
         <v>45623</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>45527</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9053,7 +9053,7 @@
         <v>45824</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>45462</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9199,7 +9199,7 @@
         <v>46069</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9272,7 +9272,7 @@
         <v>45506</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
         <v>45226</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         <v>45988</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9496,7 +9496,7 @@
         <v>45229</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9569,7 +9569,7 @@
         <v>46169</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>45084</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>45226</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         <v>45702</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>46171</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9939,7 +9939,7 @@
         <v>44789</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
         <v>45120</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10085,7 +10085,7 @@
         <v>46050</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10163,7 +10163,7 @@
         <v>44964</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10236,7 +10236,7 @@
         <v>45145</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10309,7 +10309,7 @@
         <v>46178</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10382,7 +10382,7 @@
         <v>44960</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>46061</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>45111</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10601,7 +10601,7 @@
         <v>45357</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10674,7 +10674,7 @@
         <v>44851</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10747,7 +10747,7 @@
         <v>45006</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10820,7 +10820,7 @@
         <v>46181</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10893,7 +10893,7 @@
         <v>45623</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10966,7 +10966,7 @@
         <v>45355</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11039,7 +11039,7 @@
         <v>46072</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11112,7 +11112,7 @@
         <v>45642</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11185,7 +11185,7 @@
         <v>45506</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>45642</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11336,7 +11336,7 @@
         <v>44503</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11409,7 +11409,7 @@
         <v>45625</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11482,7 +11482,7 @@
         <v>45615</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11555,7 +11555,7 @@
         <v>46190</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11628,7 +11628,7 @@
         <v>46195</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11701,7 +11701,7 @@
         <v>45366</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v>45359</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11847,7 +11847,7 @@
         <v>46195</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         <v>46100</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>46196</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12066,7 +12066,7 @@
         <v>44845</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>44902</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
         <v>45622</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12285,7 +12285,7 @@
         <v>46244</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12358,7 +12358,7 @@
         <v>46120</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12431,7 +12431,7 @@
         <v>46119</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12504,7 +12504,7 @@
         <v>46120</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>46119</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12650,7 +12650,7 @@
         <v>46122</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>46244</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12801,7 +12801,7 @@
         <v>46129</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>46129</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12947,7 +12947,7 @@
         <v>45174</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13020,7 +13020,7 @@
         <v>45943</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
         <v>45169</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13166,7 +13166,7 @@
         <v>45153</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13239,7 +13239,7 @@
         <v>45747</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>44503</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13385,7 +13385,7 @@
         <v>45478</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13458,7 +13458,7 @@
         <v>45574</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13531,7 +13531,7 @@
         <v>45254</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13604,7 +13604,7 @@
         <v>45625</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13677,7 +13677,7 @@
         <v>46252</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13750,7 +13750,7 @@
         <v>45343</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>45554</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13896,7 +13896,7 @@
         <v>46253</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13969,7 +13969,7 @@
         <v>45127</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14042,7 +14042,7 @@
         <v>45615</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14115,7 +14115,7 @@
         <v>45188</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14188,7 +14188,7 @@
         <v>45006</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14261,7 +14261,7 @@
         <v>45527</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>45615</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>44964</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>45426</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14553,7 +14553,7 @@
         <v>45244</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>45568</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         <v>45635</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14772,7 +14772,7 @@
         <v>46273</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14845,7 +14845,7 @@
         <v>46272</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14918,7 +14918,7 @@
         <v>46230</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>46231</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15064,7 +15064,7 @@
         <v>46231</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>45649</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15210,7 +15210,7 @@
         <v>46231</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15283,7 +15283,7 @@
         <v>45363</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15356,7 +15356,7 @@
         <v>45625</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>46280</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15502,7 +15502,7 @@
         <v>46259</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15575,7 +15575,7 @@
         <v>45615</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15648,7 +15648,7 @@
         <v>46280</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15721,7 +15721,7 @@
         <v>45726</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15794,7 +15794,7 @@
         <v>46259</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15867,7 +15867,7 @@
         <v>46280</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>46259</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16013,7 +16013,7 @@
         <v>46239</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16091,7 +16091,7 @@
         <v>45797</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>45229</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16237,7 +16237,7 @@
         <v>45572</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16310,7 +16310,7 @@
         <v>46239</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16388,7 +16388,7 @@
         <v>45727</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16466,7 +16466,7 @@
         <v>46239</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>45771</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16617,7 +16617,7 @@
         <v>46280</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16690,7 +16690,7 @@
         <v>45250</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>45538</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16841,7 +16841,7 @@
         <v>45758</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16914,7 +16914,7 @@
         <v>45824</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16987,7 +16987,7 @@
         <v>45834</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17060,7 +17060,7 @@
         <v>45834</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
         <v>45837</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>45252</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17279,7 +17279,7 @@
         <v>45805</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17352,7 +17352,7 @@
         <v>45867</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17425,7 +17425,7 @@
         <v>45875</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17498,7 +17498,7 @@
         <v>45558</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17571,7 +17571,7 @@
         <v>44656</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17649,7 +17649,7 @@
         <v>45688</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>45688</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17795,7 +17795,7 @@
         <v>44705</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>

--- a/Översikt LIDKÖPING.xlsx
+++ b/Översikt LIDKÖPING.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE226"/>
+  <dimension ref="A1:AE225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44631</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>46006</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>44967</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
         <v>46171</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>45478</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 32280-2022</t>
+          <t>A 34942-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44781</v>
+        <v>46259</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>8.6</v>
+        <v>18.1</v>
       </c>
       <c r="J7" t="n">
         <v>3</v>
@@ -1256,42 +1256,42 @@
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 32280-2022 artfynd.xlsx", "A 32280-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 34942-2026 artfynd.xlsx", "A 34942-2026")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 32280-2022 karta.png", "A 32280-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 34942-2026 karta.png", "A 34942-2026")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 32280-2022 georefererad karta.tif", "A 32280-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 34942-2026 georefererad karta.tif", "A 34942-2026")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 32280-2022 FSC-klagomål.docx", "A 32280-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 34942-2026 FSC-klagomål.docx", "A 34942-2026")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 32280-2022 FSC-klagomål mail.docx", "A 32280-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 34942-2026 FSC-klagomål mail.docx", "A 34942-2026")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 32280-2022 tillsynsbegäran.docx", "A 32280-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 34942-2026 tillsynsbegäran.docx", "A 34942-2026")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 32280-2022 tillsynsbegäran mail.docx", "A 32280-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 34942-2026 tillsynsbegäran mail.docx", "A 34942-2026")</f>
         <v/>
       </c>
       <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 32280-2022 prioriterade fågelarter.docx", "A 32280-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 34942-2026 prioriterade fågelarter.docx", "A 34942-2026")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 34942-2026</t>
+          <t>A 32280-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46259</v>
+        <v>44781</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>18.1</v>
+        <v>8.6</v>
       </c>
       <c r="J8" t="n">
         <v>3</v>
@@ -1368,35 +1368,35 @@
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 34942-2026 artfynd.xlsx", "A 34942-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 32280-2022 artfynd.xlsx", "A 32280-2022")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 34942-2026 karta.png", "A 34942-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 32280-2022 karta.png", "A 32280-2022")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 34942-2026 georefererad karta.tif", "A 34942-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 32280-2022 georefererad karta.tif", "A 32280-2022")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 34942-2026 FSC-klagomål.docx", "A 34942-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 32280-2022 FSC-klagomål.docx", "A 32280-2022")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 34942-2026 FSC-klagomål mail.docx", "A 34942-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 32280-2022 FSC-klagomål mail.docx", "A 32280-2022")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 34942-2026 tillsynsbegäran.docx", "A 34942-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 32280-2022 tillsynsbegäran.docx", "A 32280-2022")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 34942-2026 tillsynsbegäran mail.docx", "A 34942-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 32280-2022 tillsynsbegäran mail.docx", "A 32280-2022")</f>
         <v/>
       </c>
       <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 34942-2026 prioriterade fågelarter.docx", "A 34942-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 32280-2022 prioriterade fågelarter.docx", "A 32280-2022")</f>
         <v/>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
         <v>45688</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>45400</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>45202</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>45898</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>45702</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>44630</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>44987</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>45189</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>44924</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>46274</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>45797</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>44925</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>45649</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>44788</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>44466</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>44831</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>44820</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>44714</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>44566</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>44546</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>44627</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>44627</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>44725</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>44805</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>44705</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>44617</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>44487</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>44487</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>44770</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 27329-2022</t>
+          <t>A 37155-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3993,10 +3993,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44742</v>
+        <v>44806</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4052,7 +4052,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 37155-2022</t>
+          <t>A 27329-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4066,10 +4066,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44806</v>
+        <v>44742</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4142,7 +4142,7 @@
         <v>44515</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>44614</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>44747</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
         <v>44974</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         <v>45643</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>45260</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
         <v>45590</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>45702</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4731,7 +4731,7 @@
         <v>45111</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4804,7 +4804,7 @@
         <v>45375</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 48346-2024</t>
+          <t>A 55974-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4874,10 +4874,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45590</v>
+        <v>45623</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4933,7 +4933,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 49755-2022</t>
+          <t>A 48346-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4947,10 +4947,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44859</v>
+        <v>45590</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5023,7 +5023,7 @@
         <v>44819</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 55974-2024</t>
+          <t>A 49755-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5093,10 +5093,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45623</v>
+        <v>44859</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5169,7 +5169,7 @@
         <v>45278</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 58620-2022</t>
+          <t>A 53279-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5235,14 +5235,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44902</v>
+        <v>45229</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5298,7 +5298,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 53279-2023</t>
+          <t>A 58620-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5308,14 +5308,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45229</v>
+        <v>44902</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5328,7 +5328,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5388,7 +5388,7 @@
         <v>45670</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>44806</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5534,7 +5534,7 @@
         <v>44928</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>45702</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         <v>45702</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>45252</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 25762-2023</t>
+          <t>A 50577-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5823,10 +5823,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45090</v>
+        <v>45601</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5882,7 +5882,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 50577-2024</t>
+          <t>A 25762-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45601</v>
+        <v>45090</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5972,7 +5972,7 @@
         <v>45125</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 43445-2023</t>
+          <t>A 37195-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6038,14 +6038,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45184</v>
+        <v>45875</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6101,7 +6101,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 37098-2023</t>
+          <t>A 43445-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6115,10 +6115,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45155</v>
+        <v>45184</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6131,7 +6131,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6174,7 +6174,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 61312-2023</t>
+          <t>A 49997-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6188,10 +6188,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45264</v>
+        <v>45943</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6204,7 +6204,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6247,7 +6247,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 6913-2023</t>
+          <t>A 15374-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6261,10 +6261,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44967</v>
+        <v>45747</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6277,7 +6277,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6320,7 +6320,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 41937-2025</t>
+          <t>A 37098-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6334,10 +6334,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45903</v>
+        <v>45155</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6350,7 +6350,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.3</v>
+        <v>4.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6393,7 +6393,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 30904-2022</t>
+          <t>A 6913-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6407,10 +6407,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44767</v>
+        <v>44967</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6423,7 +6423,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>5</v>
+        <v>1.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 12175-2023</t>
+          <t>A 41937-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6480,10 +6480,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44998</v>
+        <v>45903</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6496,7 +6496,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4.3</v>
+        <v>1.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6539,7 +6539,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 48411-2022</t>
+          <t>A 61312-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6553,10 +6553,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44858</v>
+        <v>45264</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6612,7 +6612,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 20614-2025</t>
+          <t>A 48411-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6626,10 +6626,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45776</v>
+        <v>44858</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6685,7 +6685,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 24234-2025</t>
+          <t>A 30904-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6699,10 +6699,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45797</v>
+        <v>44767</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6715,7 +6715,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.8</v>
+        <v>5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6758,7 +6758,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 8953-2023</t>
+          <t>A 20614-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6772,10 +6772,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44979</v>
+        <v>45776</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6788,7 +6788,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6831,7 +6831,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 246-2025</t>
+          <t>A 12819-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6845,10 +6845,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45660</v>
+        <v>44642</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6904,7 +6904,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 12819-2022</t>
+          <t>A 12175-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6918,10 +6918,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44642</v>
+        <v>44998</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6934,7 +6934,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.5</v>
+        <v>4.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6977,7 +6977,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 7760-2025</t>
+          <t>A 24234-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6991,10 +6991,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45706</v>
+        <v>45797</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>8.300000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7067,7 +7067,7 @@
         <v>46144</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 2086-2025</t>
+          <t>A 61405-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7137,10 +7137,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45672</v>
+        <v>46001</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7152,8 +7152,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>1.3</v>
+        <v>6.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7196,7 +7201,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 62527-2021</t>
+          <t>A 49906-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7210,10 +7215,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44503</v>
+        <v>45940</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7226,7 +7231,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>22.6</v>
+        <v>3.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7269,7 +7274,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 49906-2025</t>
+          <t>A 49909-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7286,7 +7291,7 @@
         <v>45940</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7299,7 +7304,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7342,7 +7347,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 49909-2025</t>
+          <t>A 8953-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7356,10 +7361,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45940</v>
+        <v>44979</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7372,7 +7377,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7415,7 +7420,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 60290-2024</t>
+          <t>A 29433-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7429,10 +7434,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45642</v>
+        <v>45824</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7445,7 +7450,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7488,7 +7493,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 35112-2024</t>
+          <t>A 52719-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7502,10 +7507,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45529</v>
+        <v>45957</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7518,7 +7523,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7561,7 +7566,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 19759-2024</t>
+          <t>A 52640-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7575,10 +7580,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45432</v>
+        <v>45954</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7591,7 +7596,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7634,7 +7639,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 56413-2024</t>
+          <t>A 246-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7648,10 +7653,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45623</v>
+        <v>45660</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7664,7 +7669,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7707,7 +7712,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 52719-2025</t>
+          <t>A 53275-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7721,10 +7726,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7737,7 +7742,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7780,7 +7785,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 1949-2025</t>
+          <t>A 8936-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7794,10 +7799,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45672</v>
+        <v>46069</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7810,7 +7815,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7853,7 +7858,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 696-2025</t>
+          <t>A 54191-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7867,10 +7872,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45665</v>
+        <v>45964</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7883,7 +7888,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7926,7 +7931,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 52640-2025</t>
+          <t>A 7760-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7940,10 +7945,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45954</v>
+        <v>45706</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7956,7 +7961,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7999,7 +8004,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 34779-2023</t>
+          <t>A 2086-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8013,10 +8018,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45141</v>
+        <v>45672</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8029,7 +8034,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8072,7 +8077,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 53275-2025</t>
+          <t>A 62527-2021</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8086,10 +8091,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45958</v>
+        <v>44503</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8102,7 +8107,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.7</v>
+        <v>22.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8145,7 +8150,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 53274-2025</t>
+          <t>A 24279-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8159,10 +8164,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45958</v>
+        <v>46169</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8175,7 +8180,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.6</v>
+        <v>11.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8218,7 +8223,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 36835-2024</t>
+          <t>A 60290-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8232,10 +8237,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45538</v>
+        <v>45642</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8247,13 +8252,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8296,7 +8296,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 58393-2022</t>
+          <t>A 35112-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8306,14 +8306,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44901</v>
+        <v>45529</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8326,7 +8326,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8369,7 +8369,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 61405-2025</t>
+          <t>A 19759-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8383,10 +8383,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46001</v>
+        <v>45432</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8398,13 +8398,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>6.6</v>
+        <v>0.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8447,7 +8442,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 54191-2025</t>
+          <t>A 56413-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8461,10 +8456,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45964</v>
+        <v>45623</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8477,7 +8472,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.4</v>
+        <v>3.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8520,7 +8515,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 2872-2023</t>
+          <t>A 1949-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8534,10 +8529,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44945</v>
+        <v>45672</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8550,7 +8545,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8593,7 +8588,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 11949-2023</t>
+          <t>A 696-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8607,10 +8602,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44994</v>
+        <v>45665</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8623,7 +8618,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8666,7 +8661,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 54582-2023</t>
+          <t>A 34779-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8680,10 +8675,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45233</v>
+        <v>45141</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8696,7 +8691,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8739,7 +8734,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 54279-2023</t>
+          <t>A 24736-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8753,10 +8748,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45232</v>
+        <v>46171</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8768,8 +8763,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>1.3</v>
+        <v>3.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8812,7 +8812,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 36816-2024</t>
+          <t>A 59155-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8826,10 +8826,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45538</v>
+        <v>45988</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8841,13 +8841,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8890,7 +8885,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 55984-2024</t>
+          <t>A 33654-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8904,10 +8899,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45623</v>
+        <v>44789</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8920,7 +8915,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8963,7 +8958,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 35047-2024</t>
+          <t>A 36835-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8977,10 +8972,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45527</v>
+        <v>45538</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8992,8 +8987,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9036,7 +9036,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 29433-2025</t>
+          <t>A 58393-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9046,14 +9046,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45824</v>
+        <v>44901</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9066,7 +9066,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9109,7 +9109,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 25322-2024</t>
+          <t>A 2872-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9123,10 +9123,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45462</v>
+        <v>44945</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9182,7 +9182,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 8936-2026</t>
+          <t>A 25814-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9196,10 +9196,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46069</v>
+        <v>46178</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9212,7 +9212,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9255,7 +9255,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 31596-2024</t>
+          <t>A 11949-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9269,10 +9269,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45506</v>
+        <v>44994</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9284,13 +9284,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>4.3</v>
+        <v>2.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9333,7 +9328,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 52999-2023</t>
+          <t>A 54582-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9347,10 +9342,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45226</v>
+        <v>45233</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9363,7 +9358,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9406,7 +9401,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 59155-2025</t>
+          <t>A 54279-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9420,10 +9415,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45988</v>
+        <v>45232</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9436,7 +9431,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9479,7 +9474,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 53273-2023</t>
+          <t>A 36816-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9489,14 +9484,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45229</v>
+        <v>45538</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9508,8 +9503,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>6.3</v>
+        <v>1.4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9552,7 +9552,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 24279-2026</t>
+          <t>A 26148-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9566,10 +9566,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46169</v>
+        <v>46181</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>11.7</v>
+        <v>1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9625,7 +9625,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 24759-2023</t>
+          <t>A 55984-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9639,10 +9639,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45084</v>
+        <v>45623</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9655,7 +9655,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9698,7 +9698,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 52853-2023</t>
+          <t>A 35047-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9712,10 +9712,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45226</v>
+        <v>45527</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9728,7 +9728,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9771,7 +9771,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 7212-2025</t>
+          <t>A 25322-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9785,10 +9785,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45702</v>
+        <v>45462</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9844,7 +9844,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 24736-2026</t>
+          <t>A 27552-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9858,10 +9858,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46171</v>
+        <v>46190</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9873,13 +9873,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9922,7 +9917,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 33654-2022</t>
+          <t>A 5514-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9936,10 +9931,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44789</v>
+        <v>46050</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9951,8 +9946,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9995,7 +9995,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 32395-2023</t>
+          <t>A 31596-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10009,10 +10009,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45120</v>
+        <v>45506</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10024,8 +10024,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10068,7 +10073,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 5514-2026</t>
+          <t>A 28068-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10082,10 +10087,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46050</v>
+        <v>46195</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10097,13 +10102,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10146,7 +10146,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 6080-2023</t>
+          <t>A 28056-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10156,14 +10156,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44964</v>
+        <v>46195</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10219,7 +10219,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 35202-2023</t>
+          <t>A 52999-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10233,10 +10233,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45145</v>
+        <v>45226</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>11.1</v>
+        <v>0.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10292,7 +10292,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 25814-2026</t>
+          <t>A 28309-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10306,10 +10306,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46178</v>
+        <v>46196</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10365,7 +10365,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 5577-2023</t>
+          <t>A 7592-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10379,10 +10379,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44960</v>
+        <v>46061</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10395,7 +10395,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10438,7 +10438,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 7592-2026</t>
+          <t>A 9738-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10452,10 +10452,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46061</v>
+        <v>46072</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10511,7 +10511,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 30484-2023</t>
+          <t>A 53273-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10521,14 +10521,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45111</v>
+        <v>45229</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.2</v>
+        <v>6.3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10584,7 +10584,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 8950-2024</t>
+          <t>A 24759-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10598,10 +10598,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45357</v>
+        <v>45084</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10657,7 +10657,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 46876-2022</t>
+          <t>A 52853-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10671,10 +10671,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44851</v>
+        <v>45226</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10687,7 +10687,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>7.5</v>
+        <v>1.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10730,7 +10730,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 13522-2023</t>
+          <t>A 14536-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10744,10 +10744,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45006</v>
+        <v>46100</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10760,7 +10760,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10803,7 +10803,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 26148-2026</t>
+          <t>A 7212-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10817,10 +10817,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46181</v>
+        <v>45702</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10876,7 +10876,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 56419-2024</t>
+          <t>A 32395-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10890,10 +10890,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45623</v>
+        <v>45120</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>5.6</v>
+        <v>1.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10949,7 +10949,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 8626-2024</t>
+          <t>A 6080-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10959,14 +10959,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45355</v>
+        <v>44964</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10979,7 +10979,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>6.4</v>
+        <v>1.9</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11022,7 +11022,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 9738-2026</t>
+          <t>A 35202-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11036,10 +11036,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46072</v>
+        <v>45145</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.4</v>
+        <v>11.1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 60112-2024</t>
+          <t>A 17533-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11109,10 +11109,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45642</v>
+        <v>46120</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11125,7 +11125,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11168,7 +11168,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 31605-2024</t>
+          <t>A 17527-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11182,10 +11182,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45506</v>
+        <v>46119</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11197,13 +11197,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>2.7</v>
+        <v>4.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11246,7 +11241,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 60118-2024</t>
+          <t>A 17495-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11260,10 +11255,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45642</v>
+        <v>46120</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11276,7 +11271,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11319,7 +11314,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 62551-2021</t>
+          <t>A 17524-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11333,10 +11328,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44503</v>
+        <v>46119</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11349,7 +11344,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11392,7 +11387,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 56542-2024</t>
+          <t>A 17958-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11402,14 +11397,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45625</v>
+        <v>46122</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11419,6 +11414,11 @@
       <c r="G139" t="inlineStr">
         <is>
           <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I139" t="n">
@@ -11465,7 +11465,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 53814-2024</t>
+          <t>A 5577-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11479,10 +11479,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45615</v>
+        <v>44960</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11495,7 +11495,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11538,7 +11538,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 27552-2026</t>
+          <t>A 30484-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11552,10 +11552,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46190</v>
+        <v>45111</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11568,7 +11568,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>5.3</v>
+        <v>0.2</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11611,7 +11611,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 28068-2026</t>
+          <t>A 8950-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11625,10 +11625,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46195</v>
+        <v>45357</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11641,7 +11641,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11684,7 +11684,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 10524-2024</t>
+          <t>A 18834-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11698,10 +11698,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45366</v>
+        <v>46129</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11714,7 +11714,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11757,7 +11757,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 9422-2024</t>
+          <t>A 18979-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11771,10 +11771,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45359</v>
+        <v>46129</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11787,7 +11787,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11830,7 +11830,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 28056-2026</t>
+          <t>A 46876-2022</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11844,10 +11844,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46195</v>
+        <v>44851</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11860,7 +11860,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1</v>
+        <v>7.5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11903,7 +11903,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 14536-2026</t>
+          <t>A 13522-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11917,10 +11917,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46100</v>
+        <v>45006</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11976,7 +11976,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 28309-2026</t>
+          <t>A 56419-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11990,10 +11990,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46196</v>
+        <v>45623</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>3.1</v>
+        <v>5.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12049,7 +12049,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 45608-2022</t>
+          <t>A 8626-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12063,10 +12063,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44845</v>
+        <v>45355</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12079,7 +12079,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>17</v>
+        <v>6.4</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12122,7 +12122,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 58672-2022</t>
+          <t>A 60112-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12136,10 +12136,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44902</v>
+        <v>45642</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12152,7 +12152,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12195,7 +12195,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 55897-2024</t>
+          <t>A 31605-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12209,10 +12209,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45622</v>
+        <v>45506</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12224,8 +12224,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I150" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12268,7 +12273,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 32923-2026</t>
+          <t>A 33984-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12278,14 +12283,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46244</v>
+        <v>46252</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12298,7 +12303,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12341,7 +12346,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 17533-2026</t>
+          <t>A 60118-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12355,10 +12360,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46120</v>
+        <v>45642</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12371,7 +12376,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12414,7 +12419,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 17527-2026</t>
+          <t>A 62551-2021</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12428,10 +12433,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46119</v>
+        <v>44503</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12444,7 +12449,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>4.4</v>
+        <v>0.9</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12487,7 +12492,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 17495-2026</t>
+          <t>A 34112-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12501,10 +12506,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46120</v>
+        <v>46253</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12517,7 +12522,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12560,7 +12565,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 17524-2026</t>
+          <t>A 56542-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12570,14 +12575,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46119</v>
+        <v>45625</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12590,7 +12595,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12633,7 +12638,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 17958-2026</t>
+          <t>A 53814-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12647,10 +12652,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46122</v>
+        <v>45615</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12662,13 +12667,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12711,7 +12711,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 32944-2026</t>
+          <t>A 10524-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12725,10 +12725,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46244</v>
+        <v>45366</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12741,7 +12741,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12784,7 +12784,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 18834-2026</t>
+          <t>A 9422-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12798,10 +12798,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46129</v>
+        <v>45359</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12814,7 +12814,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12857,7 +12857,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 18979-2026</t>
+          <t>A 45608-2022</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12871,10 +12871,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46129</v>
+        <v>44845</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12887,7 +12887,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.8</v>
+        <v>17</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12930,7 +12930,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 41163-2023</t>
+          <t>A 58672-2022</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12944,10 +12944,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45174</v>
+        <v>44902</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12960,7 +12960,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13003,7 +13003,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 49997-2025</t>
+          <t>A 55897-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13017,10 +13017,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45943</v>
+        <v>45622</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13076,7 +13076,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 40257-2023</t>
+          <t>A 41163-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13090,10 +13090,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45169</v>
+        <v>45174</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.6</v>
+        <v>3.2</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13149,7 +13149,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 36622-2023</t>
+          <t>A 36878-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13163,10 +13163,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45153</v>
+        <v>46273</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13179,7 +13179,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13222,7 +13222,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 15374-2025</t>
+          <t>A 40257-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13236,10 +13236,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45747</v>
+        <v>45169</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13252,7 +13252,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13295,7 +13295,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 62541-2021</t>
+          <t>A 36622-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13309,10 +13309,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44503</v>
+        <v>45153</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13325,7 +13325,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13368,7 +13368,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 28850-2024</t>
+          <t>A 36716-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13382,10 +13382,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45478</v>
+        <v>46272</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13398,7 +13398,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13441,7 +13441,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 44849-2024</t>
+          <t>A 31826-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13455,10 +13455,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45574</v>
+        <v>46230</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13514,7 +13514,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 59644-2023</t>
+          <t>A 31897-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13528,10 +13528,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45254</v>
+        <v>46231</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13544,7 +13544,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13587,7 +13587,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 56365-2024</t>
+          <t>A 31899-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13601,10 +13601,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45625</v>
+        <v>46231</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13617,7 +13617,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13660,7 +13660,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 33984-2026</t>
+          <t>A 62541-2021</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13670,14 +13670,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46252</v>
+        <v>44503</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13690,7 +13690,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13733,7 +13733,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 6940-2024</t>
+          <t>A 28850-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13747,10 +13747,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45343</v>
+        <v>45478</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13763,7 +13763,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13806,7 +13806,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 40291-2024</t>
+          <t>A 31902-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13820,10 +13820,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45554</v>
+        <v>46231</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13836,7 +13836,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13879,7 +13879,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 34112-2026</t>
+          <t>A 44849-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13893,10 +13893,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46253</v>
+        <v>45574</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13909,7 +13909,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 33209-2023</t>
+          <t>A 59644-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13966,10 +13966,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45127</v>
+        <v>45254</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14025,7 +14025,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 53764-2024</t>
+          <t>A 56365-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14039,10 +14039,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45615</v>
+        <v>45625</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14055,7 +14055,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14098,7 +14098,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 44308-2023</t>
+          <t>A 6940-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14112,10 +14112,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45188</v>
+        <v>45343</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14128,7 +14128,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14171,7 +14171,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 13530-2023</t>
+          <t>A 40291-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14185,10 +14185,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45006</v>
+        <v>45554</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14201,7 +14201,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14244,7 +14244,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 35087-2024</t>
+          <t>A 37994-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14258,10 +14258,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45527</v>
+        <v>46280</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14274,7 +14274,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14317,7 +14317,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 53769-2024</t>
+          <t>A 34941-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14331,10 +14331,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45615</v>
+        <v>46259</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14390,7 +14390,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 6102-2023</t>
+          <t>A 37997-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14404,10 +14404,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44964</v>
+        <v>46280</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14420,7 +14420,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14463,7 +14463,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 18768-2024</t>
+          <t>A 33209-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14477,10 +14477,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45426</v>
+        <v>45127</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14493,7 +14493,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14536,7 +14536,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 56740-2023</t>
+          <t>A 34945-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14550,10 +14550,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45244</v>
+        <v>46259</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14609,7 +14609,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 43460-2024</t>
+          <t>A 38009-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14623,10 +14623,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45568</v>
+        <v>46280</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14682,7 +14682,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 59010-2024</t>
+          <t>A 53764-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14696,10 +14696,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45635</v>
+        <v>45615</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14712,7 +14712,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14755,7 +14755,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 36878-2026</t>
+          <t>A 34936-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14769,10 +14769,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46273</v>
+        <v>46259</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14785,7 +14785,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.4</v>
+        <v>7.4</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14828,7 +14828,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 36716-2026</t>
+          <t>A 32504-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14842,10 +14842,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46272</v>
+        <v>46239</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14855,6 +14855,11 @@
       <c r="G186" t="inlineStr">
         <is>
           <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I186" t="n">
@@ -14901,7 +14906,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 31826-2026</t>
+          <t>A 32477-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14915,10 +14920,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46230</v>
+        <v>46239</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14930,8 +14935,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I187" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14974,7 +14984,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 31897-2026</t>
+          <t>A 32497-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14988,10 +14998,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46231</v>
+        <v>46239</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15001,6 +15011,11 @@
       <c r="G188" t="inlineStr">
         <is>
           <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I188" t="n">
@@ -15047,7 +15062,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 31899-2026</t>
+          <t>A 37946-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15061,10 +15076,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46231</v>
+        <v>46280</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15077,7 +15092,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15120,7 +15135,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 61817-2024</t>
+          <t>A 44308-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15134,10 +15149,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45649</v>
+        <v>45188</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15150,7 +15165,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>4.6</v>
+        <v>0.7</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15193,7 +15208,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 31902-2026</t>
+          <t>A 13530-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15207,10 +15222,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46231</v>
+        <v>45006</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15266,7 +15281,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 9973-2024</t>
+          <t>A 35087-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15280,10 +15295,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45363</v>
+        <v>45527</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15296,7 +15311,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>4.7</v>
+        <v>1.8</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15339,7 +15354,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 56373-2024</t>
+          <t>A 53769-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15353,10 +15368,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45625</v>
+        <v>45615</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15369,7 +15384,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15412,7 +15427,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 37994-2026</t>
+          <t>A 32923-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15426,10 +15441,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46280</v>
+        <v>46244</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15442,7 +15457,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15485,7 +15500,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 34941-2026</t>
+          <t>A 32944-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15499,10 +15514,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46259</v>
+        <v>46244</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15515,7 +15530,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>9.300000000000001</v>
+        <v>1.7</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15558,7 +15573,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 53805-2024</t>
+          <t>A 6102-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15572,10 +15587,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45615</v>
+        <v>44964</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15588,7 +15603,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15631,7 +15646,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 37997-2026</t>
+          <t>A 18768-2024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15645,10 +15660,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46280</v>
+        <v>45426</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15661,7 +15676,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15704,7 +15719,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 11393-2025</t>
+          <t>A 56740-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15718,10 +15733,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45726</v>
+        <v>45244</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15734,7 +15749,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.2</v>
+        <v>4.5</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15777,7 +15792,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 34945-2026</t>
+          <t>A 43460-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15791,10 +15806,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46259</v>
+        <v>45568</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15807,7 +15822,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>6.2</v>
+        <v>0.8</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15850,7 +15865,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 38009-2026</t>
+          <t>A 59010-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15864,10 +15879,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46280</v>
+        <v>45635</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15880,7 +15895,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15923,7 +15938,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 34936-2026</t>
+          <t>A 61817-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15937,10 +15952,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46259</v>
+        <v>45649</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15953,7 +15968,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>7.4</v>
+        <v>4.6</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15996,7 +16011,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 32504-2026</t>
+          <t>A 9973-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16010,10 +16025,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46239</v>
+        <v>45363</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16025,13 +16040,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I202" t="n">
-        <v>1.3</v>
+        <v>4.7</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16074,7 +16084,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 24356-2025</t>
+          <t>A 56373-2024</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16088,10 +16098,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45797</v>
+        <v>45625</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16104,7 +16114,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16147,7 +16157,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 53275-2023</t>
+          <t>A 53805-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16157,14 +16167,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45229</v>
+        <v>45615</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16177,7 +16187,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>8.5</v>
+        <v>1.1</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16220,7 +16230,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 44104-2024</t>
+          <t>A 11393-2025</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16234,10 +16244,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45572</v>
+        <v>45726</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16250,7 +16260,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>2.4</v>
+        <v>0.2</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16293,7 +16303,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 32477-2026</t>
+          <t>A 24356-2025</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16307,10 +16317,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46239</v>
+        <v>45797</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16322,13 +16332,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I206" t="n">
-        <v>2.4</v>
+        <v>0.2</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16371,7 +16376,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 11563-2025</t>
+          <t>A 53275-2023</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16385,10 +16390,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45727</v>
+        <v>45229</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16400,13 +16405,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I207" t="n">
-        <v>0.7</v>
+        <v>8.5</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16449,7 +16449,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 32497-2026</t>
+          <t>A 44104-2024</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16463,10 +16463,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46239</v>
+        <v>45572</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16478,13 +16478,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I208" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16527,7 +16522,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 19840-2025</t>
+          <t>A 11563-2025</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16541,10 +16536,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45771</v>
+        <v>45727</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16556,8 +16551,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I209" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16600,7 +16600,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 37946-2026</t>
+          <t>A 19840-2025</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16610,14 +16610,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46280</v>
+        <v>45771</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16630,7 +16630,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16690,7 +16690,7 @@
         <v>45250</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>45538</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16841,7 +16841,7 @@
         <v>45758</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16914,7 +16914,7 @@
         <v>45824</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16987,7 +16987,7 @@
         <v>45834</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17060,7 +17060,7 @@
         <v>45834</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
         <v>45837</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>45252</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17279,7 +17279,7 @@
         <v>45805</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17352,7 +17352,7 @@
         <v>45867</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17408,24 +17408,24 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 37195-2025</t>
+          <t>S 3762-2024</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45875</v>
+        <v>45558</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17438,7 +17438,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17481,7 +17481,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>S 3762-2024</t>
+          <t>S 1807-2022</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17491,14 +17491,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Skogsbilväg</t>
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45558</v>
+        <v>44656</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17510,8 +17510,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I222" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17554,7 +17559,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>S 1807-2022</t>
+          <t>S 320-2025</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17564,14 +17569,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Skogsbilväg</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>44656</v>
+        <v>45688</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17583,13 +17588,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I223" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17632,7 +17632,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>S 320-2025</t>
+          <t>S 319-2025</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17649,7 +17649,7 @@
         <v>45688</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17662,7 +17662,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17702,10 +17702,10 @@
       </c>
       <c r="V224" s="2" t="inlineStr"/>
     </row>
-    <row r="225" ht="15" customHeight="1">
+    <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>S 319-2025</t>
+          <t>S 2767-2022</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17715,14 +17715,14 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45688</v>
+        <v>44705</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17735,7 +17735,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>2.9</v>
+        <v>0.1</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17774,79 +17774,6 @@
         <v>0</v>
       </c>
       <c r="V225" s="2" t="inlineStr"/>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>S 2767-2022</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>Åtgärd i nyckelbiotop</t>
-        </is>
-      </c>
-      <c r="D226" s="1" t="n">
-        <v>44705</v>
-      </c>
-      <c r="E226" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I226" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J226" t="n">
-        <v>0</v>
-      </c>
-      <c r="K226" t="n">
-        <v>0</v>
-      </c>
-      <c r="L226" t="n">
-        <v>0</v>
-      </c>
-      <c r="M226" t="n">
-        <v>0</v>
-      </c>
-      <c r="N226" t="n">
-        <v>0</v>
-      </c>
-      <c r="O226" t="n">
-        <v>0</v>
-      </c>
-      <c r="P226" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
-      <c r="R226" t="n">
-        <v>0</v>
-      </c>
-      <c r="S226" t="n">
-        <v>0</v>
-      </c>
-      <c r="T226" t="n">
-        <v>0</v>
-      </c>
-      <c r="U226" t="n">
-        <v>0</v>
-      </c>
-      <c r="V226" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt LIDKÖPING.xlsx
+++ b/Översikt LIDKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>44631</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>46006</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>44967</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
         <v>46171</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 28849-2024</t>
+          <t>A 32280-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45478</v>
+        <v>44781</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1097,13 +1097,13 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.6</v>
+        <v>8.6</v>
       </c>
       <c r="J6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -1136,6 +1136,118 @@
         <v>0</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Gulsparv
+Nötkråka
+Sotriska
+Skogsduva</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 32280-2022 artfynd.xlsx", "A 32280-2022")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 32280-2022 karta.png", "A 32280-2022")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 32280-2022 georefererad karta.tif", "A 32280-2022")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 32280-2022 FSC-klagomål.docx", "A 32280-2022")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 32280-2022 FSC-klagomål mail.docx", "A 32280-2022")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 32280-2022 tillsynsbegäran.docx", "A 32280-2022")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 32280-2022 tillsynsbegäran mail.docx", "A 32280-2022")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 32280-2022 prioriterade fågelarter.docx", "A 32280-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 28849-2024</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45478</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Entita
 Talltita
@@ -1143,111 +1255,111 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 28849-2024 artfynd.xlsx", "A 28849-2024")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 28849-2024 karta.png", "A 28849-2024")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 28849-2024 georefererad karta.tif", "A 28849-2024")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 28849-2024 FSC-klagomål.docx", "A 28849-2024")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 28849-2024 FSC-klagomål mail.docx", "A 28849-2024")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 28849-2024 tillsynsbegäran.docx", "A 28849-2024")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 28849-2024 tillsynsbegäran mail.docx", "A 28849-2024")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 28849-2024 prioriterade fågelarter.docx", "A 28849-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>A 34942-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
         <v>46259</v>
       </c>
-      <c r="E7" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
+      <c r="E8" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
         <v>18.1</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J8" t="n">
         <v>3</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K8" t="n">
         <v>1</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L8" t="n">
         <v>2</v>
       </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>2</v>
       </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
         <v>4</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T8" t="n">
         <v>4</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Gulsparv
 Nötkråka
@@ -1255,155 +1367,43 @@
 Skogsduva</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 34942-2026 artfynd.xlsx", "A 34942-2026")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 34942-2026 karta.png", "A 34942-2026")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 34942-2026 georefererad karta.tif", "A 34942-2026")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 34942-2026 FSC-klagomål.docx", "A 34942-2026")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 34942-2026 FSC-klagomål mail.docx", "A 34942-2026")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 34942-2026 tillsynsbegäran.docx", "A 34942-2026")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 34942-2026 tillsynsbegäran mail.docx", "A 34942-2026")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 34942-2026 prioriterade fågelarter.docx", "A 34942-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 32280-2022</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>44781</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>4</v>
-      </c>
-      <c r="T8" t="n">
-        <v>4</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Gulsparv
-Nötkråka
-Sotriska
-Skogsduva</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 32280-2022 artfynd.xlsx", "A 32280-2022")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 32280-2022 karta.png", "A 32280-2022")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 32280-2022 georefererad karta.tif", "A 32280-2022")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 32280-2022 FSC-klagomål.docx", "A 32280-2022")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 32280-2022 FSC-klagomål mail.docx", "A 32280-2022")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 32280-2022 tillsynsbegäran.docx", "A 32280-2022")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 32280-2022 tillsynsbegäran mail.docx", "A 32280-2022")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 32280-2022 prioriterade fågelarter.docx", "A 32280-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 4831-2025</t>
+          <t>A 47321-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1413,14 +1413,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45688</v>
+        <v>45202</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1433,13 +1433,13 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.3</v>
+        <v>7.3</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1448,7 +1448,7 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1457,10 +1457,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1469,262 +1469,262 @@
         <v>3</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Kråka
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 47321-2023 artfynd.xlsx", "A 47321-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 47321-2023 karta.png", "A 47321-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 47321-2023 georefererad karta.tif", "A 47321-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 47321-2023 FSC-klagomål.docx", "A 47321-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 47321-2023 FSC-klagomål mail.docx", "A 47321-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 47321-2023 tillsynsbegäran.docx", "A 47321-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 47321-2023 tillsynsbegäran mail.docx", "A 47321-2023")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 47321-2023 prioriterade fågelarter.docx", "A 47321-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 15219-2024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45400</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Tårkragskivling
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 15219-2024 artfynd.xlsx", "A 15219-2024")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 15219-2024 karta.png", "A 15219-2024")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 15219-2024 georefererad karta.tif", "A 15219-2024")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 15219-2024 FSC-klagomål.docx", "A 15219-2024")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 15219-2024 FSC-klagomål mail.docx", "A 15219-2024")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 15219-2024 tillsynsbegäran.docx", "A 15219-2024")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 15219-2024 tillsynsbegäran mail.docx", "A 15219-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 4831-2025</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45688</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Ask
 Skogsalm
 Barkticka</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 4831-2025 artfynd.xlsx", "A 4831-2025")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 4831-2025 karta.png", "A 4831-2025")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 4831-2025 georefererad karta.tif", "A 4831-2025")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 4831-2025 FSC-klagomål.docx", "A 4831-2025")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 4831-2025 FSC-klagomål mail.docx", "A 4831-2025")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 4831-2025 tillsynsbegäran.docx", "A 4831-2025")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 4831-2025 tillsynsbegäran mail.docx", "A 4831-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 15219-2024</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45400</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Tårkragskivling
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 15219-2024 artfynd.xlsx", "A 15219-2024")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 15219-2024 karta.png", "A 15219-2024")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 15219-2024 georefererad karta.tif", "A 15219-2024")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 15219-2024 FSC-klagomål.docx", "A 15219-2024")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 15219-2024 FSC-klagomål mail.docx", "A 15219-2024")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 15219-2024 tillsynsbegäran.docx", "A 15219-2024")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 15219-2024 tillsynsbegäran mail.docx", "A 15219-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 47321-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45202</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Kråka
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 47321-2023 artfynd.xlsx", "A 47321-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 47321-2023 karta.png", "A 47321-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 47321-2023 georefererad karta.tif", "A 47321-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 47321-2023 FSC-klagomål.docx", "A 47321-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 47321-2023 FSC-klagomål mail.docx", "A 47321-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 47321-2023 tillsynsbegäran.docx", "A 47321-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 47321-2023 tillsynsbegäran mail.docx", "A 47321-2023")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 47321-2023 prioriterade fågelarter.docx", "A 47321-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>45898</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>45702</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>44630</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 10476-2023</t>
+          <t>A 44680-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44987</v>
+        <v>45189</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2126,688 +2126,688 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Trädlärka</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 44680-2023 artfynd.xlsx", "A 44680-2023")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 44680-2023 karta.png", "A 44680-2023")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 44680-2023 georefererad karta.tif", "A 44680-2023")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 44680-2023 FSC-klagomål.docx", "A 44680-2023")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 44680-2023 FSC-klagomål mail.docx", "A 44680-2023")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 44680-2023 tillsynsbegäran.docx", "A 44680-2023")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 44680-2023 tillsynsbegäran mail.docx", "A 44680-2023")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 44680-2023 prioriterade fågelarter.docx", "A 44680-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 24352-2025</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45797</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J16" t="n">
         <v>1</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 24352-2025 artfynd.xlsx", "A 24352-2025")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 24352-2025 karta.png", "A 24352-2025")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 24352-2025 georefererad karta.tif", "A 24352-2025")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 24352-2025 FSC-klagomål.docx", "A 24352-2025")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 24352-2025 FSC-klagomål mail.docx", "A 24352-2025")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 24352-2025 tillsynsbegäran.docx", "A 24352-2025")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 24352-2025 tillsynsbegäran mail.docx", "A 24352-2025")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 24352-2025 prioriterade fågelarter.docx", "A 24352-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 62629-2022</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>44925</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Igelkott</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 62629-2022 artfynd.xlsx", "A 62629-2022")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 62629-2022 karta.png", "A 62629-2022")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 62629-2022 georefererad karta.tif", "A 62629-2022")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 62629-2022 FSC-klagomål.docx", "A 62629-2022")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 62629-2022 FSC-klagomål mail.docx", "A 62629-2022")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 62629-2022 tillsynsbegäran.docx", "A 62629-2022")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 62629-2022 tillsynsbegäran mail.docx", "A 62629-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 62569-2022</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>44924</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 62569-2022 artfynd.xlsx", "A 62569-2022")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 62569-2022 karta.png", "A 62569-2022")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 62569-2022 georefererad karta.tif", "A 62569-2022")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 62569-2022 FSC-klagomål.docx", "A 62569-2022")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 62569-2022 FSC-klagomål mail.docx", "A 62569-2022")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 62569-2022 tillsynsbegäran.docx", "A 62569-2022")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 62569-2022 tillsynsbegäran mail.docx", "A 62569-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 10476-2023</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>44987</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Kungsfågel</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 10476-2023 artfynd.xlsx", "A 10476-2023")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 10476-2023 karta.png", "A 10476-2023")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 10476-2023 georefererad karta.tif", "A 10476-2023")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 10476-2023 FSC-klagomål.docx", "A 10476-2023")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 10476-2023 FSC-klagomål mail.docx", "A 10476-2023")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 10476-2023 tillsynsbegäran.docx", "A 10476-2023")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 10476-2023 tillsynsbegäran mail.docx", "A 10476-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 44680-2023</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45189</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J16" t="n">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 61818-2024</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45649</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J20" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
         <v>1</v>
       </c>
-      <c r="T16" t="n">
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
         <v>1</v>
       </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Trädlärka</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 44680-2023 artfynd.xlsx", "A 44680-2023")</f>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 61818-2024 artfynd.xlsx", "A 61818-2024")</f>
         <v/>
       </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 44680-2023 karta.png", "A 44680-2023")</f>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 61818-2024 karta.png", "A 61818-2024")</f>
         <v/>
       </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 44680-2023 georefererad karta.tif", "A 44680-2023")</f>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 61818-2024 georefererad karta.tif", "A 61818-2024")</f>
         <v/>
       </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 44680-2023 FSC-klagomål.docx", "A 44680-2023")</f>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 61818-2024 FSC-klagomål.docx", "A 61818-2024")</f>
         <v/>
       </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 44680-2023 FSC-klagomål mail.docx", "A 44680-2023")</f>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 61818-2024 FSC-klagomål mail.docx", "A 61818-2024")</f>
         <v/>
       </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 44680-2023 tillsynsbegäran.docx", "A 44680-2023")</f>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 61818-2024 tillsynsbegäran.docx", "A 61818-2024")</f>
         <v/>
       </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 44680-2023 tillsynsbegäran mail.docx", "A 44680-2023")</f>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 61818-2024 tillsynsbegäran mail.docx", "A 61818-2024")</f>
         <v/>
       </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 44680-2023 prioriterade fågelarter.docx", "A 44680-2023")</f>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 61818-2024 prioriterade fågelarter.docx", "A 61818-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 62569-2022</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>44924</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 37136-2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J21" t="n">
         <v>1</v>
       </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
         <v>1</v>
       </c>
-      <c r="R17" t="n">
+      <c r="T21" t="n">
         <v>1</v>
       </c>
-      <c r="S17" t="n">
-        <v>1</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 62569-2022 artfynd.xlsx", "A 62569-2022")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 62569-2022 karta.png", "A 62569-2022")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 62569-2022 georefererad karta.tif", "A 62569-2022")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 62569-2022 FSC-klagomål.docx", "A 62569-2022")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 62569-2022 FSC-klagomål mail.docx", "A 62569-2022")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 62569-2022 tillsynsbegäran.docx", "A 62569-2022")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 62569-2022 tillsynsbegäran mail.docx", "A 62569-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 37136-2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>46274</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Fiskgjuse</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 37136-2026 artfynd.xlsx", "A 37136-2026")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 37136-2026 karta.png", "A 37136-2026")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 37136-2026 georefererad karta.tif", "A 37136-2026")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 37136-2026 FSC-klagomål.docx", "A 37136-2026")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 37136-2026 FSC-klagomål mail.docx", "A 37136-2026")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 37136-2026 tillsynsbegäran.docx", "A 37136-2026")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 37136-2026 tillsynsbegäran mail.docx", "A 37136-2026")</f>
         <v/>
       </c>
-      <c r="AE18">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 37136-2026 prioriterade fågelarter.docx", "A 37136-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 24352-2025</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45797</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 24352-2025 artfynd.xlsx", "A 24352-2025")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 24352-2025 karta.png", "A 24352-2025")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 24352-2025 georefererad karta.tif", "A 24352-2025")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 24352-2025 FSC-klagomål.docx", "A 24352-2025")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 24352-2025 FSC-klagomål mail.docx", "A 24352-2025")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 24352-2025 tillsynsbegäran.docx", "A 24352-2025")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 24352-2025 tillsynsbegäran mail.docx", "A 24352-2025")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 24352-2025 prioriterade fågelarter.docx", "A 24352-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 62629-2022</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>44925</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Igelkott</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 62629-2022 artfynd.xlsx", "A 62629-2022")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 62629-2022 karta.png", "A 62629-2022")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 62629-2022 georefererad karta.tif", "A 62629-2022")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 62629-2022 FSC-klagomål.docx", "A 62629-2022")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 62629-2022 FSC-klagomål mail.docx", "A 62629-2022")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 62629-2022 tillsynsbegäran.docx", "A 62629-2022")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 62629-2022 tillsynsbegäran mail.docx", "A 62629-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 61818-2024</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45649</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Rödvingetrast</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 61818-2024 artfynd.xlsx", "A 61818-2024")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 61818-2024 karta.png", "A 61818-2024")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 61818-2024 georefererad karta.tif", "A 61818-2024")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 61818-2024 FSC-klagomål.docx", "A 61818-2024")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 61818-2024 FSC-klagomål mail.docx", "A 61818-2024")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 61818-2024 tillsynsbegäran.docx", "A 61818-2024")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 61818-2024 tillsynsbegäran mail.docx", "A 61818-2024")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 61818-2024 prioriterade fågelarter.docx", "A 61818-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>44788</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>44466</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>44831</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>44820</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>44714</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>44566</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>44546</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>44627</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>44627</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>44725</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>44805</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>44705</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>44617</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>44487</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>44487</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>44770</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 37155-2022</t>
+          <t>A 27329-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3993,10 +3993,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44806</v>
+        <v>44742</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4052,7 +4052,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 27329-2022</t>
+          <t>A 37155-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4066,10 +4066,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44742</v>
+        <v>44806</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4142,7 +4142,7 @@
         <v>44515</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>44614</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4276,7 +4276,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 28331-2022</t>
+          <t>A 62527-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4290,10 +4290,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44747</v>
+        <v>44503</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.6</v>
+        <v>22.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4349,7 +4349,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 8124-2023</t>
+          <t>A 61817-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4363,10 +4363,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44974</v>
+        <v>45649</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.5</v>
+        <v>4.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4422,7 +4422,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 60465-2024</t>
+          <t>A 28331-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4436,10 +4436,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45643</v>
+        <v>44747</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4495,7 +4495,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 60642-2023</t>
+          <t>A 7248-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4505,14 +4505,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45260</v>
+        <v>45702</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4568,7 +4568,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 48301-2024</t>
+          <t>A 9973-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4582,10 +4582,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45590</v>
+        <v>45363</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.8</v>
+        <v>4.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4641,7 +4641,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 7247-2025</t>
+          <t>A 53273-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4651,14 +4651,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45702</v>
+        <v>45229</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.3</v>
+        <v>6.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 30399-2023</t>
+          <t>A 49755-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4728,10 +4728,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45111</v>
+        <v>44859</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4787,7 +4787,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 11795-2024</t>
+          <t>A 1949-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4801,10 +4801,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45375</v>
+        <v>45672</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4860,7 +4860,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 55974-2024</t>
+          <t>A 53805-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4874,10 +4874,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45623</v>
+        <v>45615</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4933,7 +4933,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 48346-2024</t>
+          <t>A 6940-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4947,10 +4947,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45590</v>
+        <v>45343</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5006,7 +5006,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 39800-2022</t>
+          <t>A 62541-2021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5020,10 +5020,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44819</v>
+        <v>44503</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5079,7 +5079,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 49755-2022</t>
+          <t>A 11393-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5093,10 +5093,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44859</v>
+        <v>45726</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.6</v>
+        <v>0.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5152,7 +5152,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 63778-2023</t>
+          <t>A 59068-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5166,10 +5166,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45278</v>
+        <v>45252</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.2</v>
+        <v>6.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5225,7 +5225,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 53279-2023</t>
+          <t>A 136-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5235,14 +5235,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45229</v>
+        <v>44928</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.6</v>
+        <v>4.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5298,7 +5298,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 58620-2022</t>
+          <t>A 11563-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5308,14 +5308,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44902</v>
+        <v>45727</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5327,8 +5327,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5371,7 +5376,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 1455-2025</t>
+          <t>A 53275-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5381,14 +5386,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45670</v>
+        <v>45229</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5401,7 +5406,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.4</v>
+        <v>8.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5444,7 +5449,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 37169-2022</t>
+          <t>A 44104-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5458,10 +5463,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44806</v>
+        <v>45572</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5474,7 +5479,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>17.4</v>
+        <v>2.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5517,7 +5522,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 136-2023</t>
+          <t>A 54582-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5531,10 +5536,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44928</v>
+        <v>45233</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5547,7 +5552,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5590,7 +5595,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 7223-2025</t>
+          <t>A 24356-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5604,10 +5609,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45702</v>
+        <v>45797</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5620,7 +5625,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.5</v>
+        <v>0.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5663,7 +5668,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 7248-2025</t>
+          <t>A 18768-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5677,10 +5682,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45702</v>
+        <v>45426</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5693,7 +5698,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5736,7 +5741,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 59068-2023</t>
+          <t>A 58393-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5750,10 +5755,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45252</v>
+        <v>44901</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5766,7 +5771,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>6.4</v>
+        <v>2.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5809,7 +5814,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 50577-2024</t>
+          <t>A 9422-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5823,10 +5828,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45601</v>
+        <v>45359</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5839,7 +5844,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5882,7 +5887,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 25762-2023</t>
+          <t>A 11949-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5896,10 +5901,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45090</v>
+        <v>44994</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5912,7 +5917,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5955,7 +5960,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 32952-2023</t>
+          <t>A 33209-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5969,10 +5974,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45125</v>
+        <v>45127</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5985,7 +5990,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>5.1</v>
+        <v>0.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6028,7 +6033,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 37195-2025</t>
+          <t>A 19840-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6038,14 +6043,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45875</v>
+        <v>45771</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6058,7 +6063,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6101,7 +6106,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 43445-2023</t>
+          <t>A 8626-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6115,10 +6120,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45184</v>
+        <v>45355</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6131,7 +6136,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.1</v>
+        <v>6.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6174,7 +6179,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 49997-2025</t>
+          <t>A 44849-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6188,10 +6193,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45943</v>
+        <v>45574</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6204,7 +6209,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6247,7 +6252,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 15374-2025</t>
+          <t>A 62551-2021</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6261,10 +6266,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45747</v>
+        <v>44503</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6277,7 +6282,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6320,7 +6325,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 37098-2023</t>
+          <t>A 11795-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6334,10 +6339,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45155</v>
+        <v>45375</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6350,7 +6355,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6393,7 +6398,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 6913-2023</t>
+          <t>A 35047-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6407,10 +6412,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44967</v>
+        <v>45527</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6423,7 +6428,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6466,7 +6471,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 41937-2025</t>
+          <t>A 39800-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6480,10 +6485,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45903</v>
+        <v>44819</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6496,7 +6501,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6539,7 +6544,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 61312-2023</t>
+          <t>A 45608-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6553,10 +6558,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45264</v>
+        <v>44845</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6569,7 +6574,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.7</v>
+        <v>17</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6612,7 +6617,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 48411-2022</t>
+          <t>A 31605-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6626,10 +6631,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44858</v>
+        <v>45506</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6641,8 +6646,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6685,7 +6695,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 30904-2022</t>
+          <t>A 28850-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6699,10 +6709,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44767</v>
+        <v>45478</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6715,7 +6725,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>5</v>
+        <v>1.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6758,7 +6768,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 20614-2025</t>
+          <t>A 30484-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6772,10 +6782,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45776</v>
+        <v>45111</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6788,7 +6798,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6831,7 +6841,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 12819-2022</t>
+          <t>A 37098-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6845,10 +6855,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44642</v>
+        <v>45155</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6861,7 +6871,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.5</v>
+        <v>4.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6904,7 +6914,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 12175-2023</t>
+          <t>A 35087-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6918,10 +6928,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44998</v>
+        <v>45527</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6934,7 +6944,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>4.3</v>
+        <v>1.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6977,7 +6987,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 24234-2025</t>
+          <t>A 35112-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6991,10 +7001,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45797</v>
+        <v>45529</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7007,7 +7017,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7050,7 +7060,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 21017-2026</t>
+          <t>A 36816-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7064,10 +7074,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46144</v>
+        <v>45538</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7079,8 +7089,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7123,7 +7138,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 61405-2025</t>
+          <t>A 36622-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7137,10 +7152,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46001</v>
+        <v>45153</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7152,13 +7167,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>6.6</v>
+        <v>0.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7201,7 +7211,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 49906-2025</t>
+          <t>A 61312-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7215,10 +7225,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45940</v>
+        <v>45264</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7231,7 +7241,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.2</v>
+        <v>0.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7274,7 +7284,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 49909-2025</t>
+          <t>A 10524-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7288,10 +7298,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45940</v>
+        <v>45366</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7304,7 +7314,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7347,7 +7357,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 8953-2023</t>
+          <t>A 8950-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7361,10 +7371,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44979</v>
+        <v>45357</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7377,7 +7387,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7420,7 +7430,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 29433-2025</t>
+          <t>A 58672-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7434,10 +7444,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45824</v>
+        <v>44902</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7450,7 +7460,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7493,7 +7503,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 52719-2025</t>
+          <t>A 58420-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7503,14 +7513,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45957</v>
+        <v>45250</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7523,7 +7533,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7566,7 +7576,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 52640-2025</t>
+          <t>A 43445-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7580,10 +7590,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45954</v>
+        <v>45184</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7596,7 +7606,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7639,7 +7649,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 246-2025</t>
+          <t>A 12819-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7653,10 +7663,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45660</v>
+        <v>44642</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7669,7 +7679,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7712,7 +7722,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 53275-2025</t>
+          <t>A 36945-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7726,10 +7736,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45958</v>
+        <v>45538</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7741,8 +7751,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7785,7 +7800,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 8936-2026</t>
+          <t>A 17892-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7799,10 +7814,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46069</v>
+        <v>45758</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7815,7 +7830,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7858,7 +7873,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 54191-2025</t>
+          <t>A 32395-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7872,10 +7887,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45964</v>
+        <v>45120</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7888,7 +7903,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7931,7 +7946,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 7760-2025</t>
+          <t>A 246-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7945,10 +7960,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45706</v>
+        <v>45660</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7961,7 +7976,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>8.300000000000001</v>
+        <v>1.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8004,7 +8019,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 2086-2025</t>
+          <t>A 49906-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8018,10 +8033,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45672</v>
+        <v>45940</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8034,7 +8049,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8077,7 +8092,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 62527-2021</t>
+          <t>A 8124-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8091,10 +8106,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44503</v>
+        <v>44974</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8107,7 +8122,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>22.6</v>
+        <v>1.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8150,7 +8165,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 24279-2026</t>
+          <t>A 49909-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8164,10 +8179,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46169</v>
+        <v>45940</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8180,7 +8195,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>11.7</v>
+        <v>2.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8223,7 +8238,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 60290-2024</t>
+          <t>A 40291-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8237,10 +8252,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45642</v>
+        <v>45554</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8253,7 +8268,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8296,7 +8311,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 35112-2024</t>
+          <t>A 48301-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8310,10 +8325,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45529</v>
+        <v>45590</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8326,7 +8341,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8369,7 +8384,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 19759-2024</t>
+          <t>A 30399-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8383,10 +8398,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45432</v>
+        <v>45111</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8399,7 +8414,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8442,7 +8457,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 56413-2024</t>
+          <t>A 60465-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8456,10 +8471,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45623</v>
+        <v>45643</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8472,7 +8487,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3.5</v>
+        <v>0.8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8515,7 +8530,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 1949-2025</t>
+          <t>A 25322-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8529,10 +8544,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45672</v>
+        <v>45462</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8545,7 +8560,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8588,7 +8603,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 696-2025</t>
+          <t>A 35202-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8602,10 +8617,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45665</v>
+        <v>45145</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8618,7 +8633,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1</v>
+        <v>11.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8661,7 +8676,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 34779-2023</t>
+          <t>A 31596-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8675,10 +8690,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45141</v>
+        <v>45506</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8690,8 +8705,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8734,7 +8754,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 24736-2026</t>
+          <t>A 40257-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8748,10 +8768,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46171</v>
+        <v>45169</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8763,13 +8783,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8812,7 +8827,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 59155-2025</t>
+          <t>A 19759-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8826,10 +8841,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45988</v>
+        <v>45432</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8842,7 +8857,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8885,7 +8900,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 33654-2022</t>
+          <t>A 56542-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8895,14 +8910,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44789</v>
+        <v>45625</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8915,7 +8930,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8958,7 +8973,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 36835-2024</t>
+          <t>A 24759-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8972,10 +8987,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45538</v>
+        <v>45084</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8987,13 +9002,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9036,7 +9046,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 58393-2022</t>
+          <t>A 53275-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9046,14 +9056,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44901</v>
+        <v>45958</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9066,7 +9076,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9109,7 +9119,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 2872-2023</t>
+          <t>A 52640-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9123,10 +9133,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44945</v>
+        <v>45954</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9139,7 +9149,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9182,7 +9192,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 25814-2026</t>
+          <t>A 52719-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9196,10 +9206,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46178</v>
+        <v>45957</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9212,7 +9222,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9255,7 +9265,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 11949-2023</t>
+          <t>A 7247-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9269,10 +9279,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44994</v>
+        <v>45702</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9285,7 +9295,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9328,7 +9338,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 54582-2023</t>
+          <t>A 53814-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9342,10 +9352,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45233</v>
+        <v>45615</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9358,7 +9368,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9401,7 +9411,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 54279-2023</t>
+          <t>A 37169-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9415,10 +9425,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45232</v>
+        <v>44806</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9431,7 +9441,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.3</v>
+        <v>17.4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9474,7 +9484,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 36816-2024</t>
+          <t>A 60118-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9488,10 +9498,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45538</v>
+        <v>45642</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9503,13 +9513,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9552,7 +9557,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 26148-2026</t>
+          <t>A 53769-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9566,10 +9571,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46181</v>
+        <v>45615</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9582,7 +9587,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9625,7 +9630,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 55984-2024</t>
+          <t>A 54191-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9639,10 +9644,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45623</v>
+        <v>45964</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9655,7 +9660,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9698,7 +9703,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 35047-2024</t>
+          <t>A 55984-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9712,10 +9717,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45527</v>
+        <v>45623</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9728,7 +9733,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9771,7 +9776,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 25322-2024</t>
+          <t>A 56419-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9785,10 +9790,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45462</v>
+        <v>45623</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9801,7 +9806,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.3</v>
+        <v>5.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9844,7 +9849,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 27552-2026</t>
+          <t>A 55897-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9858,10 +9863,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46190</v>
+        <v>45622</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9874,7 +9879,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>5.3</v>
+        <v>1.8</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9917,7 +9922,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 5514-2026</t>
+          <t>A 696-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9931,10 +9936,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46050</v>
+        <v>45665</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9946,13 +9951,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9995,7 +9995,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 31596-2024</t>
+          <t>A 50577-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10009,10 +10009,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45506</v>
+        <v>45601</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10024,13 +10024,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>4.3</v>
+        <v>1.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10073,7 +10068,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 28068-2026</t>
+          <t>A 63778-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10083,14 +10078,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46195</v>
+        <v>45278</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10103,7 +10098,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.7</v>
+        <v>3.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10146,7 +10141,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 28056-2026</t>
+          <t>A 13530-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10160,10 +10155,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46195</v>
+        <v>45006</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10176,7 +10171,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10219,7 +10214,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 52999-2023</t>
+          <t>A 60642-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10229,14 +10224,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45226</v>
+        <v>45260</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10249,7 +10244,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10292,7 +10287,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 28309-2026</t>
+          <t>A 5577-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10306,10 +10301,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46196</v>
+        <v>44960</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10322,7 +10317,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10365,7 +10360,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 7592-2026</t>
+          <t>A 60290-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10379,10 +10374,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46061</v>
+        <v>45642</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10395,7 +10390,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10438,7 +10433,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 9738-2026</t>
+          <t>A 44308-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10452,10 +10447,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46072</v>
+        <v>45188</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10468,7 +10463,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10511,7 +10506,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 53273-2023</t>
+          <t>A 29495-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10521,14 +10516,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45229</v>
+        <v>45824</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10541,7 +10536,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>6.3</v>
+        <v>5.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10584,7 +10579,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 24759-2023</t>
+          <t>A 12175-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10598,10 +10593,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45084</v>
+        <v>44998</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10614,7 +10609,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10657,7 +10652,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 52853-2023</t>
+          <t>A 54279-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10671,10 +10666,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45226</v>
+        <v>45232</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10687,7 +10682,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10730,7 +10725,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 14536-2026</t>
+          <t>A 7212-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10744,10 +10739,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46100</v>
+        <v>45702</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10760,7 +10755,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10803,7 +10798,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 7212-2025</t>
+          <t>A 31844-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10817,10 +10812,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45702</v>
+        <v>45834</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10833,7 +10828,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.5</v>
+        <v>6.2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10876,7 +10871,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 32395-2023</t>
+          <t>A 31825-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10890,10 +10885,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45120</v>
+        <v>45834</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10906,7 +10901,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10949,7 +10944,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 6080-2023</t>
+          <t>A 59155-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10959,14 +10954,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44964</v>
+        <v>45988</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10979,7 +10974,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11022,7 +11017,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 35202-2023</t>
+          <t>A 8953-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11036,10 +11031,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45145</v>
+        <v>44979</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11052,7 +11047,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>11.1</v>
+        <v>1.1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11095,7 +11090,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 17533-2026</t>
+          <t>A 32355-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11109,10 +11104,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46120</v>
+        <v>45837</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11125,7 +11120,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11168,7 +11163,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 17527-2026</t>
+          <t>A 59644-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11182,10 +11177,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46119</v>
+        <v>45254</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11198,7 +11193,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>4.4</v>
+        <v>0.6</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11241,7 +11236,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 17495-2026</t>
+          <t>A 6080-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11251,14 +11246,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46120</v>
+        <v>44964</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11271,7 +11266,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11314,7 +11309,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 17524-2026</t>
+          <t>A 5514-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11328,10 +11323,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46119</v>
+        <v>46050</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11343,8 +11338,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>0.2</v>
+        <v>2.5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11387,7 +11387,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 17958-2026</t>
+          <t>A 59010-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11401,10 +11401,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46122</v>
+        <v>45635</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11416,13 +11416,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11465,7 +11460,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 5577-2023</t>
+          <t>A 7592-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11479,10 +11474,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44960</v>
+        <v>46061</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11495,7 +11490,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11538,7 +11533,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 30484-2023</t>
+          <t>A 9738-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11552,10 +11547,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45111</v>
+        <v>46072</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11568,7 +11563,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11611,7 +11606,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 8950-2024</t>
+          <t>A 32923-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11625,10 +11620,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45357</v>
+        <v>46244</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11641,7 +11636,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11684,7 +11679,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 18834-2026</t>
+          <t>A 32944-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11698,10 +11693,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46129</v>
+        <v>46244</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11714,7 +11709,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11757,7 +11752,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 18979-2026</t>
+          <t>A 58620-2022</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11771,10 +11766,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46129</v>
+        <v>44902</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11787,7 +11782,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11830,7 +11825,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 46876-2022</t>
+          <t>A 26356-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11844,10 +11839,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44851</v>
+        <v>45805</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11860,7 +11855,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>7.5</v>
+        <v>0.4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11903,7 +11898,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 13522-2023</t>
+          <t>A 34779-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11917,10 +11912,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45006</v>
+        <v>45141</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11933,7 +11928,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11976,7 +11971,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 56419-2024</t>
+          <t>A 60112-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11990,10 +11985,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45623</v>
+        <v>45642</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12006,7 +12001,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>5.6</v>
+        <v>0.5</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12049,7 +12044,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 8626-2024</t>
+          <t>A 59069-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12059,14 +12054,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45355</v>
+        <v>45252</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12079,7 +12074,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>6.4</v>
+        <v>4.9</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12122,7 +12117,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 60112-2024</t>
+          <t>A 14536-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12136,10 +12131,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45642</v>
+        <v>46100</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12152,7 +12147,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12195,7 +12190,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 31605-2024</t>
+          <t>A 53279-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12205,14 +12200,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45506</v>
+        <v>45229</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12224,13 +12219,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12273,7 +12263,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 33984-2026</t>
+          <t>A 6102-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12283,14 +12273,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46252</v>
+        <v>44964</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12303,7 +12293,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12346,7 +12336,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 60118-2024</t>
+          <t>A 43460-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12360,10 +12350,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45642</v>
+        <v>45568</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12376,7 +12366,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12419,7 +12409,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 62551-2021</t>
+          <t>A 13522-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12433,10 +12423,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44503</v>
+        <v>45006</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12449,7 +12439,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12492,7 +12482,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 34112-2026</t>
+          <t>A 25762-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12506,10 +12496,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46253</v>
+        <v>45090</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12522,7 +12512,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12565,7 +12555,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 56542-2024</t>
+          <t>A 2872-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12575,14 +12565,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45625</v>
+        <v>44945</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12595,7 +12585,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12638,7 +12628,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 53814-2024</t>
+          <t>A 46876-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12652,10 +12642,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45615</v>
+        <v>44851</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12668,7 +12658,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.8</v>
+        <v>7.5</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12711,7 +12701,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 10524-2024</t>
+          <t>A 1455-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12725,10 +12715,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45366</v>
+        <v>45670</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12741,7 +12731,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12784,7 +12774,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 9422-2024</t>
+          <t>A 48346-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12798,10 +12788,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45359</v>
+        <v>45590</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12814,7 +12804,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12857,7 +12847,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 45608-2022</t>
+          <t>A 17527-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12871,10 +12861,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44845</v>
+        <v>46119</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12887,7 +12877,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>17</v>
+        <v>4.4</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12930,7 +12920,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 58672-2022</t>
+          <t>A 17524-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12944,10 +12934,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44902</v>
+        <v>46119</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12960,7 +12950,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>2.4</v>
+        <v>0.2</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13003,7 +12993,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 55897-2024</t>
+          <t>A 36208-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13017,10 +13007,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45622</v>
+        <v>45867</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13033,7 +13023,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13076,7 +13066,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 41163-2023</t>
+          <t>A 17533-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13090,10 +13080,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45174</v>
+        <v>46120</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13106,7 +13096,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13149,7 +13139,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 36878-2026</t>
+          <t>A 17495-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13163,10 +13153,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46273</v>
+        <v>46120</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13179,7 +13169,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13222,7 +13212,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 40257-2023</t>
+          <t>A 17958-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13236,10 +13226,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45169</v>
+        <v>46122</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13251,8 +13241,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I164" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13295,7 +13290,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 36622-2023</t>
+          <t>A 36835-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13309,10 +13304,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45153</v>
+        <v>45538</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13324,8 +13319,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I165" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13368,7 +13368,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 36716-2026</t>
+          <t>A 32952-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13382,10 +13382,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46272</v>
+        <v>45125</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13398,7 +13398,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.3</v>
+        <v>5.1</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13441,7 +13441,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 31826-2026</t>
+          <t>A 18834-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13455,10 +13455,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46230</v>
+        <v>46129</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13514,7 +13514,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 31897-2026</t>
+          <t>A 18979-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13528,10 +13528,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46231</v>
+        <v>46129</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13544,7 +13544,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13587,7 +13587,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 31899-2026</t>
+          <t>A 2086-2025</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13601,10 +13601,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46231</v>
+        <v>45672</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13617,7 +13617,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13660,7 +13660,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 62541-2021</t>
+          <t>A 37195-2025</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13670,14 +13670,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44503</v>
+        <v>45875</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13690,7 +13690,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13733,7 +13733,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 28850-2024</t>
+          <t>A 48411-2022</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13747,10 +13747,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45478</v>
+        <v>44858</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13763,7 +13763,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13806,7 +13806,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 31902-2026</t>
+          <t>A 30904-2022</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13820,10 +13820,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46231</v>
+        <v>44767</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13836,7 +13836,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13879,7 +13879,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 44849-2024</t>
+          <t>A 56740-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13893,10 +13893,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45574</v>
+        <v>45244</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13909,7 +13909,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 59644-2023</t>
+          <t>A 52853-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13966,10 +13966,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45254</v>
+        <v>45226</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14025,7 +14025,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 56365-2024</t>
+          <t>A 55974-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14039,10 +14039,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45625</v>
+        <v>45623</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14055,7 +14055,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14098,7 +14098,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 6940-2024</t>
+          <t>A 53764-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14112,10 +14112,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45343</v>
+        <v>45615</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14128,7 +14128,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14171,7 +14171,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 40291-2024</t>
+          <t>A 49997-2025</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14185,10 +14185,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45554</v>
+        <v>45943</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14201,7 +14201,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14244,7 +14244,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 37994-2026</t>
+          <t>A 41163-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14258,10 +14258,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46280</v>
+        <v>45174</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14274,7 +14274,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14317,7 +14317,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 34941-2026</t>
+          <t>A 6913-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14331,10 +14331,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46259</v>
+        <v>44967</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>9.300000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14390,7 +14390,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 37997-2026</t>
+          <t>A 15374-2025</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14404,10 +14404,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46280</v>
+        <v>45747</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14420,7 +14420,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14463,7 +14463,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 33209-2023</t>
+          <t>A 20614-2025</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14477,10 +14477,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45127</v>
+        <v>45776</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14493,7 +14493,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14536,7 +14536,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 34945-2026</t>
+          <t>A 7223-2025</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14550,10 +14550,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46259</v>
+        <v>45702</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>6.2</v>
+        <v>3.5</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14609,7 +14609,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 38009-2026</t>
+          <t>A 41937-2025</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14623,10 +14623,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46280</v>
+        <v>45903</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14682,7 +14682,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 53764-2024</t>
+          <t>A 24234-2025</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14696,10 +14696,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45615</v>
+        <v>45797</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14712,7 +14712,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14755,7 +14755,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 34936-2026</t>
+          <t>A 56365-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14769,10 +14769,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46259</v>
+        <v>45625</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14785,7 +14785,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>7.4</v>
+        <v>0.6</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14828,7 +14828,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 32504-2026</t>
+          <t>A 52999-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14842,10 +14842,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46239</v>
+        <v>45226</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14857,13 +14857,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I186" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14906,7 +14901,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 32477-2026</t>
+          <t>A 7760-2025</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14920,10 +14915,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46239</v>
+        <v>45706</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14935,13 +14930,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I187" t="n">
-        <v>2.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14984,7 +14974,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 32497-2026</t>
+          <t>A 56413-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14998,10 +14988,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46239</v>
+        <v>45623</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15013,13 +15003,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I188" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15062,7 +15047,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 37946-2026</t>
+          <t>A 21017-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15076,10 +15061,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46280</v>
+        <v>46144</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15092,7 +15077,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15135,7 +15120,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 44308-2023</t>
+          <t>A 56373-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15149,10 +15134,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45188</v>
+        <v>45625</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15165,7 +15150,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15208,7 +15193,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 13530-2023</t>
+          <t>A 61405-2025</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15222,10 +15207,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45006</v>
+        <v>46001</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15237,8 +15222,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I191" t="n">
-        <v>0.5</v>
+        <v>6.6</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15281,7 +15271,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 35087-2024</t>
+          <t>A 29433-2025</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15295,10 +15285,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45527</v>
+        <v>45824</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15311,7 +15301,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15354,7 +15344,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 53769-2024</t>
+          <t>A 8936-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15368,10 +15358,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45615</v>
+        <v>46069</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15384,7 +15374,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15427,7 +15417,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 32923-2026</t>
+          <t>A 24279-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15441,10 +15431,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46244</v>
+        <v>46169</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15457,7 +15447,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>2.1</v>
+        <v>11.7</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15500,7 +15490,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 32944-2026</t>
+          <t>A 24736-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15514,10 +15504,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46244</v>
+        <v>46171</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15529,8 +15519,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I195" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15573,7 +15568,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 6102-2023</t>
+          <t>A 33654-2022</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15587,10 +15582,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44964</v>
+        <v>44789</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15646,7 +15641,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 18768-2024</t>
+          <t>A 25814-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15660,10 +15655,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45426</v>
+        <v>46178</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15676,7 +15671,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15719,7 +15714,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 56740-2023</t>
+          <t>A 26148-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15733,10 +15728,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45244</v>
+        <v>46181</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15749,7 +15744,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15792,7 +15787,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 43460-2024</t>
+          <t>A 27552-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15806,10 +15801,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45568</v>
+        <v>46190</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15822,7 +15817,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0.8</v>
+        <v>5.3</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15865,7 +15860,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 59010-2024</t>
+          <t>A 28056-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15879,10 +15874,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45635</v>
+        <v>46195</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15895,7 +15890,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15938,7 +15933,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 61817-2024</t>
+          <t>A 28068-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15952,10 +15947,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45649</v>
+        <v>46195</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15968,7 +15963,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>4.6</v>
+        <v>0.7</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16011,7 +16006,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 9973-2024</t>
+          <t>A 28309-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16025,10 +16020,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45363</v>
+        <v>46196</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16041,7 +16036,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16084,7 +16079,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 56373-2024</t>
+          <t>A 33984-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16094,14 +16089,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45625</v>
+        <v>46252</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16114,7 +16109,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16157,7 +16152,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 53805-2024</t>
+          <t>A 34112-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16171,10 +16166,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45615</v>
+        <v>46253</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16187,7 +16182,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16230,7 +16225,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 11393-2025</t>
+          <t>A 36716-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16244,10 +16239,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45726</v>
+        <v>46272</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16260,7 +16255,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16303,7 +16298,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 24356-2025</t>
+          <t>A 31902-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16317,10 +16312,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45797</v>
+        <v>46231</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16333,7 +16328,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16376,7 +16371,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 53275-2023</t>
+          <t>A 36878-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16386,14 +16381,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45229</v>
+        <v>46273</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16406,7 +16401,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>8.5</v>
+        <v>1.4</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16449,7 +16444,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 44104-2024</t>
+          <t>A 31897-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16463,10 +16458,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45572</v>
+        <v>46231</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16479,7 +16474,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16522,7 +16517,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 11563-2025</t>
+          <t>A 31899-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16532,14 +16527,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45727</v>
+        <v>46231</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16551,13 +16546,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I209" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16600,7 +16590,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 19840-2025</t>
+          <t>A 31826-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16610,14 +16600,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45771</v>
+        <v>46230</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16630,7 +16620,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16673,7 +16663,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 58420-2023</t>
+          <t>A 37997-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16683,14 +16673,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45250</v>
+        <v>46280</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16703,7 +16693,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16746,7 +16736,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 36945-2024</t>
+          <t>A 37994-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16760,10 +16750,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45538</v>
+        <v>46280</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16775,13 +16765,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I212" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16824,7 +16809,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 17892-2025</t>
+          <t>A 38009-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16838,10 +16823,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45758</v>
+        <v>46280</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16854,7 +16839,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16897,7 +16882,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 29495-2025</t>
+          <t>A 32497-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16911,10 +16896,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45824</v>
+        <v>46239</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16926,8 +16911,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I214" t="n">
-        <v>5.2</v>
+        <v>1.5</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16970,7 +16960,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 31844-2025</t>
+          <t>A 32504-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16984,10 +16974,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45834</v>
+        <v>46239</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16999,8 +16989,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I215" t="n">
-        <v>6.2</v>
+        <v>1.3</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17043,7 +17038,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 31825-2025</t>
+          <t>A 34936-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17057,10 +17052,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45834</v>
+        <v>46259</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17073,7 +17068,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>1.2</v>
+        <v>7.4</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17116,7 +17111,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 32355-2025</t>
+          <t>A 34941-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17130,10 +17125,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45837</v>
+        <v>46259</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17146,7 +17141,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>2.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17189,7 +17184,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 59069-2023</t>
+          <t>A 37946-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17199,14 +17194,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45252</v>
+        <v>46280</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17219,7 +17214,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>4.9</v>
+        <v>1.3</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17262,7 +17257,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 26356-2025</t>
+          <t>A 32477-2026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17276,10 +17271,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45805</v>
+        <v>46239</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17291,8 +17286,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I219" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17335,7 +17335,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 36208-2025</t>
+          <t>A 34945-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17349,10 +17349,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45867</v>
+        <v>46259</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17365,7 +17365,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>0.9</v>
+        <v>6.2</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17408,7 +17408,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>S 3762-2024</t>
+          <t>S 1807-2022</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17418,14 +17418,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Skogsbilväg</t>
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45558</v>
+        <v>44656</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17437,8 +17437,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I221" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17481,7 +17486,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>S 1807-2022</t>
+          <t>S 3762-2024</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17491,14 +17496,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Skogsbilväg</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>44656</v>
+        <v>45558</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17510,13 +17515,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I222" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17576,7 +17576,7 @@
         <v>45688</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17649,7 +17649,7 @@
         <v>45688</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>44705</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>

--- a/Översikt LIDKÖPING.xlsx
+++ b/Översikt LIDKÖPING.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE225"/>
+  <dimension ref="A1:AE227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44631</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>46006</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>44967</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
         <v>46171</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 32280-2022</t>
+          <t>A 28849-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44781</v>
+        <v>45478</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1097,13 +1097,13 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>8.6</v>
+        <v>2.6</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -1136,6 +1136,118 @@
         <v>0</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Talltita
+Grönsiska
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 28849-2024 artfynd.xlsx", "A 28849-2024")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 28849-2024 karta.png", "A 28849-2024")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 28849-2024 georefererad karta.tif", "A 28849-2024")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 28849-2024 FSC-klagomål.docx", "A 28849-2024")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 28849-2024 FSC-klagomål mail.docx", "A 28849-2024")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 28849-2024 tillsynsbegäran.docx", "A 28849-2024")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 28849-2024 tillsynsbegäran mail.docx", "A 28849-2024")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 28849-2024 prioriterade fågelarter.docx", "A 28849-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 32280-2022</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>44781</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Gulsparv
 Nötkråka
@@ -1143,151 +1255,39 @@
 Skogsduva</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 32280-2022 artfynd.xlsx", "A 32280-2022")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 32280-2022 karta.png", "A 32280-2022")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 32280-2022 georefererad karta.tif", "A 32280-2022")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 32280-2022 FSC-klagomål.docx", "A 32280-2022")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 32280-2022 FSC-klagomål mail.docx", "A 32280-2022")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 32280-2022 tillsynsbegäran.docx", "A 32280-2022")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 32280-2022 tillsynsbegäran mail.docx", "A 32280-2022")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 32280-2022 prioriterade fågelarter.docx", "A 32280-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 28849-2024</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45478</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>4</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Talltita
-Grönsiska
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 28849-2024 artfynd.xlsx", "A 28849-2024")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 28849-2024 karta.png", "A 28849-2024")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 28849-2024 georefererad karta.tif", "A 28849-2024")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 28849-2024 FSC-klagomål.docx", "A 28849-2024")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 28849-2024 FSC-klagomål mail.docx", "A 28849-2024")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 28849-2024 tillsynsbegäran.docx", "A 28849-2024")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 28849-2024 tillsynsbegäran mail.docx", "A 28849-2024")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 28849-2024 prioriterade fågelarter.docx", "A 28849-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>46259</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 47321-2023</t>
+          <t>A 4831-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1413,14 +1413,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45202</v>
+        <v>45688</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1433,13 +1433,13 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>7.3</v>
+        <v>1.3</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1448,7 +1448,7 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1457,10 +1457,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1469,262 +1469,262 @@
         <v>3</v>
       </c>
       <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Skogsalm
+Barkticka</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 4831-2025 artfynd.xlsx", "A 4831-2025")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 4831-2025 karta.png", "A 4831-2025")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 4831-2025 georefererad karta.tif", "A 4831-2025")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 4831-2025 FSC-klagomål.docx", "A 4831-2025")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 4831-2025 FSC-klagomål mail.docx", "A 4831-2025")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 4831-2025 tillsynsbegäran.docx", "A 4831-2025")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 4831-2025 tillsynsbegäran mail.docx", "A 4831-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 15219-2024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45400</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>3</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Tårkragskivling
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 15219-2024 artfynd.xlsx", "A 15219-2024")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 15219-2024 karta.png", "A 15219-2024")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 15219-2024 georefererad karta.tif", "A 15219-2024")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 15219-2024 FSC-klagomål.docx", "A 15219-2024")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 15219-2024 FSC-klagomål mail.docx", "A 15219-2024")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 15219-2024 tillsynsbegäran.docx", "A 15219-2024")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 15219-2024 tillsynsbegäran mail.docx", "A 15219-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 47321-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45202</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Kråka
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 47321-2023 artfynd.xlsx", "A 47321-2023")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 47321-2023 karta.png", "A 47321-2023")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 47321-2023 georefererad karta.tif", "A 47321-2023")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 47321-2023 FSC-klagomål.docx", "A 47321-2023")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 47321-2023 FSC-klagomål mail.docx", "A 47321-2023")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 47321-2023 tillsynsbegäran.docx", "A 47321-2023")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 47321-2023 tillsynsbegäran mail.docx", "A 47321-2023")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 47321-2023 prioriterade fågelarter.docx", "A 47321-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 15219-2024</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45400</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Tårkragskivling
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 15219-2024 artfynd.xlsx", "A 15219-2024")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 15219-2024 karta.png", "A 15219-2024")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 15219-2024 georefererad karta.tif", "A 15219-2024")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 15219-2024 FSC-klagomål.docx", "A 15219-2024")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 15219-2024 FSC-klagomål mail.docx", "A 15219-2024")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 15219-2024 tillsynsbegäran.docx", "A 15219-2024")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 15219-2024 tillsynsbegäran mail.docx", "A 15219-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 4831-2025</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45688</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Skogsalm
-Barkticka</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 4831-2025 artfynd.xlsx", "A 4831-2025")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 4831-2025 karta.png", "A 4831-2025")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 4831-2025 georefererad karta.tif", "A 4831-2025")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 4831-2025 FSC-klagomål.docx", "A 4831-2025")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 4831-2025 FSC-klagomål mail.docx", "A 4831-2025")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 4831-2025 tillsynsbegäran.docx", "A 4831-2025")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 4831-2025 tillsynsbegäran mail.docx", "A 4831-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>45898</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>45702</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>44630</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 44680-2023</t>
+          <t>A 10476-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45189</v>
+        <v>44987</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2126,688 +2126,688 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 10476-2023 artfynd.xlsx", "A 10476-2023")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 10476-2023 karta.png", "A 10476-2023")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 10476-2023 georefererad karta.tif", "A 10476-2023")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 10476-2023 FSC-klagomål.docx", "A 10476-2023")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 10476-2023 FSC-klagomål mail.docx", "A 10476-2023")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 10476-2023 tillsynsbegäran.docx", "A 10476-2023")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 10476-2023 tillsynsbegäran mail.docx", "A 10476-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 44680-2023</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45189</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>Trädlärka</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 44680-2023 artfynd.xlsx", "A 44680-2023")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 44680-2023 karta.png", "A 44680-2023")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 44680-2023 georefererad karta.tif", "A 44680-2023")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 44680-2023 FSC-klagomål.docx", "A 44680-2023")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 44680-2023 FSC-klagomål mail.docx", "A 44680-2023")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 44680-2023 tillsynsbegäran.docx", "A 44680-2023")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 44680-2023 tillsynsbegäran mail.docx", "A 44680-2023")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 44680-2023 prioriterade fågelarter.docx", "A 44680-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 62569-2022</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>44924</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 62569-2022 artfynd.xlsx", "A 62569-2022")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 62569-2022 karta.png", "A 62569-2022")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 62569-2022 georefererad karta.tif", "A 62569-2022")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 62569-2022 FSC-klagomål.docx", "A 62569-2022")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 62569-2022 FSC-klagomål mail.docx", "A 62569-2022")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 62569-2022 tillsynsbegäran.docx", "A 62569-2022")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 62569-2022 tillsynsbegäran mail.docx", "A 62569-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 37136-2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Fiskgjuse</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 37136-2026 artfynd.xlsx", "A 37136-2026")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 37136-2026 karta.png", "A 37136-2026")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 37136-2026 georefererad karta.tif", "A 37136-2026")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 37136-2026 FSC-klagomål.docx", "A 37136-2026")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 37136-2026 FSC-klagomål mail.docx", "A 37136-2026")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 37136-2026 tillsynsbegäran.docx", "A 37136-2026")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 37136-2026 tillsynsbegäran mail.docx", "A 37136-2026")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 37136-2026 prioriterade fågelarter.docx", "A 37136-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>A 24352-2025</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
-      <c r="D16" s="1" t="n">
+      <c r="D19" s="1" t="n">
         <v>45797</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
+      <c r="E19" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>1.1</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>1</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T19" t="n">
         <v>1</v>
       </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Spillkråka</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 24352-2025 artfynd.xlsx", "A 24352-2025")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 24352-2025 karta.png", "A 24352-2025")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 24352-2025 georefererad karta.tif", "A 24352-2025")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 24352-2025 FSC-klagomål.docx", "A 24352-2025")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 24352-2025 FSC-klagomål mail.docx", "A 24352-2025")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 24352-2025 tillsynsbegäran.docx", "A 24352-2025")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 24352-2025 tillsynsbegäran mail.docx", "A 24352-2025")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 24352-2025 prioriterade fågelarter.docx", "A 24352-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>A 62629-2022</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
         <v>44925</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
+      <c r="E20" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
         <v>1.8</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>1</v>
       </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
         <v>1</v>
       </c>
-      <c r="R17" t="n">
+      <c r="R20" t="n">
         <v>1</v>
       </c>
-      <c r="S17" t="n">
+      <c r="S20" t="n">
         <v>1</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T20" t="n">
         <v>1</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U20" t="n">
         <v>1</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Igelkott</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 62629-2022 artfynd.xlsx", "A 62629-2022")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 62629-2022 karta.png", "A 62629-2022")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 62629-2022 georefererad karta.tif", "A 62629-2022")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 62629-2022 FSC-klagomål.docx", "A 62629-2022")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 62629-2022 FSC-klagomål mail.docx", "A 62629-2022")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 62629-2022 tillsynsbegäran.docx", "A 62629-2022")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 62629-2022 tillsynsbegäran mail.docx", "A 62629-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 62569-2022</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>44924</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 61818-2024</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45649</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J21" t="n">
         <v>1</v>
       </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
         <v>1</v>
       </c>
-      <c r="R18" t="n">
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>1</v>
       </c>
-      <c r="S18" t="n">
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
         <v>1</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T21" t="n">
         <v>1</v>
       </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 62569-2022 artfynd.xlsx", "A 62569-2022")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 62569-2022 karta.png", "A 62569-2022")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 62569-2022 georefererad karta.tif", "A 62569-2022")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 62569-2022 FSC-klagomål.docx", "A 62569-2022")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 62569-2022 FSC-klagomål mail.docx", "A 62569-2022")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 62569-2022 tillsynsbegäran.docx", "A 62569-2022")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 62569-2022 tillsynsbegäran mail.docx", "A 62569-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 10476-2023</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>44987</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J19" t="n">
+      <c r="U21" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 10476-2023 artfynd.xlsx", "A 10476-2023")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 10476-2023 karta.png", "A 10476-2023")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 10476-2023 georefererad karta.tif", "A 10476-2023")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 10476-2023 FSC-klagomål.docx", "A 10476-2023")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 10476-2023 FSC-klagomål mail.docx", "A 10476-2023")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 10476-2023 tillsynsbegäran.docx", "A 10476-2023")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 10476-2023 tillsynsbegäran mail.docx", "A 10476-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 61818-2024</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45649</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Rödvingetrast</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 61818-2024 artfynd.xlsx", "A 61818-2024")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 61818-2024 karta.png", "A 61818-2024")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 61818-2024 georefererad karta.tif", "A 61818-2024")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 61818-2024 FSC-klagomål.docx", "A 61818-2024")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 61818-2024 FSC-klagomål mail.docx", "A 61818-2024")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 61818-2024 tillsynsbegäran.docx", "A 61818-2024")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 61818-2024 tillsynsbegäran mail.docx", "A 61818-2024")</f>
         <v/>
       </c>
-      <c r="AE20">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 61818-2024 prioriterade fågelarter.docx", "A 61818-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 37136-2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>46274</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Fiskgjuse</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 37136-2026 artfynd.xlsx", "A 37136-2026")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 37136-2026 karta.png", "A 37136-2026")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 37136-2026 georefererad karta.tif", "A 37136-2026")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 37136-2026 FSC-klagomål.docx", "A 37136-2026")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 37136-2026 FSC-klagomål mail.docx", "A 37136-2026")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 37136-2026 tillsynsbegäran.docx", "A 37136-2026")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 37136-2026 tillsynsbegäran mail.docx", "A 37136-2026")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 37136-2026 prioriterade fågelarter.docx", "A 37136-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>44788</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>44466</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>44831</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>44820</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>44714</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>44566</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>44546</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>44627</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>44627</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>44725</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>44805</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>44705</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>44617</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>44487</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>44487</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>44770</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 27329-2022</t>
+          <t>A 37155-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3993,10 +3993,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44742</v>
+        <v>44806</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4052,7 +4052,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 37155-2022</t>
+          <t>A 27329-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4066,10 +4066,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44806</v>
+        <v>44742</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4142,7 +4142,7 @@
         <v>44515</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>44614</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4276,7 +4276,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 62527-2021</t>
+          <t>A 28331-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4290,10 +4290,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44503</v>
+        <v>44747</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>22.6</v>
+        <v>1.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4349,7 +4349,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 61817-2024</t>
+          <t>A 8124-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4363,10 +4363,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45649</v>
+        <v>44974</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4.6</v>
+        <v>1.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4422,7 +4422,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 28331-2022</t>
+          <t>A 60465-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4436,10 +4436,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44747</v>
+        <v>45643</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4495,7 +4495,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 7248-2025</t>
+          <t>A 60642-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4505,14 +4505,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45702</v>
+        <v>45260</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4568,7 +4568,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 9973-2024</t>
+          <t>A 48301-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4582,10 +4582,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45363</v>
+        <v>45590</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4.7</v>
+        <v>1.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4641,7 +4641,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 53273-2023</t>
+          <t>A 7247-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4651,14 +4651,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45229</v>
+        <v>45702</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>6.3</v>
+        <v>1.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 49755-2022</t>
+          <t>A 30399-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4728,10 +4728,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44859</v>
+        <v>45111</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4787,7 +4787,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 1949-2025</t>
+          <t>A 11795-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4801,10 +4801,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45672</v>
+        <v>45375</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4860,7 +4860,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 53805-2024</t>
+          <t>A 55974-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4874,10 +4874,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45615</v>
+        <v>45623</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4933,7 +4933,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 6940-2024</t>
+          <t>A 48346-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4947,10 +4947,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45343</v>
+        <v>45590</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5006,7 +5006,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 62541-2021</t>
+          <t>A 49755-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5020,10 +5020,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44503</v>
+        <v>44859</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5079,7 +5079,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 11393-2025</t>
+          <t>A 39800-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5093,10 +5093,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45726</v>
+        <v>44819</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5152,7 +5152,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 59068-2023</t>
+          <t>A 63778-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5166,10 +5166,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45252</v>
+        <v>45278</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>6.4</v>
+        <v>3.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5225,7 +5225,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 136-2023</t>
+          <t>A 53279-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5235,14 +5235,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44928</v>
+        <v>45229</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4.5</v>
+        <v>0.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5298,7 +5298,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 11563-2025</t>
+          <t>A 58620-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5308,14 +5308,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45727</v>
+        <v>44902</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5327,13 +5327,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5376,7 +5371,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 53275-2023</t>
+          <t>A 1455-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5386,14 +5381,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45229</v>
+        <v>45670</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5406,7 +5401,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>8.5</v>
+        <v>1.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5449,7 +5444,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 44104-2024</t>
+          <t>A 37169-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5463,10 +5458,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45572</v>
+        <v>44806</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5479,7 +5474,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.4</v>
+        <v>17.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5522,7 +5517,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 54582-2023</t>
+          <t>A 136-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5536,10 +5531,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45233</v>
+        <v>44928</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5552,7 +5547,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5595,7 +5590,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 24356-2025</t>
+          <t>A 7223-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5609,10 +5604,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45797</v>
+        <v>45702</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5625,7 +5620,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.2</v>
+        <v>3.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5668,7 +5663,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 18768-2024</t>
+          <t>A 7248-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5682,10 +5677,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45426</v>
+        <v>45702</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5698,7 +5693,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5741,7 +5736,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 58393-2022</t>
+          <t>A 59068-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5755,10 +5750,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44901</v>
+        <v>45252</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5771,7 +5766,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.1</v>
+        <v>6.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5814,7 +5809,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 9422-2024</t>
+          <t>A 25762-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5828,10 +5823,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45359</v>
+        <v>45090</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5844,7 +5839,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5887,7 +5882,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 11949-2023</t>
+          <t>A 50577-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5901,10 +5896,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44994</v>
+        <v>45601</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5917,7 +5912,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5960,7 +5955,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 33209-2023</t>
+          <t>A 32952-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5974,10 +5969,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45127</v>
+        <v>45125</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5990,7 +5985,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.9</v>
+        <v>5.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6033,7 +6028,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 19840-2025</t>
+          <t>A 36208-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6043,14 +6038,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45771</v>
+        <v>45867</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6063,7 +6058,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6106,7 +6101,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 8626-2024</t>
+          <t>A 37195-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6116,14 +6111,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45355</v>
+        <v>45875</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6136,7 +6131,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>6.4</v>
+        <v>0.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6179,7 +6174,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 44849-2024</t>
+          <t>A 43445-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6193,10 +6188,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45574</v>
+        <v>45184</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6209,7 +6204,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6252,7 +6247,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 62551-2021</t>
+          <t>A 49997-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6266,10 +6261,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44503</v>
+        <v>45943</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6282,7 +6277,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6325,7 +6320,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 11795-2024</t>
+          <t>A 37098-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6339,10 +6334,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45375</v>
+        <v>45155</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6355,7 +6350,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6398,7 +6393,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 35047-2024</t>
+          <t>A 15374-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6412,10 +6407,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45527</v>
+        <v>45747</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6428,7 +6423,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6471,7 +6466,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 39800-2022</t>
+          <t>A 6913-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6485,10 +6480,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44819</v>
+        <v>44967</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6501,7 +6496,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6544,7 +6539,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 45608-2022</t>
+          <t>A 61312-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6558,10 +6553,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44845</v>
+        <v>45264</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6574,7 +6569,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>17</v>
+        <v>0.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6617,7 +6612,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 31605-2024</t>
+          <t>A 48411-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6631,10 +6626,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45506</v>
+        <v>44858</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6646,13 +6641,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6695,7 +6685,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 28850-2024</t>
+          <t>A 30904-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6709,10 +6699,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45478</v>
+        <v>44767</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6725,7 +6715,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6768,7 +6758,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 30484-2023</t>
+          <t>A 41937-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6782,10 +6772,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45111</v>
+        <v>45903</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6798,7 +6788,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6841,7 +6831,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 37098-2023</t>
+          <t>A 12175-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6855,10 +6845,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45155</v>
+        <v>44998</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6871,7 +6861,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6914,7 +6904,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 35087-2024</t>
+          <t>A 12819-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6928,10 +6918,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45527</v>
+        <v>44642</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6944,7 +6934,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6987,7 +6977,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 35112-2024</t>
+          <t>A 49906-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7001,10 +6991,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45529</v>
+        <v>45940</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7017,7 +7007,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7060,7 +7050,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 36816-2024</t>
+          <t>A 49909-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7074,10 +7064,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45538</v>
+        <v>45940</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7089,13 +7079,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7138,7 +7123,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 36622-2023</t>
+          <t>A 8953-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7152,10 +7137,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45153</v>
+        <v>44979</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7168,7 +7153,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7211,7 +7196,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 61312-2023</t>
+          <t>A 246-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7225,10 +7210,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45264</v>
+        <v>45660</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7241,7 +7226,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7284,7 +7269,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 10524-2024</t>
+          <t>A 52719-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7298,10 +7283,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45366</v>
+        <v>45957</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7314,7 +7299,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7357,7 +7342,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 8950-2024</t>
+          <t>A 52640-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7371,10 +7356,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45357</v>
+        <v>45954</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7387,7 +7372,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7430,7 +7415,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 58672-2022</t>
+          <t>A 53275-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7444,10 +7429,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44902</v>
+        <v>45958</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7460,7 +7445,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7503,7 +7488,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 58420-2023</t>
+          <t>A 20614-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7513,14 +7498,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45250</v>
+        <v>45776</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7533,7 +7518,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7576,7 +7561,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 43445-2023</t>
+          <t>A 7760-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7590,10 +7575,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45184</v>
+        <v>45706</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7606,7 +7591,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7649,7 +7634,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 12819-2022</t>
+          <t>A 54191-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7663,10 +7648,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44642</v>
+        <v>45964</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7679,7 +7664,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7722,7 +7707,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 36945-2024</t>
+          <t>A 2086-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7736,10 +7721,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45538</v>
+        <v>45672</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7751,13 +7736,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7800,7 +7780,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 17892-2025</t>
+          <t>A 62527-2021</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7814,10 +7794,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45758</v>
+        <v>44503</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7830,7 +7810,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.3</v>
+        <v>22.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7873,7 +7853,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 32395-2023</t>
+          <t>A 24234-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7887,10 +7867,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45120</v>
+        <v>45797</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7903,7 +7883,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7946,7 +7926,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 246-2025</t>
+          <t>A 60290-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7960,10 +7940,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45660</v>
+        <v>45642</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7976,7 +7956,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8019,7 +7999,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 49906-2025</t>
+          <t>A 35112-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8033,10 +8013,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45940</v>
+        <v>45529</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8049,7 +8029,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8092,7 +8072,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 8124-2023</t>
+          <t>A 19759-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8106,10 +8086,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44974</v>
+        <v>45432</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8122,7 +8102,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8165,7 +8145,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 49909-2025</t>
+          <t>A 56413-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8179,10 +8159,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45940</v>
+        <v>45623</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8195,7 +8175,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8238,7 +8218,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 40291-2024</t>
+          <t>A 1949-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8252,10 +8232,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45554</v>
+        <v>45672</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8268,7 +8248,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8311,7 +8291,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 48301-2024</t>
+          <t>A 696-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8325,10 +8305,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45590</v>
+        <v>45665</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8341,7 +8321,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8384,7 +8364,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 30399-2023</t>
+          <t>A 34779-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8398,10 +8378,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45111</v>
+        <v>45141</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8414,7 +8394,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8457,7 +8437,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 60465-2024</t>
+          <t>A 21017-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8471,10 +8451,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45643</v>
+        <v>46144</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8487,7 +8467,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8530,7 +8510,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 25322-2024</t>
+          <t>A 36835-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8544,10 +8524,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45462</v>
+        <v>45538</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8559,8 +8539,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8603,7 +8588,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 35202-2023</t>
+          <t>A 58393-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8613,14 +8598,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45145</v>
+        <v>44901</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8633,7 +8618,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>11.1</v>
+        <v>2.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8676,7 +8661,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 31596-2024</t>
+          <t>A 61405-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8690,10 +8675,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45506</v>
+        <v>46001</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8707,11 +8692,11 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8754,7 +8739,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 40257-2023</t>
+          <t>A 59155-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8768,10 +8753,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45169</v>
+        <v>45988</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8784,7 +8769,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8827,7 +8812,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 19759-2024</t>
+          <t>A 2872-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8841,10 +8826,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45432</v>
+        <v>44945</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8857,7 +8842,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8900,7 +8885,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 56542-2024</t>
+          <t>A 11949-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8910,14 +8895,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45625</v>
+        <v>44994</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8930,7 +8915,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8973,7 +8958,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 24759-2023</t>
+          <t>A 54582-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8987,10 +8972,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45084</v>
+        <v>45233</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9003,7 +8988,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9046,7 +9031,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 53275-2025</t>
+          <t>A 29433-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9060,10 +9045,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45958</v>
+        <v>45824</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9076,7 +9061,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9119,7 +9104,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 52640-2025</t>
+          <t>A 54279-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9133,10 +9118,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45954</v>
+        <v>45232</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9149,7 +9134,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9192,7 +9177,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 52719-2025</t>
+          <t>A 36816-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9206,10 +9191,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45957</v>
+        <v>45538</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9221,8 +9206,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9265,7 +9255,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 7247-2025</t>
+          <t>A 8936-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9279,10 +9269,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45702</v>
+        <v>46069</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9295,7 +9285,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9338,7 +9328,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 53814-2024</t>
+          <t>A 55984-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9352,10 +9342,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45615</v>
+        <v>45623</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9368,7 +9358,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9411,7 +9401,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 37169-2022</t>
+          <t>A 35047-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9425,10 +9415,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44806</v>
+        <v>45527</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9441,7 +9431,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>17.4</v>
+        <v>0.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9484,7 +9474,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 60118-2024</t>
+          <t>A 25322-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9498,10 +9488,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45642</v>
+        <v>45462</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9514,7 +9504,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9557,7 +9547,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 53769-2024</t>
+          <t>A 31596-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9571,10 +9561,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45615</v>
+        <v>45506</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9586,8 +9576,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>1.2</v>
+        <v>4.3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9630,7 +9625,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 54191-2025</t>
+          <t>A 52999-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9644,10 +9639,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45964</v>
+        <v>45226</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9660,7 +9655,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9703,7 +9698,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 55984-2024</t>
+          <t>A 5514-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9717,10 +9712,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45623</v>
+        <v>46050</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9732,8 +9727,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9776,7 +9776,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 56419-2024</t>
+          <t>A 24279-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9790,10 +9790,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45623</v>
+        <v>46169</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9806,7 +9806,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>5.6</v>
+        <v>11.7</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9849,7 +9849,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 55897-2024</t>
+          <t>A 53273-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9859,14 +9859,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45622</v>
+        <v>45229</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9879,7 +9879,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.8</v>
+        <v>6.3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9922,7 +9922,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 696-2025</t>
+          <t>A 7592-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9936,10 +9936,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45665</v>
+        <v>46061</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9952,7 +9952,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9995,7 +9995,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 50577-2024</t>
+          <t>A 24759-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10009,10 +10009,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45601</v>
+        <v>45084</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10025,7 +10025,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10068,7 +10068,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 63778-2023</t>
+          <t>A 9738-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10078,14 +10078,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45278</v>
+        <v>46072</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10141,7 +10141,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 13530-2023</t>
+          <t>A 52853-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10155,10 +10155,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45006</v>
+        <v>45226</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10214,7 +10214,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 60642-2023</t>
+          <t>A 24736-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10224,14 +10224,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45260</v>
+        <v>46171</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10243,8 +10243,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>1.3</v>
+        <v>3.8</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10287,7 +10292,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 5577-2023</t>
+          <t>A 33654-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10301,10 +10306,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44960</v>
+        <v>44789</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10360,7 +10365,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 60290-2024</t>
+          <t>A 25814-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10374,10 +10379,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45642</v>
+        <v>46178</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10390,7 +10395,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10433,7 +10438,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 44308-2023</t>
+          <t>A 7212-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10447,10 +10452,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45188</v>
+        <v>45702</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10463,7 +10468,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10506,7 +10511,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 29495-2025</t>
+          <t>A 32395-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10520,10 +10525,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45824</v>
+        <v>45120</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10536,7 +10541,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>5.2</v>
+        <v>1.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10579,7 +10584,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 12175-2023</t>
+          <t>A 14536-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10593,10 +10598,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44998</v>
+        <v>46100</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10609,7 +10614,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>4.3</v>
+        <v>2.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10652,7 +10657,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 54279-2023</t>
+          <t>A 26148-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10666,10 +10671,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45232</v>
+        <v>46181</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10682,7 +10687,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10725,7 +10730,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 7212-2025</t>
+          <t>A 6080-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10735,14 +10740,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45702</v>
+        <v>44964</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10755,7 +10760,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10798,7 +10803,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 31844-2025</t>
+          <t>A 35202-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10812,10 +10817,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45834</v>
+        <v>45145</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10828,7 +10833,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>6.2</v>
+        <v>11.1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10871,7 +10876,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 31825-2025</t>
+          <t>A 5577-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10885,10 +10890,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45834</v>
+        <v>44960</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10901,7 +10906,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10944,7 +10949,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 59155-2025</t>
+          <t>A 17533-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10958,10 +10963,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45988</v>
+        <v>46120</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10974,7 +10979,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11017,7 +11022,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 8953-2023</t>
+          <t>A 17527-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11031,10 +11036,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44979</v>
+        <v>46119</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11047,7 +11052,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11090,7 +11095,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 32355-2025</t>
+          <t>A 27552-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11104,10 +11109,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45837</v>
+        <v>46190</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11120,7 +11125,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.3</v>
+        <v>5.3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11163,7 +11168,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 59644-2023</t>
+          <t>A 17495-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11177,10 +11182,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45254</v>
+        <v>46120</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11193,7 +11198,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11236,7 +11241,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 6080-2023</t>
+          <t>A 30484-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11246,14 +11251,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44964</v>
+        <v>45111</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11266,7 +11271,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11309,7 +11314,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 5514-2026</t>
+          <t>A 17524-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11323,10 +11328,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46050</v>
+        <v>46119</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11338,13 +11343,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11387,7 +11387,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 59010-2024</t>
+          <t>A 8950-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11401,10 +11401,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45635</v>
+        <v>45357</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11417,7 +11417,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11460,7 +11460,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 7592-2026</t>
+          <t>A 17958-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11474,10 +11474,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46061</v>
+        <v>46122</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11489,8 +11489,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11533,7 +11538,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 9738-2026</t>
+          <t>A 46876-2022</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11547,10 +11552,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46072</v>
+        <v>44851</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11563,7 +11568,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.4</v>
+        <v>7.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11606,7 +11611,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 32923-2026</t>
+          <t>A 13522-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11620,10 +11625,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46244</v>
+        <v>45006</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11636,7 +11641,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11679,7 +11684,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 32944-2026</t>
+          <t>A 56419-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11693,10 +11698,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46244</v>
+        <v>45623</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11709,7 +11714,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.7</v>
+        <v>5.6</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11752,7 +11757,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 58620-2022</t>
+          <t>A 8626-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11766,10 +11771,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44902</v>
+        <v>45355</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11782,7 +11787,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.5</v>
+        <v>6.4</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11825,7 +11830,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 26356-2025</t>
+          <t>A 60112-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11839,10 +11844,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45805</v>
+        <v>45642</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11855,7 +11860,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11898,7 +11903,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 34779-2023</t>
+          <t>A 18834-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11912,10 +11917,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45141</v>
+        <v>46129</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11928,7 +11933,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11971,7 +11976,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 60112-2024</t>
+          <t>A 18979-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11985,10 +11990,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45642</v>
+        <v>46129</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12001,7 +12006,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12044,7 +12049,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 59069-2023</t>
+          <t>A 31605-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12054,14 +12059,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45252</v>
+        <v>45506</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12073,8 +12078,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>4.9</v>
+        <v>2.7</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12117,7 +12127,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 14536-2026</t>
+          <t>A 28068-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12131,10 +12141,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46100</v>
+        <v>46195</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12147,7 +12157,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12190,7 +12200,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 53279-2023</t>
+          <t>A 28056-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12200,14 +12210,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45229</v>
+        <v>46195</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12220,7 +12230,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12263,7 +12273,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 6102-2023</t>
+          <t>A 60118-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12277,10 +12287,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44964</v>
+        <v>45642</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12293,7 +12303,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12336,7 +12346,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 43460-2024</t>
+          <t>A 28309-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12350,10 +12360,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45568</v>
+        <v>46196</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12366,7 +12376,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12409,7 +12419,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 13522-2023</t>
+          <t>A 62551-2021</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12423,10 +12433,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45006</v>
+        <v>44503</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12439,7 +12449,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12482,7 +12492,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 25762-2023</t>
+          <t>A 56542-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12492,14 +12502,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45090</v>
+        <v>45625</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12555,7 +12565,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 2872-2023</t>
+          <t>A 53814-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12569,10 +12579,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44945</v>
+        <v>45615</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12585,7 +12595,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12628,7 +12638,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 46876-2022</t>
+          <t>A 10524-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12642,10 +12652,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44851</v>
+        <v>45366</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12658,7 +12668,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>7.5</v>
+        <v>0.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12701,7 +12711,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 1455-2025</t>
+          <t>A 9422-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12715,10 +12725,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45670</v>
+        <v>45359</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12731,7 +12741,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12774,7 +12784,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 48346-2024</t>
+          <t>A 45608-2022</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12788,10 +12798,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45590</v>
+        <v>44845</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12804,7 +12814,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.8</v>
+        <v>17</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12847,7 +12857,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 17527-2026</t>
+          <t>A 58672-2022</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12861,10 +12871,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46119</v>
+        <v>44902</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12877,7 +12887,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>4.4</v>
+        <v>2.4</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12920,7 +12930,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 17524-2026</t>
+          <t>A 55897-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12934,10 +12944,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46119</v>
+        <v>45622</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12950,7 +12960,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.2</v>
+        <v>1.8</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12993,7 +13003,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 36208-2025</t>
+          <t>A 33984-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13003,14 +13013,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45867</v>
+        <v>46252</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13023,7 +13033,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13066,7 +13076,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 17533-2026</t>
+          <t>A 34112-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13080,10 +13090,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46120</v>
+        <v>46253</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13096,7 +13106,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13139,7 +13149,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 17495-2026</t>
+          <t>A 41163-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13153,10 +13163,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46120</v>
+        <v>45174</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13169,7 +13179,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13212,7 +13222,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 17958-2026</t>
+          <t>A 40257-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13226,10 +13236,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46122</v>
+        <v>45169</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13241,13 +13251,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I164" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13290,7 +13295,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 36835-2024</t>
+          <t>A 36622-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13304,10 +13309,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45538</v>
+        <v>45153</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13319,13 +13324,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I165" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13368,7 +13368,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 32952-2023</t>
+          <t>A 62541-2021</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13382,10 +13382,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45125</v>
+        <v>44503</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13398,7 +13398,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>5.1</v>
+        <v>2.3</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13441,7 +13441,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 18834-2026</t>
+          <t>A 28850-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13455,10 +13455,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46129</v>
+        <v>45478</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13514,7 +13514,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 18979-2026</t>
+          <t>A 44849-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13528,10 +13528,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46129</v>
+        <v>45574</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13544,7 +13544,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13587,7 +13587,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 2086-2025</t>
+          <t>A 59644-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13601,10 +13601,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45672</v>
+        <v>45254</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13617,7 +13617,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13660,7 +13660,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 37195-2025</t>
+          <t>A 56365-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13670,14 +13670,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45875</v>
+        <v>45625</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13690,7 +13690,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13733,7 +13733,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 48411-2022</t>
+          <t>A 6940-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13747,10 +13747,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44858</v>
+        <v>45343</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13763,7 +13763,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13806,7 +13806,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 30904-2022</t>
+          <t>A 40291-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13820,10 +13820,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44767</v>
+        <v>45554</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13836,7 +13836,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>5</v>
+        <v>1.3</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13879,7 +13879,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 56740-2023</t>
+          <t>A 33209-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13893,10 +13893,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45244</v>
+        <v>45127</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13909,7 +13909,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>4.5</v>
+        <v>0.9</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 52853-2023</t>
+          <t>A 53764-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13966,10 +13966,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45226</v>
+        <v>45615</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14025,7 +14025,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 55974-2024</t>
+          <t>A 36878-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14039,10 +14039,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45623</v>
+        <v>46273</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14055,7 +14055,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14098,7 +14098,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 53764-2024</t>
+          <t>A 36716-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14112,10 +14112,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45615</v>
+        <v>46272</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14128,7 +14128,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14171,7 +14171,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 49997-2025</t>
+          <t>A 31826-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14185,10 +14185,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45943</v>
+        <v>46230</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14201,7 +14201,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14244,7 +14244,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 41163-2023</t>
+          <t>A 44308-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14258,10 +14258,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45174</v>
+        <v>45188</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14274,7 +14274,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>3.2</v>
+        <v>0.7</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14317,7 +14317,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 6913-2023</t>
+          <t>A 31897-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14331,10 +14331,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44967</v>
+        <v>46231</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14390,7 +14390,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 15374-2025</t>
+          <t>A 31899-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14404,10 +14404,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45747</v>
+        <v>46231</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14420,7 +14420,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14463,7 +14463,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 20614-2025</t>
+          <t>A 13530-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14477,10 +14477,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45776</v>
+        <v>45006</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14493,7 +14493,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14536,7 +14536,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 7223-2025</t>
+          <t>A 31902-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14550,10 +14550,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45702</v>
+        <v>46231</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14609,7 +14609,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 41937-2025</t>
+          <t>A 35087-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14623,10 +14623,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45903</v>
+        <v>45527</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14682,7 +14682,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 24234-2025</t>
+          <t>A 53769-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14696,10 +14696,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45797</v>
+        <v>45615</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14712,7 +14712,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14755,7 +14755,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 56365-2024</t>
+          <t>A 6102-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14769,10 +14769,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45625</v>
+        <v>44964</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14785,7 +14785,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14828,7 +14828,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 52999-2023</t>
+          <t>A 18768-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14842,10 +14842,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45226</v>
+        <v>45426</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14858,7 +14858,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14901,7 +14901,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 7760-2025</t>
+          <t>A 37994-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14915,10 +14915,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45706</v>
+        <v>46280</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>8.300000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14974,7 +14974,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 56413-2024</t>
+          <t>A 56740-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14988,10 +14988,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45623</v>
+        <v>45244</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15004,7 +15004,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15047,7 +15047,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 21017-2026</t>
+          <t>A 34941-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15061,10 +15061,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46144</v>
+        <v>46259</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15120,7 +15120,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 56373-2024</t>
+          <t>A 37997-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15134,10 +15134,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45625</v>
+        <v>46280</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15150,7 +15150,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15193,7 +15193,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 61405-2025</t>
+          <t>A 43460-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15207,10 +15207,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46001</v>
+        <v>45568</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15222,13 +15222,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I191" t="n">
-        <v>6.6</v>
+        <v>0.8</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15271,7 +15266,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 29433-2025</t>
+          <t>A 34945-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15285,10 +15280,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45824</v>
+        <v>46259</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15301,7 +15296,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1.4</v>
+        <v>6.2</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15344,7 +15339,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 8936-2026</t>
+          <t>A 38009-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15358,10 +15353,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46069</v>
+        <v>46280</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15374,7 +15369,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15417,7 +15412,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 24279-2026</t>
+          <t>A 59010-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15431,10 +15426,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46169</v>
+        <v>45635</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15447,7 +15442,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>11.7</v>
+        <v>3.5</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15490,7 +15485,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 24736-2026</t>
+          <t>A 34936-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15504,10 +15499,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46171</v>
+        <v>46259</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15519,13 +15514,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I195" t="n">
-        <v>3.8</v>
+        <v>7.4</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15568,7 +15558,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 33654-2022</t>
+          <t>A 32504-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15582,10 +15572,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44789</v>
+        <v>46239</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15597,8 +15587,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I196" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15641,7 +15636,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 25814-2026</t>
+          <t>A 32477-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15655,10 +15650,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46178</v>
+        <v>46239</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15670,8 +15665,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I197" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15714,7 +15714,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 26148-2026</t>
+          <t>A 32497-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15728,10 +15728,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46181</v>
+        <v>46239</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15743,8 +15743,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I198" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15787,7 +15792,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 27552-2026</t>
+          <t>A 37946-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15801,10 +15806,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46190</v>
+        <v>46280</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15817,7 +15822,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>5.3</v>
+        <v>1.3</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15860,7 +15865,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 28056-2026</t>
+          <t>A 61817-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15874,10 +15879,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46195</v>
+        <v>45649</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15890,7 +15895,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1</v>
+        <v>4.6</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15933,7 +15938,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 28068-2026</t>
+          <t>A 9973-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15947,10 +15952,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46195</v>
+        <v>45363</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15963,7 +15968,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.7</v>
+        <v>4.7</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16006,7 +16011,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 28309-2026</t>
+          <t>A 56373-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16020,10 +16025,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46196</v>
+        <v>45625</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16036,7 +16041,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16079,7 +16084,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 33984-2026</t>
+          <t>A 32923-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16089,14 +16094,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46252</v>
+        <v>46244</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16109,7 +16114,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16152,7 +16157,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 34112-2026</t>
+          <t>A 32944-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16166,10 +16171,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46253</v>
+        <v>46244</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16182,7 +16187,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16225,7 +16230,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 36716-2026</t>
+          <t>A 53805-2024</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16239,10 +16244,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46272</v>
+        <v>45615</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16255,7 +16260,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16298,7 +16303,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 31902-2026</t>
+          <t>A 11393-2025</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16312,10 +16317,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46231</v>
+        <v>45726</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16328,7 +16333,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16371,7 +16376,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 36878-2026</t>
+          <t>A 39646-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16385,10 +16390,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46273</v>
+        <v>46289</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16401,7 +16406,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1.4</v>
+        <v>12.4</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16444,7 +16449,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 31897-2026</t>
+          <t>A 24356-2025</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16458,10 +16463,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46231</v>
+        <v>45797</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16474,7 +16479,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16517,7 +16522,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 31899-2026</t>
+          <t>A 53275-2023</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16527,14 +16532,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46231</v>
+        <v>45229</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16547,7 +16552,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>0.9</v>
+        <v>8.5</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16590,7 +16595,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 31826-2026</t>
+          <t>A 44104-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16604,10 +16609,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46230</v>
+        <v>45572</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16620,7 +16625,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16663,7 +16668,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 37997-2026</t>
+          <t>A 11563-2025</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16673,14 +16678,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46280</v>
+        <v>45727</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16692,8 +16697,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I211" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16736,7 +16746,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 37994-2026</t>
+          <t>A 19840-2025</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16746,14 +16756,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46280</v>
+        <v>45771</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16766,7 +16776,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16809,7 +16819,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 38009-2026</t>
+          <t>A 39588-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16823,10 +16833,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46280</v>
+        <v>46289</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16839,7 +16849,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16882,7 +16892,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 32497-2026</t>
+          <t>A 58420-2023</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16892,14 +16902,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46239</v>
+        <v>45250</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16911,13 +16921,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I214" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16960,7 +16965,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 32504-2026</t>
+          <t>A 36945-2024</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16974,10 +16979,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46239</v>
+        <v>45538</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16991,11 +16996,11 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17038,7 +17043,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 34936-2026</t>
+          <t>A 17892-2025</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17052,10 +17057,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46259</v>
+        <v>45758</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17068,7 +17073,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>7.4</v>
+        <v>1.3</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17111,7 +17116,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 34941-2026</t>
+          <t>A 29495-2025</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17125,10 +17130,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46259</v>
+        <v>45824</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17141,7 +17146,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>9.300000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17184,7 +17189,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 37946-2026</t>
+          <t>A 31844-2025</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17198,10 +17203,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46280</v>
+        <v>45834</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17214,7 +17219,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1.3</v>
+        <v>6.2</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17257,7 +17262,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 32477-2026</t>
+          <t>A 31825-2025</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17271,10 +17276,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>46239</v>
+        <v>45834</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17286,13 +17291,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I219" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17335,7 +17335,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 34945-2026</t>
+          <t>A 32355-2025</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17349,10 +17349,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46259</v>
+        <v>45837</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17365,7 +17365,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>6.2</v>
+        <v>2.3</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17408,24 +17408,24 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>S 1807-2022</t>
+          <t>A 59069-2023</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Skogsbilväg</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>44656</v>
+        <v>45252</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17437,13 +17437,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I221" t="n">
-        <v>1.3</v>
+        <v>4.9</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17486,24 +17481,24 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>S 3762-2024</t>
+          <t>A 26356-2025</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45558</v>
+        <v>45805</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17559,7 +17554,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>S 320-2025</t>
+          <t>S 3762-2024</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17573,10 +17568,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45688</v>
+        <v>45558</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17632,148 +17627,299 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
+          <t>S 1807-2022</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Skogsbilväg</t>
+        </is>
+      </c>
+      <c r="D224" s="1" t="n">
+        <v>44656</v>
+      </c>
+      <c r="E224" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I224" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J224" t="n">
+        <v>0</v>
+      </c>
+      <c r="K224" t="n">
+        <v>0</v>
+      </c>
+      <c r="L224" t="n">
+        <v>0</v>
+      </c>
+      <c r="M224" t="n">
+        <v>0</v>
+      </c>
+      <c r="N224" t="n">
+        <v>0</v>
+      </c>
+      <c r="O224" t="n">
+        <v>0</v>
+      </c>
+      <c r="P224" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q224" t="n">
+        <v>0</v>
+      </c>
+      <c r="R224" t="n">
+        <v>0</v>
+      </c>
+      <c r="S224" t="n">
+        <v>0</v>
+      </c>
+      <c r="T224" t="n">
+        <v>0</v>
+      </c>
+      <c r="U224" t="n">
+        <v>0</v>
+      </c>
+      <c r="V224" s="2" t="inlineStr"/>
+    </row>
+    <row r="225" ht="15" customHeight="1">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>S 320-2025</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D225" s="1" t="n">
+        <v>45688</v>
+      </c>
+      <c r="E225" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I225" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J225" t="n">
+        <v>0</v>
+      </c>
+      <c r="K225" t="n">
+        <v>0</v>
+      </c>
+      <c r="L225" t="n">
+        <v>0</v>
+      </c>
+      <c r="M225" t="n">
+        <v>0</v>
+      </c>
+      <c r="N225" t="n">
+        <v>0</v>
+      </c>
+      <c r="O225" t="n">
+        <v>0</v>
+      </c>
+      <c r="P225" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q225" t="n">
+        <v>0</v>
+      </c>
+      <c r="R225" t="n">
+        <v>0</v>
+      </c>
+      <c r="S225" t="n">
+        <v>0</v>
+      </c>
+      <c r="T225" t="n">
+        <v>0</v>
+      </c>
+      <c r="U225" t="n">
+        <v>0</v>
+      </c>
+      <c r="V225" s="2" t="inlineStr"/>
+    </row>
+    <row r="226" ht="15" customHeight="1">
+      <c r="A226" t="inlineStr">
+        <is>
           <t>S 319-2025</t>
         </is>
       </c>
-      <c r="B224" t="inlineStr">
+      <c r="B226" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C224" t="inlineStr">
+      <c r="C226" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D224" s="1" t="n">
+      <c r="D226" s="1" t="n">
         <v>45688</v>
       </c>
-      <c r="E224" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I224" t="n">
+      <c r="E226" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I226" t="n">
         <v>2.9</v>
       </c>
-      <c r="J224" t="n">
-        <v>0</v>
-      </c>
-      <c r="K224" t="n">
-        <v>0</v>
-      </c>
-      <c r="L224" t="n">
-        <v>0</v>
-      </c>
-      <c r="M224" t="n">
-        <v>0</v>
-      </c>
-      <c r="N224" t="n">
-        <v>0</v>
-      </c>
-      <c r="O224" t="n">
-        <v>0</v>
-      </c>
-      <c r="P224" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
-      <c r="R224" t="n">
-        <v>0</v>
-      </c>
-      <c r="S224" t="n">
-        <v>0</v>
-      </c>
-      <c r="T224" t="n">
-        <v>0</v>
-      </c>
-      <c r="U224" t="n">
-        <v>0</v>
-      </c>
-      <c r="V224" s="2" t="inlineStr"/>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
+      <c r="J226" t="n">
+        <v>0</v>
+      </c>
+      <c r="K226" t="n">
+        <v>0</v>
+      </c>
+      <c r="L226" t="n">
+        <v>0</v>
+      </c>
+      <c r="M226" t="n">
+        <v>0</v>
+      </c>
+      <c r="N226" t="n">
+        <v>0</v>
+      </c>
+      <c r="O226" t="n">
+        <v>0</v>
+      </c>
+      <c r="P226" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q226" t="n">
+        <v>0</v>
+      </c>
+      <c r="R226" t="n">
+        <v>0</v>
+      </c>
+      <c r="S226" t="n">
+        <v>0</v>
+      </c>
+      <c r="T226" t="n">
+        <v>0</v>
+      </c>
+      <c r="U226" t="n">
+        <v>0</v>
+      </c>
+      <c r="V226" s="2" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
         <is>
           <t>S 2767-2022</t>
         </is>
       </c>
-      <c r="B225" t="inlineStr">
+      <c r="B227" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C225" t="inlineStr">
+      <c r="C227" t="inlineStr">
         <is>
           <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
-      <c r="D225" s="1" t="n">
+      <c r="D227" s="1" t="n">
         <v>44705</v>
       </c>
-      <c r="E225" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I225" t="n">
+      <c r="E227" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I227" t="n">
         <v>0.1</v>
       </c>
-      <c r="J225" t="n">
-        <v>0</v>
-      </c>
-      <c r="K225" t="n">
-        <v>0</v>
-      </c>
-      <c r="L225" t="n">
-        <v>0</v>
-      </c>
-      <c r="M225" t="n">
-        <v>0</v>
-      </c>
-      <c r="N225" t="n">
-        <v>0</v>
-      </c>
-      <c r="O225" t="n">
-        <v>0</v>
-      </c>
-      <c r="P225" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
-      <c r="R225" t="n">
-        <v>0</v>
-      </c>
-      <c r="S225" t="n">
-        <v>0</v>
-      </c>
-      <c r="T225" t="n">
-        <v>0</v>
-      </c>
-      <c r="U225" t="n">
-        <v>0</v>
-      </c>
-      <c r="V225" s="2" t="inlineStr"/>
+      <c r="J227" t="n">
+        <v>0</v>
+      </c>
+      <c r="K227" t="n">
+        <v>0</v>
+      </c>
+      <c r="L227" t="n">
+        <v>0</v>
+      </c>
+      <c r="M227" t="n">
+        <v>0</v>
+      </c>
+      <c r="N227" t="n">
+        <v>0</v>
+      </c>
+      <c r="O227" t="n">
+        <v>0</v>
+      </c>
+      <c r="P227" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q227" t="n">
+        <v>0</v>
+      </c>
+      <c r="R227" t="n">
+        <v>0</v>
+      </c>
+      <c r="S227" t="n">
+        <v>0</v>
+      </c>
+      <c r="T227" t="n">
+        <v>0</v>
+      </c>
+      <c r="U227" t="n">
+        <v>0</v>
+      </c>
+      <c r="V227" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt LIDKÖPING.xlsx
+++ b/Översikt LIDKÖPING.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE227"/>
+  <dimension ref="A1:AE228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44631</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>46006</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 6898-2023</t>
+          <t>A 24727-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44967</v>
+        <v>46171</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -861,20 +861,25 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I4" t="n">
-        <v>18</v>
+        <v>6.9</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -886,21 +891,138 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
       </c>
       <c r="T4" t="n">
+        <v>8</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Veckticka
+Blodticka
+Västlig hakmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 24727-2026 artfynd.xlsx", "A 24727-2026")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 24727-2026 karta.png", "A 24727-2026")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 24727-2026 georefererad karta.tif", "A 24727-2026")</f>
+        <v/>
+      </c>
+      <c r="Z4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/knärot/A 24727-2026 karta knärot.png", "A 24727-2026")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 24727-2026 FSC-klagomål.docx", "A 24727-2026")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 24727-2026 FSC-klagomål mail.docx", "A 24727-2026")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 24727-2026 tillsynsbegäran.docx", "A 24727-2026")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 24727-2026 tillsynsbegäran mail.docx", "A 24727-2026")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 24727-2026 prioriterade fågelarter.docx", "A 24727-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 6898-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44967</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>18</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
         <v>5</v>
       </c>
-      <c r="U4" t="n">
+      <c r="T5" t="n">
         <v>5</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="U5" t="n">
+        <v>5</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Grönsångare
 Göktyta
@@ -909,165 +1031,43 @@
 Röd glada</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 6898-2023 artfynd.xlsx", "A 6898-2023")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 6898-2023 karta.png", "A 6898-2023")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 6898-2023 georefererad karta.tif", "A 6898-2023")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 6898-2023 FSC-klagomål.docx", "A 6898-2023")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 6898-2023 FSC-klagomål mail.docx", "A 6898-2023")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 6898-2023 tillsynsbegäran.docx", "A 6898-2023")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 6898-2023 tillsynsbegäran mail.docx", "A 6898-2023")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 6898-2023 prioriterade fågelarter.docx", "A 6898-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 24727-2026</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>46171</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>5</v>
-      </c>
-      <c r="T5" t="n">
-        <v>8</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Veckticka
-Blodticka
-Västlig hakmossa
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 24727-2026 artfynd.xlsx", "A 24727-2026")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 24727-2026 karta.png", "A 24727-2026")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 24727-2026 georefererad karta.tif", "A 24727-2026")</f>
-        <v/>
-      </c>
-      <c r="Z5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/knärot/A 24727-2026 karta knärot.png", "A 24727-2026")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 24727-2026 FSC-klagomål.docx", "A 24727-2026")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 24727-2026 FSC-klagomål mail.docx", "A 24727-2026")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 24727-2026 tillsynsbegäran.docx", "A 24727-2026")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 24727-2026 tillsynsbegäran mail.docx", "A 24727-2026")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 24727-2026 prioriterade fågelarter.docx", "A 24727-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 28849-2024</t>
+          <t>A 32280-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45478</v>
+        <v>44781</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1097,13 +1097,13 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.6</v>
+        <v>8.6</v>
       </c>
       <c r="J6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -1136,6 +1136,118 @@
         <v>0</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Gulsparv
+Nötkråka
+Sotriska
+Skogsduva</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 32280-2022 artfynd.xlsx", "A 32280-2022")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 32280-2022 karta.png", "A 32280-2022")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 32280-2022 georefererad karta.tif", "A 32280-2022")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 32280-2022 FSC-klagomål.docx", "A 32280-2022")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 32280-2022 FSC-klagomål mail.docx", "A 32280-2022")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 32280-2022 tillsynsbegäran.docx", "A 32280-2022")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 32280-2022 tillsynsbegäran mail.docx", "A 32280-2022")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 32280-2022 prioriterade fågelarter.docx", "A 32280-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 28849-2024</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45478</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Entita
 Talltita
@@ -1143,111 +1255,111 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 28849-2024 artfynd.xlsx", "A 28849-2024")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 28849-2024 karta.png", "A 28849-2024")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 28849-2024 georefererad karta.tif", "A 28849-2024")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 28849-2024 FSC-klagomål.docx", "A 28849-2024")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 28849-2024 FSC-klagomål mail.docx", "A 28849-2024")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 28849-2024 tillsynsbegäran.docx", "A 28849-2024")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 28849-2024 tillsynsbegäran mail.docx", "A 28849-2024")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 28849-2024 prioriterade fågelarter.docx", "A 28849-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 32280-2022</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>44781</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J7" t="n">
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 34942-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="J8" t="n">
         <v>3</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K8" t="n">
         <v>1</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L8" t="n">
         <v>2</v>
       </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>2</v>
       </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
         <v>4</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T8" t="n">
         <v>4</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Gulsparv
 Nötkråka
@@ -1255,118 +1367,6 @@
 Skogsduva</t>
         </is>
       </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 32280-2022 artfynd.xlsx", "A 32280-2022")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 32280-2022 karta.png", "A 32280-2022")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 32280-2022 georefererad karta.tif", "A 32280-2022")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 32280-2022 FSC-klagomål.docx", "A 32280-2022")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 32280-2022 FSC-klagomål mail.docx", "A 32280-2022")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 32280-2022 tillsynsbegäran.docx", "A 32280-2022")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 32280-2022 tillsynsbegäran mail.docx", "A 32280-2022")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 32280-2022 prioriterade fågelarter.docx", "A 32280-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 34942-2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>46259</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>4</v>
-      </c>
-      <c r="T8" t="n">
-        <v>4</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Gulsparv
-Nötkråka
-Sotriska
-Skogsduva</t>
-        </is>
-      </c>
       <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 34942-2026 artfynd.xlsx", "A 34942-2026")</f>
         <v/>
@@ -1403,7 +1403,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 4831-2025</t>
+          <t>A 15219-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1413,14 +1413,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45688</v>
+        <v>45400</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1433,22 +1433,22 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.3</v>
+        <v>6.7</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1460,7 +1460,7 @@
         <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1472,148 +1472,148 @@
         <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Tårkragskivling
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 15219-2024 artfynd.xlsx", "A 15219-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 15219-2024 karta.png", "A 15219-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 15219-2024 georefererad karta.tif", "A 15219-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 15219-2024 FSC-klagomål.docx", "A 15219-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 15219-2024 FSC-klagomål mail.docx", "A 15219-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 15219-2024 tillsynsbegäran.docx", "A 15219-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 15219-2024 tillsynsbegäran mail.docx", "A 15219-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 4831-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45688</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Ask
 Skogsalm
 Barkticka</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 4831-2025 artfynd.xlsx", "A 4831-2025")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 4831-2025 karta.png", "A 4831-2025")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 4831-2025 georefererad karta.tif", "A 4831-2025")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 4831-2025 FSC-klagomål.docx", "A 4831-2025")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 4831-2025 FSC-klagomål mail.docx", "A 4831-2025")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 4831-2025 tillsynsbegäran.docx", "A 4831-2025")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 4831-2025 tillsynsbegäran mail.docx", "A 4831-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 15219-2024</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45400</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Tårkragskivling
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 15219-2024 artfynd.xlsx", "A 15219-2024")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 15219-2024 karta.png", "A 15219-2024")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 15219-2024 georefererad karta.tif", "A 15219-2024")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 15219-2024 FSC-klagomål.docx", "A 15219-2024")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 15219-2024 FSC-klagomål mail.docx", "A 15219-2024")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 15219-2024 tillsynsbegäran.docx", "A 15219-2024")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 15219-2024 tillsynsbegäran mail.docx", "A 15219-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>45202</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>45898</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>45702</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>44630</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 10476-2023</t>
+          <t>A 44680-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44987</v>
+        <v>45189</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2126,688 +2126,688 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Trädlärka</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 44680-2023 artfynd.xlsx", "A 44680-2023")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 44680-2023 karta.png", "A 44680-2023")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 44680-2023 georefererad karta.tif", "A 44680-2023")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 44680-2023 FSC-klagomål.docx", "A 44680-2023")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 44680-2023 FSC-klagomål mail.docx", "A 44680-2023")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 44680-2023 tillsynsbegäran.docx", "A 44680-2023")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 44680-2023 tillsynsbegäran mail.docx", "A 44680-2023")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 44680-2023 prioriterade fågelarter.docx", "A 44680-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 24352-2025</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45797</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J16" t="n">
         <v>1</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 24352-2025 artfynd.xlsx", "A 24352-2025")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 24352-2025 karta.png", "A 24352-2025")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 24352-2025 georefererad karta.tif", "A 24352-2025")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 24352-2025 FSC-klagomål.docx", "A 24352-2025")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 24352-2025 FSC-klagomål mail.docx", "A 24352-2025")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 24352-2025 tillsynsbegäran.docx", "A 24352-2025")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 24352-2025 tillsynsbegäran mail.docx", "A 24352-2025")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 24352-2025 prioriterade fågelarter.docx", "A 24352-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 62629-2022</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>44925</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Igelkott</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 62629-2022 artfynd.xlsx", "A 62629-2022")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 62629-2022 karta.png", "A 62629-2022")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 62629-2022 georefererad karta.tif", "A 62629-2022")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 62629-2022 FSC-klagomål.docx", "A 62629-2022")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 62629-2022 FSC-klagomål mail.docx", "A 62629-2022")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 62629-2022 tillsynsbegäran.docx", "A 62629-2022")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 62629-2022 tillsynsbegäran mail.docx", "A 62629-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 62569-2022</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>44924</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 62569-2022 artfynd.xlsx", "A 62569-2022")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 62569-2022 karta.png", "A 62569-2022")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 62569-2022 georefererad karta.tif", "A 62569-2022")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 62569-2022 FSC-klagomål.docx", "A 62569-2022")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 62569-2022 FSC-klagomål mail.docx", "A 62569-2022")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 62569-2022 tillsynsbegäran.docx", "A 62569-2022")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 62569-2022 tillsynsbegäran mail.docx", "A 62569-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 61818-2024</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45649</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 61818-2024 artfynd.xlsx", "A 61818-2024")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 61818-2024 karta.png", "A 61818-2024")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 61818-2024 georefererad karta.tif", "A 61818-2024")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 61818-2024 FSC-klagomål.docx", "A 61818-2024")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 61818-2024 FSC-klagomål mail.docx", "A 61818-2024")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 61818-2024 tillsynsbegäran.docx", "A 61818-2024")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 61818-2024 tillsynsbegäran mail.docx", "A 61818-2024")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 61818-2024 prioriterade fågelarter.docx", "A 61818-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 37136-2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Fiskgjuse</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 37136-2026 artfynd.xlsx", "A 37136-2026")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 37136-2026 karta.png", "A 37136-2026")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 37136-2026 georefererad karta.tif", "A 37136-2026")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 37136-2026 FSC-klagomål.docx", "A 37136-2026")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 37136-2026 FSC-klagomål mail.docx", "A 37136-2026")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 37136-2026 tillsynsbegäran.docx", "A 37136-2026")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 37136-2026 tillsynsbegäran mail.docx", "A 37136-2026")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 37136-2026 prioriterade fågelarter.docx", "A 37136-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 10476-2023</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>44987</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Kungsfågel</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 10476-2023 artfynd.xlsx", "A 10476-2023")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 10476-2023 karta.png", "A 10476-2023")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 10476-2023 georefererad karta.tif", "A 10476-2023")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 10476-2023 FSC-klagomål.docx", "A 10476-2023")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 10476-2023 FSC-klagomål mail.docx", "A 10476-2023")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 10476-2023 tillsynsbegäran.docx", "A 10476-2023")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 10476-2023 tillsynsbegäran mail.docx", "A 10476-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 44680-2023</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45189</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Trädlärka</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 44680-2023 artfynd.xlsx", "A 44680-2023")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 44680-2023 karta.png", "A 44680-2023")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 44680-2023 georefererad karta.tif", "A 44680-2023")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 44680-2023 FSC-klagomål.docx", "A 44680-2023")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 44680-2023 FSC-klagomål mail.docx", "A 44680-2023")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 44680-2023 tillsynsbegäran.docx", "A 44680-2023")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 44680-2023 tillsynsbegäran mail.docx", "A 44680-2023")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 44680-2023 prioriterade fågelarter.docx", "A 44680-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 62569-2022</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>44924</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 62569-2022 artfynd.xlsx", "A 62569-2022")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 62569-2022 karta.png", "A 62569-2022")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 62569-2022 georefererad karta.tif", "A 62569-2022")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 62569-2022 FSC-klagomål.docx", "A 62569-2022")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 62569-2022 FSC-klagomål mail.docx", "A 62569-2022")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 62569-2022 tillsynsbegäran.docx", "A 62569-2022")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 62569-2022 tillsynsbegäran mail.docx", "A 62569-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 37136-2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>46274</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Fiskgjuse</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 37136-2026 artfynd.xlsx", "A 37136-2026")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 37136-2026 karta.png", "A 37136-2026")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 37136-2026 georefererad karta.tif", "A 37136-2026")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 37136-2026 FSC-klagomål.docx", "A 37136-2026")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 37136-2026 FSC-klagomål mail.docx", "A 37136-2026")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 37136-2026 tillsynsbegäran.docx", "A 37136-2026")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 37136-2026 tillsynsbegäran mail.docx", "A 37136-2026")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 37136-2026 prioriterade fågelarter.docx", "A 37136-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 24352-2025</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45797</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 24352-2025 artfynd.xlsx", "A 24352-2025")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 24352-2025 karta.png", "A 24352-2025")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 24352-2025 georefererad karta.tif", "A 24352-2025")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 24352-2025 FSC-klagomål.docx", "A 24352-2025")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 24352-2025 FSC-klagomål mail.docx", "A 24352-2025")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 24352-2025 tillsynsbegäran.docx", "A 24352-2025")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 24352-2025 tillsynsbegäran mail.docx", "A 24352-2025")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 24352-2025 prioriterade fågelarter.docx", "A 24352-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 62629-2022</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>44925</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Igelkott</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 62629-2022 artfynd.xlsx", "A 62629-2022")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 62629-2022 karta.png", "A 62629-2022")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 62629-2022 georefererad karta.tif", "A 62629-2022")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 62629-2022 FSC-klagomål.docx", "A 62629-2022")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 62629-2022 FSC-klagomål mail.docx", "A 62629-2022")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 62629-2022 tillsynsbegäran.docx", "A 62629-2022")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 62629-2022 tillsynsbegäran mail.docx", "A 62629-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 61818-2024</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45649</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Rödvingetrast</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 61818-2024 artfynd.xlsx", "A 61818-2024")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 61818-2024 karta.png", "A 61818-2024")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 61818-2024 georefererad karta.tif", "A 61818-2024")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 61818-2024 FSC-klagomål.docx", "A 61818-2024")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 61818-2024 FSC-klagomål mail.docx", "A 61818-2024")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 61818-2024 tillsynsbegäran.docx", "A 61818-2024")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 61818-2024 tillsynsbegäran mail.docx", "A 61818-2024")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 61818-2024 prioriterade fågelarter.docx", "A 61818-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>44788</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>44466</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>44831</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>44820</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>44714</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>44566</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>44546</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>44627</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>44627</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>44725</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>44805</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>44705</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>44617</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>44487</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>44487</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>44770</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 37155-2022</t>
+          <t>A 27329-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3993,10 +3993,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44806</v>
+        <v>44742</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4052,7 +4052,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 27329-2022</t>
+          <t>A 37155-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4066,10 +4066,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44742</v>
+        <v>44806</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4142,7 +4142,7 @@
         <v>44515</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>44614</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>44747</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 8124-2023</t>
+          <t>A 53273-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4359,14 +4359,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44974</v>
+        <v>45229</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.5</v>
+        <v>6.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4422,7 +4422,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 60465-2024</t>
+          <t>A 7248-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4436,10 +4436,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45643</v>
+        <v>45702</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4495,7 +4495,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 60642-2023</t>
+          <t>A 49755-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4505,14 +4505,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45260</v>
+        <v>44859</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4568,7 +4568,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 48301-2024</t>
+          <t>A 6940-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4582,10 +4582,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45590</v>
+        <v>45343</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4641,7 +4641,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 7247-2025</t>
+          <t>A 59068-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4651,14 +4651,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45702</v>
+        <v>45252</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.3</v>
+        <v>6.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 30399-2023</t>
+          <t>A 136-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4728,10 +4728,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45111</v>
+        <v>44928</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.4</v>
+        <v>4.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4787,7 +4787,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 11795-2024</t>
+          <t>A 18768-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4801,10 +4801,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45375</v>
+        <v>45426</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4860,7 +4860,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 55974-2024</t>
+          <t>A 9422-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4874,10 +4874,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45623</v>
+        <v>45359</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4933,7 +4933,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 48346-2024</t>
+          <t>A 11563-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4943,14 +4943,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45590</v>
+        <v>45727</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4962,8 +4962,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5006,7 +5011,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 49755-2022</t>
+          <t>A 53275-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5016,14 +5021,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44859</v>
+        <v>45229</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5036,7 +5041,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.6</v>
+        <v>8.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5079,7 +5084,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 39800-2022</t>
+          <t>A 44104-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5093,10 +5098,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44819</v>
+        <v>45572</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5109,7 +5114,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5152,7 +5157,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 63778-2023</t>
+          <t>A 45608-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5162,14 +5167,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45278</v>
+        <v>44845</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5182,7 +5187,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.2</v>
+        <v>17</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5225,7 +5230,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 53279-2023</t>
+          <t>A 24356-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5235,14 +5240,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45229</v>
+        <v>45797</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5255,7 +5260,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5298,7 +5303,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 58620-2022</t>
+          <t>A 31605-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5312,10 +5317,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44902</v>
+        <v>45506</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5327,8 +5332,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5371,7 +5381,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 1455-2025</t>
+          <t>A 28850-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5385,10 +5395,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45670</v>
+        <v>45478</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5401,7 +5411,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5444,7 +5454,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 37169-2022</t>
+          <t>A 37098-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5458,10 +5468,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44806</v>
+        <v>45155</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5474,7 +5484,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>17.4</v>
+        <v>4.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5517,7 +5527,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 136-2023</t>
+          <t>A 19840-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5527,14 +5537,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44928</v>
+        <v>45771</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5547,7 +5557,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.5</v>
+        <v>0.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5590,7 +5600,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 7223-2025</t>
+          <t>A 36816-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5604,10 +5614,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45702</v>
+        <v>45538</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5619,8 +5629,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5663,7 +5678,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 7248-2025</t>
+          <t>A 36622-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5677,10 +5692,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45702</v>
+        <v>45153</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5693,7 +5708,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5736,7 +5751,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 59068-2023</t>
+          <t>A 5514-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5746,14 +5761,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45252</v>
+        <v>46050</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5765,8 +5780,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>6.4</v>
+        <v>2.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5809,7 +5829,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 25762-2023</t>
+          <t>A 10524-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5823,10 +5843,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45090</v>
+        <v>45366</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5839,7 +5859,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5882,7 +5902,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 50577-2024</t>
+          <t>A 8950-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5896,10 +5916,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45601</v>
+        <v>45357</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5912,7 +5932,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5955,7 +5975,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 32952-2023</t>
+          <t>A 58672-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5969,10 +5989,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45125</v>
+        <v>44902</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5985,7 +6005,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>5.1</v>
+        <v>2.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6028,7 +6048,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 36208-2025</t>
+          <t>A 43445-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6042,10 +6062,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45867</v>
+        <v>45184</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6058,7 +6078,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6101,7 +6121,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 37195-2025</t>
+          <t>A 7592-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6111,14 +6131,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45875</v>
+        <v>46061</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6131,7 +6151,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6174,7 +6194,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 43445-2023</t>
+          <t>A 32395-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6188,10 +6208,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45184</v>
+        <v>45120</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6204,7 +6224,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6247,7 +6267,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 49997-2025</t>
+          <t>A 8124-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6261,10 +6281,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45943</v>
+        <v>44974</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6277,7 +6297,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6320,7 +6340,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 37098-2023</t>
+          <t>A 9738-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6334,10 +6354,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45155</v>
+        <v>46072</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6350,7 +6370,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6393,7 +6413,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 15374-2025</t>
+          <t>A 40291-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6407,10 +6427,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45747</v>
+        <v>45554</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6423,7 +6443,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6466,7 +6486,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 6913-2023</t>
+          <t>A 12819-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6480,10 +6500,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44967</v>
+        <v>44642</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6496,7 +6516,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6539,7 +6559,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 61312-2023</t>
+          <t>A 58420-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6549,14 +6569,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45264</v>
+        <v>45250</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6569,7 +6589,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6612,7 +6632,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 48411-2022</t>
+          <t>A 49906-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6626,10 +6646,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44858</v>
+        <v>45940</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6642,7 +6662,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6685,7 +6705,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 30904-2022</t>
+          <t>A 49909-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6699,10 +6719,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44767</v>
+        <v>45940</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6715,7 +6735,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6758,7 +6778,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 41937-2025</t>
+          <t>A 7247-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6772,10 +6792,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45903</v>
+        <v>45702</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6831,7 +6851,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 12175-2023</t>
+          <t>A 14536-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6845,10 +6865,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44998</v>
+        <v>46100</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6861,7 +6881,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.3</v>
+        <v>2.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6904,7 +6924,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 12819-2022</t>
+          <t>A 53814-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6918,10 +6938,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44642</v>
+        <v>45615</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6934,7 +6954,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6977,7 +6997,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 49906-2025</t>
+          <t>A 55984-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6991,10 +7011,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45940</v>
+        <v>45623</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7007,7 +7027,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.2</v>
+        <v>1.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7050,7 +7070,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 49909-2025</t>
+          <t>A 56419-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7064,10 +7084,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45940</v>
+        <v>45623</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7080,7 +7100,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.8</v>
+        <v>5.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7123,7 +7143,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 8953-2023</t>
+          <t>A 55897-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7137,10 +7157,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44979</v>
+        <v>45622</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7153,7 +7173,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7196,7 +7216,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 246-2025</t>
+          <t>A 53275-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7210,10 +7230,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45660</v>
+        <v>45958</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7226,7 +7246,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7269,7 +7289,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 52719-2025</t>
+          <t>A 50577-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7283,10 +7303,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45957</v>
+        <v>45601</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7299,7 +7319,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7342,7 +7362,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 52640-2025</t>
+          <t>A 63778-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7352,14 +7372,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45954</v>
+        <v>45278</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7372,7 +7392,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.9</v>
+        <v>3.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7415,7 +7435,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 53275-2025</t>
+          <t>A 36945-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7429,10 +7449,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45958</v>
+        <v>45538</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7444,8 +7464,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7488,7 +7513,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 20614-2025</t>
+          <t>A 52640-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7502,10 +7527,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45776</v>
+        <v>45954</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7518,7 +7543,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7561,7 +7586,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 7760-2025</t>
+          <t>A 52719-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7575,10 +7600,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45706</v>
+        <v>45957</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7591,7 +7616,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>8.300000000000001</v>
+        <v>1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7634,7 +7659,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 54191-2025</t>
+          <t>A 17527-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7648,10 +7673,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45964</v>
+        <v>46119</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7664,7 +7689,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.4</v>
+        <v>4.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7707,7 +7732,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 2086-2025</t>
+          <t>A 17524-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7721,10 +7746,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45672</v>
+        <v>46119</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7737,7 +7762,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7780,7 +7805,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 62527-2021</t>
+          <t>A 17533-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7794,10 +7819,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44503</v>
+        <v>46120</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7810,7 +7835,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>22.6</v>
+        <v>3.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7853,7 +7878,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 24234-2025</t>
+          <t>A 17495-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7867,10 +7892,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45797</v>
+        <v>46120</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7883,7 +7908,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7926,7 +7951,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 60290-2024</t>
+          <t>A 13530-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7940,10 +7965,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45642</v>
+        <v>45006</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7956,7 +7981,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7999,7 +8024,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 35112-2024</t>
+          <t>A 17958-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8013,10 +8038,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45529</v>
+        <v>46122</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8028,8 +8053,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8072,7 +8102,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 19759-2024</t>
+          <t>A 54191-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8086,10 +8116,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45432</v>
+        <v>45964</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8102,7 +8132,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8145,7 +8175,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 56413-2024</t>
+          <t>A 5577-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8159,10 +8189,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45623</v>
+        <v>44960</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8175,7 +8205,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3.5</v>
+        <v>0.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8218,7 +8248,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 1949-2025</t>
+          <t>A 60290-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8232,10 +8262,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45672</v>
+        <v>45642</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8248,7 +8278,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8291,7 +8321,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 696-2025</t>
+          <t>A 17892-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8305,10 +8335,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45665</v>
+        <v>45758</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8321,7 +8351,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8364,7 +8394,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 34779-2023</t>
+          <t>A 18834-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8378,10 +8408,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45141</v>
+        <v>46129</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8394,7 +8424,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8437,7 +8467,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 21017-2026</t>
+          <t>A 18979-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8451,10 +8481,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46144</v>
+        <v>46129</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8467,7 +8497,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8510,7 +8540,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 36835-2024</t>
+          <t>A 12175-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8524,10 +8554,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45538</v>
+        <v>44998</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8539,13 +8569,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>2.4</v>
+        <v>4.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8588,7 +8613,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 58393-2022</t>
+          <t>A 62527-2021</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8598,14 +8623,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44901</v>
+        <v>44503</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8618,7 +8643,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.1</v>
+        <v>22.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8661,7 +8686,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 61405-2025</t>
+          <t>A 59155-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8675,10 +8700,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46001</v>
+        <v>45988</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8690,13 +8715,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>6.6</v>
+        <v>2.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8739,7 +8759,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 59155-2025</t>
+          <t>A 49997-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8753,10 +8773,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45988</v>
+        <v>45943</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8769,7 +8789,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8812,7 +8832,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 2872-2023</t>
+          <t>A 6913-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8826,10 +8846,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44945</v>
+        <v>44967</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8842,7 +8862,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8885,7 +8905,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 11949-2023</t>
+          <t>A 15374-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8899,10 +8919,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44994</v>
+        <v>45747</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8915,7 +8935,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8958,7 +8978,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 54582-2023</t>
+          <t>A 20614-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8972,10 +8992,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45233</v>
+        <v>45776</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9031,7 +9051,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 29433-2025</t>
+          <t>A 41937-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9045,10 +9065,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45824</v>
+        <v>45903</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9061,7 +9081,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9104,7 +9124,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 54279-2023</t>
+          <t>A 1949-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9118,10 +9138,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45232</v>
+        <v>45672</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9134,7 +9154,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9177,7 +9197,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 36816-2024</t>
+          <t>A 24234-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9191,10 +9211,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45538</v>
+        <v>45797</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9206,13 +9226,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9255,7 +9270,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 8936-2026</t>
+          <t>A 62541-2021</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9269,10 +9284,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46069</v>
+        <v>44503</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9285,7 +9300,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9328,7 +9343,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 55984-2024</t>
+          <t>A 29495-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9342,10 +9357,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45623</v>
+        <v>45824</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9358,7 +9373,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.7</v>
+        <v>5.2</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9401,7 +9416,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 35047-2024</t>
+          <t>A 21017-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9415,10 +9430,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45527</v>
+        <v>46144</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9431,7 +9446,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9474,7 +9489,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 25322-2024</t>
+          <t>A 31844-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9488,10 +9503,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45462</v>
+        <v>45834</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9504,7 +9519,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.3</v>
+        <v>6.2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9547,7 +9562,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 31596-2024</t>
+          <t>A 54582-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9561,10 +9576,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45506</v>
+        <v>45233</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9576,13 +9591,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>4.3</v>
+        <v>0.7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9625,7 +9635,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 52999-2023</t>
+          <t>A 31825-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9639,10 +9649,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45226</v>
+        <v>45834</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9655,7 +9665,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9698,7 +9708,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 5514-2026</t>
+          <t>A 32355-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9712,10 +9722,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46050</v>
+        <v>45837</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9727,13 +9737,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9776,7 +9781,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 24279-2026</t>
+          <t>A 61405-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9790,10 +9795,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46169</v>
+        <v>46001</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9805,8 +9810,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>11.7</v>
+        <v>6.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9849,7 +9859,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 53273-2023</t>
+          <t>A 29433-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9859,14 +9869,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45229</v>
+        <v>45824</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9879,7 +9889,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>6.3</v>
+        <v>1.4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9922,7 +9932,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 7592-2026</t>
+          <t>A 8936-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9936,10 +9946,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46061</v>
+        <v>46069</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9952,7 +9962,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9995,7 +10005,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 24759-2023</t>
+          <t>A 58393-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10005,14 +10015,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45084</v>
+        <v>44901</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10025,7 +10035,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10068,7 +10078,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 9738-2026</t>
+          <t>A 11949-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10082,10 +10092,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46072</v>
+        <v>44994</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10098,7 +10108,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10141,7 +10151,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 52853-2023</t>
+          <t>A 33209-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10155,10 +10165,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45226</v>
+        <v>45127</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10171,7 +10181,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10214,7 +10224,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 24736-2026</t>
+          <t>A 26356-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10228,10 +10238,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46171</v>
+        <v>45805</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10243,13 +10253,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>3.8</v>
+        <v>0.4</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10292,7 +10297,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 33654-2022</t>
+          <t>A 59069-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10302,14 +10307,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44789</v>
+        <v>45252</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10322,7 +10327,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.8</v>
+        <v>4.9</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10365,7 +10370,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 25814-2026</t>
+          <t>A 8626-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10379,10 +10384,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46178</v>
+        <v>45355</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10395,7 +10400,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.7</v>
+        <v>6.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10438,7 +10443,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 7212-2025</t>
+          <t>A 44849-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10452,10 +10457,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45702</v>
+        <v>45574</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10468,7 +10473,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10511,7 +10516,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 32395-2023</t>
+          <t>A 62551-2021</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10525,10 +10530,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45120</v>
+        <v>44503</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10541,7 +10546,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10584,7 +10589,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 14536-2026</t>
+          <t>A 11795-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10598,10 +10603,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46100</v>
+        <v>45375</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10614,7 +10619,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10657,7 +10662,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 26148-2026</t>
+          <t>A 35047-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10671,10 +10676,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46181</v>
+        <v>45527</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10687,7 +10692,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10730,7 +10735,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 6080-2023</t>
+          <t>A 24279-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10740,14 +10745,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44964</v>
+        <v>46169</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10760,7 +10765,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.9</v>
+        <v>11.7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10803,7 +10808,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 35202-2023</t>
+          <t>A 39800-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10817,10 +10822,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45145</v>
+        <v>44819</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10833,7 +10838,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>11.1</v>
+        <v>2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10876,7 +10881,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 5577-2023</t>
+          <t>A 24736-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10890,10 +10895,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44960</v>
+        <v>46171</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10905,8 +10910,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10949,7 +10959,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 17533-2026</t>
+          <t>A 30484-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10963,10 +10973,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46120</v>
+        <v>45111</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10979,7 +10989,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>3.8</v>
+        <v>0.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11022,7 +11032,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 17527-2026</t>
+          <t>A 36208-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11036,10 +11046,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46119</v>
+        <v>45867</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11052,7 +11062,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>4.4</v>
+        <v>0.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11095,7 +11105,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 27552-2026</t>
+          <t>A 33654-2022</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11109,10 +11119,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46190</v>
+        <v>44789</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11125,7 +11135,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>5.3</v>
+        <v>0.8</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11168,7 +11178,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 17495-2026</t>
+          <t>A 25814-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11182,10 +11192,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46120</v>
+        <v>46178</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11198,7 +11208,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11241,7 +11251,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 30484-2023</t>
+          <t>A 35087-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11255,10 +11265,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45111</v>
+        <v>45527</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11271,7 +11281,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.2</v>
+        <v>1.8</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11314,7 +11324,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 17524-2026</t>
+          <t>A 35112-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11328,10 +11338,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46119</v>
+        <v>45529</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11344,7 +11354,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11387,7 +11397,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 8950-2024</t>
+          <t>A 26148-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11401,10 +11411,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45357</v>
+        <v>46181</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11417,7 +11427,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11460,7 +11470,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 17958-2026</t>
+          <t>A 61312-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11474,10 +11484,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46122</v>
+        <v>45264</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11489,13 +11499,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I140" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11538,7 +11543,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 46876-2022</t>
+          <t>A 27552-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11552,10 +11557,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44851</v>
+        <v>46190</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11568,7 +11573,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>7.5</v>
+        <v>5.3</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11611,7 +11616,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 13522-2023</t>
+          <t>A 246-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11625,10 +11630,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45006</v>
+        <v>45660</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11641,7 +11646,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11684,7 +11689,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 56419-2024</t>
+          <t>A 37195-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11694,14 +11699,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45623</v>
+        <v>45875</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11714,7 +11719,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>5.6</v>
+        <v>0.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11757,7 +11762,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 8626-2024</t>
+          <t>A 28056-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11771,10 +11776,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45355</v>
+        <v>46195</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11787,7 +11792,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>6.4</v>
+        <v>1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11830,7 +11835,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 60112-2024</t>
+          <t>A 28068-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11844,10 +11849,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45642</v>
+        <v>46195</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11860,7 +11865,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11903,7 +11908,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 18834-2026</t>
+          <t>A 28309-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11917,10 +11922,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46129</v>
+        <v>46196</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11933,7 +11938,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11976,7 +11981,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 18979-2026</t>
+          <t>A 48301-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11990,10 +11995,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46129</v>
+        <v>45590</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12006,7 +12011,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12049,7 +12054,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 31605-2024</t>
+          <t>A 30399-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12063,10 +12068,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45506</v>
+        <v>45111</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12078,13 +12083,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12127,7 +12127,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 28068-2026</t>
+          <t>A 60465-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12141,10 +12141,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46195</v>
+        <v>45643</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12157,7 +12157,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12200,7 +12200,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 28056-2026</t>
+          <t>A 25322-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12214,10 +12214,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46195</v>
+        <v>45462</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12230,7 +12230,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12273,7 +12273,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 60118-2024</t>
+          <t>A 35202-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12287,10 +12287,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45642</v>
+        <v>45145</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.6</v>
+        <v>11.1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12346,7 +12346,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 28309-2026</t>
+          <t>A 31596-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12360,10 +12360,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46196</v>
+        <v>45506</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12375,8 +12375,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12419,7 +12424,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 62551-2021</t>
+          <t>A 40257-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12433,10 +12438,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44503</v>
+        <v>45169</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12449,7 +12454,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12492,7 +12497,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 56542-2024</t>
+          <t>A 19759-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12502,14 +12507,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45625</v>
+        <v>45432</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12565,7 +12570,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 53814-2024</t>
+          <t>A 56542-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12575,14 +12580,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45615</v>
+        <v>45625</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12595,7 +12600,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12638,7 +12643,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 10524-2024</t>
+          <t>A 24759-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12652,10 +12657,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45366</v>
+        <v>45084</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12668,7 +12673,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12711,7 +12716,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 9422-2024</t>
+          <t>A 48411-2022</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12725,10 +12730,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45359</v>
+        <v>44858</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12741,7 +12746,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12784,7 +12789,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 45608-2022</t>
+          <t>A 33984-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12794,14 +12799,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44845</v>
+        <v>46252</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12814,7 +12819,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>17</v>
+        <v>2.9</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12857,7 +12862,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 58672-2022</t>
+          <t>A 37169-2022</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12871,10 +12876,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44902</v>
+        <v>44806</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12887,7 +12892,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>2.4</v>
+        <v>17.4</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12930,7 +12935,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 55897-2024</t>
+          <t>A 60118-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12944,10 +12949,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45622</v>
+        <v>45642</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12960,7 +12965,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13003,7 +13008,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 33984-2026</t>
+          <t>A 53769-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13013,14 +13018,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46252</v>
+        <v>45615</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13033,7 +13038,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13093,7 +13098,7 @@
         <v>46253</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13149,7 +13154,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 41163-2023</t>
+          <t>A 696-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13163,10 +13168,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45174</v>
+        <v>45665</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13179,7 +13184,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13222,7 +13227,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 40257-2023</t>
+          <t>A 60642-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13232,14 +13237,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45169</v>
+        <v>45260</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13252,7 +13257,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13295,7 +13300,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 36622-2023</t>
+          <t>A 44308-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13309,10 +13314,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45153</v>
+        <v>45188</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13325,7 +13330,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13368,7 +13373,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 62541-2021</t>
+          <t>A 54279-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13382,10 +13387,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44503</v>
+        <v>45232</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13398,7 +13403,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13441,7 +13446,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 28850-2024</t>
+          <t>A 7212-2025</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13455,10 +13460,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45478</v>
+        <v>45702</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13471,7 +13476,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13514,7 +13519,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 44849-2024</t>
+          <t>A 8953-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13528,10 +13533,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45574</v>
+        <v>44979</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13544,7 +13549,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>3.8</v>
+        <v>1.1</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13604,7 +13609,7 @@
         <v>45254</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13660,7 +13665,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 56365-2024</t>
+          <t>A 36716-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13674,10 +13679,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45625</v>
+        <v>46272</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13690,7 +13695,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13733,7 +13738,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 6940-2024</t>
+          <t>A 31902-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13747,10 +13752,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45343</v>
+        <v>46231</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13763,7 +13768,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13806,7 +13811,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 40291-2024</t>
+          <t>A 36878-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13820,10 +13825,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45554</v>
+        <v>46273</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13836,7 +13841,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13879,7 +13884,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 33209-2023</t>
+          <t>A 6080-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13889,14 +13894,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45127</v>
+        <v>44964</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13909,7 +13914,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13952,7 +13957,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 53764-2024</t>
+          <t>A 31897-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13966,10 +13971,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45615</v>
+        <v>46231</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13982,7 +13987,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14025,7 +14030,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 36878-2026</t>
+          <t>A 31899-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14039,10 +14044,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46273</v>
+        <v>46231</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14055,7 +14060,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14098,7 +14103,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 36716-2026</t>
+          <t>A 31826-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14112,10 +14117,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46272</v>
+        <v>46230</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14128,7 +14133,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14171,7 +14176,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 31826-2026</t>
+          <t>A 37997-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14185,10 +14190,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46230</v>
+        <v>46280</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14201,7 +14206,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14244,7 +14249,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 44308-2023</t>
+          <t>A 37994-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14258,10 +14263,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45188</v>
+        <v>46280</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14274,7 +14279,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14317,7 +14322,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 31897-2026</t>
+          <t>A 38009-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14331,10 +14336,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46231</v>
+        <v>46280</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14347,7 +14352,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14390,7 +14395,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 31899-2026</t>
+          <t>A 59010-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14404,10 +14409,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46231</v>
+        <v>45635</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14420,7 +14425,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14463,7 +14468,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 13530-2023</t>
+          <t>A 32497-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14477,10 +14482,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45006</v>
+        <v>46239</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14492,8 +14497,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I181" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14536,7 +14546,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 31902-2026</t>
+          <t>A 32504-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14550,10 +14560,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46231</v>
+        <v>46239</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14565,8 +14575,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I182" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14609,7 +14624,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 35087-2024</t>
+          <t>A 34936-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14623,10 +14638,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45527</v>
+        <v>46259</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14639,7 +14654,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.8</v>
+        <v>7.4</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14682,7 +14697,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 53769-2024</t>
+          <t>A 34941-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14696,10 +14711,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45615</v>
+        <v>46259</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14712,7 +14727,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14755,7 +14770,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 6102-2023</t>
+          <t>A 37946-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14769,10 +14784,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44964</v>
+        <v>46280</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14785,7 +14800,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14828,7 +14843,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 18768-2024</t>
+          <t>A 32477-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14842,10 +14857,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45426</v>
+        <v>46239</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14857,8 +14872,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I186" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14901,7 +14921,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 37994-2026</t>
+          <t>A 34945-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14915,10 +14935,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46280</v>
+        <v>46259</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14931,7 +14951,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0.5</v>
+        <v>6.2</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14974,7 +14994,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 56740-2023</t>
+          <t>A 58620-2022</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14988,10 +15008,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45244</v>
+        <v>44902</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15004,7 +15024,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15047,7 +15067,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 34941-2026</t>
+          <t>A 32923-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15061,10 +15081,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46259</v>
+        <v>46244</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15077,7 +15097,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>9.300000000000001</v>
+        <v>2.1</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15120,7 +15140,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 37997-2026</t>
+          <t>A 32944-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15134,10 +15154,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46280</v>
+        <v>46244</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15150,7 +15170,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15193,7 +15213,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 43460-2024</t>
+          <t>A 39646-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15207,10 +15227,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45568</v>
+        <v>46289</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15223,7 +15243,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0.8</v>
+        <v>12.4</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15266,7 +15286,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 34945-2026</t>
+          <t>A 39914-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15276,14 +15296,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46259</v>
+        <v>46290</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15296,7 +15316,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>6.2</v>
+        <v>1.2</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15339,7 +15359,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 38009-2026</t>
+          <t>A 34779-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15353,10 +15373,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46280</v>
+        <v>45141</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15369,7 +15389,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15412,7 +15432,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 59010-2024</t>
+          <t>A 60112-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15426,10 +15446,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45635</v>
+        <v>45642</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15442,7 +15462,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15485,7 +15505,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 34936-2026</t>
+          <t>A 39588-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15499,10 +15519,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46259</v>
+        <v>46289</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15515,7 +15535,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>7.4</v>
+        <v>2.2</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15558,7 +15578,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 32504-2026</t>
+          <t>A 53279-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15568,14 +15588,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46239</v>
+        <v>45229</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15587,13 +15607,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I196" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15636,7 +15651,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 32477-2026</t>
+          <t>A 6102-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15650,10 +15665,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46239</v>
+        <v>44964</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15665,13 +15680,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I197" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15714,7 +15724,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 32497-2026</t>
+          <t>A 43460-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15728,10 +15738,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46239</v>
+        <v>45568</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15743,13 +15753,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I198" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15792,7 +15797,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 37946-2026</t>
+          <t>A 13522-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15806,10 +15811,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46280</v>
+        <v>45006</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15822,7 +15827,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15865,7 +15870,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 61817-2024</t>
+          <t>A 25762-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15879,10 +15884,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45649</v>
+        <v>45090</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15895,7 +15900,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>4.6</v>
+        <v>0.9</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15938,7 +15943,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 9973-2024</t>
+          <t>A 2872-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15952,10 +15957,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45363</v>
+        <v>44945</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15968,7 +15973,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>4.7</v>
+        <v>0.5</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16011,7 +16016,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 56373-2024</t>
+          <t>A 46876-2022</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16025,10 +16030,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45625</v>
+        <v>44851</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16041,7 +16046,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.3</v>
+        <v>7.5</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16084,7 +16089,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 32923-2026</t>
+          <t>A 1455-2025</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16098,10 +16103,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46244</v>
+        <v>45670</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16114,7 +16119,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16157,7 +16162,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 32944-2026</t>
+          <t>A 48346-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16171,10 +16176,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46244</v>
+        <v>45590</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16187,7 +16192,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16230,7 +16235,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 53805-2024</t>
+          <t>A 36835-2024</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16244,10 +16249,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45615</v>
+        <v>45538</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16259,8 +16264,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I205" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16303,7 +16313,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 11393-2025</t>
+          <t>A 32952-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16317,10 +16327,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45726</v>
+        <v>45125</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16333,7 +16343,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>0.2</v>
+        <v>5.1</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16376,7 +16386,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 39646-2026</t>
+          <t>A 2086-2025</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16390,10 +16400,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46289</v>
+        <v>45672</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16406,7 +16416,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>12.4</v>
+        <v>1.3</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16449,7 +16459,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 24356-2025</t>
+          <t>A 30904-2022</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16463,10 +16473,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45797</v>
+        <v>44767</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16479,7 +16489,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0.2</v>
+        <v>5</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16522,7 +16532,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 53275-2023</t>
+          <t>A 56740-2023</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16532,14 +16542,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45229</v>
+        <v>45244</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16552,7 +16562,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>8.5</v>
+        <v>4.5</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16595,7 +16605,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 44104-2024</t>
+          <t>A 52853-2023</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16609,10 +16619,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45572</v>
+        <v>45226</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16625,7 +16635,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16668,7 +16678,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 11563-2025</t>
+          <t>A 55974-2024</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16678,14 +16688,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45727</v>
+        <v>45623</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16697,13 +16707,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I211" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16746,7 +16751,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 19840-2025</t>
+          <t>A 53764-2024</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16756,14 +16761,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45771</v>
+        <v>45615</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16776,7 +16781,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16819,7 +16824,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 39588-2026</t>
+          <t>A 41163-2023</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16833,10 +16838,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46289</v>
+        <v>45174</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16849,7 +16854,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16892,7 +16897,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 58420-2023</t>
+          <t>A 7223-2025</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16902,14 +16907,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45250</v>
+        <v>45702</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16922,7 +16927,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16965,7 +16970,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 36945-2024</t>
+          <t>A 56365-2024</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16979,10 +16984,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45538</v>
+        <v>45625</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16994,13 +16999,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I215" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17043,7 +17043,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 17892-2025</t>
+          <t>A 52999-2023</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17057,10 +17057,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45758</v>
+        <v>45226</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17073,7 +17073,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17116,7 +17116,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 29495-2025</t>
+          <t>A 7760-2025</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17130,10 +17130,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45824</v>
+        <v>45706</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17146,7 +17146,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>5.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17189,7 +17189,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 31844-2025</t>
+          <t>A 56413-2024</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17203,10 +17203,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45834</v>
+        <v>45623</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17219,7 +17219,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>6.2</v>
+        <v>3.5</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17262,7 +17262,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 31825-2025</t>
+          <t>A 56373-2024</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17276,10 +17276,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45834</v>
+        <v>45625</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17292,7 +17292,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17335,7 +17335,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 32355-2025</t>
+          <t>A 61817-2024</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17349,10 +17349,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45837</v>
+        <v>45649</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17365,7 +17365,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>2.3</v>
+        <v>4.6</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17408,7 +17408,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 59069-2023</t>
+          <t>A 9973-2024</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17418,14 +17418,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45252</v>
+        <v>45363</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17438,7 +17438,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17481,7 +17481,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 26356-2025</t>
+          <t>A 53805-2024</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17495,10 +17495,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45805</v>
+        <v>45615</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17511,7 +17511,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17554,24 +17554,24 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>S 3762-2024</t>
+          <t>A 11393-2025</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45558</v>
+        <v>45726</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17584,7 +17584,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17644,7 +17644,7 @@
         <v>44656</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17705,7 +17705,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>S 320-2025</t>
+          <t>S 3762-2024</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17719,10 +17719,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45688</v>
+        <v>45558</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17778,7 +17778,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>S 319-2025</t>
+          <t>S 320-2025</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17795,7 +17795,7 @@
         <v>45688</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17808,118 +17808,191 @@
         </is>
       </c>
       <c r="I226" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J226" t="n">
+        <v>0</v>
+      </c>
+      <c r="K226" t="n">
+        <v>0</v>
+      </c>
+      <c r="L226" t="n">
+        <v>0</v>
+      </c>
+      <c r="M226" t="n">
+        <v>0</v>
+      </c>
+      <c r="N226" t="n">
+        <v>0</v>
+      </c>
+      <c r="O226" t="n">
+        <v>0</v>
+      </c>
+      <c r="P226" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q226" t="n">
+        <v>0</v>
+      </c>
+      <c r="R226" t="n">
+        <v>0</v>
+      </c>
+      <c r="S226" t="n">
+        <v>0</v>
+      </c>
+      <c r="T226" t="n">
+        <v>0</v>
+      </c>
+      <c r="U226" t="n">
+        <v>0</v>
+      </c>
+      <c r="V226" s="2" t="inlineStr"/>
+    </row>
+    <row r="227" ht="15" customHeight="1">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>S 319-2025</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D227" s="1" t="n">
+        <v>45688</v>
+      </c>
+      <c r="E227" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I227" t="n">
         <v>2.9</v>
       </c>
-      <c r="J226" t="n">
-        <v>0</v>
-      </c>
-      <c r="K226" t="n">
-        <v>0</v>
-      </c>
-      <c r="L226" t="n">
-        <v>0</v>
-      </c>
-      <c r="M226" t="n">
-        <v>0</v>
-      </c>
-      <c r="N226" t="n">
-        <v>0</v>
-      </c>
-      <c r="O226" t="n">
-        <v>0</v>
-      </c>
-      <c r="P226" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
-      <c r="R226" t="n">
-        <v>0</v>
-      </c>
-      <c r="S226" t="n">
-        <v>0</v>
-      </c>
-      <c r="T226" t="n">
-        <v>0</v>
-      </c>
-      <c r="U226" t="n">
-        <v>0</v>
-      </c>
-      <c r="V226" s="2" t="inlineStr"/>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
+      <c r="J227" t="n">
+        <v>0</v>
+      </c>
+      <c r="K227" t="n">
+        <v>0</v>
+      </c>
+      <c r="L227" t="n">
+        <v>0</v>
+      </c>
+      <c r="M227" t="n">
+        <v>0</v>
+      </c>
+      <c r="N227" t="n">
+        <v>0</v>
+      </c>
+      <c r="O227" t="n">
+        <v>0</v>
+      </c>
+      <c r="P227" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q227" t="n">
+        <v>0</v>
+      </c>
+      <c r="R227" t="n">
+        <v>0</v>
+      </c>
+      <c r="S227" t="n">
+        <v>0</v>
+      </c>
+      <c r="T227" t="n">
+        <v>0</v>
+      </c>
+      <c r="U227" t="n">
+        <v>0</v>
+      </c>
+      <c r="V227" s="2" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
         <is>
           <t>S 2767-2022</t>
         </is>
       </c>
-      <c r="B227" t="inlineStr">
+      <c r="B228" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C227" t="inlineStr">
+      <c r="C228" t="inlineStr">
         <is>
           <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
-      <c r="D227" s="1" t="n">
+      <c r="D228" s="1" t="n">
         <v>44705</v>
       </c>
-      <c r="E227" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I227" t="n">
+      <c r="E228" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I228" t="n">
         <v>0.1</v>
       </c>
-      <c r="J227" t="n">
-        <v>0</v>
-      </c>
-      <c r="K227" t="n">
-        <v>0</v>
-      </c>
-      <c r="L227" t="n">
-        <v>0</v>
-      </c>
-      <c r="M227" t="n">
-        <v>0</v>
-      </c>
-      <c r="N227" t="n">
-        <v>0</v>
-      </c>
-      <c r="O227" t="n">
-        <v>0</v>
-      </c>
-      <c r="P227" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q227" t="n">
-        <v>0</v>
-      </c>
-      <c r="R227" t="n">
-        <v>0</v>
-      </c>
-      <c r="S227" t="n">
-        <v>0</v>
-      </c>
-      <c r="T227" t="n">
-        <v>0</v>
-      </c>
-      <c r="U227" t="n">
-        <v>0</v>
-      </c>
-      <c r="V227" s="2" t="inlineStr"/>
+      <c r="J228" t="n">
+        <v>0</v>
+      </c>
+      <c r="K228" t="n">
+        <v>0</v>
+      </c>
+      <c r="L228" t="n">
+        <v>0</v>
+      </c>
+      <c r="M228" t="n">
+        <v>0</v>
+      </c>
+      <c r="N228" t="n">
+        <v>0</v>
+      </c>
+      <c r="O228" t="n">
+        <v>0</v>
+      </c>
+      <c r="P228" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q228" t="n">
+        <v>0</v>
+      </c>
+      <c r="R228" t="n">
+        <v>0</v>
+      </c>
+      <c r="S228" t="n">
+        <v>0</v>
+      </c>
+      <c r="T228" t="n">
+        <v>0</v>
+      </c>
+      <c r="U228" t="n">
+        <v>0</v>
+      </c>
+      <c r="V228" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt LIDKÖPING.xlsx
+++ b/Översikt LIDKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>44631</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>46006</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>46171</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>44967</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>44781</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>45478</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>46259</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>45400</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>45688</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>45202</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>45898</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>45702</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>44630</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>45189</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>45797</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>44925</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>44924</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>45649</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>46274</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>44987</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>44788</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>44466</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>44831</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>44820</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>44714</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>44566</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>44546</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>44627</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>44627</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>44725</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>44805</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>44705</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>44617</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>44487</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>44487</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>44770</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>44742</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>44806</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         <v>44515</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>44614</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>44747</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
         <v>45229</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         <v>45702</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>44859</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
         <v>45343</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>45252</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4731,7 +4731,7 @@
         <v>44928</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4804,7 +4804,7 @@
         <v>45426</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4877,7 +4877,7 @@
         <v>45359</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4950,7 +4950,7 @@
         <v>45727</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>45229</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>45572</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>44845</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>45797</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
         <v>45506</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         <v>45478</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         <v>45155</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         <v>45771</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5617,7 +5617,7 @@
         <v>45538</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>45153</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
         <v>46050</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>45366</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5919,7 +5919,7 @@
         <v>45357</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5992,7 +5992,7 @@
         <v>44902</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6065,7 +6065,7 @@
         <v>45184</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>46061</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
         <v>45120</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
         <v>44974</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6357,7 +6357,7 @@
         <v>46072</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
         <v>45554</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6503,7 +6503,7 @@
         <v>44642</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>45250</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         <v>45940</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6722,7 +6722,7 @@
         <v>45940</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         <v>45702</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         <v>46100</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6941,7 +6941,7 @@
         <v>45615</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>45623</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>45623</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
         <v>45622</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7233,7 +7233,7 @@
         <v>45958</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>45601</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         <v>45278</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         <v>45538</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
         <v>45954</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         <v>45957</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         <v>46119</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>46119</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>46120</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>46120</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>45006</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
         <v>46122</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>45964</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>44960</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8265,7 +8265,7 @@
         <v>45642</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         <v>45758</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>46129</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8484,7 +8484,7 @@
         <v>46129</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8557,7 +8557,7 @@
         <v>44998</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>44503</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8703,7 +8703,7 @@
         <v>45988</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>45943</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>44967</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>45747</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>45776</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9068,7 +9068,7 @@
         <v>45903</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
         <v>45672</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>45797</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         <v>44503</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>45824</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>46144</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         <v>45834</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>45233</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>45834</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>45837</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
         <v>46001</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9876,7 +9876,7 @@
         <v>45824</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         <v>46069</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>44901</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         <v>44994</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         <v>45127</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10241,7 +10241,7 @@
         <v>45805</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
         <v>45252</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>45355</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10460,7 +10460,7 @@
         <v>45574</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         <v>44503</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10606,7 +10606,7 @@
         <v>45375</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10679,7 +10679,7 @@
         <v>45527</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10752,7 +10752,7 @@
         <v>46169</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10825,7 +10825,7 @@
         <v>44819</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         <v>46171</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10976,7 +10976,7 @@
         <v>45111</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
         <v>45867</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         <v>44789</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11195,7 +11195,7 @@
         <v>46178</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>45527</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11341,7 +11341,7 @@
         <v>45529</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
         <v>46181</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11487,7 +11487,7 @@
         <v>45264</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         <v>46190</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11633,7 +11633,7 @@
         <v>45660</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11706,7 +11706,7 @@
         <v>45875</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11779,7 +11779,7 @@
         <v>46195</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
         <v>46195</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>46196</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11998,7 +11998,7 @@
         <v>45590</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12071,7 +12071,7 @@
         <v>45111</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>45643</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12217,7 +12217,7 @@
         <v>45462</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12290,7 +12290,7 @@
         <v>45145</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12363,7 +12363,7 @@
         <v>45506</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12441,7 +12441,7 @@
         <v>45169</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12514,7 +12514,7 @@
         <v>45432</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
         <v>45625</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12660,7 +12660,7 @@
         <v>45084</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>44858</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12806,7 +12806,7 @@
         <v>46252</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12879,7 +12879,7 @@
         <v>44806</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12952,7 +12952,7 @@
         <v>45642</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13025,7 +13025,7 @@
         <v>45615</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13098,7 +13098,7 @@
         <v>46253</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13171,7 +13171,7 @@
         <v>45665</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13244,7 +13244,7 @@
         <v>45260</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13317,7 +13317,7 @@
         <v>45188</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
         <v>45232</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
         <v>45702</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13536,7 +13536,7 @@
         <v>44979</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13609,7 +13609,7 @@
         <v>45254</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>46272</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13755,7 +13755,7 @@
         <v>46231</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
         <v>46273</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13901,7 +13901,7 @@
         <v>44964</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>46231</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14047,7 +14047,7 @@
         <v>46231</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14120,7 +14120,7 @@
         <v>46230</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14193,7 +14193,7 @@
         <v>46280</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14266,7 +14266,7 @@
         <v>46280</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14339,7 +14339,7 @@
         <v>46280</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14412,7 +14412,7 @@
         <v>45635</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14485,7 +14485,7 @@
         <v>46239</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14563,7 +14563,7 @@
         <v>46239</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14641,7 +14641,7 @@
         <v>46259</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14714,7 +14714,7 @@
         <v>46259</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14787,7 +14787,7 @@
         <v>46280</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>46239</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14938,7 +14938,7 @@
         <v>46259</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15011,7 +15011,7 @@
         <v>44902</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15084,7 +15084,7 @@
         <v>46244</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
         <v>46244</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15230,7 +15230,7 @@
         <v>46289</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15303,7 +15303,7 @@
         <v>46290</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15376,7 +15376,7 @@
         <v>45141</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15449,7 +15449,7 @@
         <v>45642</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15522,7 +15522,7 @@
         <v>46289</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>45229</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15668,7 +15668,7 @@
         <v>44964</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15741,7 +15741,7 @@
         <v>45568</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15814,7 +15814,7 @@
         <v>45006</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15887,7 +15887,7 @@
         <v>45090</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>44945</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16033,7 +16033,7 @@
         <v>44851</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16106,7 +16106,7 @@
         <v>45670</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16179,7 +16179,7 @@
         <v>45590</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16252,7 +16252,7 @@
         <v>45538</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16330,7 +16330,7 @@
         <v>45125</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16403,7 +16403,7 @@
         <v>45672</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16476,7 +16476,7 @@
         <v>44767</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16549,7 +16549,7 @@
         <v>45244</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16622,7 +16622,7 @@
         <v>45226</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16695,7 +16695,7 @@
         <v>45623</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16768,7 +16768,7 @@
         <v>45615</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16841,7 +16841,7 @@
         <v>45174</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16914,7 +16914,7 @@
         <v>45702</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16987,7 +16987,7 @@
         <v>45625</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17060,7 +17060,7 @@
         <v>45226</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
         <v>45706</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>45623</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17279,7 +17279,7 @@
         <v>45625</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17352,7 +17352,7 @@
         <v>45649</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17425,7 +17425,7 @@
         <v>45363</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17498,7 +17498,7 @@
         <v>45615</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17571,7 +17571,7 @@
         <v>45726</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17644,7 +17644,7 @@
         <v>44656</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>45558</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17795,7 +17795,7 @@
         <v>45688</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17868,7 +17868,7 @@
         <v>45688</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17941,7 +17941,7 @@
         <v>44705</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>

--- a/Översikt LIDKÖPING.xlsx
+++ b/Översikt LIDKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>44631</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>46006</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>46171</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>44967</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>44781</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>45478</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>46259</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>45400</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>45688</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>45202</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>45898</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>45702</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>44630</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>45189</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>45797</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>44925</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>44924</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>45649</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>46274</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>44987</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>44788</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>44466</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>44831</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>44820</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>44714</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>44566</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>44546</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>44627</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>44627</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>44725</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>44805</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>44705</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>44617</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>44487</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>44487</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>44770</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>44742</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>44806</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         <v>44515</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>44614</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>44747</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
         <v>45229</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         <v>45702</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>44859</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
         <v>45343</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>45252</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4731,7 +4731,7 @@
         <v>44928</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4804,7 +4804,7 @@
         <v>45426</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4877,7 +4877,7 @@
         <v>45359</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4950,7 +4950,7 @@
         <v>45727</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>45229</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>45572</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>44845</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>45797</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
         <v>45506</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         <v>45478</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         <v>45155</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         <v>45771</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5617,7 +5617,7 @@
         <v>45538</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>45153</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
         <v>46050</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>45366</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5919,7 +5919,7 @@
         <v>45357</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5992,7 +5992,7 @@
         <v>44902</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6065,7 +6065,7 @@
         <v>45184</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>46061</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
         <v>45120</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
         <v>44974</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6357,7 +6357,7 @@
         <v>46072</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
         <v>45554</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6503,7 +6503,7 @@
         <v>44642</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>45250</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         <v>45940</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6722,7 +6722,7 @@
         <v>45940</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         <v>45702</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         <v>46100</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6941,7 +6941,7 @@
         <v>45615</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>45623</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>45623</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
         <v>45622</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7233,7 +7233,7 @@
         <v>45958</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>45601</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         <v>45278</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         <v>45538</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
         <v>45954</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         <v>45957</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         <v>46119</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>46119</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>46120</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>46120</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>45006</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
         <v>46122</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>45964</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>44960</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8265,7 +8265,7 @@
         <v>45642</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         <v>45758</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>46129</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8484,7 +8484,7 @@
         <v>46129</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8557,7 +8557,7 @@
         <v>44998</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>44503</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8703,7 +8703,7 @@
         <v>45988</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>45943</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>44967</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>45747</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>45776</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9068,7 +9068,7 @@
         <v>45903</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
         <v>45672</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>45797</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         <v>44503</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>45824</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>46144</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         <v>45834</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>45233</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>45834</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>45837</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
         <v>46001</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9876,7 +9876,7 @@
         <v>45824</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         <v>46069</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>44901</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         <v>44994</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         <v>45127</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10241,7 +10241,7 @@
         <v>45805</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
         <v>45252</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>45355</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10460,7 +10460,7 @@
         <v>45574</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         <v>44503</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10606,7 +10606,7 @@
         <v>45375</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10679,7 +10679,7 @@
         <v>45527</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10752,7 +10752,7 @@
         <v>46169</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10825,7 +10825,7 @@
         <v>44819</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         <v>46171</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10976,7 +10976,7 @@
         <v>45111</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
         <v>45867</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         <v>44789</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11195,7 +11195,7 @@
         <v>46178</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>45527</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11341,7 +11341,7 @@
         <v>45529</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
         <v>46181</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11487,7 +11487,7 @@
         <v>45264</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         <v>46190</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11633,7 +11633,7 @@
         <v>45660</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11706,7 +11706,7 @@
         <v>45875</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11779,7 +11779,7 @@
         <v>46195</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
         <v>46195</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>46196</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11998,7 +11998,7 @@
         <v>45590</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12071,7 +12071,7 @@
         <v>45111</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>45643</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12217,7 +12217,7 @@
         <v>45462</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12290,7 +12290,7 @@
         <v>45145</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12363,7 +12363,7 @@
         <v>45506</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12441,7 +12441,7 @@
         <v>45169</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12514,7 +12514,7 @@
         <v>45432</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
         <v>45625</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12660,7 +12660,7 @@
         <v>45084</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>44858</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12806,7 +12806,7 @@
         <v>46252</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12879,7 +12879,7 @@
         <v>44806</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12952,7 +12952,7 @@
         <v>45642</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13025,7 +13025,7 @@
         <v>45615</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13098,7 +13098,7 @@
         <v>46253</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13171,7 +13171,7 @@
         <v>45665</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13244,7 +13244,7 @@
         <v>45260</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13317,7 +13317,7 @@
         <v>45188</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
         <v>45232</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
         <v>45702</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13536,7 +13536,7 @@
         <v>44979</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13609,7 +13609,7 @@
         <v>45254</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>46272</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13755,7 +13755,7 @@
         <v>46231</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
         <v>46273</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13901,7 +13901,7 @@
         <v>44964</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>46231</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14047,7 +14047,7 @@
         <v>46231</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14120,7 +14120,7 @@
         <v>46230</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14193,7 +14193,7 @@
         <v>46280</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14266,7 +14266,7 @@
         <v>46280</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14339,7 +14339,7 @@
         <v>46280</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14412,7 +14412,7 @@
         <v>45635</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14485,7 +14485,7 @@
         <v>46239</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14563,7 +14563,7 @@
         <v>46239</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14641,7 +14641,7 @@
         <v>46259</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14714,7 +14714,7 @@
         <v>46259</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14787,7 +14787,7 @@
         <v>46280</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>46239</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14938,7 +14938,7 @@
         <v>46259</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15011,7 +15011,7 @@
         <v>44902</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15084,7 +15084,7 @@
         <v>46244</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
         <v>46244</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15230,7 +15230,7 @@
         <v>46289</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15303,7 +15303,7 @@
         <v>46290</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15376,7 +15376,7 @@
         <v>45141</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15449,7 +15449,7 @@
         <v>45642</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15522,7 +15522,7 @@
         <v>46289</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>45229</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15668,7 +15668,7 @@
         <v>44964</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15741,7 +15741,7 @@
         <v>45568</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15814,7 +15814,7 @@
         <v>45006</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15887,7 +15887,7 @@
         <v>45090</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>44945</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16033,7 +16033,7 @@
         <v>44851</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16106,7 +16106,7 @@
         <v>45670</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16179,7 +16179,7 @@
         <v>45590</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16252,7 +16252,7 @@
         <v>45538</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16330,7 +16330,7 @@
         <v>45125</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16403,7 +16403,7 @@
         <v>45672</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16476,7 +16476,7 @@
         <v>44767</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16549,7 +16549,7 @@
         <v>45244</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16622,7 +16622,7 @@
         <v>45226</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16695,7 +16695,7 @@
         <v>45623</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16768,7 +16768,7 @@
         <v>45615</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16841,7 +16841,7 @@
         <v>45174</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16914,7 +16914,7 @@
         <v>45702</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16987,7 +16987,7 @@
         <v>45625</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17060,7 +17060,7 @@
         <v>45226</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
         <v>45706</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>45623</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17279,7 +17279,7 @@
         <v>45625</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17352,7 +17352,7 @@
         <v>45649</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17425,7 +17425,7 @@
         <v>45363</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17498,7 +17498,7 @@
         <v>45615</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17571,7 +17571,7 @@
         <v>45726</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17644,7 +17644,7 @@
         <v>44656</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>45558</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17795,7 +17795,7 @@
         <v>45688</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17868,7 +17868,7 @@
         <v>45688</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17941,7 +17941,7 @@
         <v>44705</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>

--- a/Översikt LIDKÖPING.xlsx
+++ b/Översikt LIDKÖPING.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE228"/>
+  <dimension ref="A1:AE227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44631</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>46006</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 24727-2026</t>
+          <t>A 6898-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46171</v>
+        <v>44967</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -861,25 +861,20 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I4" t="n">
-        <v>6.9</v>
+        <v>18</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -891,21 +886,139 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
       </c>
       <c r="T4" t="n">
+        <v>5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>5</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Grönsångare
+Göktyta
+Älg
+Buskskvätta
+Röd glada</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 6898-2023 artfynd.xlsx", "A 6898-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 6898-2023 karta.png", "A 6898-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 6898-2023 georefererad karta.tif", "A 6898-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 6898-2023 FSC-klagomål.docx", "A 6898-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 6898-2023 FSC-klagomål mail.docx", "A 6898-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 6898-2023 tillsynsbegäran.docx", "A 6898-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 6898-2023 tillsynsbegäran mail.docx", "A 6898-2023")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 6898-2023 prioriterade fågelarter.docx", "A 6898-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 24727-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="n">
         <v>8</v>
       </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Veckticka
@@ -914,160 +1027,47 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 24727-2026 artfynd.xlsx", "A 24727-2026")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 24727-2026 karta.png", "A 24727-2026")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 24727-2026 georefererad karta.tif", "A 24727-2026")</f>
         <v/>
       </c>
-      <c r="Z4">
+      <c r="Z5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/knärot/A 24727-2026 karta knärot.png", "A 24727-2026")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 24727-2026 FSC-klagomål.docx", "A 24727-2026")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 24727-2026 FSC-klagomål mail.docx", "A 24727-2026")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 24727-2026 tillsynsbegäran.docx", "A 24727-2026")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 24727-2026 tillsynsbegäran mail.docx", "A 24727-2026")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 24727-2026 prioriterade fågelarter.docx", "A 24727-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 6898-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>44967</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>18</v>
-      </c>
-      <c r="J5" t="n">
-        <v>4</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>3</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>5</v>
-      </c>
-      <c r="T5" t="n">
-        <v>5</v>
-      </c>
-      <c r="U5" t="n">
-        <v>5</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Grönsångare
-Göktyta
-Älg
-Buskskvätta
-Röd glada</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 6898-2023 artfynd.xlsx", "A 6898-2023")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 6898-2023 karta.png", "A 6898-2023")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 6898-2023 georefererad karta.tif", "A 6898-2023")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 6898-2023 FSC-klagomål.docx", "A 6898-2023")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 6898-2023 FSC-klagomål mail.docx", "A 6898-2023")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 6898-2023 tillsynsbegäran.docx", "A 6898-2023")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 6898-2023 tillsynsbegäran mail.docx", "A 6898-2023")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 6898-2023 prioriterade fågelarter.docx", "A 6898-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 32280-2022</t>
+          <t>A 28849-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44781</v>
+        <v>45478</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1097,13 +1097,13 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>8.6</v>
+        <v>2.6</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -1136,6 +1136,118 @@
         <v>0</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Talltita
+Grönsiska
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 28849-2024 artfynd.xlsx", "A 28849-2024")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 28849-2024 karta.png", "A 28849-2024")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 28849-2024 georefererad karta.tif", "A 28849-2024")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 28849-2024 FSC-klagomål.docx", "A 28849-2024")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 28849-2024 FSC-klagomål mail.docx", "A 28849-2024")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 28849-2024 tillsynsbegäran.docx", "A 28849-2024")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 28849-2024 tillsynsbegäran mail.docx", "A 28849-2024")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 28849-2024 prioriterade fågelarter.docx", "A 28849-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 32280-2022</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>44781</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Gulsparv
 Nötkråka
@@ -1143,151 +1255,39 @@
 Skogsduva</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 32280-2022 artfynd.xlsx", "A 32280-2022")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 32280-2022 karta.png", "A 32280-2022")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 32280-2022 georefererad karta.tif", "A 32280-2022")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 32280-2022 FSC-klagomål.docx", "A 32280-2022")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 32280-2022 FSC-klagomål mail.docx", "A 32280-2022")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 32280-2022 tillsynsbegäran.docx", "A 32280-2022")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 32280-2022 tillsynsbegäran mail.docx", "A 32280-2022")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 32280-2022 prioriterade fågelarter.docx", "A 32280-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 28849-2024</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45478</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>4</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Talltita
-Grönsiska
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 28849-2024 artfynd.xlsx", "A 28849-2024")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 28849-2024 karta.png", "A 28849-2024")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 28849-2024 georefererad karta.tif", "A 28849-2024")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 28849-2024 FSC-klagomål.docx", "A 28849-2024")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 28849-2024 FSC-klagomål mail.docx", "A 28849-2024")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 28849-2024 tillsynsbegäran.docx", "A 28849-2024")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 28849-2024 tillsynsbegäran mail.docx", "A 28849-2024")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 28849-2024 prioriterade fågelarter.docx", "A 28849-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>46259</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 15219-2024</t>
+          <t>A 4831-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1413,14 +1413,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45400</v>
+        <v>45688</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1433,22 +1433,22 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>6.7</v>
+        <v>1.3</v>
       </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>1</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
       <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>2</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1460,7 +1460,7 @@
         <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1472,148 +1472,148 @@
         <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Skogsalm
+Barkticka</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 4831-2025 artfynd.xlsx", "A 4831-2025")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 4831-2025 karta.png", "A 4831-2025")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 4831-2025 georefererad karta.tif", "A 4831-2025")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 4831-2025 FSC-klagomål.docx", "A 4831-2025")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 4831-2025 FSC-klagomål mail.docx", "A 4831-2025")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 4831-2025 tillsynsbegäran.docx", "A 4831-2025")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 4831-2025 tillsynsbegäran mail.docx", "A 4831-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 15219-2024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45400</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Tårkragskivling
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 15219-2024 artfynd.xlsx", "A 15219-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 15219-2024 karta.png", "A 15219-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 15219-2024 georefererad karta.tif", "A 15219-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 15219-2024 FSC-klagomål.docx", "A 15219-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 15219-2024 FSC-klagomål mail.docx", "A 15219-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 15219-2024 tillsynsbegäran.docx", "A 15219-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 15219-2024 tillsynsbegäran mail.docx", "A 15219-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 4831-2025</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45688</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Skogsalm
-Barkticka</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 4831-2025 artfynd.xlsx", "A 4831-2025")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 4831-2025 karta.png", "A 4831-2025")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 4831-2025 georefererad karta.tif", "A 4831-2025")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 4831-2025 FSC-klagomål.docx", "A 4831-2025")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 4831-2025 FSC-klagomål mail.docx", "A 4831-2025")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 4831-2025 tillsynsbegäran.docx", "A 4831-2025")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 4831-2025 tillsynsbegäran mail.docx", "A 4831-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>45202</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>45898</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>45702</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>44630</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 44680-2023</t>
+          <t>A 24352-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2070,14 +2070,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45189</v>
+        <v>45797</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2130,46 +2130,46 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 44680-2023 artfynd.xlsx", "A 44680-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 24352-2025 artfynd.xlsx", "A 24352-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 44680-2023 karta.png", "A 44680-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 24352-2025 karta.png", "A 24352-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 44680-2023 georefererad karta.tif", "A 44680-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 24352-2025 georefererad karta.tif", "A 24352-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 44680-2023 FSC-klagomål.docx", "A 44680-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 24352-2025 FSC-klagomål.docx", "A 24352-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 44680-2023 FSC-klagomål mail.docx", "A 44680-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 24352-2025 FSC-klagomål mail.docx", "A 24352-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 44680-2023 tillsynsbegäran.docx", "A 44680-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 24352-2025 tillsynsbegäran.docx", "A 24352-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 44680-2023 tillsynsbegäran mail.docx", "A 44680-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 24352-2025 tillsynsbegäran mail.docx", "A 24352-2025")</f>
         <v/>
       </c>
       <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 44680-2023 prioriterade fågelarter.docx", "A 44680-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 24352-2025 prioriterade fågelarter.docx", "A 24352-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 24352-2025</t>
+          <t>A 10476-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2179,14 +2179,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45797</v>
+        <v>44987</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2235,43 +2235,39 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 24352-2025 artfynd.xlsx", "A 24352-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 10476-2023 artfynd.xlsx", "A 10476-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 24352-2025 karta.png", "A 24352-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 10476-2023 karta.png", "A 10476-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 24352-2025 georefererad karta.tif", "A 24352-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 10476-2023 georefererad karta.tif", "A 10476-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 24352-2025 FSC-klagomål.docx", "A 24352-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 10476-2023 FSC-klagomål.docx", "A 10476-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 24352-2025 FSC-klagomål mail.docx", "A 24352-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 10476-2023 FSC-klagomål mail.docx", "A 10476-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 24352-2025 tillsynsbegäran.docx", "A 24352-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 10476-2023 tillsynsbegäran.docx", "A 10476-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 24352-2025 tillsynsbegäran mail.docx", "A 24352-2025")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 24352-2025 prioriterade fågelarter.docx", "A 24352-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 10476-2023 tillsynsbegäran mail.docx", "A 10476-2023")</f>
         <v/>
       </c>
     </row>
@@ -2295,7 +2291,7 @@
         <v>44925</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2383,7 +2379,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 62569-2022</t>
+          <t>A 44680-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2397,10 +2393,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44924</v>
+        <v>45189</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2413,10 +2409,10 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -2428,7 +2424,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2437,10 +2433,10 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2453,361 +2449,365 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
+          <t>Trädlärka</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 44680-2023 artfynd.xlsx", "A 44680-2023")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 44680-2023 karta.png", "A 44680-2023")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 44680-2023 georefererad karta.tif", "A 44680-2023")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 44680-2023 FSC-klagomål.docx", "A 44680-2023")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 44680-2023 FSC-klagomål mail.docx", "A 44680-2023")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 44680-2023 tillsynsbegäran.docx", "A 44680-2023")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 44680-2023 tillsynsbegäran mail.docx", "A 44680-2023")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 44680-2023 prioriterade fågelarter.docx", "A 44680-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 62569-2022</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>44924</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
           <t>Skogsalm</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 62569-2022 artfynd.xlsx", "A 62569-2022")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 62569-2022 karta.png", "A 62569-2022")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 62569-2022 georefererad karta.tif", "A 62569-2022")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 62569-2022 FSC-klagomål.docx", "A 62569-2022")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 62569-2022 FSC-klagomål mail.docx", "A 62569-2022")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 62569-2022 tillsynsbegäran.docx", "A 62569-2022")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 62569-2022 tillsynsbegäran mail.docx", "A 62569-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>A 61818-2024</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
         <v>45649</v>
       </c>
-      <c r="E19" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
+      <c r="E20" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
         <v>6.2</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J20" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
         <v>1</v>
       </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
         <v>1</v>
       </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>1</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T20" t="n">
         <v>1</v>
       </c>
-      <c r="U19" t="n">
+      <c r="U20" t="n">
         <v>1</v>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Rödvingetrast</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 61818-2024 artfynd.xlsx", "A 61818-2024")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 61818-2024 karta.png", "A 61818-2024")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 61818-2024 georefererad karta.tif", "A 61818-2024")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 61818-2024 FSC-klagomål.docx", "A 61818-2024")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 61818-2024 FSC-klagomål mail.docx", "A 61818-2024")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 61818-2024 tillsynsbegäran.docx", "A 61818-2024")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 61818-2024 tillsynsbegäran mail.docx", "A 61818-2024")</f>
         <v/>
       </c>
-      <c r="AE19">
+      <c r="AE20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 61818-2024 prioriterade fågelarter.docx", "A 61818-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>A 37136-2026</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
         <v>46274</v>
       </c>
-      <c r="E20" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
+      <c r="E21" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>LIDKÖPING</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
         <v>6.6</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J21" t="n">
         <v>1</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
         <v>1</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T21" t="n">
         <v>1</v>
       </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Fiskgjuse</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 37136-2026 artfynd.xlsx", "A 37136-2026")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 37136-2026 karta.png", "A 37136-2026")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 37136-2026 georefererad karta.tif", "A 37136-2026")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 37136-2026 FSC-klagomål.docx", "A 37136-2026")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 37136-2026 FSC-klagomål mail.docx", "A 37136-2026")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 37136-2026 tillsynsbegäran.docx", "A 37136-2026")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 37136-2026 tillsynsbegäran mail.docx", "A 37136-2026")</f>
         <v/>
       </c>
-      <c r="AE20">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1494/fåglar/A 37136-2026 prioriterade fågelarter.docx", "A 37136-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 10476-2023</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>44987</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>LIDKÖPING</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/artfynd/A 10476-2023 artfynd.xlsx", "A 10476-2023")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor/A 10476-2023 karta.png", "A 10476-2023")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/kartor_geotiff/A 10476-2023 georefererad karta.tif", "A 10476-2023")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomål/A 10476-2023 FSC-klagomål.docx", "A 10476-2023")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/klagomålsmail/A 10476-2023 FSC-klagomål mail.docx", "A 10476-2023")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsyn/A 10476-2023 tillsynsbegäran.docx", "A 10476-2023")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1494/tillsynsmail/A 10476-2023 tillsynsbegäran mail.docx", "A 10476-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>44788</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 52954-2021</t>
+          <t>A 42563-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2898,10 +2898,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44466</v>
+        <v>44831</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2957,7 +2957,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 42563-2022</t>
+          <t>A 40028-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2971,10 +2971,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44831</v>
+        <v>44820</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3030,7 +3030,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 40028-2022</t>
+          <t>A 22660-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3044,10 +3044,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44820</v>
+        <v>44714</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3103,7 +3103,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 22660-2022</t>
+          <t>A 560-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3117,10 +3117,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44714</v>
+        <v>44566</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3176,7 +3176,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 560-2022</t>
+          <t>A 72632-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3190,10 +3190,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44566</v>
+        <v>44546</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3249,7 +3249,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 72632-2021</t>
+          <t>A 10791-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3263,10 +3263,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44546</v>
+        <v>44627</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3322,7 +3322,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 10791-2022</t>
+          <t>A 10811-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3339,7 +3339,7 @@
         <v>44627</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3395,7 +3395,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 10811-2022</t>
+          <t>A 24139-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44627</v>
+        <v>44725</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3468,7 +3468,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 24139-2022</t>
+          <t>A 36744-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3482,10 +3482,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44725</v>
+        <v>44805</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3541,7 +3541,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 36744-2022</t>
+          <t>A 21335-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3555,10 +3555,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44805</v>
+        <v>44705</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3614,7 +3614,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 21335-2022</t>
+          <t>A 9528-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3628,10 +3628,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44705</v>
+        <v>44617</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.8</v>
+        <v>20.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3687,7 +3687,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 9528-2022</t>
+          <t>A 58120-2021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3701,10 +3701,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44617</v>
+        <v>44487</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>20.3</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3760,7 +3760,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 58120-2021</t>
+          <t>A 57990-2021</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3777,7 +3777,7 @@
         <v>44487</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3833,7 +3833,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 57990-2021</t>
+          <t>A 31159-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3847,10 +3847,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44487</v>
+        <v>44770</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3906,7 +3906,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 31159-2022</t>
+          <t>A 27329-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44770</v>
+        <v>44742</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3979,7 +3979,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 27329-2022</t>
+          <t>A 37155-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3993,10 +3993,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44742</v>
+        <v>44806</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4052,7 +4052,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 37155-2022</t>
+          <t>A 65341-2021</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4066,10 +4066,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44806</v>
+        <v>44515</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4125,7 +4125,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 65341-2021</t>
+          <t>A 8790-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4139,10 +4139,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44515</v>
+        <v>44614</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4154,8 +4154,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4198,7 +4203,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 8790-2022</t>
+          <t>A 28331-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4212,10 +4217,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44614</v>
+        <v>44747</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4227,13 +4232,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4276,7 +4276,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 28331-2022</t>
+          <t>A 60465-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4290,10 +4290,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44747</v>
+        <v>45643</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4349,7 +4349,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 53273-2023</t>
+          <t>A 60642-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4363,10 +4363,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45229</v>
+        <v>45260</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>6.3</v>
+        <v>1.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4422,7 +4422,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 7248-2025</t>
+          <t>A 48301-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4436,10 +4436,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45702</v>
+        <v>45590</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4495,7 +4495,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 49755-2022</t>
+          <t>A 56373-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4509,10 +4509,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44859</v>
+        <v>45625</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4568,7 +4568,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 6940-2024</t>
+          <t>A 8124-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4582,10 +4582,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45343</v>
+        <v>44974</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4641,7 +4641,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 59068-2023</t>
+          <t>A 30399-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4651,14 +4651,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45252</v>
+        <v>45111</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>6.4</v>
+        <v>1.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 136-2023</t>
+          <t>A 48411-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4728,10 +4728,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44928</v>
+        <v>44858</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4.5</v>
+        <v>2.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4787,7 +4787,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 18768-2024</t>
+          <t>A 7247-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4801,10 +4801,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45426</v>
+        <v>45702</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4860,7 +4860,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 9422-2024</t>
+          <t>A 53805-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4874,10 +4874,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45359</v>
+        <v>45615</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4933,7 +4933,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 11563-2025</t>
+          <t>A 11393-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4943,14 +4943,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45727</v>
+        <v>45726</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4962,13 +4962,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5011,7 +5006,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 53275-2023</t>
+          <t>A 24356-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5021,14 +5016,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45229</v>
+        <v>45797</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5041,7 +5036,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>8.5</v>
+        <v>0.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5084,7 +5079,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 44104-2024</t>
+          <t>A 53275-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5094,14 +5089,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45572</v>
+        <v>45229</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5114,7 +5109,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.4</v>
+        <v>8.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5157,7 +5152,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 45608-2022</t>
+          <t>A 44104-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5171,10 +5166,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44845</v>
+        <v>45572</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5187,7 +5182,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>17</v>
+        <v>2.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5230,7 +5225,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 24356-2025</t>
+          <t>A 11563-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5240,14 +5235,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45797</v>
+        <v>45727</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5259,8 +5254,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5303,7 +5303,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 31605-2024</t>
+          <t>A 19840-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5313,14 +5313,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45506</v>
+        <v>45771</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5332,13 +5332,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>2.7</v>
+        <v>0.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5381,7 +5376,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 28850-2024</t>
+          <t>A 58420-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5391,14 +5386,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45478</v>
+        <v>45250</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5411,7 +5406,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5454,7 +5449,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 37098-2023</t>
+          <t>A 36945-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5468,10 +5463,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45155</v>
+        <v>45538</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5483,8 +5478,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5527,7 +5527,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 19840-2025</t>
+          <t>A 17892-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5537,14 +5537,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45771</v>
+        <v>45758</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5557,7 +5557,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5600,7 +5600,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 36816-2024</t>
+          <t>A 11795-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5614,10 +5614,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45538</v>
+        <v>45375</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5629,13 +5629,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5678,7 +5673,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 36622-2023</t>
+          <t>A 29495-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5692,10 +5687,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45153</v>
+        <v>45824</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5708,7 +5703,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.4</v>
+        <v>5.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5751,7 +5746,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 5514-2026</t>
+          <t>A 55974-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5765,10 +5760,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46050</v>
+        <v>45623</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5780,13 +5775,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5829,7 +5819,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 10524-2024</t>
+          <t>A 48346-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5843,10 +5833,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45366</v>
+        <v>45590</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5859,7 +5849,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5902,7 +5892,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 8950-2024</t>
+          <t>A 39800-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5916,10 +5906,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45357</v>
+        <v>44819</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5932,7 +5922,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5975,7 +5965,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 58672-2022</t>
+          <t>A 31844-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5989,10 +5979,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44902</v>
+        <v>45834</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6005,7 +5995,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.4</v>
+        <v>6.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6048,7 +6038,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 43445-2023</t>
+          <t>A 31825-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6062,10 +6052,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45184</v>
+        <v>45834</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6078,7 +6068,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6121,7 +6111,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 7592-2026</t>
+          <t>A 12819-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6135,10 +6125,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46061</v>
+        <v>44642</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6151,7 +6141,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6194,7 +6184,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 32395-2023</t>
+          <t>A 49755-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6208,10 +6198,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45120</v>
+        <v>44859</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6224,7 +6214,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6267,7 +6257,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 8124-2023</t>
+          <t>A 32355-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6281,10 +6271,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44974</v>
+        <v>45837</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6297,7 +6287,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6340,7 +6330,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 9738-2026</t>
+          <t>A 63778-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6350,14 +6340,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46072</v>
+        <v>45278</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6370,7 +6360,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6413,7 +6403,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 40291-2024</t>
+          <t>A 53279-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6423,14 +6413,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45554</v>
+        <v>45229</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6443,7 +6433,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6486,7 +6476,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 12819-2022</t>
+          <t>A 49906-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6500,10 +6490,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44642</v>
+        <v>45940</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6516,7 +6506,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6559,7 +6549,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 58420-2023</t>
+          <t>A 59069-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6573,10 +6563,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45250</v>
+        <v>45252</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6589,7 +6579,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.5</v>
+        <v>4.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6632,7 +6622,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 49906-2025</t>
+          <t>A 49909-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6649,7 +6639,7 @@
         <v>45940</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6662,7 +6652,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6705,7 +6695,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 49909-2025</t>
+          <t>A 26356-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6719,10 +6709,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45940</v>
+        <v>45805</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6735,7 +6725,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.8</v>
+        <v>0.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6778,7 +6768,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 7247-2025</t>
+          <t>A 136-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6792,10 +6782,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45702</v>
+        <v>44928</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6808,7 +6798,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.3</v>
+        <v>4.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6851,7 +6841,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 14536-2026</t>
+          <t>A 58620-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6865,10 +6855,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46100</v>
+        <v>44902</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6881,7 +6871,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6924,7 +6914,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 53814-2024</t>
+          <t>A 1455-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6938,10 +6928,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45615</v>
+        <v>45670</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6954,7 +6944,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6997,7 +6987,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 55984-2024</t>
+          <t>A 37169-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7011,10 +7001,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45623</v>
+        <v>44806</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7027,7 +7017,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.7</v>
+        <v>17.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7070,7 +7060,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 56419-2024</t>
+          <t>A 7223-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7084,10 +7074,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45623</v>
+        <v>45702</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7100,7 +7090,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>5.6</v>
+        <v>3.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7143,7 +7133,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 55897-2024</t>
+          <t>A 52719-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7157,10 +7147,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45622</v>
+        <v>45957</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7173,7 +7163,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7216,7 +7206,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 53275-2025</t>
+          <t>A 52640-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7230,10 +7220,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45958</v>
+        <v>45954</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7246,7 +7236,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7289,7 +7279,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 50577-2024</t>
+          <t>A 36208-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7303,10 +7293,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45601</v>
+        <v>45867</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7319,7 +7309,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7362,7 +7352,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 63778-2023</t>
+          <t>A 53275-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7372,14 +7362,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45278</v>
+        <v>45958</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7392,7 +7382,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.2</v>
+        <v>0.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7435,7 +7425,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 36945-2024</t>
+          <t>A 59068-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7445,14 +7435,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45538</v>
+        <v>45252</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7464,13 +7454,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>1</v>
+        <v>6.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7513,7 +7498,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 52640-2025</t>
+          <t>A 7248-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7527,10 +7512,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45954</v>
+        <v>45702</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7543,7 +7528,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7586,7 +7571,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 52719-2025</t>
+          <t>A 37195-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7596,14 +7581,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45957</v>
+        <v>45875</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7616,7 +7601,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7659,7 +7644,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 17527-2026</t>
+          <t>A 54191-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7673,10 +7658,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46119</v>
+        <v>45964</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7689,7 +7674,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4.4</v>
+        <v>0.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7732,7 +7717,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 17524-2026</t>
+          <t>A 50577-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7746,10 +7731,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46119</v>
+        <v>45601</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7762,7 +7747,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7805,7 +7790,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 17533-2026</t>
+          <t>A 25762-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7819,10 +7804,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46120</v>
+        <v>45090</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7835,7 +7820,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7878,7 +7863,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 17495-2026</t>
+          <t>A 32952-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7892,10 +7877,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46120</v>
+        <v>45125</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7908,7 +7893,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.6</v>
+        <v>5.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7951,7 +7936,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 13530-2023</t>
+          <t>A 43445-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7965,10 +7950,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45006</v>
+        <v>45184</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7981,7 +7966,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8024,7 +8009,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 17958-2026</t>
+          <t>A 5514-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8038,10 +8023,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46122</v>
+        <v>46050</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8055,11 +8040,11 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8102,7 +8087,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 54191-2025</t>
+          <t>A 37098-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8116,10 +8101,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45964</v>
+        <v>45155</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8132,7 +8117,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.4</v>
+        <v>4.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8175,7 +8160,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 5577-2023</t>
+          <t>A 59155-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8189,10 +8174,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44960</v>
+        <v>45988</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8205,7 +8190,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8248,7 +8233,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 60290-2024</t>
+          <t>A 61312-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8262,10 +8247,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45642</v>
+        <v>45264</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8278,7 +8263,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8321,7 +8306,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 17892-2025</t>
+          <t>A 7592-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8335,10 +8320,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45758</v>
+        <v>46061</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8351,7 +8336,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8394,7 +8379,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 18834-2026</t>
+          <t>A 9738-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8408,10 +8393,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46129</v>
+        <v>46072</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8424,7 +8409,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8467,7 +8452,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 18979-2026</t>
+          <t>A 30904-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8481,10 +8466,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46129</v>
+        <v>44767</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8497,7 +8482,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.8</v>
+        <v>5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8557,7 +8542,7 @@
         <v>44998</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8613,7 +8598,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 62527-2021</t>
+          <t>A 8953-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8627,10 +8612,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44503</v>
+        <v>44979</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8643,7 +8628,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>22.6</v>
+        <v>1.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8686,7 +8671,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 59155-2025</t>
+          <t>A 14536-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8700,10 +8685,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45988</v>
+        <v>46100</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8716,7 +8701,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8759,7 +8744,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 49997-2025</t>
+          <t>A 246-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8773,10 +8758,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45943</v>
+        <v>45660</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8789,7 +8774,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8832,7 +8817,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 6913-2023</t>
+          <t>A 7760-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8846,10 +8831,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44967</v>
+        <v>45706</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8862,7 +8847,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8905,7 +8890,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 15374-2025</t>
+          <t>A 2086-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8919,10 +8904,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45747</v>
+        <v>45672</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8935,7 +8920,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8978,7 +8963,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 20614-2025</t>
+          <t>A 17533-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8992,10 +8977,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45776</v>
+        <v>46120</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9008,7 +8993,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.7</v>
+        <v>3.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9051,7 +9036,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 41937-2025</t>
+          <t>A 17527-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9065,10 +9050,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45903</v>
+        <v>46119</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9081,7 +9066,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.3</v>
+        <v>4.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9124,7 +9109,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 1949-2025</t>
+          <t>A 17495-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9138,10 +9123,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45672</v>
+        <v>46120</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9154,7 +9139,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9197,7 +9182,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 24234-2025</t>
+          <t>A 62527-2021</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9211,10 +9196,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45797</v>
+        <v>44503</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9227,7 +9212,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.8</v>
+        <v>22.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9270,7 +9255,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 62541-2021</t>
+          <t>A 17524-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9284,10 +9269,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44503</v>
+        <v>46119</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9300,7 +9285,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.3</v>
+        <v>0.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9343,7 +9328,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 29495-2025</t>
+          <t>A 17958-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9357,10 +9342,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45824</v>
+        <v>46122</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9372,8 +9357,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>5.2</v>
+        <v>0.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9416,7 +9406,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 21017-2026</t>
+          <t>A 60290-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9430,10 +9420,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46144</v>
+        <v>45642</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9446,7 +9436,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9489,7 +9479,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 31844-2025</t>
+          <t>A 35112-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9503,10 +9493,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45834</v>
+        <v>45529</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9519,7 +9509,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>6.2</v>
+        <v>1.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9562,7 +9552,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 54582-2023</t>
+          <t>A 19759-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9576,10 +9566,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45233</v>
+        <v>45432</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9592,7 +9582,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9635,7 +9625,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 31825-2025</t>
+          <t>A 18834-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9649,10 +9639,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45834</v>
+        <v>46129</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9665,7 +9655,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9708,7 +9698,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 32355-2025</t>
+          <t>A 18979-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9722,10 +9712,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45837</v>
+        <v>46129</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9738,7 +9728,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9781,7 +9771,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 61405-2025</t>
+          <t>A 56413-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9795,10 +9785,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46001</v>
+        <v>45623</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9810,13 +9800,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I117" t="n">
-        <v>6.6</v>
+        <v>3.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9859,7 +9844,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 29433-2025</t>
+          <t>A 1949-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9873,10 +9858,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45824</v>
+        <v>45672</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9889,7 +9874,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9932,7 +9917,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 8936-2026</t>
+          <t>A 696-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9946,10 +9931,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46069</v>
+        <v>45665</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9962,7 +9947,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10005,7 +9990,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 58393-2022</t>
+          <t>A 34779-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10015,14 +10000,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44901</v>
+        <v>45141</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10035,7 +10020,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10078,7 +10063,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 11949-2023</t>
+          <t>A 49997-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10092,10 +10077,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44994</v>
+        <v>45943</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10108,7 +10093,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10151,7 +10136,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 33209-2023</t>
+          <t>A 36835-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10165,10 +10150,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45127</v>
+        <v>45538</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10180,8 +10165,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10224,7 +10214,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 26356-2025</t>
+          <t>A 58393-2022</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10234,14 +10224,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45805</v>
+        <v>44901</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10254,7 +10244,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10297,7 +10287,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 59069-2023</t>
+          <t>A 15374-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10307,14 +10297,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45252</v>
+        <v>45747</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10327,7 +10317,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10370,7 +10360,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 8626-2024</t>
+          <t>A 2872-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10384,10 +10374,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45355</v>
+        <v>44945</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10400,7 +10390,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>6.4</v>
+        <v>0.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10443,7 +10433,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 44849-2024</t>
+          <t>A 6913-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10457,10 +10447,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45574</v>
+        <v>44967</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10473,7 +10463,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10516,7 +10506,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 62551-2021</t>
+          <t>A 41937-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10530,10 +10520,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44503</v>
+        <v>45903</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10546,7 +10536,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10589,7 +10579,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 11795-2024</t>
+          <t>A 11949-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10603,10 +10593,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45375</v>
+        <v>44994</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10619,7 +10609,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10662,7 +10652,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 35047-2024</t>
+          <t>A 54582-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10676,10 +10666,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45527</v>
+        <v>45233</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10692,7 +10682,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10735,7 +10725,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 24279-2026</t>
+          <t>A 54279-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10749,10 +10739,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46169</v>
+        <v>45232</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10765,7 +10755,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>11.7</v>
+        <v>1.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10808,7 +10798,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 39800-2022</t>
+          <t>A 36816-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10822,10 +10812,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44819</v>
+        <v>45538</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10837,8 +10827,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10881,7 +10876,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 24736-2026</t>
+          <t>A 55984-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10895,10 +10890,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46171</v>
+        <v>45623</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10910,13 +10905,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10959,7 +10949,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 30484-2023</t>
+          <t>A 35047-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10973,10 +10963,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45111</v>
+        <v>45527</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10989,7 +10979,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11032,7 +11022,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 36208-2025</t>
+          <t>A 20614-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11046,10 +11036,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45867</v>
+        <v>45776</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11062,7 +11052,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11105,7 +11095,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 33654-2022</t>
+          <t>A 25322-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11119,10 +11109,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44789</v>
+        <v>45462</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11135,7 +11125,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11178,7 +11168,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 25814-2026</t>
+          <t>A 24234-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11192,10 +11182,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46178</v>
+        <v>45797</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11208,7 +11198,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11251,7 +11241,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 35087-2024</t>
+          <t>A 31596-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11265,10 +11255,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45527</v>
+        <v>45506</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11280,8 +11270,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I137" t="n">
-        <v>1.8</v>
+        <v>4.3</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11324,7 +11319,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 35112-2024</t>
+          <t>A 52999-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11338,10 +11333,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45529</v>
+        <v>45226</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11354,7 +11349,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11397,7 +11392,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 26148-2026</t>
+          <t>A 21017-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11411,10 +11406,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46181</v>
+        <v>46144</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11427,7 +11422,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11470,7 +11465,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 61312-2023</t>
+          <t>A 61405-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11484,10 +11479,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45264</v>
+        <v>46001</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11499,8 +11494,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>0.7</v>
+        <v>6.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11543,7 +11543,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 27552-2026</t>
+          <t>A 53273-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11553,14 +11553,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46190</v>
+        <v>45229</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11573,7 +11573,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>5.3</v>
+        <v>6.3</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11616,7 +11616,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 246-2025</t>
+          <t>A 24759-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11630,10 +11630,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45660</v>
+        <v>45084</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11646,7 +11646,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11689,7 +11689,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 37195-2025</t>
+          <t>A 29433-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11699,14 +11699,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45875</v>
+        <v>45824</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11762,7 +11762,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 28056-2026</t>
+          <t>A 8936-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11776,10 +11776,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46195</v>
+        <v>46069</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11835,7 +11835,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 28068-2026</t>
+          <t>A 52853-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11849,10 +11849,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46195</v>
+        <v>45226</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11865,7 +11865,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11908,7 +11908,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 28309-2026</t>
+          <t>A 24279-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11922,10 +11922,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46196</v>
+        <v>46169</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11938,7 +11938,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>3.1</v>
+        <v>11.7</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11981,7 +11981,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 48301-2024</t>
+          <t>A 7212-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11995,10 +11995,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45590</v>
+        <v>45702</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12011,7 +12011,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12054,7 +12054,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 30399-2023</t>
+          <t>A 32395-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12068,10 +12068,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45111</v>
+        <v>45120</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12084,7 +12084,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12127,7 +12127,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 60465-2024</t>
+          <t>A 6080-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12137,14 +12137,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45643</v>
+        <v>44964</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12157,7 +12157,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12200,7 +12200,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 25322-2024</t>
+          <t>A 35202-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12214,10 +12214,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45462</v>
+        <v>45145</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12230,7 +12230,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.3</v>
+        <v>11.1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12273,7 +12273,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 35202-2023</t>
+          <t>A 24736-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12287,10 +12287,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45145</v>
+        <v>46171</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12302,8 +12302,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I151" t="n">
-        <v>11.1</v>
+        <v>3.8</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12346,7 +12351,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 31596-2024</t>
+          <t>A 33654-2022</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12360,10 +12365,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45506</v>
+        <v>44789</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12375,13 +12380,8 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I152" t="n">
-        <v>4.3</v>
+        <v>0.8</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12424,7 +12424,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 40257-2023</t>
+          <t>A 5577-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12438,10 +12438,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45169</v>
+        <v>44960</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12454,7 +12454,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12497,7 +12497,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 19759-2024</t>
+          <t>A 25814-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12511,10 +12511,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45432</v>
+        <v>46178</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12570,7 +12570,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 56542-2024</t>
+          <t>A 30484-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12580,14 +12580,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45625</v>
+        <v>45111</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12600,7 +12600,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12643,7 +12643,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 24759-2023</t>
+          <t>A 8950-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12657,10 +12657,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45084</v>
+        <v>45357</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12716,7 +12716,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 48411-2022</t>
+          <t>A 46876-2022</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12730,10 +12730,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>44858</v>
+        <v>44851</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12746,7 +12746,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>2.2</v>
+        <v>7.5</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12789,7 +12789,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 33984-2026</t>
+          <t>A 13522-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12799,14 +12799,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46252</v>
+        <v>45006</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12819,7 +12819,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12862,7 +12862,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 37169-2022</t>
+          <t>A 56419-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12876,10 +12876,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44806</v>
+        <v>45623</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12892,7 +12892,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>17.4</v>
+        <v>5.6</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12935,7 +12935,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 60118-2024</t>
+          <t>A 8626-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12949,10 +12949,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45642</v>
+        <v>45355</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12965,7 +12965,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.6</v>
+        <v>6.4</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13008,7 +13008,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 53769-2024</t>
+          <t>A 60112-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13022,10 +13022,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45615</v>
+        <v>45642</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13038,7 +13038,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13081,7 +13081,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 34112-2026</t>
+          <t>A 26148-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13095,10 +13095,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46253</v>
+        <v>46181</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13111,7 +13111,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13154,7 +13154,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 696-2025</t>
+          <t>A 31605-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13168,10 +13168,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45665</v>
+        <v>45506</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13183,8 +13183,13 @@
           <t>LIDKÖPING</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I163" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13227,7 +13232,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 60642-2023</t>
+          <t>A 60118-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13237,14 +13242,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45260</v>
+        <v>45642</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13257,7 +13262,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13300,7 +13305,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 44308-2023</t>
+          <t>A 62551-2021</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13314,10 +13319,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45188</v>
+        <v>44503</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13330,7 +13335,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13373,7 +13378,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 54279-2023</t>
+          <t>A 56542-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13383,14 +13388,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45232</v>
+        <v>45625</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13403,7 +13408,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13446,7 +13451,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 7212-2025</t>
+          <t>A 27552-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13460,10 +13465,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45702</v>
+        <v>46190</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13476,7 +13481,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.5</v>
+        <v>5.3</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13519,7 +13524,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 8953-2023</t>
+          <t>A 53814-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13533,10 +13538,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44979</v>
+        <v>45615</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13549,7 +13554,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13592,7 +13597,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 59644-2023</t>
+          <t>A 28068-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13606,10 +13611,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45254</v>
+        <v>46195</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13622,7 +13627,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13665,7 +13670,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 36716-2026</t>
+          <t>A 28056-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13679,10 +13684,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46272</v>
+        <v>46195</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13695,7 +13700,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13738,7 +13743,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 31902-2026</t>
+          <t>A 28309-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13752,10 +13757,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46231</v>
+        <v>46196</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13768,7 +13773,7 @@
         </i